--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -556,10 +556,10 @@
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>297000</v>
+        <v>297238.554216868</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -3826,10 +3826,10 @@
         <v>23</v>
       </c>
       <c r="N85" t="n">
-        <v>14857.623272727</v>
+        <v>14857.623287671</v>
       </c>
       <c r="O85" t="n">
-        <v>341725.335272721</v>
+        <v>341725.335616433</v>
       </c>
       <c r="P85" t="n">
         <v>34900</v>
@@ -11963,10 +11963,10 @@
         <v>133</v>
       </c>
       <c r="N273" t="n">
-        <v>10600</v>
+        <v>10603.665283541</v>
       </c>
       <c r="O273" t="n">
-        <v>1409800</v>
+        <v>1410287.482710953</v>
       </c>
       <c r="P273" t="n">
         <v>17200</v>
@@ -12009,10 +12009,10 @@
         <v>82</v>
       </c>
       <c r="N274" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O274" t="n">
-        <v>427785.4704922906</v>
+        <v>427785.4704434268</v>
       </c>
       <c r="P274" t="n">
         <v>8500</v>
@@ -12891,22 +12891,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M294" t="n">
-        <v>3435</v>
+        <v>3315</v>
       </c>
       <c r="N294" t="n">
         <v>156.25</v>
       </c>
       <c r="O294" t="n">
-        <v>536718.75</v>
+        <v>517968.75</v>
       </c>
       <c r="P294" t="n">
         <v>250</v>
       </c>
       <c r="Q294" t="n">
-        <v>858750</v>
+        <v>828750</v>
       </c>
     </row>
     <row r="295">
@@ -14239,10 +14239,10 @@
         <v>81</v>
       </c>
       <c r="N324" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O324" t="n">
-        <v>291134.5184958192</v>
+        <v>291337.3996933779</v>
       </c>
       <c r="P324" t="n">
         <v>6500</v>
@@ -15208,10 +15208,10 @@
         <v>195</v>
       </c>
       <c r="N346" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O346" t="n">
-        <v>852378.3959411565</v>
+        <v>852494.507968935</v>
       </c>
       <c r="P346" t="n">
         <v>8900</v>
@@ -17498,10 +17498,10 @@
         <v>1639</v>
       </c>
       <c r="N398" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O398" t="n">
-        <v>2540768.602064595</v>
+        <v>2540768.608874476</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -17590,10 +17590,10 @@
         <v>891</v>
       </c>
       <c r="N400" t="n">
-        <v>2403.5165803524</v>
+        <v>2403.5166025127</v>
       </c>
       <c r="O400" t="n">
-        <v>2141533.273093989</v>
+        <v>2141533.292838816</v>
       </c>
       <c r="P400" t="n">
         <v>3500</v>
@@ -25598,10 +25598,10 @@
         <v>18</v>
       </c>
       <c r="N587" t="n">
-        <v>1561.0035960591</v>
+        <v>1561.003634439</v>
       </c>
       <c r="O587" t="n">
-        <v>28098.0647290638</v>
+        <v>28098.065419902</v>
       </c>
       <c r="P587" t="n">
         <v>2900</v>
@@ -36115,10 +36115,10 @@
         <v>432</v>
       </c>
       <c r="N818" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O818" t="n">
-        <v>654928.7420756735</v>
+        <v>654928.7419123776</v>
       </c>
       <c r="P818" t="n">
         <v>2300</v>
@@ -36389,10 +36389,10 @@
         <v>578</v>
       </c>
       <c r="N824" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O824" t="n">
-        <v>1201883.652546581</v>
+        <v>1201883.61360649</v>
       </c>
       <c r="P824" t="n">
         <v>2900</v>
@@ -37126,10 +37126,10 @@
         <v>2</v>
       </c>
       <c r="N840" t="n">
-        <v>1906.1790510949</v>
+        <v>1906.1788059701</v>
       </c>
       <c r="O840" t="n">
-        <v>3812.3581021898</v>
+        <v>3812.3576119402</v>
       </c>
       <c r="P840" t="n">
         <v>2900</v>
@@ -37350,22 +37350,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M845" t="n">
-        <v>468</v>
+        <v>324</v>
       </c>
       <c r="N845" t="n">
         <v>1801</v>
       </c>
       <c r="O845" t="n">
-        <v>842868</v>
+        <v>583524</v>
       </c>
       <c r="P845" t="n">
         <v>2900</v>
       </c>
       <c r="Q845" t="n">
-        <v>1357200</v>
+        <v>939600</v>
       </c>
     </row>
     <row r="846">
@@ -40296,10 +40296,10 @@
         <v>2423</v>
       </c>
       <c r="N910" t="n">
-        <v>517.2940518305199</v>
+        <v>517.72052761748</v>
       </c>
       <c r="O910" t="n">
-        <v>1253403.48758535</v>
+        <v>1254436.838417154</v>
       </c>
       <c r="P910" t="n">
         <v>900</v>
@@ -40744,10 +40744,10 @@
         <v>1381</v>
       </c>
       <c r="N920" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O920" t="n">
-        <v>971940.6703330784</v>
+        <v>972040.6770901565</v>
       </c>
       <c r="P920" t="n">
         <v>900</v>
@@ -43212,10 +43212,10 @@
         <v>1</v>
       </c>
       <c r="N974" t="n">
-        <v>1783.7988761992</v>
+        <v>1783.7988756856</v>
       </c>
       <c r="O974" t="n">
-        <v>1783.7988761992</v>
+        <v>1783.7988756856</v>
       </c>
       <c r="P974" t="n">
         <v>1500</v>
@@ -45096,10 +45096,10 @@
         <v>6</v>
       </c>
       <c r="N1014" t="n">
-        <v>315.02726865672</v>
+        <v>315.02740121581</v>
       </c>
       <c r="O1014" t="n">
-        <v>1890.16361194032</v>
+        <v>1890.16440729486</v>
       </c>
       <c r="P1014" t="n">
         <v>2200</v>
@@ -48007,10 +48007,10 @@
         <v>55</v>
       </c>
       <c r="N1082" t="n">
-        <v>5077</v>
+        <v>5150.0503597122</v>
       </c>
       <c r="O1082" t="n">
-        <v>279235</v>
+        <v>283252.769784171</v>
       </c>
       <c r="P1082" t="n">
         <v>8500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1385,10 +1385,10 @@
         <v>71</v>
       </c>
       <c r="N24" t="n">
-        <v>1990.0434548944</v>
+        <v>1990.0434042553</v>
       </c>
       <c r="O24" t="n">
-        <v>141293.0852975024</v>
+        <v>141293.0817021263</v>
       </c>
       <c r="P24" t="n">
         <v>4400</v>
@@ -5477,22 +5477,22 @@
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>22267.552777778</v>
+        <v>26721.063333333</v>
       </c>
       <c r="O123" t="n">
-        <v>66802.65833333399</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
         <v>46300</v>
       </c>
       <c r="Q123" t="n">
-        <v>138900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -6006,22 +6006,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N135" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O135" t="n">
-        <v>424250.6538613801</v>
+        <v>283770.30490066</v>
       </c>
       <c r="P135" t="n">
         <v>251900</v>
       </c>
       <c r="Q135" t="n">
-        <v>755700</v>
+        <v>503800</v>
       </c>
     </row>
     <row r="136">
@@ -6048,22 +6048,22 @@
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N136" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O136" t="n">
-        <v>2400866.42603772</v>
+        <v>2221754.16885719</v>
       </c>
       <c r="P136" t="n">
         <v>312000</v>
       </c>
       <c r="Q136" t="n">
-        <v>3744000</v>
+        <v>3432000</v>
       </c>
     </row>
     <row r="137">
@@ -6983,22 +6983,22 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M158" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O158" t="n">
-        <v>370001.245027626</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
         <v>98900</v>
       </c>
       <c r="Q158" t="n">
-        <v>593400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -11917,10 +11917,10 @@
         <v>177</v>
       </c>
       <c r="N272" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O272" t="n">
-        <v>457059.1591992099</v>
+        <v>457059.1581471573</v>
       </c>
       <c r="P272" t="n">
         <v>4500</v>
@@ -12444,10 +12444,10 @@
         <v>79</v>
       </c>
       <c r="N284" t="n">
-        <v>8214</v>
+        <v>8701.9603960396</v>
       </c>
       <c r="O284" t="n">
-        <v>648906</v>
+        <v>687454.8712871284</v>
       </c>
       <c r="P284" t="n">
         <v>7900</v>
@@ -16882,10 +16882,10 @@
         <v>97</v>
       </c>
       <c r="N384" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O384" t="n">
-        <v>1156375.8</v>
+        <v>1159126.892307696</v>
       </c>
       <c r="P384" t="n">
         <v>19900</v>
@@ -17363,10 +17363,10 @@
         <v>291</v>
       </c>
       <c r="N395" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O395" t="n">
-        <v>474598.9522632165</v>
+        <v>474598.9543022536</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
@@ -17634,10 +17634,10 @@
         <v>891</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O401" t="n">
-        <v>2141533.570808808</v>
+        <v>2141533.579021778</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
@@ -25304,10 +25304,10 @@
         <v>38</v>
       </c>
       <c r="N580" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O580" t="n">
-        <v>645038.22</v>
+        <v>648995.5096932519</v>
       </c>
       <c r="P580" t="n">
         <v>26900</v>
@@ -26085,10 +26085,10 @@
         <v>1</v>
       </c>
       <c r="N598" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="O598" t="n">
-        <v>9627.34</v>
+        <v>11147.446315789</v>
       </c>
       <c r="P598" t="n">
         <v>15900</v>
@@ -27318,10 +27318,10 @@
         <v>1</v>
       </c>
       <c r="N627" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="O627" t="n">
-        <v>7700</v>
+        <v>7812.5456760049</v>
       </c>
       <c r="P627" t="n">
         <v>13900</v>
@@ -27778,10 +27778,10 @@
         <v>20</v>
       </c>
       <c r="N637" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O637" t="n">
-        <v>104363.411624834</v>
+        <v>104363.41165563</v>
       </c>
       <c r="P637" t="n">
         <v>8500</v>
@@ -36159,10 +36159,10 @@
         <v>432</v>
       </c>
       <c r="N819" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O819" t="n">
-        <v>654928.7407118928</v>
+        <v>654928.7406025104</v>
       </c>
       <c r="P819" t="n">
         <v>2300</v>
@@ -40340,10 +40340,10 @@
         <v>2403</v>
       </c>
       <c r="N911" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O911" t="n">
-        <v>1243057.866894373</v>
+        <v>1244300.853704384</v>
       </c>
       <c r="P911" t="n">
         <v>900</v>
@@ -40788,10 +40788,10 @@
         <v>1368</v>
       </c>
       <c r="N921" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O921" t="n">
-        <v>962791.3257117781</v>
+        <v>962791.3246180622</v>
       </c>
       <c r="P921" t="n">
         <v>900</v>
@@ -46897,10 +46897,10 @@
         <v>223</v>
       </c>
       <c r="N1056" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O1056" t="n">
-        <v>709563.7000000001</v>
+        <v>724315.5440748514</v>
       </c>
       <c r="P1056" t="n">
         <v>5100</v>
@@ -48721,10 +48721,10 @@
         <v>125</v>
       </c>
       <c r="N1098" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O1098" t="n">
-        <v>244082.5</v>
+        <v>248881.875</v>
       </c>
       <c r="P1098" t="n">
         <v>3500</v>
@@ -48997,10 +48997,10 @@
         <v>7</v>
       </c>
       <c r="N1104" t="n">
-        <v>6336</v>
+        <v>6620.7640449438</v>
       </c>
       <c r="O1104" t="n">
-        <v>44352</v>
+        <v>46345.3483146066</v>
       </c>
       <c r="P1104" t="n">
         <v>7500</v>
@@ -50837,10 +50837,10 @@
         <v>1</v>
       </c>
       <c r="N1144" t="n">
-        <v>751.45</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="O1144" t="n">
-        <v>751.45</v>
+        <v>1093.0181818182</v>
       </c>
       <c r="P1144" t="n">
         <v>2500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1179"/>
+  <dimension ref="A1:Q1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1301,22 +1301,22 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O22" t="n">
-        <v>547015.2549450576</v>
+        <v>541581.3364729547</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
       </c>
       <c r="Q22" t="n">
-        <v>785200</v>
+        <v>777400</v>
       </c>
     </row>
     <row r="23">
@@ -2385,22 +2385,22 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>15970.739066667</v>
+        <v>15970.739014085</v>
       </c>
       <c r="O49" t="n">
-        <v>63882.956266668</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>26900</v>
       </c>
       <c r="Q49" t="n">
-        <v>107600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4891,22 +4891,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N109" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O109" t="n">
-        <v>230809.706206898</v>
+        <v>181350.479823007</v>
       </c>
       <c r="P109" t="n">
         <v>30500</v>
       </c>
       <c r="Q109" t="n">
-        <v>427000</v>
+        <v>335500</v>
       </c>
     </row>
     <row r="110">
@@ -5113,22 +5113,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M114" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N114" t="n">
-        <v>13712.84</v>
+        <v>13712.837142857</v>
       </c>
       <c r="O114" t="n">
-        <v>233118.28</v>
+        <v>191979.719999998</v>
       </c>
       <c r="P114" t="n">
         <v>22600</v>
       </c>
       <c r="Q114" t="n">
-        <v>384200</v>
+        <v>316400</v>
       </c>
     </row>
     <row r="115">
@@ -10104,22 +10104,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M230" t="n">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="N230" t="n">
-        <v>1098.0633365079</v>
+        <v>1098.0633810433</v>
       </c>
       <c r="O230" t="n">
-        <v>451304.0313047469</v>
+        <v>444715.6693225365</v>
       </c>
       <c r="P230" t="n">
         <v>1500</v>
       </c>
       <c r="Q230" t="n">
-        <v>616500</v>
+        <v>607500</v>
       </c>
     </row>
     <row r="231">
@@ -11460,22 +11460,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M262" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="N262" t="n">
         <v>2913</v>
       </c>
       <c r="O262" t="n">
-        <v>235953</v>
+        <v>218475</v>
       </c>
       <c r="P262" t="n">
         <v>4950</v>
       </c>
       <c r="Q262" t="n">
-        <v>400950</v>
+        <v>371250</v>
       </c>
     </row>
     <row r="263">
@@ -12300,22 +12300,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M281" t="n">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="N281" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O281" t="n">
-        <v>1866886.754233383</v>
+        <v>1816344.981234808</v>
       </c>
       <c r="P281" t="n">
         <v>5600</v>
       </c>
       <c r="Q281" t="n">
-        <v>3309600</v>
+        <v>3220000</v>
       </c>
     </row>
     <row r="282">
@@ -12794,22 +12794,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M292" t="n">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="N292" t="n">
         <v>1026.13</v>
       </c>
       <c r="O292" t="n">
-        <v>489464.0100000001</v>
+        <v>474072.0600000001</v>
       </c>
       <c r="P292" t="n">
         <v>1900</v>
       </c>
       <c r="Q292" t="n">
-        <v>906300</v>
+        <v>877800</v>
       </c>
     </row>
     <row r="293">
@@ -13128,10 +13128,10 @@
         <v>282</v>
       </c>
       <c r="N299" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O299" t="n">
-        <v>1070390.222147345</v>
+        <v>1070390.22214774</v>
       </c>
       <c r="P299" t="n">
         <v>6200</v>
@@ -13301,22 +13301,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M303" t="n">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N303" t="n">
         <v>2379.63</v>
       </c>
       <c r="O303" t="n">
-        <v>121361.13</v>
+        <v>49972.23</v>
       </c>
       <c r="P303" t="n">
         <v>4500</v>
       </c>
       <c r="Q303" t="n">
-        <v>229500</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="304">
@@ -13708,22 +13708,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M312" t="n">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="N312" t="n">
-        <v>2267.0481062554</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O312" t="n">
-        <v>3454981.31393323</v>
+        <v>3443646.067226306</v>
       </c>
       <c r="P312" t="n">
         <v>3900</v>
       </c>
       <c r="Q312" t="n">
-        <v>5943600</v>
+        <v>5924100</v>
       </c>
     </row>
     <row r="313">
@@ -13879,25 +13879,25 @@
         <v>400</v>
       </c>
       <c r="K316" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N316" t="n">
         <v>156</v>
       </c>
       <c r="O316" t="n">
-        <v>62400</v>
+        <v>93600</v>
       </c>
       <c r="P316" t="n">
         <v>195</v>
       </c>
       <c r="Q316" t="n">
-        <v>78000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="317">
@@ -14845,22 +14845,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M338" t="n">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N338" t="n">
         <v>1381.75</v>
       </c>
       <c r="O338" t="n">
-        <v>721273.5</v>
+        <v>712983</v>
       </c>
       <c r="P338" t="n">
         <v>2500</v>
       </c>
       <c r="Q338" t="n">
-        <v>1305000</v>
+        <v>1290000</v>
       </c>
     </row>
     <row r="339">
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M350" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="N350" t="n">
         <v>2224.56</v>
       </c>
       <c r="O350" t="n">
-        <v>162392.88</v>
+        <v>151270.08</v>
       </c>
       <c r="P350" t="n">
         <v>3900</v>
       </c>
       <c r="Q350" t="n">
-        <v>284700</v>
+        <v>265200</v>
       </c>
     </row>
     <row r="351">
@@ -16159,22 +16159,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M368" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="N368" t="n">
         <v>1343.77</v>
       </c>
       <c r="O368" t="n">
-        <v>382974.45</v>
+        <v>378943.14</v>
       </c>
       <c r="P368" t="n">
         <v>2500</v>
       </c>
       <c r="Q368" t="n">
-        <v>712500</v>
+        <v>705000</v>
       </c>
     </row>
     <row r="369">
@@ -16291,22 +16291,22 @@
         <v>0</v>
       </c>
       <c r="L371" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M371" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N371" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O371" t="n">
-        <v>414229.64</v>
+        <v>367158.09</v>
       </c>
       <c r="P371" t="n">
         <v>16900</v>
       </c>
       <c r="Q371" t="n">
-        <v>743600</v>
+        <v>659100</v>
       </c>
     </row>
     <row r="372">
@@ -16686,22 +16686,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M380" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N380" t="n">
         <v>5853</v>
       </c>
       <c r="O380" t="n">
-        <v>924774</v>
+        <v>901362</v>
       </c>
       <c r="P380" t="n">
         <v>9900</v>
       </c>
       <c r="Q380" t="n">
-        <v>1564200</v>
+        <v>1524600</v>
       </c>
     </row>
     <row r="381">
@@ -17531,22 +17531,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M399" t="n">
-        <v>2065</v>
+        <v>2035</v>
       </c>
       <c r="N399" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O399" t="n">
-        <v>3201151.524206888</v>
+        <v>3154645.723513108</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
       </c>
       <c r="Q399" t="n">
-        <v>5162500</v>
+        <v>5087500</v>
       </c>
     </row>
     <row r="400">
@@ -17583,10 +17583,10 @@
         <v>3</v>
       </c>
       <c r="N400" t="n">
-        <v>1579.38564</v>
+        <v>1579.3847234043</v>
       </c>
       <c r="O400" t="n">
-        <v>4738.156919999999</v>
+        <v>4738.1541702129</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -17629,10 +17629,10 @@
         <v>1219</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O401" t="n">
-        <v>2929887.519458606</v>
+        <v>2929887.566246507</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
@@ -17887,10 +17887,10 @@
         <v>26</v>
       </c>
       <c r="N407" t="n">
-        <v>1232.8060309278</v>
+        <v>1232.8059585492</v>
       </c>
       <c r="O407" t="n">
-        <v>32052.9568041228</v>
+        <v>32052.9549222792</v>
       </c>
       <c r="P407" t="n">
         <v>2400</v>
@@ -19246,22 +19246,22 @@
         <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M438" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="N438" t="n">
-        <v>204.05094594595</v>
+        <v>204.05098591549</v>
       </c>
       <c r="O438" t="n">
-        <v>26322.57202702755</v>
+        <v>25098.27126760527</v>
       </c>
       <c r="P438" t="n">
         <v>500</v>
       </c>
       <c r="Q438" t="n">
-        <v>64500</v>
+        <v>61500</v>
       </c>
     </row>
     <row r="439">
@@ -21524,22 +21524,22 @@
         <v>0</v>
       </c>
       <c r="L492" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M492" t="n">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="N492" t="n">
-        <v>2029.8740849673</v>
+        <v>2029.874091653</v>
       </c>
       <c r="O492" t="n">
-        <v>862696.4861111025</v>
+        <v>856606.866677566</v>
       </c>
       <c r="P492" t="n">
         <v>3600</v>
       </c>
       <c r="Q492" t="n">
-        <v>1530000</v>
+        <v>1519200</v>
       </c>
     </row>
     <row r="493">
@@ -21852,22 +21852,22 @@
         <v>0</v>
       </c>
       <c r="L500" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M500" t="n">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="N500" t="n">
         <v>1866.74</v>
       </c>
       <c r="O500" t="n">
-        <v>1213381</v>
+        <v>1204047.3</v>
       </c>
       <c r="P500" t="n">
         <v>2900</v>
       </c>
       <c r="Q500" t="n">
-        <v>1885000</v>
+        <v>1870500</v>
       </c>
     </row>
     <row r="501">
@@ -22439,22 +22439,22 @@
         <v>0</v>
       </c>
       <c r="L514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M514" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N514" t="n">
         <v>26595</v>
       </c>
       <c r="O514" t="n">
-        <v>159570</v>
+        <v>132975</v>
       </c>
       <c r="P514" t="n">
         <v>39900</v>
       </c>
       <c r="Q514" t="n">
-        <v>239400</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="515">
@@ -22706,10 +22706,10 @@
         <v>18</v>
       </c>
       <c r="N520" t="n">
-        <v>3731.024440678</v>
+        <v>3731.0244863014</v>
       </c>
       <c r="O520" t="n">
-        <v>67158.439932204</v>
+        <v>67158.44075342519</v>
       </c>
       <c r="P520" t="n">
         <v>5200</v>
@@ -23602,22 +23602,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M541" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="N541" t="n">
         <v>1430.38</v>
       </c>
       <c r="O541" t="n">
-        <v>44341.78000000001</v>
+        <v>30037.98</v>
       </c>
       <c r="P541" t="n">
         <v>4000</v>
       </c>
       <c r="Q541" t="n">
-        <v>124000</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="542">
@@ -23996,22 +23996,22 @@
         <v>0</v>
       </c>
       <c r="L550" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M550" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N550" t="n">
-        <v>12005.15982684</v>
+        <v>12005.159823789</v>
       </c>
       <c r="O550" t="n">
-        <v>696299.2699567199</v>
+        <v>648278.6304846059</v>
       </c>
       <c r="P550" t="n">
         <v>19500</v>
       </c>
       <c r="Q550" t="n">
-        <v>1131000</v>
+        <v>1053000</v>
       </c>
     </row>
     <row r="551">
@@ -24580,22 +24580,22 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M564" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N564" t="n">
         <v>3754</v>
       </c>
       <c r="O564" t="n">
-        <v>518052</v>
+        <v>514298</v>
       </c>
       <c r="P564" t="n">
         <v>6400</v>
       </c>
       <c r="Q564" t="n">
-        <v>883200</v>
+        <v>876800</v>
       </c>
     </row>
     <row r="565">
@@ -25588,22 +25588,22 @@
         <v>0</v>
       </c>
       <c r="L587" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M587" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="N587" t="n">
         <v>5431.12</v>
       </c>
       <c r="O587" t="n">
-        <v>640872.16</v>
+        <v>624578.7999999999</v>
       </c>
       <c r="P587" t="n">
         <v>8900</v>
       </c>
       <c r="Q587" t="n">
-        <v>1050200</v>
+        <v>1023500</v>
       </c>
     </row>
     <row r="588">
@@ -27949,22 +27949,22 @@
         <v>0</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M641" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N641" t="n">
         <v>5194</v>
       </c>
       <c r="O641" t="n">
-        <v>109074</v>
+        <v>93492</v>
       </c>
       <c r="P641" t="n">
         <v>9000</v>
       </c>
       <c r="Q641" t="n">
-        <v>189000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="642">
@@ -32053,22 +32053,22 @@
         <v>0</v>
       </c>
       <c r="L730" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M730" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N730" t="n">
         <v>32332</v>
       </c>
       <c r="O730" t="n">
-        <v>2521896</v>
+        <v>2457232</v>
       </c>
       <c r="P730" t="n">
         <v>55900</v>
       </c>
       <c r="Q730" t="n">
-        <v>4360200</v>
+        <v>4248400</v>
       </c>
     </row>
     <row r="731">
@@ -32651,22 +32651,22 @@
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M743" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N743" t="n">
-        <v>4907.8225450902</v>
+        <v>4907.8225656566</v>
       </c>
       <c r="O743" t="n">
-        <v>68709.5156312628</v>
+        <v>49078.225656566</v>
       </c>
       <c r="P743" t="n">
         <v>8200</v>
       </c>
       <c r="Q743" t="n">
-        <v>114800</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="744">
@@ -33796,22 +33796,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M768" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N768" t="n">
         <v>13098</v>
       </c>
       <c r="O768" t="n">
-        <v>1034742</v>
+        <v>982350</v>
       </c>
       <c r="P768" t="n">
         <v>21200</v>
       </c>
       <c r="Q768" t="n">
-        <v>1674800</v>
+        <v>1590000</v>
       </c>
     </row>
     <row r="769">
@@ -36198,10 +36198,10 @@
         <v>432</v>
       </c>
       <c r="N820" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O820" t="n">
-        <v>654928.7406025104</v>
+        <v>654928.7403835729</v>
       </c>
       <c r="P820" t="n">
         <v>2300</v>
@@ -36512,22 +36512,22 @@
         <v>0</v>
       </c>
       <c r="L827" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M827" t="n">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="N827" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O827" t="n">
-        <v>1703850.582369789</v>
+        <v>1696638.530471961</v>
       </c>
       <c r="P827" t="n">
         <v>2500</v>
       </c>
       <c r="Q827" t="n">
-        <v>2362500</v>
+        <v>2352500</v>
       </c>
     </row>
     <row r="828">
@@ -36696,22 +36696,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M831" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="N831" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O831" t="n">
-        <v>2058138.395162049</v>
+        <v>2037577.532104086</v>
       </c>
       <c r="P831" t="n">
         <v>2900</v>
       </c>
       <c r="Q831" t="n">
-        <v>2902900</v>
+        <v>2873900</v>
       </c>
     </row>
     <row r="832">
@@ -37157,22 +37157,22 @@
         <v>0</v>
       </c>
       <c r="L841" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M841" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N841" t="n">
         <v>5347.73</v>
       </c>
       <c r="O841" t="n">
-        <v>213909.2</v>
+        <v>197866.01</v>
       </c>
       <c r="P841" t="n">
         <v>9500</v>
       </c>
       <c r="Q841" t="n">
-        <v>380000</v>
+        <v>351500</v>
       </c>
     </row>
     <row r="842">
@@ -37295,22 +37295,22 @@
         <v>0</v>
       </c>
       <c r="L844" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M844" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N844" t="n">
-        <v>2546.982132964</v>
+        <v>2546.9817919075</v>
       </c>
       <c r="O844" t="n">
-        <v>117161.178116344</v>
+        <v>78956.4355491325</v>
       </c>
       <c r="P844" t="n">
         <v>3900</v>
       </c>
       <c r="Q844" t="n">
-        <v>179400</v>
+        <v>120900</v>
       </c>
     </row>
     <row r="845">
@@ -40373,22 +40373,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M912" t="n">
-        <v>3555</v>
+        <v>3549</v>
       </c>
       <c r="N912" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O912" t="n">
-        <v>1838981.211213392</v>
+        <v>1835877.470937712</v>
       </c>
       <c r="P912" t="n">
         <v>900</v>
       </c>
       <c r="Q912" t="n">
-        <v>3199500</v>
+        <v>3194100</v>
       </c>
     </row>
     <row r="913">
@@ -40733,22 +40733,22 @@
         <v>0</v>
       </c>
       <c r="L920" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M920" t="n">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="N920" t="n">
         <v>2030.02</v>
       </c>
       <c r="O920" t="n">
-        <v>893208.8</v>
+        <v>887118.74</v>
       </c>
       <c r="P920" t="n">
         <v>3600</v>
       </c>
       <c r="Q920" t="n">
-        <v>1584000</v>
+        <v>1573200</v>
       </c>
     </row>
     <row r="921">
@@ -41924,22 +41924,22 @@
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M947" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="N947" t="n">
         <v>1567.02</v>
       </c>
       <c r="O947" t="n">
-        <v>313404</v>
+        <v>304001.88</v>
       </c>
       <c r="P947" t="n">
         <v>2900</v>
       </c>
       <c r="Q947" t="n">
-        <v>580000</v>
+        <v>562600</v>
       </c>
     </row>
     <row r="948">
@@ -42452,22 +42452,22 @@
         <v>0</v>
       </c>
       <c r="L958" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M958" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N958" t="n">
         <v>10548.76</v>
       </c>
       <c r="O958" t="n">
-        <v>158231.4</v>
+        <v>126585.12</v>
       </c>
       <c r="P958" t="n">
         <v>35900</v>
       </c>
       <c r="Q958" t="n">
-        <v>538500</v>
+        <v>430800</v>
       </c>
     </row>
     <row r="959">
@@ -43295,10 +43295,10 @@
         <v>1</v>
       </c>
       <c r="N976" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O976" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="P976" t="n">
         <v>1500</v>
@@ -44732,22 +44732,22 @@
         <v>0</v>
       </c>
       <c r="L1007" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1007" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="N1007" t="n">
         <v>1338.14</v>
       </c>
       <c r="O1007" t="n">
-        <v>123108.88</v>
+        <v>109727.48</v>
       </c>
       <c r="P1007" t="n">
         <v>2500</v>
       </c>
       <c r="Q1007" t="n">
-        <v>230000</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="1008">
@@ -45304,22 +45304,22 @@
         <v>0</v>
       </c>
       <c r="L1019" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1019" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N1019" t="n">
         <v>2752.52</v>
       </c>
       <c r="O1019" t="n">
-        <v>30277.72</v>
+        <v>16515.12</v>
       </c>
       <c r="P1019" t="n">
         <v>4500</v>
       </c>
       <c r="Q1019" t="n">
-        <v>49500</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="1020">
@@ -46886,22 +46886,22 @@
         <v>0</v>
       </c>
       <c r="L1056" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1056" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="N1056" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1056" t="n">
-        <v>58828.5</v>
+        <v>55298.78999999999</v>
       </c>
       <c r="P1056" t="n">
         <v>1900</v>
       </c>
       <c r="Q1056" t="n">
-        <v>95000</v>
+        <v>89300</v>
       </c>
     </row>
     <row r="1057">
@@ -48376,12 +48376,15 @@
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
-          <t>CH-448-04</t>
-        </is>
+          <t>CH-436</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>TAJA LAPUZ HUELLITA CH-448-04</t>
+          <t>GLOBO 18 PULGADAS CH-436</t>
         </is>
       </c>
       <c r="E1091" t="inlineStr">
@@ -48395,39 +48398,39 @@
         </is>
       </c>
       <c r="J1091" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K1091" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L1091" t="n">
         <v>0</v>
       </c>
       <c r="M1091" t="n">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="N1091" t="n">
-        <v>2367.6159558824</v>
+        <v>1760</v>
       </c>
       <c r="O1091" t="n">
-        <v>134954.1094852968</v>
+        <v>880000</v>
       </c>
       <c r="P1091" t="n">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="Q1091" t="n">
-        <v>165300</v>
+        <v>1150000</v>
       </c>
     </row>
     <row r="1092">
       <c r="A1092" t="inlineStr">
         <is>
-          <t>CM-MORRAL01</t>
+          <t>CH-448-04</t>
         </is>
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
+          <t>TAJA LAPUZ HUELLITA CH-448-04</t>
         </is>
       </c>
       <c r="E1092" t="inlineStr">
@@ -48441,7 +48444,7 @@
         </is>
       </c>
       <c r="J1092" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K1092" t="n">
         <v>0</v>
@@ -48450,39 +48453,44 @@
         <v>0</v>
       </c>
       <c r="M1092" t="n">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="N1092" t="n">
-        <v>31846.46</v>
+        <v>2367.6159558824</v>
       </c>
       <c r="O1092" t="n">
-        <v>573236.28</v>
+        <v>134954.1094852968</v>
       </c>
       <c r="P1092" t="n">
-        <v>55900</v>
+        <v>2900</v>
       </c>
       <c r="Q1092" t="n">
-        <v>1006200</v>
+        <v>165300</v>
       </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>CM2198</t>
+          <t>CM-MORRAL01</t>
         </is>
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>JUEGO MAGNETICO</t>
+          <t>MORRAL GRANDE PARA NIÑAS PRINCESS</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1093" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="K1093" t="n">
         <v>0</v>
@@ -48491,30 +48499,30 @@
         <v>0</v>
       </c>
       <c r="M1093" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="N1093" t="n">
-        <v>9823</v>
+        <v>31846.46</v>
       </c>
       <c r="O1093" t="n">
-        <v>19646</v>
+        <v>573236.28</v>
       </c>
       <c r="P1093" t="n">
-        <v>16900</v>
+        <v>55900</v>
       </c>
       <c r="Q1093" t="n">
-        <v>33800</v>
+        <v>1006200</v>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>CR-2</t>
+          <t>CM2198</t>
         </is>
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>SET PORTAMINAS BORRADOR</t>
+          <t>JUEGO MAGNETICO</t>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
@@ -48523,7 +48531,7 @@
         </is>
       </c>
       <c r="J1094" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K1094" t="n">
         <v>0</v>
@@ -48532,30 +48540,30 @@
         <v>0</v>
       </c>
       <c r="M1094" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N1094" t="n">
-        <v>5500</v>
+        <v>9823</v>
       </c>
       <c r="O1094" t="n">
-        <v>55000</v>
+        <v>19646</v>
       </c>
       <c r="P1094" t="n">
-        <v>6600</v>
+        <v>16900</v>
       </c>
       <c r="Q1094" t="n">
-        <v>66000</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>CR-5</t>
+          <t>CR-2</t>
         </is>
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>CRAYOLAS SANRIO</t>
+          <t>SET PORTAMINAS BORRADOR</t>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
@@ -48564,7 +48572,7 @@
         </is>
       </c>
       <c r="J1095" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K1095" t="n">
         <v>0</v>
@@ -48573,44 +48581,39 @@
         <v>0</v>
       </c>
       <c r="M1095" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N1095" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="O1095" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="P1095" t="n">
-        <v>3000</v>
+        <v>6600</v>
       </c>
       <c r="Q1095" t="n">
-        <v>24000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>DPC06</t>
+          <t>CR-5</t>
         </is>
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>PELUCHE OSO 3 COLORES 30CM AB-46 DPC06</t>
-        </is>
-      </c>
-      <c r="E1096" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>CRAYOLAS SANRIO</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1096" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K1096" t="n">
         <v>0</v>
@@ -48619,35 +48622,35 @@
         <v>0</v>
       </c>
       <c r="M1096" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N1096" t="n">
-        <v>12601.09</v>
+        <v>2500</v>
       </c>
       <c r="O1096" t="n">
-        <v>25202.18</v>
+        <v>20000</v>
       </c>
       <c r="P1096" t="n">
-        <v>15900</v>
+        <v>3000</v>
       </c>
       <c r="Q1096" t="n">
-        <v>31800</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
         <is>
-          <t>FG028</t>
+          <t>DPC06</t>
         </is>
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>DIDACTICO DINOSAURIO 5002A</t>
+          <t>PELUCHE OSO 3 COLORES 30CM AB-46 DPC06</t>
         </is>
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1097" t="inlineStr">
@@ -48656,7 +48659,7 @@
         </is>
       </c>
       <c r="J1097" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1097" t="n">
         <v>0</v>
@@ -48665,35 +48668,35 @@
         <v>0</v>
       </c>
       <c r="M1097" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1097" t="n">
-        <v>7824.52</v>
+        <v>12601.09</v>
       </c>
       <c r="O1097" t="n">
-        <v>7824.52</v>
+        <v>25202.18</v>
       </c>
       <c r="P1097" t="n">
-        <v>8100</v>
+        <v>15900</v>
       </c>
       <c r="Q1097" t="n">
-        <v>8100</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1098">
       <c r="A1098" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG028</t>
         </is>
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>DIDACTICO DINOSAURIO 5002A</t>
         </is>
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1098" t="inlineStr">
@@ -48702,7 +48705,7 @@
         </is>
       </c>
       <c r="J1098" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K1098" t="n">
         <v>0</v>
@@ -48711,35 +48714,35 @@
         <v>0</v>
       </c>
       <c r="M1098" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="N1098" t="n">
-        <v>2644.9</v>
+        <v>7824.52</v>
       </c>
       <c r="O1098" t="n">
-        <v>68767.40000000001</v>
+        <v>7824.52</v>
       </c>
       <c r="P1098" t="n">
-        <v>3900</v>
+        <v>8100</v>
       </c>
       <c r="Q1098" t="n">
-        <v>101400</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="1099">
       <c r="A1099" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E1099" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I1099" t="inlineStr">
@@ -48748,7 +48751,7 @@
         </is>
       </c>
       <c r="J1099" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="K1099" t="n">
         <v>0</v>
@@ -48757,30 +48760,30 @@
         <v>0</v>
       </c>
       <c r="M1099" t="n">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="N1099" t="n">
-        <v>1952.66</v>
+        <v>2644.9</v>
       </c>
       <c r="O1099" t="n">
-        <v>205029.3</v>
+        <v>68767.40000000001</v>
       </c>
       <c r="P1099" t="n">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="Q1099" t="n">
-        <v>367500</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
         <is>
-          <t>FG075</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>BLEY BLEY X 1 BLISTER 6869-1</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
         </is>
       </c>
       <c r="E1100" t="inlineStr">
@@ -48794,7 +48797,7 @@
         </is>
       </c>
       <c r="J1100" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="K1100" t="n">
         <v>0</v>
@@ -48803,35 +48806,35 @@
         <v>0</v>
       </c>
       <c r="M1100" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="N1100" t="n">
-        <v>2124.34</v>
+        <v>1952.66</v>
       </c>
       <c r="O1100" t="n">
-        <v>4248.68</v>
+        <v>205029.3</v>
       </c>
       <c r="P1100" t="n">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="Q1100" t="n">
-        <v>6400</v>
+        <v>367500</v>
       </c>
     </row>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
-          <t>FP-319</t>
+          <t>FG075</t>
         </is>
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>PELUCHE SURTIDO ECO 25CM FP-319</t>
+          <t>BLEY BLEY X 1 BLISTER 6869-1</t>
         </is>
       </c>
       <c r="E1101" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1101" t="inlineStr">
@@ -48840,7 +48843,7 @@
         </is>
       </c>
       <c r="J1101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1101" t="n">
         <v>0</v>
@@ -48849,30 +48852,30 @@
         <v>0</v>
       </c>
       <c r="M1101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1101" t="n">
-        <v>9450</v>
+        <v>2124.34</v>
       </c>
       <c r="O1101" t="n">
-        <v>28350</v>
+        <v>4248.68</v>
       </c>
       <c r="P1101" t="n">
-        <v>11900</v>
+        <v>3200</v>
       </c>
       <c r="Q1101" t="n">
-        <v>35700</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="1102">
       <c r="A1102" t="inlineStr">
         <is>
-          <t>GPH18148/VE</t>
+          <t>FP-319</t>
         </is>
       </c>
       <c r="C1102" t="inlineStr">
         <is>
-          <t>CICCIOBELLO ARRE ARRE</t>
+          <t>PELUCHE SURTIDO ECO 25CM FP-319</t>
         </is>
       </c>
       <c r="E1102" t="inlineStr">
@@ -48882,11 +48885,11 @@
       </c>
       <c r="I1102" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1102" t="n">
         <v>0</v>
@@ -48895,30 +48898,30 @@
         <v>0</v>
       </c>
       <c r="M1102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1102" t="n">
-        <v>21664.372222222</v>
+        <v>9450</v>
       </c>
       <c r="O1102" t="n">
-        <v>43328.744444444</v>
+        <v>28350</v>
       </c>
       <c r="P1102" t="n">
-        <v>30000</v>
+        <v>11900</v>
       </c>
       <c r="Q1102" t="n">
-        <v>60000</v>
+        <v>35700</v>
       </c>
     </row>
     <row r="1103">
       <c r="A1103" t="inlineStr">
         <is>
-          <t>HY-110K</t>
+          <t>GPH18148/VE</t>
         </is>
       </c>
       <c r="C1103" t="inlineStr">
         <is>
-          <t>TIJERAS PUNTA ROMA HY-110K</t>
+          <t>CICCIOBELLO ARRE ARRE</t>
         </is>
       </c>
       <c r="E1103" t="inlineStr">
@@ -48928,11 +48931,11 @@
       </c>
       <c r="I1103" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1103" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K1103" t="n">
         <v>0</v>
@@ -48941,30 +48944,30 @@
         <v>0</v>
       </c>
       <c r="M1103" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="N1103" t="n">
-        <v>1160.1556923077</v>
+        <v>21664.372222222</v>
       </c>
       <c r="O1103" t="n">
-        <v>33644.5150769233</v>
+        <v>43328.744444444</v>
       </c>
       <c r="P1103" t="n">
-        <v>1600</v>
+        <v>30000</v>
       </c>
       <c r="Q1103" t="n">
-        <v>46400</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>HY-110K</t>
         </is>
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>TIJERAS PUNTA ROMA HY-110K</t>
         </is>
       </c>
       <c r="E1104" t="inlineStr">
@@ -48978,7 +48981,7 @@
         </is>
       </c>
       <c r="J1104" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K1104" t="n">
         <v>0</v>
@@ -48987,30 +48990,30 @@
         <v>0</v>
       </c>
       <c r="M1104" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="N1104" t="n">
-        <v>7480</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O1104" t="n">
-        <v>7480</v>
+        <v>33644.5150769233</v>
       </c>
       <c r="P1104" t="n">
-        <v>9500</v>
+        <v>1600</v>
       </c>
       <c r="Q1104" t="n">
-        <v>9500</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="1105">
       <c r="A1105" t="inlineStr">
         <is>
-          <t>J-1314</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>PERRO CON GAFAS CAMINA J-1314</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E1105" t="inlineStr">
@@ -49024,7 +49027,7 @@
         </is>
       </c>
       <c r="J1105" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K1105" t="n">
         <v>0</v>
@@ -49033,30 +49036,30 @@
         <v>0</v>
       </c>
       <c r="M1105" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N1105" t="n">
-        <v>6336</v>
+        <v>7480</v>
       </c>
       <c r="O1105" t="n">
-        <v>44352</v>
+        <v>7480</v>
       </c>
       <c r="P1105" t="n">
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="Q1105" t="n">
-        <v>52500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="1106">
       <c r="A1106" t="inlineStr">
         <is>
-          <t>J-1316</t>
+          <t>J-1314</t>
         </is>
       </c>
       <c r="C1106" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>PERRO CON GAFAS CAMINA J-1314</t>
         </is>
       </c>
       <c r="E1106" t="inlineStr">
@@ -49070,7 +49073,7 @@
         </is>
       </c>
       <c r="J1106" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="K1106" t="n">
         <v>0</v>
@@ -49079,30 +49082,30 @@
         <v>0</v>
       </c>
       <c r="M1106" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="N1106" t="n">
-        <v>5280</v>
+        <v>6336</v>
       </c>
       <c r="O1106" t="n">
-        <v>459360</v>
+        <v>44352</v>
       </c>
       <c r="P1106" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q1106" t="n">
-        <v>600300</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
         <is>
-          <t>J-1317</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E1107" t="inlineStr">
@@ -49116,7 +49119,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -49125,30 +49128,30 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="N1107" t="n">
         <v>5280</v>
       </c>
       <c r="O1107" t="n">
-        <v>739200</v>
+        <v>459360</v>
       </c>
       <c r="P1107" t="n">
         <v>6900</v>
       </c>
       <c r="Q1107" t="n">
-        <v>966000</v>
+        <v>600300</v>
       </c>
     </row>
     <row r="1108">
       <c r="A1108" t="inlineStr">
         <is>
-          <t>J-1323</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E1108" t="inlineStr">
@@ -49162,7 +49165,7 @@
         </is>
       </c>
       <c r="J1108" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="K1108" t="n">
         <v>0</v>
@@ -49171,30 +49174,30 @@
         <v>0</v>
       </c>
       <c r="M1108" t="n">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N1108" t="n">
-        <v>3872</v>
+        <v>5280</v>
       </c>
       <c r="O1108" t="n">
-        <v>394944</v>
+        <v>739200</v>
       </c>
       <c r="P1108" t="n">
-        <v>4900</v>
+        <v>6900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>499800</v>
+        <v>966000</v>
       </c>
     </row>
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>J-1331</t>
+          <t>J-1323</t>
         </is>
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
+          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
         </is>
       </c>
       <c r="E1109" t="inlineStr">
@@ -49208,7 +49211,7 @@
         </is>
       </c>
       <c r="J1109" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="K1109" t="n">
         <v>0</v>
@@ -49217,30 +49220,30 @@
         <v>0</v>
       </c>
       <c r="M1109" t="n">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="N1109" t="n">
-        <v>4400</v>
+        <v>3872</v>
       </c>
       <c r="O1109" t="n">
-        <v>294800</v>
+        <v>394944</v>
       </c>
       <c r="P1109" t="n">
-        <v>5900</v>
+        <v>4900</v>
       </c>
       <c r="Q1109" t="n">
-        <v>395300</v>
+        <v>499800</v>
       </c>
     </row>
     <row r="1110">
       <c r="A1110" t="inlineStr">
         <is>
-          <t>J-556</t>
+          <t>J-1331</t>
         </is>
       </c>
       <c r="C1110" t="inlineStr">
         <is>
-          <t>VUVUCELA 25CM J-556</t>
+          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
         </is>
       </c>
       <c r="E1110" t="inlineStr">
@@ -49254,7 +49257,7 @@
         </is>
       </c>
       <c r="J1110" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="K1110" t="n">
         <v>0</v>
@@ -49263,30 +49266,30 @@
         <v>0</v>
       </c>
       <c r="M1110" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="N1110" t="n">
-        <v>1260</v>
+        <v>4400</v>
       </c>
       <c r="O1110" t="n">
-        <v>22680</v>
+        <v>294800</v>
       </c>
       <c r="P1110" t="n">
-        <v>1700</v>
+        <v>5900</v>
       </c>
       <c r="Q1110" t="n">
-        <v>30600</v>
+        <v>395300</v>
       </c>
     </row>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
-          <t>J-557</t>
+          <t>J-138</t>
         </is>
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>VUVUCELA 50 cm J-557</t>
+          <t>PERRO CAMINA J-138</t>
         </is>
       </c>
       <c r="E1111" t="inlineStr">
@@ -49300,39 +49303,42 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K1111" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L1111" t="n">
         <v>0</v>
       </c>
       <c r="M1111" t="n">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="N1111" t="n">
-        <v>2250</v>
+        <v>6160</v>
       </c>
       <c r="O1111" t="n">
-        <v>6750</v>
+        <v>1774080</v>
       </c>
       <c r="P1111" t="n">
-        <v>3000</v>
+        <v>7500</v>
       </c>
       <c r="Q1111" t="n">
-        <v>9000</v>
+        <v>2160000</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112" t="inlineStr">
         <is>
-          <t>J-582</t>
-        </is>
+          <t>J-1385</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C1112" t="inlineStr">
         <is>
-          <t>BURBUJERO ALAS J-582</t>
+          <t>PELOTA NUBES J-1385</t>
         </is>
       </c>
       <c r="E1112" t="inlineStr">
@@ -49346,39 +49352,42 @@
         </is>
       </c>
       <c r="J1112" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="K1112" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L1112" t="n">
         <v>0</v>
       </c>
       <c r="M1112" t="n">
-        <v>268</v>
+        <v>1200</v>
       </c>
       <c r="N1112" t="n">
-        <v>9240</v>
+        <v>1056</v>
       </c>
       <c r="O1112" t="n">
-        <v>2476320</v>
+        <v>1267200</v>
       </c>
       <c r="P1112" t="n">
-        <v>11500</v>
+        <v>1400</v>
       </c>
       <c r="Q1112" t="n">
-        <v>3082000</v>
+        <v>1680000</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113" t="inlineStr">
         <is>
-          <t>J-687</t>
-        </is>
+          <t>J-1387</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>BOLITRON OJO 3 COLORES J-687</t>
+          <t>VARA LUZ OSO 37cm J-1387</t>
         </is>
       </c>
       <c r="E1113" t="inlineStr">
@@ -49392,39 +49401,42 @@
         </is>
       </c>
       <c r="J1113" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="K1113" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L1113" t="n">
         <v>0</v>
       </c>
       <c r="M1113" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="N1113" t="n">
-        <v>2288</v>
+        <v>7920</v>
       </c>
       <c r="O1113" t="n">
-        <v>366080</v>
+        <v>1140480</v>
       </c>
       <c r="P1113" t="n">
-        <v>2900</v>
+        <v>10500</v>
       </c>
       <c r="Q1113" t="n">
-        <v>464000</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
         <is>
-          <t>J-718</t>
-        </is>
+          <t>J-1389</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>7700154271143</v>
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>VARA LUZ PRINCESA 37cm J-1389</t>
         </is>
       </c>
       <c r="E1114" t="inlineStr">
@@ -49438,39 +49450,39 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="K1114" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="L1114" t="n">
         <v>0</v>
       </c>
       <c r="M1114" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="N1114" t="n">
-        <v>4576</v>
+        <v>7920</v>
       </c>
       <c r="O1114" t="n">
-        <v>329472</v>
+        <v>1140480</v>
       </c>
       <c r="P1114" t="n">
-        <v>5900</v>
+        <v>10500</v>
       </c>
       <c r="Q1114" t="n">
-        <v>424800</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>J-556</t>
         </is>
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>VUVUCELA 25CM J-556</t>
         </is>
       </c>
       <c r="E1115" t="inlineStr">
@@ -49484,7 +49496,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49493,30 +49505,30 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="N1115" t="n">
-        <v>5280</v>
+        <v>1260</v>
       </c>
       <c r="O1115" t="n">
-        <v>1441440</v>
+        <v>22680</v>
       </c>
       <c r="P1115" t="n">
-        <v>6900</v>
+        <v>1700</v>
       </c>
       <c r="Q1115" t="n">
-        <v>1883700</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116" t="inlineStr">
         <is>
-          <t>J-984</t>
+          <t>J-557</t>
         </is>
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>PELOTA LUNAR J-984</t>
+          <t>VUVUCELA 50 cm J-557</t>
         </is>
       </c>
       <c r="E1116" t="inlineStr">
@@ -49530,7 +49542,7 @@
         </is>
       </c>
       <c r="J1116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
@@ -49539,30 +49551,30 @@
         <v>0</v>
       </c>
       <c r="M1116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1116" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="O1116" t="n">
-        <v>1800</v>
+        <v>6750</v>
       </c>
       <c r="P1116" t="n">
-        <v>2200</v>
+        <v>3000</v>
       </c>
       <c r="Q1116" t="n">
-        <v>2200</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117" t="inlineStr">
         <is>
-          <t>JBL0531</t>
+          <t>J-582</t>
         </is>
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>RESALTADORES FLUORESCENTE X6 JBL0531</t>
+          <t>BURBUJERO ALAS J-582</t>
         </is>
       </c>
       <c r="E1117" t="inlineStr">
@@ -49576,39 +49588,39 @@
         </is>
       </c>
       <c r="J1117" t="n">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1117" t="n">
-        <v>11</v>
+        <v>263</v>
       </c>
       <c r="N1117" t="n">
-        <v>4200</v>
+        <v>9240</v>
       </c>
       <c r="O1117" t="n">
-        <v>46200</v>
+        <v>2430120</v>
       </c>
       <c r="P1117" t="n">
-        <v>5100</v>
+        <v>11500</v>
       </c>
       <c r="Q1117" t="n">
-        <v>56100</v>
+        <v>3024500</v>
       </c>
     </row>
     <row r="1118">
       <c r="A1118" t="inlineStr">
         <is>
-          <t>JBL0536</t>
+          <t>J-687</t>
         </is>
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>SET DE REGLAS X7PCS JBL0536</t>
+          <t>BOLITRON OJO 3 COLORES J-687</t>
         </is>
       </c>
       <c r="E1118" t="inlineStr">
@@ -49622,39 +49634,39 @@
         </is>
       </c>
       <c r="J1118" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="K1118" t="n">
         <v>0</v>
       </c>
       <c r="L1118" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M1118" t="n">
-        <v>8</v>
+        <v>145</v>
       </c>
       <c r="N1118" t="n">
-        <v>5900</v>
+        <v>2288</v>
       </c>
       <c r="O1118" t="n">
-        <v>47200</v>
+        <v>331760</v>
       </c>
       <c r="P1118" t="n">
-        <v>7100</v>
+        <v>2900</v>
       </c>
       <c r="Q1118" t="n">
-        <v>56800</v>
+        <v>420500</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119" t="inlineStr">
         <is>
-          <t>JBL0538</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C1119" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA X12JBL0538</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E1119" t="inlineStr">
@@ -49668,7 +49680,7 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
@@ -49677,30 +49689,30 @@
         <v>0</v>
       </c>
       <c r="M1119" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="N1119" t="n">
-        <v>9500</v>
+        <v>4576</v>
       </c>
       <c r="O1119" t="n">
-        <v>19000</v>
+        <v>329472</v>
       </c>
       <c r="P1119" t="n">
-        <v>11400</v>
+        <v>5900</v>
       </c>
       <c r="Q1119" t="n">
-        <v>22800</v>
+        <v>424800</v>
       </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
         <is>
-          <t>JBL0539</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E1120" t="inlineStr">
@@ -49714,7 +49726,7 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
@@ -49723,30 +49735,30 @@
         <v>0</v>
       </c>
       <c r="M1120" t="n">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="N1120" t="n">
-        <v>17500</v>
+        <v>5280</v>
       </c>
       <c r="O1120" t="n">
-        <v>175000</v>
+        <v>1441440</v>
       </c>
       <c r="P1120" t="n">
-        <v>21000</v>
+        <v>6900</v>
       </c>
       <c r="Q1120" t="n">
-        <v>210000</v>
+        <v>1883700</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>JBL0540</t>
+          <t>J-984</t>
         </is>
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
+          <t>PELOTA LUNAR J-984</t>
         </is>
       </c>
       <c r="E1121" t="inlineStr">
@@ -49760,7 +49772,7 @@
         </is>
       </c>
       <c r="J1121" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K1121" t="n">
         <v>0</v>
@@ -49769,30 +49781,30 @@
         <v>0</v>
       </c>
       <c r="M1121" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N1121" t="n">
-        <v>25000</v>
+        <v>1800</v>
       </c>
       <c r="O1121" t="n">
-        <v>575000</v>
+        <v>1800</v>
       </c>
       <c r="P1121" t="n">
-        <v>30000</v>
+        <v>2200</v>
       </c>
       <c r="Q1121" t="n">
-        <v>690000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>JBL0541</t>
+          <t>JBL0531</t>
         </is>
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>ESFERO DE COLOR LAVABLE OSITOS JBL0541</t>
+          <t>RESALTADORES FLUORESCENTE X6 JBL0531</t>
         </is>
       </c>
       <c r="E1122" t="inlineStr">
@@ -49806,7 +49818,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49815,30 +49827,30 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N1122" t="n">
-        <v>4500</v>
+        <v>4200</v>
       </c>
       <c r="O1122" t="n">
-        <v>4500</v>
+        <v>46200</v>
       </c>
       <c r="P1122" t="n">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="Q1122" t="n">
-        <v>5400</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>JBL0554</t>
+          <t>JBL0536</t>
         </is>
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
+          <t>SET DE REGLAS X7PCS JBL0536</t>
         </is>
       </c>
       <c r="E1123" t="inlineStr">
@@ -49852,7 +49864,7 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
@@ -49861,30 +49873,30 @@
         <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N1123" t="n">
-        <v>9500</v>
+        <v>5900</v>
       </c>
       <c r="O1123" t="n">
-        <v>161500</v>
+        <v>47200</v>
       </c>
       <c r="P1123" t="n">
-        <v>11400</v>
+        <v>7100</v>
       </c>
       <c r="Q1123" t="n">
-        <v>193800</v>
+        <v>56800</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>JBL0557</t>
+          <t>JBL0538</t>
         </is>
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
+          <t>MARCADORES CAJA X12JBL0538</t>
         </is>
       </c>
       <c r="E1124" t="inlineStr">
@@ -49898,7 +49910,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -49907,30 +49919,30 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="N1124" t="n">
-        <v>2900</v>
+        <v>9500</v>
       </c>
       <c r="O1124" t="n">
-        <v>110200</v>
+        <v>19000</v>
       </c>
       <c r="P1124" t="n">
-        <v>3500</v>
+        <v>11400</v>
       </c>
       <c r="Q1124" t="n">
-        <v>133000</v>
+        <v>22800</v>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>JBL0657</t>
+          <t>JBL0539</t>
         </is>
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
+          <t>MARCADORES CAJA PLASTICA X24 JBL0539</t>
         </is>
       </c>
       <c r="E1125" t="inlineStr">
@@ -49944,7 +49956,7 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
@@ -49953,30 +49965,30 @@
         <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="N1125" t="n">
-        <v>1000</v>
+        <v>17500</v>
       </c>
       <c r="O1125" t="n">
-        <v>29000</v>
+        <v>175000</v>
       </c>
       <c r="P1125" t="n">
-        <v>1200</v>
+        <v>21000</v>
       </c>
       <c r="Q1125" t="n">
-        <v>34800</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>JBL0707</t>
+          <t>JBL0540</t>
         </is>
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
+          <t>MARCADORES CAJA PLASTICA X36 JBL0540</t>
         </is>
       </c>
       <c r="E1126" t="inlineStr">
@@ -49990,7 +50002,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -49999,30 +50011,30 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N1126" t="n">
-        <v>3600</v>
+        <v>25000</v>
       </c>
       <c r="O1126" t="n">
-        <v>64800</v>
+        <v>575000</v>
       </c>
       <c r="P1126" t="n">
-        <v>4400</v>
+        <v>30000</v>
       </c>
       <c r="Q1126" t="n">
-        <v>79200</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>JBL0729</t>
+          <t>JBL0541</t>
         </is>
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
+          <t>ESFERO DE COLOR LAVABLE OSITOS JBL0541</t>
         </is>
       </c>
       <c r="E1127" t="inlineStr">
@@ -50036,7 +50048,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50045,30 +50057,30 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N1127" t="n">
-        <v>9300</v>
+        <v>4500</v>
       </c>
       <c r="O1127" t="n">
-        <v>65100</v>
+        <v>4500</v>
       </c>
       <c r="P1127" t="n">
-        <v>11200</v>
+        <v>5400</v>
       </c>
       <c r="Q1127" t="n">
-        <v>78400</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>JO-129</t>
+          <t>JBL0554</t>
         </is>
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
+          <t>CAJA DE COLORES X 12 PCS JBL0554</t>
         </is>
       </c>
       <c r="E1128" t="inlineStr">
@@ -50082,7 +50094,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -50091,30 +50103,30 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N1128" t="n">
-        <v>4500</v>
+        <v>9500</v>
       </c>
       <c r="O1128" t="n">
-        <v>58500</v>
+        <v>161500</v>
       </c>
       <c r="P1128" t="n">
-        <v>5400</v>
+        <v>11400</v>
       </c>
       <c r="Q1128" t="n">
-        <v>70200</v>
+        <v>193800</v>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>JO-139</t>
+          <t>JBL0557</t>
         </is>
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
+          <t>CAJA COLORES MINI X 12 PCS  JBL0557</t>
         </is>
       </c>
       <c r="E1129" t="inlineStr">
@@ -50128,7 +50140,7 @@
         </is>
       </c>
       <c r="J1129" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="K1129" t="n">
         <v>0</v>
@@ -50137,30 +50149,30 @@
         <v>0</v>
       </c>
       <c r="M1129" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="N1129" t="n">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="O1129" t="n">
-        <v>145800</v>
+        <v>110200</v>
       </c>
       <c r="P1129" t="n">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="Q1129" t="n">
-        <v>178200</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>JO-141</t>
+          <t>JBL0657</t>
         </is>
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE FAST FOOD JO-141</t>
+          <t>TAJALAPIZ CON DEPOSITO JBL0657</t>
         </is>
       </c>
       <c r="E1130" t="inlineStr">
@@ -50174,7 +50186,7 @@
         </is>
       </c>
       <c r="J1130" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="K1130" t="n">
         <v>0</v>
@@ -50183,30 +50195,30 @@
         <v>0</v>
       </c>
       <c r="M1130" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="N1130" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="O1130" t="n">
-        <v>102000</v>
+        <v>29000</v>
       </c>
       <c r="P1130" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="Q1130" t="n">
-        <v>122400</v>
+        <v>34800</v>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>JO-142</t>
+          <t>JBL0707</t>
         </is>
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
+          <t>SET GEOMETRICO FLEXIBLE X 4 PCS JBL0707</t>
         </is>
       </c>
       <c r="E1131" t="inlineStr">
@@ -50220,7 +50232,7 @@
         </is>
       </c>
       <c r="J1131" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="K1131" t="n">
         <v>0</v>
@@ -50229,30 +50241,30 @@
         <v>0</v>
       </c>
       <c r="M1131" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="N1131" t="n">
-        <v>1900</v>
+        <v>3600</v>
       </c>
       <c r="O1131" t="n">
-        <v>134900</v>
+        <v>64800</v>
       </c>
       <c r="P1131" t="n">
-        <v>2300</v>
+        <v>4400</v>
       </c>
       <c r="Q1131" t="n">
-        <v>163300</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>JO-143</t>
+          <t>JBL0729</t>
         </is>
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
+          <t>LONCHERA INFANTIL MODELOS STD 22,5cm JBL0729</t>
         </is>
       </c>
       <c r="E1132" t="inlineStr">
@@ -50266,7 +50278,7 @@
         </is>
       </c>
       <c r="J1132" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="K1132" t="n">
         <v>0</v>
@@ -50275,30 +50287,30 @@
         <v>0</v>
       </c>
       <c r="M1132" t="n">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="N1132" t="n">
-        <v>1400</v>
+        <v>9300</v>
       </c>
       <c r="O1132" t="n">
-        <v>95200</v>
+        <v>65100</v>
       </c>
       <c r="P1132" t="n">
-        <v>1700</v>
+        <v>11200</v>
       </c>
       <c r="Q1132" t="n">
-        <v>115600</v>
+        <v>78400</v>
       </c>
     </row>
     <row r="1133">
       <c r="A1133" t="inlineStr">
         <is>
-          <t>JO-144</t>
+          <t>JO-129</t>
         </is>
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
+          <t>LAPICES COLORES X12 DOBLE PUNTA JO-129</t>
         </is>
       </c>
       <c r="E1133" t="inlineStr">
@@ -50312,7 +50324,7 @@
         </is>
       </c>
       <c r="J1133" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="K1133" t="n">
         <v>0</v>
@@ -50321,30 +50333,30 @@
         <v>0</v>
       </c>
       <c r="M1133" t="n">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="N1133" t="n">
-        <v>1900</v>
+        <v>4500</v>
       </c>
       <c r="O1133" t="n">
-        <v>133000</v>
+        <v>58500</v>
       </c>
       <c r="P1133" t="n">
-        <v>2300</v>
+        <v>5400</v>
       </c>
       <c r="Q1133" t="n">
-        <v>161000</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134" t="inlineStr">
         <is>
-          <t>JO-145</t>
+          <t>JO-139</t>
         </is>
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
+          <t>ESFERO GIRATORIO 10 MINAS MUÑECA JO-139</t>
         </is>
       </c>
       <c r="E1134" t="inlineStr">
@@ -50358,7 +50370,7 @@
         </is>
       </c>
       <c r="J1134" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="K1134" t="n">
         <v>0</v>
@@ -50367,30 +50379,30 @@
         <v>0</v>
       </c>
       <c r="M1134" t="n">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="N1134" t="n">
-        <v>1900</v>
+        <v>2700</v>
       </c>
       <c r="O1134" t="n">
-        <v>239400</v>
+        <v>145800</v>
       </c>
       <c r="P1134" t="n">
-        <v>2300</v>
+        <v>3300</v>
       </c>
       <c r="Q1134" t="n">
-        <v>289800</v>
+        <v>178200</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135" t="inlineStr">
         <is>
-          <t>JOE-1813</t>
+          <t>JO-141</t>
         </is>
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
+          <t>ESFERO BORRABLE FAST FOOD JO-141</t>
         </is>
       </c>
       <c r="E1135" t="inlineStr">
@@ -50404,7 +50416,7 @@
         </is>
       </c>
       <c r="J1135" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="K1135" t="n">
         <v>0</v>
@@ -50413,30 +50425,30 @@
         <v>0</v>
       </c>
       <c r="M1135" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="N1135" t="n">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="O1135" t="n">
-        <v>78000</v>
+        <v>102000</v>
       </c>
       <c r="P1135" t="n">
-        <v>7200</v>
+        <v>1800</v>
       </c>
       <c r="Q1135" t="n">
-        <v>93600</v>
+        <v>122400</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>JOE-9812</t>
+          <t>JO-142</t>
         </is>
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
+          <t>ESFERO BORRABLE CON BORRADOR ASTRONAUTA JO-142</t>
         </is>
       </c>
       <c r="E1136" t="inlineStr">
@@ -50450,7 +50462,7 @@
         </is>
       </c>
       <c r="J1136" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="K1136" t="n">
         <v>0</v>
@@ -50459,30 +50471,30 @@
         <v>0</v>
       </c>
       <c r="M1136" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="N1136" t="n">
-        <v>5000</v>
+        <v>1900</v>
       </c>
       <c r="O1136" t="n">
-        <v>45000</v>
+        <v>134900</v>
       </c>
       <c r="P1136" t="n">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="Q1136" t="n">
-        <v>54000</v>
+        <v>163300</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137" t="inlineStr">
         <is>
-          <t>JT-13</t>
+          <t>JO-143</t>
         </is>
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>CORRECTOR EN CINTA JT-13</t>
+          <t>ESFERO BORRABKLE CON BORRADOR ARCOIRIS JO-143</t>
         </is>
       </c>
       <c r="E1137" t="inlineStr">
@@ -50496,7 +50508,7 @@
         </is>
       </c>
       <c r="J1137" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="K1137" t="n">
         <v>0</v>
@@ -50505,39 +50517,44 @@
         <v>0</v>
       </c>
       <c r="M1137" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N1137" t="n">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="O1137" t="n">
-        <v>55200</v>
+        <v>95200</v>
       </c>
       <c r="P1137" t="n">
-        <v>2900</v>
+        <v>1700</v>
       </c>
       <c r="Q1137" t="n">
-        <v>66700</v>
+        <v>115600</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138" t="inlineStr">
         <is>
-          <t>KBX-3088</t>
+          <t>JO-144</t>
         </is>
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>BORRADOR PORTAMINAS</t>
+          <t>ESFERO BORRABLE CON BORRADOR PANDA JO-144</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1138" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1138" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="K1138" t="n">
         <v>0</v>
@@ -50546,30 +50563,30 @@
         <v>0</v>
       </c>
       <c r="M1138" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N1138" t="n">
-        <v>3000</v>
+        <v>1900</v>
       </c>
       <c r="O1138" t="n">
-        <v>69000</v>
+        <v>133000</v>
       </c>
       <c r="P1138" t="n">
-        <v>3600</v>
+        <v>2300</v>
       </c>
       <c r="Q1138" t="n">
-        <v>82800</v>
+        <v>161000</v>
       </c>
     </row>
     <row r="1139">
       <c r="A1139" t="inlineStr">
         <is>
-          <t>LY6807</t>
+          <t>JO-145</t>
         </is>
       </c>
       <c r="C1139" t="inlineStr">
         <is>
-          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
+          <t>ESFERO BORRABLE CON BORRADOR OSITO JO-145</t>
         </is>
       </c>
       <c r="E1139" t="inlineStr">
@@ -50583,7 +50600,7 @@
         </is>
       </c>
       <c r="J1139" t="n">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="K1139" t="n">
         <v>0</v>
@@ -50592,30 +50609,30 @@
         <v>0</v>
       </c>
       <c r="M1139" t="n">
-        <v>3</v>
+        <v>126</v>
       </c>
       <c r="N1139" t="n">
-        <v>415.07</v>
+        <v>1900</v>
       </c>
       <c r="O1139" t="n">
-        <v>1245.21</v>
+        <v>239400</v>
       </c>
       <c r="P1139" t="n">
-        <v>2900</v>
+        <v>2300</v>
       </c>
       <c r="Q1139" t="n">
-        <v>8700</v>
+        <v>289800</v>
       </c>
     </row>
     <row r="1140">
       <c r="A1140" t="inlineStr">
         <is>
-          <t>MC121011-E</t>
+          <t>JOE-1813</t>
         </is>
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
+          <t>SET MARCADORES ACUARELA LAVAVBLE TUBO X 18 PCS JOE-1813</t>
         </is>
       </c>
       <c r="E1140" t="inlineStr">
@@ -50629,7 +50646,7 @@
         </is>
       </c>
       <c r="J1140" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K1140" t="n">
         <v>0</v>
@@ -50638,30 +50655,30 @@
         <v>0</v>
       </c>
       <c r="M1140" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N1140" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="O1140" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="P1140" t="n">
-        <v>7800</v>
+        <v>7200</v>
       </c>
       <c r="Q1140" t="n">
-        <v>46800</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
-          <t>MC121206-E</t>
+          <t>JOE-9812</t>
         </is>
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>SET DE LAPICES CON BORRADOR  MC121206-E</t>
+          <t>SET MARCADORES JUMBO ACUARELA X12/14cm</t>
         </is>
       </c>
       <c r="E1141" t="inlineStr">
@@ -50675,7 +50692,7 @@
         </is>
       </c>
       <c r="J1141" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1141" t="n">
         <v>0</v>
@@ -50684,30 +50701,30 @@
         <v>0</v>
       </c>
       <c r="M1141" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N1141" t="n">
-        <v>6500</v>
+        <v>5000</v>
       </c>
       <c r="O1141" t="n">
-        <v>39000</v>
+        <v>45000</v>
       </c>
       <c r="P1141" t="n">
-        <v>7800</v>
+        <v>6000</v>
       </c>
       <c r="Q1141" t="n">
-        <v>46800</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142" t="inlineStr">
         <is>
-          <t>MC121212</t>
+          <t>JT-13</t>
         </is>
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
+          <t>CORRECTOR EN CINTA JT-13</t>
         </is>
       </c>
       <c r="E1142" t="inlineStr">
@@ -50721,7 +50738,7 @@
         </is>
       </c>
       <c r="J1142" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K1142" t="n">
         <v>0</v>
@@ -50730,44 +50747,39 @@
         <v>0</v>
       </c>
       <c r="M1142" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="N1142" t="n">
-        <v>6500</v>
+        <v>2400</v>
       </c>
       <c r="O1142" t="n">
-        <v>104000</v>
+        <v>55200</v>
       </c>
       <c r="P1142" t="n">
-        <v>7800</v>
+        <v>2900</v>
       </c>
       <c r="Q1142" t="n">
-        <v>124800</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="1143">
       <c r="A1143" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>KBX-3088</t>
         </is>
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
-        </is>
-      </c>
-      <c r="E1143" t="inlineStr">
-        <is>
-          <t>MUÑECO</t>
+          <t>BORRADOR PORTAMINAS</t>
         </is>
       </c>
       <c r="I1143" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1143" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K1143" t="n">
         <v>0</v>
@@ -50776,35 +50788,35 @@
         <v>0</v>
       </c>
       <c r="M1143" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N1143" t="n">
-        <v>576.58</v>
+        <v>3000</v>
       </c>
       <c r="O1143" t="n">
-        <v>9801.860000000001</v>
+        <v>69000</v>
       </c>
       <c r="P1143" t="n">
-        <v>5900</v>
+        <v>3600</v>
       </c>
       <c r="Q1143" t="n">
-        <v>100300</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>LY6807</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>JUGUETE PATINETA DE CUATRO RUEDAS LY6807</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1144" t="inlineStr">
@@ -50813,7 +50825,7 @@
         </is>
       </c>
       <c r="J1144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1144" t="n">
         <v>0</v>
@@ -50822,40 +50834,35 @@
         <v>0</v>
       </c>
       <c r="M1144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1144" t="n">
-        <v>8174.05</v>
+        <v>415.07</v>
       </c>
       <c r="O1144" t="n">
-        <v>8174.05</v>
+        <v>1245.21</v>
       </c>
       <c r="P1144" t="n">
-        <v>8900</v>
+        <v>2900</v>
       </c>
       <c r="Q1144" t="n">
-        <v>8900</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B1145" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MC121011-E</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SET LAPIZ CON BORRADOR OSITOS MC121011-E</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1145" t="inlineStr">
@@ -50864,7 +50871,7 @@
         </is>
       </c>
       <c r="J1145" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1145" t="n">
         <v>0</v>
@@ -50873,35 +50880,35 @@
         <v>0</v>
       </c>
       <c r="M1145" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N1145" t="n">
-        <v>751.45</v>
+        <v>6500</v>
       </c>
       <c r="O1145" t="n">
-        <v>751.45</v>
+        <v>39000</v>
       </c>
       <c r="P1145" t="n">
-        <v>2500</v>
+        <v>7800</v>
       </c>
       <c r="Q1145" t="n">
-        <v>2500</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>MG40207</t>
+          <t>MC121206-E</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>SONAJERO DOBLE HELICE MG40207</t>
+          <t>SET DE LAPICES CON BORRADOR  MC121206-E</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1146" t="inlineStr">
@@ -50910,7 +50917,7 @@
         </is>
       </c>
       <c r="J1146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1146" t="n">
         <v>0</v>
@@ -50919,35 +50926,35 @@
         <v>0</v>
       </c>
       <c r="M1146" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N1146" t="n">
-        <v>323.9775</v>
+        <v>6500</v>
       </c>
       <c r="O1146" t="n">
-        <v>323.9775</v>
+        <v>39000</v>
       </c>
       <c r="P1146" t="n">
-        <v>1500</v>
+        <v>7800</v>
       </c>
       <c r="Q1146" t="n">
-        <v>1500</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MC121212</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
         </is>
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1147" t="inlineStr">
@@ -50956,7 +50963,7 @@
         </is>
       </c>
       <c r="J1147" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K1147" t="n">
         <v>0</v>
@@ -50965,35 +50972,35 @@
         <v>0</v>
       </c>
       <c r="M1147" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N1147" t="n">
-        <v>310.4175</v>
+        <v>6500</v>
       </c>
       <c r="O1147" t="n">
-        <v>1862.505</v>
+        <v>104000</v>
       </c>
       <c r="P1147" t="n">
-        <v>1800</v>
+        <v>7800</v>
       </c>
       <c r="Q1147" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I1148" t="inlineStr">
@@ -51002,7 +51009,7 @@
         </is>
       </c>
       <c r="J1148" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="K1148" t="n">
         <v>0</v>
@@ -51011,35 +51018,35 @@
         <v>0</v>
       </c>
       <c r="M1148" t="n">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="N1148" t="n">
-        <v>227.41614285714</v>
+        <v>576.58</v>
       </c>
       <c r="O1148" t="n">
-        <v>17965.87528571406</v>
+        <v>9801.860000000001</v>
       </c>
       <c r="P1148" t="n">
-        <v>1200</v>
+        <v>5900</v>
       </c>
       <c r="Q1148" t="n">
-        <v>94800</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>MG40836</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>MUÑECO GUERRERO BOLSA MG40836</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1149" t="inlineStr">
@@ -51048,7 +51055,7 @@
         </is>
       </c>
       <c r="J1149" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="K1149" t="n">
         <v>0</v>
@@ -51057,40 +51064,40 @@
         <v>0</v>
       </c>
       <c r="M1149" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="N1149" t="n">
-        <v>1441.78</v>
+        <v>8174.05</v>
       </c>
       <c r="O1149" t="n">
-        <v>121109.52</v>
+        <v>8174.05</v>
       </c>
       <c r="P1149" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="Q1149" t="n">
-        <v>201600</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>MG40952</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>MG40952</t>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>CAMIONETA BLACK MG40952</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I1150" t="inlineStr">
@@ -51111,32 +51118,37 @@
         <v>1</v>
       </c>
       <c r="N1150" t="n">
-        <v>38043.57</v>
+        <v>751.45</v>
       </c>
       <c r="O1150" t="n">
-        <v>38043.57</v>
+        <v>751.45</v>
       </c>
       <c r="P1150" t="n">
-        <v>70900</v>
+        <v>2500</v>
       </c>
       <c r="Q1150" t="n">
-        <v>70900</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>P155</t>
+          <t>MG40207</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
+          <t>SONAJERO DOBLE HELICE MG40207</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1151" t="n">
@@ -51152,36 +51164,41 @@
         <v>1</v>
       </c>
       <c r="N1151" t="n">
-        <v>1461.53</v>
+        <v>323.9775</v>
       </c>
       <c r="O1151" t="n">
-        <v>1461.53</v>
+        <v>323.9775</v>
       </c>
       <c r="P1151" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="Q1151" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>P214</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
+          <t>ATARY COCODRILO MG40226</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1152" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -51190,39 +51207,44 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N1152" t="n">
-        <v>3153.85</v>
+        <v>310.4175</v>
       </c>
       <c r="O1152" t="n">
-        <v>3153.85</v>
+        <v>1862.505</v>
       </c>
       <c r="P1152" t="n">
-        <v>4100</v>
+        <v>1800</v>
       </c>
       <c r="Q1152" t="n">
-        <v>4100</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>P458</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1153" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1153" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="K1153" t="n">
         <v>0</v>
@@ -51231,35 +51253,35 @@
         <v>0</v>
       </c>
       <c r="M1153" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="N1153" t="n">
-        <v>1230.76</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O1153" t="n">
-        <v>39384.32</v>
+        <v>17965.87528571406</v>
       </c>
       <c r="P1153" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="Q1153" t="n">
-        <v>51200</v>
+        <v>94800</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>PT14026</t>
+          <t>MG40836</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
+          <t>MUÑECO GUERRERO BOLSA MG40836</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -51268,7 +51290,7 @@
         </is>
       </c>
       <c r="J1154" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="K1154" t="n">
         <v>0</v>
@@ -51277,39 +51299,49 @@
         <v>0</v>
       </c>
       <c r="M1154" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="N1154" t="n">
-        <v>2690.69</v>
+        <v>1441.78</v>
       </c>
       <c r="O1154" t="n">
-        <v>2690.69</v>
+        <v>121109.52</v>
       </c>
       <c r="P1154" t="n">
-        <v>5900</v>
+        <v>2400</v>
       </c>
       <c r="Q1154" t="n">
-        <v>5900</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>Q1241</t>
+          <t>MG40952</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>MG40952</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>RESALTADOR BOTELLA</t>
+          <t>CAMIONETA BLACK MG40952</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1155" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
@@ -51318,44 +51350,39 @@
         <v>0</v>
       </c>
       <c r="M1155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1155" t="n">
-        <v>5000</v>
+        <v>38043.57</v>
       </c>
       <c r="O1155" t="n">
-        <v>15000</v>
+        <v>38043.57</v>
       </c>
       <c r="P1155" t="n">
-        <v>6000</v>
+        <v>70900</v>
       </c>
       <c r="Q1155" t="n">
-        <v>18000</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>QH-8308</t>
+          <t>P155</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
-        </is>
-      </c>
-      <c r="E1156" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1156" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K1156" t="n">
         <v>0</v>
@@ -51364,44 +51391,39 @@
         <v>0</v>
       </c>
       <c r="M1156" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N1156" t="n">
-        <v>2200</v>
+        <v>1461.53</v>
       </c>
       <c r="O1156" t="n">
-        <v>26400</v>
+        <v>1461.53</v>
       </c>
       <c r="P1156" t="n">
-        <v>2700</v>
+        <v>1900</v>
       </c>
       <c r="Q1156" t="n">
-        <v>32400</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>QH-8311</t>
+          <t>P214</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>SET BORRADORES ANIMALES QH-8311</t>
-        </is>
-      </c>
-      <c r="E1157" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
         </is>
       </c>
       <c r="I1157" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -51410,44 +51432,39 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N1157" t="n">
-        <v>2200</v>
+        <v>3153.85</v>
       </c>
       <c r="O1157" t="n">
-        <v>24200</v>
+        <v>3153.85</v>
       </c>
       <c r="P1157" t="n">
-        <v>2700</v>
+        <v>4100</v>
       </c>
       <c r="Q1157" t="n">
-        <v>29700</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>QH-8314</t>
+          <t>P458</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>SET BORRADORES DEPORTES QH-8314</t>
-        </is>
-      </c>
-      <c r="E1158" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
         </is>
       </c>
       <c r="I1158" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
@@ -51456,35 +51473,35 @@
         <v>0</v>
       </c>
       <c r="M1158" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="N1158" t="n">
-        <v>2200</v>
+        <v>1230.76</v>
       </c>
       <c r="O1158" t="n">
-        <v>39600</v>
+        <v>39384.32</v>
       </c>
       <c r="P1158" t="n">
-        <v>2700</v>
+        <v>1600</v>
       </c>
       <c r="Q1158" t="n">
-        <v>48600</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>QH-8317</t>
+          <t>PT14026</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>SET BORRADORES POSTRES QH-8317</t>
+          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1159" t="inlineStr">
@@ -51493,7 +51510,7 @@
         </is>
       </c>
       <c r="J1159" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K1159" t="n">
         <v>0</v>
@@ -51502,44 +51519,39 @@
         <v>0</v>
       </c>
       <c r="M1159" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N1159" t="n">
-        <v>2200</v>
+        <v>2690.69</v>
       </c>
       <c r="O1159" t="n">
-        <v>19800</v>
+        <v>2690.69</v>
       </c>
       <c r="P1159" t="n">
-        <v>2700</v>
+        <v>5900</v>
       </c>
       <c r="Q1159" t="n">
-        <v>24300</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>QH-8385</t>
+          <t>Q1241</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>SET BORRADORES ESPACIAL QH-8385</t>
-        </is>
-      </c>
-      <c r="E1160" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RESALTADOR BOTELLA</t>
         </is>
       </c>
       <c r="I1160" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1160" t="n">
         <v>0</v>
@@ -51548,30 +51560,30 @@
         <v>0</v>
       </c>
       <c r="M1160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1160" t="n">
-        <v>2200</v>
+        <v>5000</v>
       </c>
       <c r="O1160" t="n">
-        <v>4400</v>
+        <v>15000</v>
       </c>
       <c r="P1160" t="n">
-        <v>2700</v>
+        <v>6000</v>
       </c>
       <c r="Q1160" t="n">
-        <v>5400</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QH-8308</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
@@ -51585,7 +51597,7 @@
         </is>
       </c>
       <c r="J1161" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="K1161" t="n">
         <v>0</v>
@@ -51594,30 +51606,30 @@
         <v>0</v>
       </c>
       <c r="M1161" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="N1161" t="n">
         <v>2200</v>
       </c>
       <c r="O1161" t="n">
-        <v>158400</v>
+        <v>26400</v>
       </c>
       <c r="P1161" t="n">
         <v>2700</v>
       </c>
       <c r="Q1161" t="n">
-        <v>194400</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>QH-8311</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>SET BORRADORES ANIMALES QH-8311</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -51631,7 +51643,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51640,30 +51652,30 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="N1162" t="n">
         <v>2200</v>
       </c>
       <c r="O1162" t="n">
-        <v>151800</v>
+        <v>24200</v>
       </c>
       <c r="P1162" t="n">
         <v>2700</v>
       </c>
       <c r="Q1162" t="n">
-        <v>186300</v>
+        <v>29700</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>QH-8314</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>SET BORRADORES DEPORTES QH-8314</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
@@ -51677,7 +51689,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51686,30 +51698,30 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="N1163" t="n">
         <v>2200</v>
       </c>
       <c r="O1163" t="n">
-        <v>154000</v>
+        <v>39600</v>
       </c>
       <c r="P1163" t="n">
         <v>2700</v>
       </c>
       <c r="Q1163" t="n">
-        <v>189000</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>QH-8317</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>SET BORRADORES POSTRES QH-8317</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
@@ -51723,7 +51735,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51732,30 +51744,30 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N1164" t="n">
-        <v>5026.665862069</v>
+        <v>2200</v>
       </c>
       <c r="O1164" t="n">
-        <v>70373.32206896599</v>
+        <v>19800</v>
       </c>
       <c r="P1164" t="n">
-        <v>6300</v>
+        <v>2700</v>
       </c>
       <c r="Q1164" t="n">
-        <v>88200</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>QH-8385</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>SET BORRADORES ESPACIAL QH-8385</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
@@ -51769,7 +51781,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51778,30 +51790,30 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N1165" t="n">
-        <v>5200</v>
+        <v>2200</v>
       </c>
       <c r="O1165" t="n">
-        <v>78000</v>
+        <v>4400</v>
       </c>
       <c r="P1165" t="n">
-        <v>6300</v>
+        <v>2700</v>
       </c>
       <c r="Q1165" t="n">
-        <v>94500</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>QT512452-E</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
@@ -51815,7 +51827,7 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -51824,30 +51836,30 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="N1166" t="n">
-        <v>8800</v>
+        <v>2200</v>
       </c>
       <c r="O1166" t="n">
-        <v>149600</v>
+        <v>158400</v>
       </c>
       <c r="P1166" t="n">
-        <v>10600</v>
+        <v>2700</v>
       </c>
       <c r="Q1166" t="n">
-        <v>180200</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>QQ-1503</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
@@ -51861,7 +51873,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51870,39 +51882,44 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="N1167" t="n">
-        <v>8800</v>
+        <v>2200</v>
       </c>
       <c r="O1167" t="n">
-        <v>149600</v>
+        <v>151800</v>
       </c>
       <c r="P1167" t="n">
-        <v>10600</v>
+        <v>2700</v>
       </c>
       <c r="Q1167" t="n">
-        <v>180200</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>S145</t>
+          <t>QQ-1525</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1168" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -51911,30 +51928,30 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="N1168" t="n">
-        <v>11538.4</v>
+        <v>2200</v>
       </c>
       <c r="O1168" t="n">
-        <v>11538.4</v>
+        <v>154000</v>
       </c>
       <c r="P1168" t="n">
-        <v>15000</v>
+        <v>2700</v>
       </c>
       <c r="Q1168" t="n">
-        <v>15000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
@@ -51948,7 +51965,7 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>260</v>
+        <v>14</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -51957,30 +51974,30 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>260</v>
+        <v>14</v>
       </c>
       <c r="N1169" t="n">
-        <v>4550</v>
+        <v>5026.665862069</v>
       </c>
       <c r="O1169" t="n">
-        <v>1183000</v>
+        <v>70373.32206896599</v>
       </c>
       <c r="P1169" t="n">
-        <v>5500</v>
+        <v>6300</v>
       </c>
       <c r="Q1169" t="n">
-        <v>1430000</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
@@ -51994,7 +52011,7 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -52003,39 +52020,44 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N1170" t="n">
-        <v>1059.1847727273</v>
+        <v>5200</v>
       </c>
       <c r="O1170" t="n">
-        <v>8473.4781818184</v>
+        <v>78000</v>
       </c>
       <c r="P1170" t="n">
-        <v>9500</v>
+        <v>6300</v>
       </c>
       <c r="Q1170" t="n">
-        <v>76000</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>SY-661-A08</t>
+          <t>QT512452-E</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER HEROES</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1171" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -52044,39 +52066,44 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N1171" t="n">
-        <v>7500</v>
+        <v>8800</v>
       </c>
       <c r="O1171" t="n">
-        <v>45000</v>
+        <v>149600</v>
       </c>
       <c r="P1171" t="n">
-        <v>9000</v>
+        <v>10600</v>
       </c>
       <c r="Q1171" t="n">
-        <v>54000</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>SY-661-A09</t>
+          <t>QT512453-E</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER MARIO</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1172" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -52085,44 +52112,39 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N1172" t="n">
-        <v>7500</v>
+        <v>8800</v>
       </c>
       <c r="O1172" t="n">
-        <v>105000</v>
+        <v>149600</v>
       </c>
       <c r="P1172" t="n">
-        <v>9000</v>
+        <v>10600</v>
       </c>
       <c r="Q1172" t="n">
-        <v>126000</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>S145</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
-        </is>
-      </c>
-      <c r="E1173" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
         </is>
       </c>
       <c r="I1173" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
@@ -52131,35 +52153,35 @@
         <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1173" t="n">
-        <v>12392.16</v>
+        <v>11538.4</v>
       </c>
       <c r="O1173" t="n">
-        <v>24784.32</v>
+        <v>11538.4</v>
       </c>
       <c r="P1173" t="n">
-        <v>15900</v>
+        <v>15000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>31800</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1174" t="inlineStr">
@@ -52168,44 +52190,44 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>2</v>
+        <v>260</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
       </c>
       <c r="L1174" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1174" t="n">
-        <v>2</v>
+        <v>255</v>
       </c>
       <c r="N1174" t="n">
-        <v>5186.45</v>
+        <v>4550</v>
       </c>
       <c r="O1174" t="n">
-        <v>10372.9</v>
+        <v>1160250</v>
       </c>
       <c r="P1174" t="n">
-        <v>7200</v>
+        <v>5500</v>
       </c>
       <c r="Q1174" t="n">
-        <v>14400</v>
+        <v>1402500</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>T219</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E1175" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1175" t="inlineStr">
@@ -52214,7 +52236,7 @@
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K1175" t="n">
         <v>0</v>
@@ -52223,30 +52245,30 @@
         <v>0</v>
       </c>
       <c r="M1175" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N1175" t="n">
-        <v>8746.92</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O1175" t="n">
-        <v>87469.2</v>
+        <v>8473.4781818184</v>
       </c>
       <c r="P1175" t="n">
-        <v>11000</v>
+        <v>9500</v>
       </c>
       <c r="Q1175" t="n">
-        <v>110000</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>WT-E170</t>
+          <t>SY-661-A08</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
+          <t>RESALTADOR SUPER HEROES</t>
         </is>
       </c>
       <c r="I1176" t="inlineStr">
@@ -52255,7 +52277,7 @@
         </is>
       </c>
       <c r="J1176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1176" t="n">
         <v>0</v>
@@ -52264,44 +52286,39 @@
         <v>0</v>
       </c>
       <c r="M1176" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N1176" t="n">
-        <v>73405.77</v>
+        <v>7500</v>
       </c>
       <c r="O1176" t="n">
-        <v>367028.85</v>
+        <v>45000</v>
       </c>
       <c r="P1176" t="n">
-        <v>77900</v>
+        <v>9000</v>
       </c>
       <c r="Q1176" t="n">
-        <v>389500</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>XP-2984</t>
+          <t>SY-661-A09</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL XP-2984</t>
-        </is>
-      </c>
-      <c r="E1177" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RESALTADOR SUPER MARIO</t>
         </is>
       </c>
       <c r="I1177" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
@@ -52310,35 +52327,35 @@
         <v>0</v>
       </c>
       <c r="M1177" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="N1177" t="n">
-        <v>2403.97703125</v>
+        <v>7500</v>
       </c>
       <c r="O1177" t="n">
-        <v>103371.01234375</v>
+        <v>105000</v>
       </c>
       <c r="P1177" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="Q1177" t="n">
-        <v>129000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>XP-2986</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1178" t="inlineStr">
@@ -52347,7 +52364,7 @@
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
@@ -52356,39 +52373,44 @@
         <v>0</v>
       </c>
       <c r="M1178" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="N1178" t="n">
-        <v>2402.6741007194</v>
+        <v>12392.16</v>
       </c>
       <c r="O1178" t="n">
-        <v>103314.9863309342</v>
+        <v>24784.32</v>
       </c>
       <c r="P1178" t="n">
-        <v>3000</v>
+        <v>15900</v>
       </c>
       <c r="Q1178" t="n">
-        <v>129000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>YOYO2001</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>ZET LAPIZ</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1179" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
@@ -52397,18 +52419,238 @@
         <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N1179" t="n">
-        <v>6000</v>
+        <v>5186.45</v>
       </c>
       <c r="O1179" t="n">
-        <v>246000</v>
+        <v>10372.9</v>
       </c>
       <c r="P1179" t="n">
         <v>7200</v>
       </c>
       <c r="Q1179" t="n">
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>T219</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1180" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1180" t="n">
+        <v>10</v>
+      </c>
+      <c r="N1180" t="n">
+        <v>8746.92</v>
+      </c>
+      <c r="O1180" t="n">
+        <v>87469.2</v>
+      </c>
+      <c r="P1180" t="n">
+        <v>11000</v>
+      </c>
+      <c r="Q1180" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>WT-E170</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J1181" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1181" t="n">
+        <v>5</v>
+      </c>
+      <c r="N1181" t="n">
+        <v>73405.77</v>
+      </c>
+      <c r="O1181" t="n">
+        <v>367028.85</v>
+      </c>
+      <c r="P1181" t="n">
+        <v>77900</v>
+      </c>
+      <c r="Q1181" t="n">
+        <v>389500</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>XP-2984</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>BORRADOR RETRACTIL XP-2984</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1182" t="n">
+        <v>43</v>
+      </c>
+      <c r="K1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1182" t="n">
+        <v>43</v>
+      </c>
+      <c r="N1182" t="n">
+        <v>2403.97703125</v>
+      </c>
+      <c r="O1182" t="n">
+        <v>103371.01234375</v>
+      </c>
+      <c r="P1182" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q1182" t="n">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>XP-2986</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1183" t="n">
+        <v>43</v>
+      </c>
+      <c r="K1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1183" t="n">
+        <v>43</v>
+      </c>
+      <c r="N1183" t="n">
+        <v>2402.6741007194</v>
+      </c>
+      <c r="O1183" t="n">
+        <v>103314.9863309342</v>
+      </c>
+      <c r="P1183" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q1183" t="n">
+        <v>129000</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>YOYO2001</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>ZET LAPIZ</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+      <c r="J1184" t="n">
+        <v>41</v>
+      </c>
+      <c r="K1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1184" t="n">
+        <v>41</v>
+      </c>
+      <c r="N1184" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O1184" t="n">
+        <v>246000</v>
+      </c>
+      <c r="P1184" t="n">
+        <v>7200</v>
+      </c>
+      <c r="Q1184" t="n">
         <v>295200</v>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1700,10 +1700,10 @@
         <v>99</v>
       </c>
       <c r="N32" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O32" t="n">
-        <v>403128</v>
+        <v>404800.7302904598</v>
       </c>
       <c r="P32" t="n">
         <v>7500</v>
@@ -4858,10 +4858,10 @@
         <v>11</v>
       </c>
       <c r="N108" t="n">
-        <v>16486.407256637</v>
+        <v>16486.407142857</v>
       </c>
       <c r="O108" t="n">
-        <v>181350.479823007</v>
+        <v>181350.478571427</v>
       </c>
       <c r="P108" t="n">
         <v>30500</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9353,19 +9353,19 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="N212" t="n">
-        <v>1950.2139862543</v>
+        <v>1950.2139585731</v>
       </c>
       <c r="O212" t="n">
-        <v>1125273.470068731</v>
+        <v>1113572.17034524</v>
       </c>
       <c r="P212" t="n">
         <v>2900</v>
       </c>
       <c r="Q212" t="n">
-        <v>1673300</v>
+        <v>1655900</v>
       </c>
     </row>
     <row r="213">
@@ -9607,10 +9607,10 @@
         <v>112</v>
       </c>
       <c r="N218" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O218" t="n">
-        <v>552978.7385263119</v>
+        <v>552978.7385402559</v>
       </c>
       <c r="P218" t="n">
         <v>7500</v>
@@ -11222,10 +11222,10 @@
         <v>2</v>
       </c>
       <c r="N256" t="n">
-        <v>13593.35</v>
+        <v>13626.343567961</v>
       </c>
       <c r="O256" t="n">
-        <v>27186.7</v>
+        <v>27252.687135922</v>
       </c>
       <c r="P256" t="n">
         <v>25500</v>
@@ -11861,7 +11861,7 @@
         </is>
       </c>
       <c r="J271" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -11870,19 +11870,19 @@
         <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N271" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O271" t="n">
-        <v>353768.9419776429</v>
+        <v>343439.9207912456</v>
       </c>
       <c r="P271" t="n">
         <v>4500</v>
       </c>
       <c r="Q271" t="n">
-        <v>616500</v>
+        <v>598500</v>
       </c>
     </row>
     <row r="272">
@@ -11965,10 +11965,10 @@
         <v>80</v>
       </c>
       <c r="N273" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O273" t="n">
-        <v>417351.677140728</v>
+        <v>417600.433914472</v>
       </c>
       <c r="P273" t="n">
         <v>8500</v>
@@ -13043,10 +13043,10 @@
         <v>133</v>
       </c>
       <c r="N297" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O297" t="n">
-        <v>865431</v>
+        <v>866290.1307081385</v>
       </c>
       <c r="P297" t="n">
         <v>9900</v>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13219,19 +13219,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N301" t="n">
         <v>4357.55</v>
       </c>
       <c r="O301" t="n">
-        <v>810504.3</v>
+        <v>797431.65</v>
       </c>
       <c r="P301" t="n">
         <v>7500</v>
       </c>
       <c r="Q301" t="n">
-        <v>1395000</v>
+        <v>1372500</v>
       </c>
     </row>
     <row r="302">
@@ -13895,10 +13895,10 @@
         <v>64</v>
       </c>
       <c r="N316" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O316" t="n">
-        <v>554368</v>
+        <v>555526.5538140032</v>
       </c>
       <c r="P316" t="n">
         <v>14200</v>
@@ -14195,10 +14195,10 @@
         <v>75</v>
       </c>
       <c r="N323" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O323" t="n">
-        <v>269568.9864479325</v>
+        <v>269568.98608137</v>
       </c>
       <c r="P323" t="n">
         <v>6500</v>
@@ -14502,10 +14502,10 @@
         <v>50</v>
       </c>
       <c r="N330" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O330" t="n">
-        <v>741118.94139195</v>
+        <v>742024.95476775</v>
       </c>
       <c r="P330" t="n">
         <v>24900</v>
@@ -14763,10 +14763,10 @@
         <v>8</v>
       </c>
       <c r="N336" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O336" t="n">
-        <v>21323.2</v>
+        <v>21349.9040701312</v>
       </c>
       <c r="P336" t="n">
         <v>20900</v>
@@ -14800,7 +14800,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14809,19 +14809,19 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="N337" t="n">
         <v>1381.75</v>
       </c>
       <c r="O337" t="n">
-        <v>696402</v>
+        <v>688111.5</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>1260000</v>
+        <v>1245000</v>
       </c>
     </row>
     <row r="338">
@@ -14943,10 +14943,10 @@
         <v>58</v>
       </c>
       <c r="N340" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O340" t="n">
-        <v>201392.0176959006</v>
+        <v>202477.6139212136</v>
       </c>
       <c r="P340" t="n">
         <v>5900</v>
@@ -15775,10 +15775,10 @@
         <v>184</v>
       </c>
       <c r="N359" t="n">
-        <v>6242.93</v>
+        <v>6260.7161253561</v>
       </c>
       <c r="O359" t="n">
-        <v>1148699.12</v>
+        <v>1151971.767065522</v>
       </c>
       <c r="P359" t="n">
         <v>10400</v>
@@ -16460,7 +16460,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -16469,19 +16469,19 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N375" t="n">
         <v>13304.13</v>
       </c>
       <c r="O375" t="n">
-        <v>359211.51</v>
+        <v>345907.38</v>
       </c>
       <c r="P375" t="n">
         <v>20900</v>
       </c>
       <c r="Q375" t="n">
-        <v>564300</v>
+        <v>543400</v>
       </c>
     </row>
     <row r="376">
@@ -16641,7 +16641,7 @@
         </is>
       </c>
       <c r="J379" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
@@ -16650,19 +16650,19 @@
         <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N379" t="n">
         <v>5853</v>
       </c>
       <c r="O379" t="n">
-        <v>883803</v>
+        <v>866244</v>
       </c>
       <c r="P379" t="n">
         <v>9900</v>
       </c>
       <c r="Q379" t="n">
-        <v>1494900</v>
+        <v>1465200</v>
       </c>
     </row>
     <row r="380">
@@ -17227,10 +17227,10 @@
         <v>58</v>
       </c>
       <c r="N392" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O392" t="n">
-        <v>574374</v>
+        <v>575271.4593750001</v>
       </c>
       <c r="P392" t="n">
         <v>15900</v>
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
@@ -17316,19 +17316,19 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="N394" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O394" t="n">
-        <v>1074779.127028077</v>
+        <v>1063362.662336068</v>
       </c>
       <c r="P394" t="n">
         <v>2500</v>
       </c>
       <c r="Q394" t="n">
-        <v>1647500</v>
+        <v>1630000</v>
       </c>
     </row>
     <row r="395">
@@ -17498,10 +17498,10 @@
         <v>2023</v>
       </c>
       <c r="N398" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O398" t="n">
-        <v>3136043.495262017</v>
+        <v>3136043.514157041</v>
       </c>
       <c r="P398" t="n">
         <v>2500</v>
@@ -17590,10 +17590,10 @@
         <v>1216</v>
       </c>
       <c r="N400" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O400" t="n">
-        <v>2922677.653027577</v>
+        <v>2922677.734031661</v>
       </c>
       <c r="P400" t="n">
         <v>3500</v>
@@ -17622,7 +17622,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -17631,19 +17631,19 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N401" t="n">
         <v>24267.77</v>
       </c>
       <c r="O401" t="n">
-        <v>922175.26</v>
+        <v>897907.49</v>
       </c>
       <c r="P401" t="n">
         <v>33400</v>
       </c>
       <c r="Q401" t="n">
-        <v>1269200</v>
+        <v>1235800</v>
       </c>
     </row>
     <row r="402">
@@ -21491,10 +21491,10 @@
         <v>422</v>
       </c>
       <c r="N491" t="n">
-        <v>2029.8740983607</v>
+        <v>2029.8741050903</v>
       </c>
       <c r="O491" t="n">
-        <v>856606.8695082153</v>
+        <v>856606.8723481066</v>
       </c>
       <c r="P491" t="n">
         <v>3600</v>
@@ -23871,10 +23871,10 @@
         <v>48</v>
       </c>
       <c r="N547" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O547" t="n">
-        <v>554977.8440677921</v>
+        <v>559721.244444432</v>
       </c>
       <c r="P547" t="n">
         <v>18500</v>
@@ -23917,10 +23917,10 @@
         <v>50</v>
       </c>
       <c r="N548" t="n">
-        <v>13513.643445378</v>
+        <v>13744.645897436</v>
       </c>
       <c r="O548" t="n">
-        <v>675682.1722689</v>
+        <v>687232.2948718</v>
       </c>
       <c r="P548" t="n">
         <v>21900</v>
@@ -25468,10 +25468,10 @@
         <v>10</v>
       </c>
       <c r="N584" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O584" t="n">
-        <v>41004.5</v>
+        <v>41148.123467601</v>
       </c>
       <c r="P584" t="n">
         <v>26900</v>
@@ -25642,10 +25642,10 @@
         <v>18</v>
       </c>
       <c r="N588" t="n">
-        <v>1561.0038892883</v>
+        <v>1561.0040101523</v>
       </c>
       <c r="O588" t="n">
-        <v>28098.0700071894</v>
+        <v>28098.0721827414</v>
       </c>
       <c r="P588" t="n">
         <v>2900</v>
@@ -25957,10 +25957,10 @@
         <v>126</v>
       </c>
       <c r="N595" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O595" t="n">
-        <v>1004213.721339486</v>
+        <v>1006538.290138886</v>
       </c>
       <c r="P595" t="n">
         <v>12900</v>
@@ -26085,10 +26085,10 @@
         <v>1</v>
       </c>
       <c r="N598" t="n">
-        <v>9627.34</v>
+        <v>9794.2880924855</v>
       </c>
       <c r="O598" t="n">
-        <v>9627.34</v>
+        <v>9794.2880924855</v>
       </c>
       <c r="P598" t="n">
         <v>15900</v>
@@ -28284,10 +28284,10 @@
         <v>362</v>
       </c>
       <c r="N648" t="n">
-        <v>1664.3409571788</v>
+        <v>1664.3408838384</v>
       </c>
       <c r="O648" t="n">
-        <v>602491.4264987255</v>
+        <v>602491.3999495008</v>
       </c>
       <c r="P648" t="n">
         <v>2900</v>
@@ -29210,10 +29210,10 @@
         <v>23</v>
       </c>
       <c r="N668" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O668" t="n">
-        <v>522997</v>
+        <v>525674.459044377</v>
       </c>
       <c r="P668" t="n">
         <v>36900</v>
@@ -30860,7 +30860,7 @@
         </is>
       </c>
       <c r="J704" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K704" t="n">
         <v>0</v>
@@ -30869,19 +30869,19 @@
         <v>0</v>
       </c>
       <c r="M704" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N704" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O704" t="n">
-        <v>1067586</v>
+        <v>1062241.208443261</v>
       </c>
       <c r="P704" t="n">
         <v>21900</v>
       </c>
       <c r="Q704" t="n">
-        <v>1708200</v>
+        <v>1686300</v>
       </c>
     </row>
     <row r="705">
@@ -31182,7 +31182,7 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
@@ -31191,19 +31191,19 @@
         <v>0</v>
       </c>
       <c r="M711" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N711" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O711" t="n">
-        <v>2657448</v>
+        <v>2652929.419202612</v>
       </c>
       <c r="P711" t="n">
         <v>15500</v>
       </c>
       <c r="Q711" t="n">
-        <v>4650000</v>
+        <v>4634500</v>
       </c>
     </row>
     <row r="712">
@@ -32192,7 +32192,7 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
@@ -32201,19 +32201,19 @@
         <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N733" t="n">
         <v>3519</v>
       </c>
       <c r="O733" t="n">
-        <v>784737</v>
+        <v>781218</v>
       </c>
       <c r="P733" t="n">
         <v>5900</v>
       </c>
       <c r="Q733" t="n">
-        <v>1315700</v>
+        <v>1309800</v>
       </c>
     </row>
     <row r="734">
@@ -32284,7 +32284,7 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
@@ -32293,19 +32293,19 @@
         <v>0</v>
       </c>
       <c r="M735" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N735" t="n">
         <v>9003</v>
       </c>
       <c r="O735" t="n">
-        <v>468156</v>
+        <v>459153</v>
       </c>
       <c r="P735" t="n">
         <v>14900</v>
       </c>
       <c r="Q735" t="n">
-        <v>774800</v>
+        <v>759900</v>
       </c>
     </row>
     <row r="736">
@@ -32330,7 +32330,7 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
@@ -32339,19 +32339,19 @@
         <v>0</v>
       </c>
       <c r="M736" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N736" t="n">
         <v>9178</v>
       </c>
       <c r="O736" t="n">
-        <v>605748</v>
+        <v>596570</v>
       </c>
       <c r="P736" t="n">
         <v>14900</v>
       </c>
       <c r="Q736" t="n">
-        <v>983400</v>
+        <v>968500</v>
       </c>
     </row>
     <row r="737">
@@ -32882,7 +32882,7 @@
         </is>
       </c>
       <c r="J748" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K748" t="n">
         <v>0</v>
@@ -32891,19 +32891,19 @@
         <v>0</v>
       </c>
       <c r="M748" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N748" t="n">
-        <v>3903.7390742358</v>
+        <v>3903.7391243433</v>
       </c>
       <c r="O748" t="n">
-        <v>148342.0848209604</v>
+        <v>136630.8693520155</v>
       </c>
       <c r="P748" t="n">
         <v>7500</v>
       </c>
       <c r="Q748" t="n">
-        <v>285000</v>
+        <v>262500</v>
       </c>
     </row>
     <row r="749">
@@ -32935,10 +32935,10 @@
         <v>25</v>
       </c>
       <c r="N749" t="n">
-        <v>20726</v>
+        <v>21127.148387097</v>
       </c>
       <c r="O749" t="n">
-        <v>518150</v>
+        <v>528178.709677425</v>
       </c>
       <c r="P749" t="n">
         <v>33900</v>
@@ -33027,10 +33027,10 @@
         <v>27</v>
       </c>
       <c r="N751" t="n">
-        <v>12113</v>
+        <v>13082.04</v>
       </c>
       <c r="O751" t="n">
-        <v>327051</v>
+        <v>353215.08</v>
       </c>
       <c r="P751" t="n">
         <v>19900</v>
@@ -33487,10 +33487,10 @@
         <v>90</v>
       </c>
       <c r="N761" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O761" t="n">
-        <v>616428</v>
+        <v>617013.401709402</v>
       </c>
       <c r="P761" t="n">
         <v>11500</v>
@@ -33567,7 +33567,7 @@
         </is>
       </c>
       <c r="J763" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K763" t="n">
         <v>0</v>
@@ -33576,19 +33576,19 @@
         <v>0</v>
       </c>
       <c r="M763" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N763" t="n">
         <v>5772</v>
       </c>
       <c r="O763" t="n">
-        <v>571428</v>
+        <v>565656</v>
       </c>
       <c r="P763" t="n">
         <v>9900</v>
       </c>
       <c r="Q763" t="n">
-        <v>980100</v>
+        <v>970200</v>
       </c>
     </row>
     <row r="764">
@@ -33613,7 +33613,7 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
@@ -33622,19 +33622,19 @@
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N764" t="n">
         <v>6268</v>
       </c>
       <c r="O764" t="n">
-        <v>658140</v>
+        <v>645604</v>
       </c>
       <c r="P764" t="n">
         <v>10900</v>
       </c>
       <c r="Q764" t="n">
-        <v>1144500</v>
+        <v>1122700</v>
       </c>
     </row>
     <row r="765">
@@ -33889,7 +33889,7 @@
         </is>
       </c>
       <c r="J770" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K770" t="n">
         <v>0</v>
@@ -33898,19 +33898,19 @@
         <v>0</v>
       </c>
       <c r="M770" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N770" t="n">
         <v>7562</v>
       </c>
       <c r="O770" t="n">
-        <v>264670</v>
+        <v>257108</v>
       </c>
       <c r="P770" t="n">
         <v>12900</v>
       </c>
       <c r="Q770" t="n">
-        <v>451500</v>
+        <v>438600</v>
       </c>
     </row>
     <row r="771">
@@ -34073,7 +34073,7 @@
         </is>
       </c>
       <c r="J774" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K774" t="n">
         <v>0</v>
@@ -34082,19 +34082,19 @@
         <v>0</v>
       </c>
       <c r="M774" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N774" t="n">
         <v>5682</v>
       </c>
       <c r="O774" t="n">
-        <v>1102308</v>
+        <v>1096626</v>
       </c>
       <c r="P774" t="n">
         <v>9900</v>
       </c>
       <c r="Q774" t="n">
-        <v>1920600</v>
+        <v>1910700</v>
       </c>
     </row>
     <row r="775">
@@ -35006,10 +35006,10 @@
         <v>3</v>
       </c>
       <c r="N794" t="n">
-        <v>20014</v>
+        <v>21040.358974359</v>
       </c>
       <c r="O794" t="n">
-        <v>60042</v>
+        <v>63121.07692307699</v>
       </c>
       <c r="P794" t="n">
         <v>33900</v>
@@ -35776,7 +35776,7 @@
         </is>
       </c>
       <c r="J811" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K811" t="n">
         <v>0</v>
@@ -35785,19 +35785,19 @@
         <v>0</v>
       </c>
       <c r="M811" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N811" t="n">
         <v>7253</v>
       </c>
       <c r="O811" t="n">
-        <v>108795</v>
+        <v>94289</v>
       </c>
       <c r="P811" t="n">
         <v>11900</v>
       </c>
       <c r="Q811" t="n">
-        <v>178500</v>
+        <v>154700</v>
       </c>
     </row>
     <row r="812">
@@ -35868,7 +35868,7 @@
         </is>
       </c>
       <c r="J813" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K813" t="n">
         <v>0</v>
@@ -35877,19 +35877,19 @@
         <v>0</v>
       </c>
       <c r="M813" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="N813" t="n">
         <v>5476</v>
       </c>
       <c r="O813" t="n">
-        <v>2256112</v>
+        <v>2245160</v>
       </c>
       <c r="P813" t="n">
         <v>8900</v>
       </c>
       <c r="Q813" t="n">
-        <v>3666800</v>
+        <v>3649000</v>
       </c>
     </row>
     <row r="814">
@@ -36147,7 +36147,7 @@
         </is>
       </c>
       <c r="J819" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="K819" t="n">
         <v>0</v>
@@ -36156,19 +36156,19 @@
         <v>0</v>
       </c>
       <c r="M819" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="N819" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O819" t="n">
-        <v>645832.5059816508</v>
+        <v>635220.2343819304</v>
       </c>
       <c r="P819" t="n">
         <v>2300</v>
       </c>
       <c r="Q819" t="n">
-        <v>979800</v>
+        <v>963700</v>
       </c>
     </row>
     <row r="820">
@@ -36295,10 +36295,10 @@
         <v>1092</v>
       </c>
       <c r="N822" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O822" t="n">
-        <v>2684695.776415708</v>
+        <v>2731050.232964071</v>
       </c>
       <c r="P822" t="n">
         <v>3500</v>
@@ -36387,10 +36387,10 @@
         <v>462</v>
       </c>
       <c r="N824" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O824" t="n">
-        <v>818243.3022580739</v>
+        <v>848088.0427659486</v>
       </c>
       <c r="P824" t="n">
         <v>2500</v>
@@ -36433,10 +36433,10 @@
         <v>578</v>
       </c>
       <c r="N825" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O825" t="n">
-        <v>1201883.562341936</v>
+        <v>1201883.559453381</v>
       </c>
       <c r="P825" t="n">
         <v>2900</v>
@@ -36479,10 +36479,10 @@
         <v>941</v>
       </c>
       <c r="N826" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O826" t="n">
-        <v>1696638.6307293</v>
+        <v>1729006.935290175</v>
       </c>
       <c r="P826" t="n">
         <v>2500</v>
@@ -36525,10 +36525,10 @@
         <v>143</v>
       </c>
       <c r="N827" t="n">
-        <v>3306.5944272446</v>
+        <v>3645.1535836177</v>
       </c>
       <c r="O827" t="n">
-        <v>472843.0030959778</v>
+        <v>521256.9624573311</v>
       </c>
       <c r="P827" t="n">
         <v>4900</v>
@@ -36663,10 +36663,10 @@
         <v>991</v>
       </c>
       <c r="N830" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O830" t="n">
-        <v>2037577.509098715</v>
+        <v>2074978.549418694</v>
       </c>
       <c r="P830" t="n">
         <v>2900</v>
@@ -36755,10 +36755,10 @@
         <v>562</v>
       </c>
       <c r="N832" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O832" t="n">
-        <v>930632.4006807798</v>
+        <v>984236.82696</v>
       </c>
       <c r="P832" t="n">
         <v>2500</v>
@@ -37170,10 +37170,10 @@
         <v>2</v>
       </c>
       <c r="N841" t="n">
-        <v>1906.1764864865</v>
+        <v>1906.1759813084</v>
       </c>
       <c r="O841" t="n">
-        <v>3812.352972973</v>
+        <v>3812.3519626168</v>
       </c>
       <c r="P841" t="n">
         <v>2900</v>
@@ -37992,10 +37992,10 @@
         <v>1</v>
       </c>
       <c r="N859" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="O859" t="n">
-        <v>15423.36</v>
+        <v>15646.886956522</v>
       </c>
       <c r="P859" t="n">
         <v>24900</v>
@@ -39406,7 +39406,7 @@
         </is>
       </c>
       <c r="J890" t="n">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="K890" t="n">
         <v>0</v>
@@ -39415,19 +39415,19 @@
         <v>0</v>
       </c>
       <c r="M890" t="n">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="N890" t="n">
-        <v>2286.1645279383</v>
+        <v>2286.164496124</v>
       </c>
       <c r="O890" t="n">
-        <v>1344264.74242772</v>
+        <v>1330547.736744168</v>
       </c>
       <c r="P890" t="n">
         <v>3000</v>
       </c>
       <c r="Q890" t="n">
-        <v>1764000</v>
+        <v>1746000</v>
       </c>
     </row>
     <row r="891">
@@ -40328,7 +40328,7 @@
         </is>
       </c>
       <c r="J911" t="n">
-        <v>3521</v>
+        <v>3497</v>
       </c>
       <c r="K911" t="n">
         <v>0</v>
@@ -40337,19 +40337,19 @@
         <v>0</v>
       </c>
       <c r="M911" t="n">
-        <v>3521</v>
+        <v>3497</v>
       </c>
       <c r="N911" t="n">
-        <v>517.2943625967</v>
+        <v>517.29445253004</v>
       </c>
       <c r="O911" t="n">
-        <v>1821393.450702981</v>
+        <v>1808978.70049755</v>
       </c>
       <c r="P911" t="n">
         <v>900</v>
       </c>
       <c r="Q911" t="n">
-        <v>3168900</v>
+        <v>3147300</v>
       </c>
     </row>
     <row r="912">
@@ -40560,22 +40560,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M916" t="n">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="N916" t="n">
-        <v>3110.8379310345</v>
+        <v>3110.8378564067</v>
       </c>
       <c r="O916" t="n">
-        <v>1630079.075862078</v>
+        <v>1574083.95534179</v>
       </c>
       <c r="P916" t="n">
         <v>4500</v>
       </c>
       <c r="Q916" t="n">
-        <v>2358000</v>
+        <v>2277000</v>
       </c>
     </row>
     <row r="917">
@@ -40788,10 +40788,10 @@
         <v>1316</v>
       </c>
       <c r="N921" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O921" t="n">
-        <v>926193.9709534616</v>
+        <v>926193.9454349187</v>
       </c>
       <c r="P921" t="n">
         <v>900</v>
@@ -44229,7 +44229,7 @@
         </is>
       </c>
       <c r="J996" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K996" t="n">
         <v>0</v>
@@ -44238,19 +44238,19 @@
         <v>0</v>
       </c>
       <c r="M996" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N996" t="n">
         <v>7465.9</v>
       </c>
       <c r="O996" t="n">
-        <v>462885.8</v>
+        <v>455419.9</v>
       </c>
       <c r="P996" t="n">
         <v>11900</v>
       </c>
       <c r="Q996" t="n">
-        <v>737800</v>
+        <v>725900</v>
       </c>
     </row>
     <row r="997">
@@ -44368,7 +44368,7 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
@@ -44377,19 +44377,19 @@
         <v>0</v>
       </c>
       <c r="M999" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N999" t="n">
         <v>24338.47</v>
       </c>
       <c r="O999" t="n">
-        <v>1874062.19</v>
+        <v>1849723.72</v>
       </c>
       <c r="P999" t="n">
         <v>27900</v>
       </c>
       <c r="Q999" t="n">
-        <v>2148300</v>
+        <v>2120400</v>
       </c>
     </row>
     <row r="1000">
@@ -48039,7 +48039,7 @@
         </is>
       </c>
       <c r="J1083" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K1083" t="n">
         <v>0</v>
@@ -48048,19 +48048,19 @@
         <v>0</v>
       </c>
       <c r="M1083" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N1083" t="n">
         <v>5077</v>
       </c>
       <c r="O1083" t="n">
-        <v>258927</v>
+        <v>243696</v>
       </c>
       <c r="P1083" t="n">
         <v>8500</v>
       </c>
       <c r="Q1083" t="n">
-        <v>433500</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="1084">
@@ -48213,7 +48213,7 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
@@ -48222,19 +48222,19 @@
         <v>0</v>
       </c>
       <c r="M1087" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="N1087" t="n">
-        <v>4985.4069767442</v>
+        <v>4985.4071856287</v>
       </c>
       <c r="O1087" t="n">
-        <v>334022.2674418614</v>
+        <v>309095.2455089794</v>
       </c>
       <c r="P1087" t="n">
         <v>7900</v>
       </c>
       <c r="Q1087" t="n">
-        <v>529300</v>
+        <v>489800</v>
       </c>
     </row>
     <row r="1088">
@@ -48276,10 +48276,10 @@
         <v>7</v>
       </c>
       <c r="N1088" t="n">
-        <v>1757.3206205251</v>
+        <v>1757.3206220096</v>
       </c>
       <c r="O1088" t="n">
-        <v>12301.2443436757</v>
+        <v>12301.2443540672</v>
       </c>
       <c r="P1088" t="n">
         <v>2000</v>
@@ -49172,7 +49172,7 @@
         </is>
       </c>
       <c r="J1108" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K1108" t="n">
         <v>0</v>
@@ -49181,19 +49181,19 @@
         <v>0</v>
       </c>
       <c r="M1108" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="N1108" t="n">
         <v>3872</v>
       </c>
       <c r="O1108" t="n">
-        <v>375584</v>
+        <v>348480</v>
       </c>
       <c r="P1108" t="n">
         <v>4900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>475300</v>
+        <v>441000</v>
       </c>
     </row>
     <row r="1109">
@@ -49374,10 +49374,10 @@
         <v>144</v>
       </c>
       <c r="N1112" t="n">
-        <v>7920</v>
+        <v>7940</v>
       </c>
       <c r="O1112" t="n">
-        <v>1140480</v>
+        <v>1143360</v>
       </c>
       <c r="P1112" t="n">
         <v>10500</v>
@@ -49423,10 +49423,10 @@
         <v>144</v>
       </c>
       <c r="N1113" t="n">
-        <v>7920</v>
+        <v>7961.0362694301</v>
       </c>
       <c r="O1113" t="n">
-        <v>1140480</v>
+        <v>1146389.222797934</v>
       </c>
       <c r="P1113" t="n">
         <v>10500</v>
@@ -49549,7 +49549,7 @@
         </is>
       </c>
       <c r="J1116" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
@@ -49558,19 +49558,19 @@
         <v>0</v>
       </c>
       <c r="M1116" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N1116" t="n">
         <v>9240</v>
       </c>
       <c r="O1116" t="n">
-        <v>2383920</v>
+        <v>2356200</v>
       </c>
       <c r="P1116" t="n">
         <v>11500</v>
       </c>
       <c r="Q1116" t="n">
-        <v>2967000</v>
+        <v>2932500</v>
       </c>
     </row>
     <row r="1117">
@@ -49641,7 +49641,7 @@
         </is>
       </c>
       <c r="J1118" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K1118" t="n">
         <v>0</v>
@@ -49650,19 +49650,19 @@
         <v>0</v>
       </c>
       <c r="M1118" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N1118" t="n">
         <v>4576</v>
       </c>
       <c r="O1118" t="n">
-        <v>320320</v>
+        <v>311168</v>
       </c>
       <c r="P1118" t="n">
         <v>5900</v>
       </c>
       <c r="Q1118" t="n">
-        <v>413000</v>
+        <v>401200</v>
       </c>
     </row>
     <row r="1119">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1700,10 +1700,10 @@
         <v>99</v>
       </c>
       <c r="N32" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O32" t="n">
-        <v>404800.7302904598</v>
+        <v>403128</v>
       </c>
       <c r="P32" t="n">
         <v>7500</v>
@@ -4939,10 +4939,10 @@
         <v>21</v>
       </c>
       <c r="N110" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O110" t="n">
-        <v>333879.243750003</v>
+        <v>329951.251249998</v>
       </c>
       <c r="P110" t="n">
         <v>28500</v>
@@ -8368,10 +8368,10 @@
         <v>16</v>
       </c>
       <c r="N189" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O189" t="n">
-        <v>42305.9430215824</v>
+        <v>41122.56</v>
       </c>
       <c r="P189" t="n">
         <v>4700</v>
@@ -8788,10 +8788,10 @@
         <v>3</v>
       </c>
       <c r="N199" t="n">
-        <v>4368.6523333333</v>
+        <v>4273.6816666667</v>
       </c>
       <c r="O199" t="n">
-        <v>13105.9569999999</v>
+        <v>12821.0450000001</v>
       </c>
       <c r="P199" t="n">
         <v>6500</v>
@@ -8832,10 +8832,10 @@
         <v>22</v>
       </c>
       <c r="N200" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O200" t="n">
-        <v>58501.647476635</v>
+        <v>56393.48</v>
       </c>
       <c r="P200" t="n">
         <v>4700</v>
@@ -11263,10 +11263,10 @@
         <v>55</v>
       </c>
       <c r="N257" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O257" t="n">
-        <v>949465.4096122799</v>
+        <v>946407.55</v>
       </c>
       <c r="P257" t="n">
         <v>20000</v>
@@ -13675,10 +13675,10 @@
         <v>1519</v>
       </c>
       <c r="N311" t="n">
-        <v>2271.9151051954</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O311" t="n">
-        <v>3451039.044791813</v>
+        <v>3443646.067226306</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14195,10 +14195,10 @@
         <v>72</v>
       </c>
       <c r="N323" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O323" t="n">
-        <v>258786.2245161312</v>
+        <v>258786.2234482776</v>
       </c>
       <c r="P323" t="n">
         <v>6500</v>
@@ -14853,10 +14853,10 @@
         <v>55</v>
       </c>
       <c r="N338" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O338" t="n">
-        <v>149536.29978903</v>
+        <v>148284.95</v>
       </c>
       <c r="P338" t="n">
         <v>8200</v>
@@ -15775,10 +15775,10 @@
         <v>184</v>
       </c>
       <c r="N359" t="n">
-        <v>6260.7161253561</v>
+        <v>6242.93</v>
       </c>
       <c r="O359" t="n">
-        <v>1151971.767065522</v>
+        <v>1148699.12</v>
       </c>
       <c r="P359" t="n">
         <v>10400</v>
@@ -16214,10 +16214,10 @@
         <v>758</v>
       </c>
       <c r="N369" t="n">
-        <v>1660.4491721419</v>
+        <v>1647.46</v>
       </c>
       <c r="O369" t="n">
-        <v>1258620.47248356</v>
+        <v>1248774.68</v>
       </c>
       <c r="P369" t="n">
         <v>2900</v>
@@ -17935,10 +17935,10 @@
         <v>1</v>
       </c>
       <c r="N408" t="n">
-        <v>17733.6</v>
+        <v>14778</v>
       </c>
       <c r="O408" t="n">
-        <v>17733.6</v>
+        <v>14778</v>
       </c>
       <c r="P408" t="n">
         <v>24900</v>
@@ -20707,10 +20707,10 @@
         <v>193</v>
       </c>
       <c r="N472" t="n">
-        <v>2701.9479396985</v>
+        <v>2661.82</v>
       </c>
       <c r="O472" t="n">
-        <v>521475.9523618105</v>
+        <v>513731.26</v>
       </c>
       <c r="P472" t="n">
         <v>3200</v>
@@ -20830,10 +20830,10 @@
         <v>90</v>
       </c>
       <c r="N475" t="n">
-        <v>2633.2</v>
+        <v>2610</v>
       </c>
       <c r="O475" t="n">
-        <v>236988</v>
+        <v>234900</v>
       </c>
       <c r="P475" t="n">
         <v>3200</v>
@@ -23738,10 +23738,10 @@
         <v>4</v>
       </c>
       <c r="N544" t="n">
-        <v>30262.214828189</v>
+        <v>30244.600034945</v>
       </c>
       <c r="O544" t="n">
-        <v>121048.859312756</v>
+        <v>120978.40013978</v>
       </c>
       <c r="P544" t="n">
         <v>48900</v>
@@ -24009,10 +24009,10 @@
         <v>6</v>
       </c>
       <c r="N550" t="n">
-        <v>61248.535714286</v>
+        <v>60174</v>
       </c>
       <c r="O550" t="n">
-        <v>367491.214285716</v>
+        <v>361044</v>
       </c>
       <c r="P550" t="n">
         <v>96900</v>
@@ -25125,10 +25125,10 @@
         <v>1</v>
       </c>
       <c r="N576" t="n">
-        <v>15768.141666667</v>
+        <v>13515.55</v>
       </c>
       <c r="O576" t="n">
-        <v>15768.141666667</v>
+        <v>13515.55</v>
       </c>
       <c r="P576" t="n">
         <v>30900</v>
@@ -25217,10 +25217,10 @@
         <v>29</v>
       </c>
       <c r="N578" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O578" t="n">
-        <v>789767.318727278</v>
+        <v>786589.1800202071</v>
       </c>
       <c r="P578" t="n">
         <v>44500</v>
@@ -25601,10 +25601,10 @@
         <v>18</v>
       </c>
       <c r="N587" t="n">
-        <v>1561.0041954445</v>
+        <v>1561.004375</v>
       </c>
       <c r="O587" t="n">
-        <v>28098.075518001</v>
+        <v>28098.07875</v>
       </c>
       <c r="P587" t="n">
         <v>2900</v>
@@ -25916,10 +25916,10 @@
         <v>126</v>
       </c>
       <c r="N594" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O594" t="n">
-        <v>1006538.290138886</v>
+        <v>1004213.721388891</v>
       </c>
       <c r="P594" t="n">
         <v>12900</v>
@@ -26044,10 +26044,10 @@
         <v>1</v>
       </c>
       <c r="N597" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="O597" t="n">
-        <v>9794.2880924855</v>
+        <v>9627.34</v>
       </c>
       <c r="P597" t="n">
         <v>15900</v>
@@ -27323,10 +27323,10 @@
         <v>11</v>
       </c>
       <c r="N627" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O627" t="n">
-        <v>29125.9767167919</v>
+        <v>28980.71</v>
       </c>
       <c r="P627" t="n">
         <v>4200</v>
@@ -27369,10 +27369,10 @@
         <v>8</v>
       </c>
       <c r="N628" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O628" t="n">
-        <v>25052.0600848656</v>
+        <v>24911.120226308</v>
       </c>
       <c r="P628" t="n">
         <v>5000</v>
@@ -27553,10 +27553,10 @@
         <v>9</v>
       </c>
       <c r="N632" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="O632" t="n">
-        <v>39573.4105617975</v>
+        <v>37468.44202247191</v>
       </c>
       <c r="P632" t="n">
         <v>6700</v>
@@ -27645,10 +27645,10 @@
         <v>8</v>
       </c>
       <c r="N634" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O634" t="n">
-        <v>20087.1221983272</v>
+        <v>19967.84</v>
       </c>
       <c r="P634" t="n">
         <v>4100</v>
@@ -28013,10 +28013,10 @@
         <v>8</v>
       </c>
       <c r="N642" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O642" t="n">
-        <v>46873.44</v>
+        <v>46328.4</v>
       </c>
       <c r="P642" t="n">
         <v>9300</v>
@@ -28338,10 +28338,10 @@
         <v>15</v>
       </c>
       <c r="N649" t="n">
-        <v>9379.0968275862</v>
+        <v>9188.98</v>
       </c>
       <c r="O649" t="n">
-        <v>140686.452413793</v>
+        <v>137834.7</v>
       </c>
       <c r="P649" t="n">
         <v>12900</v>
@@ -29261,10 +29261,10 @@
         <v>54</v>
       </c>
       <c r="N669" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O669" t="n">
-        <v>869021.1764705699</v>
+        <v>867132</v>
       </c>
       <c r="P669" t="n">
         <v>25900</v>
@@ -29307,10 +29307,10 @@
         <v>29</v>
       </c>
       <c r="N670" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O670" t="n">
-        <v>741729.8174692109</v>
+        <v>740486</v>
       </c>
       <c r="P670" t="n">
         <v>40900</v>
@@ -29678,10 +29678,10 @@
         <v>32</v>
       </c>
       <c r="N678" t="n">
-        <v>9927.272727272701</v>
+        <v>9750</v>
       </c>
       <c r="O678" t="n">
-        <v>317672.7272727264</v>
+        <v>312000</v>
       </c>
       <c r="P678" t="n">
         <v>15600</v>
@@ -29816,10 +29816,10 @@
         <v>56</v>
       </c>
       <c r="N681" t="n">
-        <v>7278.6868686869</v>
+        <v>7230</v>
       </c>
       <c r="O681" t="n">
-        <v>407606.4646464664</v>
+        <v>404880</v>
       </c>
       <c r="P681" t="n">
         <v>11600</v>
@@ -30647,10 +30647,10 @@
         <v>1</v>
       </c>
       <c r="N699" t="n">
-        <v>162480</v>
+        <v>54160</v>
       </c>
       <c r="O699" t="n">
-        <v>162480</v>
+        <v>54160</v>
       </c>
       <c r="P699" t="n">
         <v>86900</v>
@@ -30831,10 +30831,10 @@
         <v>78</v>
       </c>
       <c r="N703" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O703" t="n">
-        <v>1076014.310526324</v>
+        <v>1067586</v>
       </c>
       <c r="P703" t="n">
         <v>21900</v>
@@ -31245,10 +31245,10 @@
         <v>5</v>
       </c>
       <c r="N712" t="n">
-        <v>10485.899280576</v>
+        <v>10411</v>
       </c>
       <c r="O712" t="n">
-        <v>52429.49640288</v>
+        <v>52055</v>
       </c>
       <c r="P712" t="n">
         <v>16900</v>
@@ -31979,10 +31979,10 @@
         <v>76</v>
       </c>
       <c r="N728" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O728" t="n">
-        <v>2475081.142857132</v>
+        <v>2457232</v>
       </c>
       <c r="P728" t="n">
         <v>55900</v>
@@ -32485,10 +32485,10 @@
         <v>113</v>
       </c>
       <c r="N739" t="n">
-        <v>3412.5148218527</v>
+        <v>3396.38</v>
       </c>
       <c r="O739" t="n">
-        <v>385614.1748693551</v>
+        <v>383790.94</v>
       </c>
       <c r="P739" t="n">
         <v>6500</v>
@@ -32669,10 +32669,10 @@
         <v>182</v>
       </c>
       <c r="N743" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O743" t="n">
-        <v>2408452.781690228</v>
+        <v>2404220</v>
       </c>
       <c r="P743" t="n">
         <v>23900</v>
@@ -33354,10 +33354,10 @@
         <v>89</v>
       </c>
       <c r="N758" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O758" t="n">
-        <v>236494.6723366178</v>
+        <v>233981</v>
       </c>
       <c r="P758" t="n">
         <v>4500</v>
@@ -33446,10 +33446,10 @@
         <v>90</v>
       </c>
       <c r="N760" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O760" t="n">
-        <v>619366.169685411</v>
+        <v>616428</v>
       </c>
       <c r="P760" t="n">
         <v>11500</v>
@@ -33584,10 +33584,10 @@
         <v>103</v>
       </c>
       <c r="N763" t="n">
-        <v>6279.1629563669</v>
+        <v>6268</v>
       </c>
       <c r="O763" t="n">
-        <v>646753.7845057907</v>
+        <v>645604</v>
       </c>
       <c r="P763" t="n">
         <v>10900</v>
@@ -33998,10 +33998,10 @@
         <v>69</v>
       </c>
       <c r="N772" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O772" t="n">
-        <v>527109.7216783196</v>
+        <v>526815</v>
       </c>
       <c r="P772" t="n">
         <v>13900</v>
@@ -34231,10 +34231,10 @@
         <v>506</v>
       </c>
       <c r="N777" t="n">
-        <v>766.64130434783</v>
+        <v>753</v>
       </c>
       <c r="O777" t="n">
-        <v>387920.500000002</v>
+        <v>381018</v>
       </c>
       <c r="P777" t="n">
         <v>1600</v>
@@ -35149,10 +35149,10 @@
         <v>53</v>
       </c>
       <c r="N797" t="n">
-        <v>5322.5257731959</v>
+        <v>5215</v>
       </c>
       <c r="O797" t="n">
-        <v>282093.8659793827</v>
+        <v>276395</v>
       </c>
       <c r="P797" t="n">
         <v>8900</v>
@@ -35425,10 +35425,10 @@
         <v>67</v>
       </c>
       <c r="N803" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O803" t="n">
-        <v>584332.1867321853</v>
+        <v>582900</v>
       </c>
       <c r="P803" t="n">
         <v>14900</v>
@@ -35563,10 +35563,10 @@
         <v>19</v>
       </c>
       <c r="N806" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O806" t="n">
-        <v>415800.910112354</v>
+        <v>413478</v>
       </c>
       <c r="P806" t="n">
         <v>35900</v>
@@ -35609,10 +35609,10 @@
         <v>184</v>
       </c>
       <c r="N807" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O807" t="n">
-        <v>703545.2210814497</v>
+        <v>703064</v>
       </c>
       <c r="P807" t="n">
         <v>5900</v>
@@ -35747,10 +35747,10 @@
         <v>15</v>
       </c>
       <c r="N810" t="n">
-        <v>7295.3326848249</v>
+        <v>7253</v>
       </c>
       <c r="O810" t="n">
-        <v>109429.9902723735</v>
+        <v>108795</v>
       </c>
       <c r="P810" t="n">
         <v>11900</v>
@@ -37221,10 +37221,10 @@
         <v>27</v>
       </c>
       <c r="N842" t="n">
-        <v>2546.9807189542</v>
+        <v>2546.9805333333</v>
       </c>
       <c r="O842" t="n">
-        <v>68768.4794117634</v>
+        <v>68768.4743999991</v>
       </c>
       <c r="P842" t="n">
         <v>3900</v>
@@ -37585,10 +37585,10 @@
         <v>348</v>
       </c>
       <c r="N850" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O850" t="n">
-        <v>680612.4186346728</v>
+        <v>680422.5153357624</v>
       </c>
       <c r="P850" t="n">
         <v>3000</v>
@@ -37631,10 +37631,10 @@
         <v>503</v>
       </c>
       <c r="N851" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O851" t="n">
-        <v>596464.7874185503</v>
+        <v>596215.7414870418</v>
       </c>
       <c r="P851" t="n">
         <v>1900</v>
@@ -38656,10 +38656,10 @@
         <v>369</v>
       </c>
       <c r="N873" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O873" t="n">
-        <v>567506.5973425889</v>
+        <v>564736.0198283091</v>
       </c>
       <c r="P873" t="n">
         <v>2600</v>
@@ -39392,10 +39392,10 @@
         <v>78</v>
       </c>
       <c r="N889" t="n">
-        <v>8915.3355918367</v>
+        <v>8702.219999999999</v>
       </c>
       <c r="O889" t="n">
-        <v>695396.1761632626</v>
+        <v>678773.1599999999</v>
       </c>
       <c r="P889" t="n">
         <v>8900</v>
@@ -40894,10 +40894,10 @@
         <v>1249</v>
       </c>
       <c r="N923" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O923" t="n">
-        <v>879039.6696723074</v>
+        <v>880140.1314151537</v>
       </c>
       <c r="P923" t="n">
         <v>900</v>
@@ -43925,10 +43925,10 @@
         <v>2</v>
       </c>
       <c r="N989" t="n">
-        <v>10912.902659574</v>
+        <v>10798.03</v>
       </c>
       <c r="O989" t="n">
-        <v>21825.805319148</v>
+        <v>21596.06</v>
       </c>
       <c r="P989" t="n">
         <v>45000</v>
@@ -44107,10 +44107,10 @@
         <v>8</v>
       </c>
       <c r="N993" t="n">
-        <v>5272.2028268551</v>
+        <v>5216.9</v>
       </c>
       <c r="O993" t="n">
-        <v>42177.6226148408</v>
+        <v>41735.2</v>
       </c>
       <c r="P993" t="n">
         <v>20500</v>
@@ -44347,10 +44347,10 @@
         <v>60</v>
       </c>
       <c r="N998" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O998" t="n">
-        <v>456326.971962618</v>
+        <v>447954</v>
       </c>
       <c r="P998" t="n">
         <v>11900</v>
@@ -44666,10 +44666,10 @@
         <v>10</v>
       </c>
       <c r="N1005" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O1005" t="n">
-        <v>446548.75337423</v>
+        <v>441136.04171779</v>
       </c>
       <c r="P1005" t="n">
         <v>71900</v>
@@ -47003,10 +47003,10 @@
         <v>298</v>
       </c>
       <c r="N1058" t="n">
-        <v>3186.7802147239</v>
+        <v>3181.9</v>
       </c>
       <c r="O1058" t="n">
-        <v>949660.5039877222</v>
+        <v>948206.2000000001</v>
       </c>
       <c r="P1058" t="n">
         <v>5100</v>
@@ -48157,10 +48157,10 @@
         <v>49</v>
       </c>
       <c r="N1085" t="n">
-        <v>5959.9565217391</v>
+        <v>5077</v>
       </c>
       <c r="O1085" t="n">
-        <v>292037.8695652159</v>
+        <v>248773</v>
       </c>
       <c r="P1085" t="n">
         <v>8500</v>
@@ -48244,10 +48244,10 @@
         <v>17</v>
       </c>
       <c r="N1087" t="n">
-        <v>2098.7012987013</v>
+        <v>1600</v>
       </c>
       <c r="O1087" t="n">
-        <v>35677.9220779221</v>
+        <v>27200</v>
       </c>
       <c r="P1087" t="n">
         <v>3500</v>
@@ -48290,10 +48290,10 @@
         <v>266</v>
       </c>
       <c r="N1088" t="n">
-        <v>707.69883076923</v>
+        <v>705.5279692307701</v>
       </c>
       <c r="O1088" t="n">
-        <v>188247.8889846152</v>
+        <v>187670.4398153848</v>
       </c>
       <c r="P1088" t="n">
         <v>1500</v>
@@ -48692,10 +48692,10 @@
         <v>8</v>
       </c>
       <c r="N1097" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="O1097" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="P1097" t="n">
         <v>3000</v>
@@ -48830,10 +48830,10 @@
         <v>26</v>
       </c>
       <c r="N1100" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O1100" t="n">
-        <v>69043.3895652176</v>
+        <v>68767.40000000001</v>
       </c>
       <c r="P1100" t="n">
         <v>3900</v>
@@ -49943,10 +49943,10 @@
         <v>8</v>
       </c>
       <c r="N1124" t="n">
-        <v>6162.2222222222</v>
+        <v>5900</v>
       </c>
       <c r="O1124" t="n">
-        <v>49297.7777777776</v>
+        <v>47200</v>
       </c>
       <c r="P1124" t="n">
         <v>7100</v>
@@ -50081,10 +50081,10 @@
         <v>23</v>
       </c>
       <c r="N1127" t="n">
-        <v>26102.941176471</v>
+        <v>25000</v>
       </c>
       <c r="O1127" t="n">
-        <v>600367.6470588329</v>
+        <v>575000</v>
       </c>
       <c r="P1127" t="n">
         <v>30000</v>
@@ -50127,10 +50127,10 @@
         <v>1</v>
       </c>
       <c r="N1128" t="n">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="O1128" t="n">
-        <v>6750</v>
+        <v>4500</v>
       </c>
       <c r="P1128" t="n">
         <v>5400</v>
@@ -50725,10 +50725,10 @@
         <v>12</v>
       </c>
       <c r="N1141" t="n">
-        <v>6250</v>
+        <v>6000</v>
       </c>
       <c r="O1141" t="n">
-        <v>75000</v>
+        <v>72000</v>
       </c>
       <c r="P1141" t="n">
         <v>7200</v>
@@ -51630,10 +51630,10 @@
         <v>3</v>
       </c>
       <c r="N1161" t="n">
-        <v>6666.6666666667</v>
+        <v>5000</v>
       </c>
       <c r="O1161" t="n">
-        <v>20000.0000000001</v>
+        <v>15000</v>
       </c>
       <c r="P1161" t="n">
         <v>6000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -3709,10 +3709,10 @@
         <v>18</v>
       </c>
       <c r="N82" t="n">
-        <v>31566.3666</v>
+        <v>31409.32</v>
       </c>
       <c r="O82" t="n">
-        <v>568194.5988</v>
+        <v>565367.76</v>
       </c>
       <c r="P82" t="n">
         <v>45500</v>
@@ -9356,10 +9356,10 @@
         <v>571</v>
       </c>
       <c r="N212" t="n">
-        <v>1953.5860864553</v>
+        <v>1950.2139481268</v>
       </c>
       <c r="O212" t="n">
-        <v>1115497.655365976</v>
+        <v>1113572.164380403</v>
       </c>
       <c r="P212" t="n">
         <v>2900</v>
@@ -11222,10 +11222,10 @@
         <v>2</v>
       </c>
       <c r="N256" t="n">
-        <v>13609.886922141</v>
+        <v>13593.35</v>
       </c>
       <c r="O256" t="n">
-        <v>27219.773844282</v>
+        <v>27186.7</v>
       </c>
       <c r="P256" t="n">
         <v>25500</v>
@@ -11873,10 +11873,10 @@
         <v>123</v>
       </c>
       <c r="N271" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O271" t="n">
-        <v>317777.2114544592</v>
+        <v>317617.3634524386</v>
       </c>
       <c r="P271" t="n">
         <v>4500</v>
@@ -12267,10 +12267,10 @@
         <v>575</v>
       </c>
       <c r="N280" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O280" t="n">
-        <v>1817429.205479285</v>
+        <v>1816344.982527465</v>
       </c>
       <c r="P280" t="n">
         <v>5600</v>
@@ -12400,10 +12400,10 @@
         <v>79</v>
       </c>
       <c r="N283" t="n">
-        <v>8252.563380281699</v>
+        <v>8214</v>
       </c>
       <c r="O283" t="n">
-        <v>651952.5070422542</v>
+        <v>648906</v>
       </c>
       <c r="P283" t="n">
         <v>7900</v>
@@ -12449,10 +12449,10 @@
         <v>11</v>
       </c>
       <c r="N284" t="n">
-        <v>3283.163260274</v>
+        <v>3230.0662191781</v>
       </c>
       <c r="O284" t="n">
-        <v>36114.795863014</v>
+        <v>35530.7284109591</v>
       </c>
       <c r="P284" t="n">
         <v>6200</v>
@@ -12948,10 +12948,10 @@
         <v>153</v>
       </c>
       <c r="N295" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O295" t="n">
-        <v>1349460</v>
+        <v>1345788</v>
       </c>
       <c r="P295" t="n">
         <v>14900</v>
@@ -15254,10 +15254,10 @@
         <v>195</v>
       </c>
       <c r="N347" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O347" t="n">
-        <v>852552.7661507025</v>
+        <v>852378.396259806</v>
       </c>
       <c r="P347" t="n">
         <v>8900</v>
@@ -16087,10 +16087,10 @@
         <v>306</v>
       </c>
       <c r="N366" t="n">
-        <v>1534.4227525419</v>
+        <v>1532.6290227489</v>
       </c>
       <c r="O366" t="n">
-        <v>469533.3622778214</v>
+        <v>468984.4809611634</v>
       </c>
       <c r="P366" t="n">
         <v>1200</v>
@@ -16748,10 +16748,10 @@
         <v>55</v>
       </c>
       <c r="N381" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O381" t="n">
-        <v>207691.9689119165</v>
+        <v>206888</v>
       </c>
       <c r="P381" t="n">
         <v>6900</v>
@@ -18022,10 +18022,10 @@
         <v>1</v>
       </c>
       <c r="N410" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="O410" t="n">
-        <v>19114.611111111</v>
+        <v>18598</v>
       </c>
       <c r="P410" t="n">
         <v>21900</v>
@@ -21040,10 +21040,10 @@
         <v>67</v>
       </c>
       <c r="N480" t="n">
-        <v>1974.990872211</v>
+        <v>1969</v>
       </c>
       <c r="O480" t="n">
-        <v>132324.388438137</v>
+        <v>131923</v>
       </c>
       <c r="P480" t="n">
         <v>1500</v>
@@ -21081,10 +21081,10 @@
         <v>144</v>
       </c>
       <c r="N481" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O481" t="n">
-        <v>1267123.036734691</v>
+        <v>1266405.12</v>
       </c>
       <c r="P481" t="n">
         <v>14500</v>
@@ -22585,10 +22585,10 @@
         <v>37</v>
       </c>
       <c r="N517" t="n">
-        <v>57801.91954023</v>
+        <v>56503</v>
       </c>
       <c r="O517" t="n">
-        <v>2138671.02298851</v>
+        <v>2090611</v>
       </c>
       <c r="P517" t="n">
         <v>90500</v>
@@ -24951,10 +24951,10 @@
         <v>46</v>
       </c>
       <c r="N572" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O572" t="n">
-        <v>1047013.148933876</v>
+        <v>1045602.08</v>
       </c>
       <c r="P572" t="n">
         <v>36900</v>
@@ -25345,10 +25345,10 @@
         <v>33</v>
       </c>
       <c r="N581" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O581" t="n">
-        <v>135394.2601232397</v>
+        <v>135314.85</v>
       </c>
       <c r="P581" t="n">
         <v>26900</v>
@@ -25432,10 +25432,10 @@
         <v>115</v>
       </c>
       <c r="N583" t="n">
-        <v>5455.0456387665</v>
+        <v>5431.12</v>
       </c>
       <c r="O583" t="n">
-        <v>627330.2484581475</v>
+        <v>624578.7999999999</v>
       </c>
       <c r="P583" t="n">
         <v>8900</v>
@@ -28256,10 +28256,10 @@
         <v>15</v>
       </c>
       <c r="N647" t="n">
-        <v>9252.7923611111</v>
+        <v>9188.98</v>
       </c>
       <c r="O647" t="n">
-        <v>138791.8854166665</v>
+        <v>137834.7</v>
       </c>
       <c r="P647" t="n">
         <v>12900</v>
@@ -29041,10 +29041,10 @@
         <v>12</v>
       </c>
       <c r="N664" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O664" t="n">
-        <v>216278.4768</v>
+        <v>216192</v>
       </c>
       <c r="P664" t="n">
         <v>29900</v>
@@ -30381,10 +30381,10 @@
         <v>3</v>
       </c>
       <c r="N693" t="n">
-        <v>7961.912</v>
+        <v>7108.85</v>
       </c>
       <c r="O693" t="n">
-        <v>23885.736</v>
+        <v>21326.55</v>
       </c>
       <c r="P693" t="n">
         <v>7900</v>
@@ -31071,10 +31071,10 @@
         <v>5</v>
       </c>
       <c r="N708" t="n">
-        <v>10448.584837545</v>
+        <v>10411</v>
       </c>
       <c r="O708" t="n">
-        <v>52242.924187725</v>
+        <v>52055</v>
       </c>
       <c r="P708" t="n">
         <v>16900</v>
@@ -31347,10 +31347,10 @@
         <v>6</v>
       </c>
       <c r="N714" t="n">
-        <v>6074.962962963</v>
+        <v>5858</v>
       </c>
       <c r="O714" t="n">
-        <v>36449.777777778</v>
+        <v>35148</v>
       </c>
       <c r="P714" t="n">
         <v>9500</v>
@@ -34512,10 +34512,10 @@
         <v>129</v>
       </c>
       <c r="N783" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O783" t="n">
-        <v>7752108.631921815</v>
+        <v>7718586</v>
       </c>
       <c r="P783" t="n">
         <v>7900</v>
@@ -35159,10 +35159,10 @@
         <v>50</v>
       </c>
       <c r="N797" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O797" t="n">
-        <v>2015942.33128835</v>
+        <v>2003650</v>
       </c>
       <c r="P797" t="n">
         <v>64900</v>
@@ -35711,10 +35711,10 @@
         <v>83</v>
       </c>
       <c r="N809" t="n">
-        <v>15334.994264706</v>
+        <v>15223.06</v>
       </c>
       <c r="O809" t="n">
-        <v>1272804.523970598</v>
+        <v>1263513.98</v>
       </c>
       <c r="P809" t="n">
         <v>17500</v>
@@ -36080,10 +36080,10 @@
         <v>1092</v>
       </c>
       <c r="N817" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O817" t="n">
-        <v>2690479.571116646</v>
+        <v>2684695.649019712</v>
       </c>
       <c r="P817" t="n">
         <v>3500</v>
@@ -38672,10 +38672,10 @@
         <v>3</v>
       </c>
       <c r="N873" t="n">
-        <v>3650.5019029126</v>
+        <v>3629.36</v>
       </c>
       <c r="O873" t="n">
-        <v>10951.5057087378</v>
+        <v>10888.08</v>
       </c>
       <c r="P873" t="n">
         <v>3900</v>
@@ -38898,10 +38898,10 @@
         <v>15</v>
       </c>
       <c r="N878" t="n">
-        <v>2479.6920689655</v>
+        <v>2357.74</v>
       </c>
       <c r="O878" t="n">
-        <v>37195.3810344825</v>
+        <v>35366.1</v>
       </c>
       <c r="P878" t="n">
         <v>3000</v>
@@ -39360,10 +39360,10 @@
         <v>309</v>
       </c>
       <c r="N888" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O888" t="n">
-        <v>106800.9955656121</v>
+        <v>106777.5412669672</v>
       </c>
       <c r="P888" t="n">
         <v>600</v>
@@ -39404,10 +39404,10 @@
         <v>1443</v>
       </c>
       <c r="N889" t="n">
-        <v>711.87861852814</v>
+        <v>711.33664519481</v>
       </c>
       <c r="O889" t="n">
-        <v>1027240.846536106</v>
+        <v>1026458.779016111</v>
       </c>
       <c r="P889" t="n">
         <v>900</v>
@@ -44318,10 +44318,10 @@
         <v>179</v>
       </c>
       <c r="N997" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O997" t="n">
-        <v>1263039.35071166</v>
+        <v>1261402.229024444</v>
       </c>
       <c r="P997" t="n">
         <v>9900</v>
@@ -46318,10 +46318,10 @@
         <v>45</v>
       </c>
       <c r="N1042" t="n">
-        <v>2490.4710359188</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O1042" t="n">
-        <v>112071.196616346</v>
+        <v>112012.8868297755</v>
       </c>
       <c r="P1042" t="n">
         <v>3000</v>
@@ -47007,10 +47007,10 @@
         <v>165</v>
       </c>
       <c r="N1058" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O1058" t="n">
-        <v>296357.296716327</v>
+        <v>296057.512982781</v>
       </c>
       <c r="P1058" t="n">
         <v>1600</v>
@@ -48984,10 +48984,10 @@
         <v>1</v>
       </c>
       <c r="N1103" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="O1103" t="n">
-        <v>7496.4757709251</v>
+        <v>7480</v>
       </c>
       <c r="P1103" t="n">
         <v>9500</v>
@@ -49030,10 +49030,10 @@
         <v>7</v>
       </c>
       <c r="N1104" t="n">
-        <v>6525.1343283582</v>
+        <v>6336</v>
       </c>
       <c r="O1104" t="n">
-        <v>45675.9402985074</v>
+        <v>44352</v>
       </c>
       <c r="P1104" t="n">
         <v>7500</v>
@@ -49122,10 +49122,10 @@
         <v>134</v>
       </c>
       <c r="N1106" t="n">
-        <v>5320.824742268</v>
+        <v>5280</v>
       </c>
       <c r="O1106" t="n">
-        <v>712990.5154639119</v>
+        <v>707520</v>
       </c>
       <c r="P1106" t="n">
         <v>6900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1182"/>
+  <dimension ref="A1:Q1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1010,19 +1010,19 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N15" t="n">
         <v>27000</v>
       </c>
       <c r="O15" t="n">
-        <v>783000</v>
+        <v>729000</v>
       </c>
       <c r="P15" t="n">
         <v>20000</v>
       </c>
       <c r="Q15" t="n">
-        <v>580000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="16">
@@ -1307,10 +1307,10 @@
         <v>297</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3091666667</v>
+        <v>1811.3093916756</v>
       </c>
       <c r="O22" t="n">
-        <v>537958.8225000099</v>
+        <v>537958.8893276532</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1382,19 +1382,19 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N24" t="n">
-        <v>1990.0434042553</v>
+        <v>1990.0433657588</v>
       </c>
       <c r="O24" t="n">
-        <v>141293.0817021263</v>
+        <v>135322.9488715984</v>
       </c>
       <c r="P24" t="n">
         <v>4400</v>
       </c>
       <c r="Q24" t="n">
-        <v>312400</v>
+        <v>299200</v>
       </c>
     </row>
     <row r="25">
@@ -2840,10 +2840,10 @@
         <v>35</v>
       </c>
       <c r="N60" t="n">
-        <v>6272.8551336898</v>
+        <v>6272.8551705566</v>
       </c>
       <c r="O60" t="n">
-        <v>219549.929679143</v>
+        <v>219549.930969481</v>
       </c>
       <c r="P60" t="n">
         <v>7900</v>
@@ -2957,10 +2957,10 @@
         <v>36</v>
       </c>
       <c r="N63" t="n">
-        <v>3926.8370787689</v>
+        <v>3926.8370772443</v>
       </c>
       <c r="O63" t="n">
-        <v>141366.1348356804</v>
+        <v>141366.1347807948</v>
       </c>
       <c r="P63" t="n">
         <v>4800</v>
@@ -3397,10 +3397,10 @@
         <v>167</v>
       </c>
       <c r="N74" t="n">
-        <v>3716.3301963993</v>
+        <v>3716.3301967213</v>
       </c>
       <c r="O74" t="n">
-        <v>620627.1427986831</v>
+        <v>620627.1428524571</v>
       </c>
       <c r="P74" t="n">
         <v>9500</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3628,19 +3628,19 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N80" t="n">
         <v>27000</v>
       </c>
       <c r="O80" t="n">
-        <v>486000</v>
+        <v>459000</v>
       </c>
       <c r="P80" t="n">
         <v>30000</v>
       </c>
       <c r="Q80" t="n">
-        <v>540000</v>
+        <v>510000</v>
       </c>
     </row>
     <row r="81">
@@ -4095,10 +4095,10 @@
         <v>34</v>
       </c>
       <c r="N91" t="n">
-        <v>3910.6279357798</v>
+        <v>3910.6279310345</v>
       </c>
       <c r="O91" t="n">
-        <v>132961.3498165132</v>
+        <v>132961.349655173</v>
       </c>
       <c r="P91" t="n">
         <v>9100</v>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N199" t="n">
-        <v>4273.6816666667</v>
+        <v>4273.6817045455</v>
       </c>
       <c r="O199" t="n">
-        <v>12821.0450000001</v>
+        <v>4273.6817045455</v>
       </c>
       <c r="P199" t="n">
         <v>6500</v>
       </c>
       <c r="Q199" t="n">
-        <v>19500</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="200">
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -9041,19 +9041,19 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N205" t="n">
         <v>12000</v>
       </c>
       <c r="O205" t="n">
-        <v>216000</v>
+        <v>192000</v>
       </c>
       <c r="P205" t="n">
         <v>14400</v>
       </c>
       <c r="Q205" t="n">
-        <v>259200</v>
+        <v>230400</v>
       </c>
     </row>
     <row r="206">
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9353,19 +9353,19 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="N212" t="n">
-        <v>1950.2139481268</v>
+        <v>1950.2139095128</v>
       </c>
       <c r="O212" t="n">
-        <v>1113572.164380403</v>
+        <v>1092119.789327168</v>
       </c>
       <c r="P212" t="n">
         <v>2900</v>
       </c>
       <c r="Q212" t="n">
-        <v>1655900</v>
+        <v>1624000</v>
       </c>
     </row>
     <row r="213">
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>1540</v>
+        <v>1483</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9517,19 +9517,19 @@
         <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>1540</v>
+        <v>1483</v>
       </c>
       <c r="N216" t="n">
         <v>1726.32</v>
       </c>
       <c r="O216" t="n">
-        <v>2658532.8</v>
+        <v>2560132.56</v>
       </c>
       <c r="P216" t="n">
         <v>1500</v>
       </c>
       <c r="Q216" t="n">
-        <v>2310000</v>
+        <v>2224500</v>
       </c>
     </row>
     <row r="217">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9604,19 +9604,19 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="N218" t="n">
-        <v>4937.3101685824</v>
+        <v>4937.310172549</v>
       </c>
       <c r="O218" t="n">
-        <v>533229.4982068993</v>
+        <v>385110.193458822</v>
       </c>
       <c r="P218" t="n">
         <v>7500</v>
       </c>
       <c r="Q218" t="n">
-        <v>810000</v>
+        <v>585000</v>
       </c>
     </row>
     <row r="219">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>399</v>
+        <v>28</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -10068,19 +10068,19 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>399</v>
+        <v>28</v>
       </c>
       <c r="N229" t="n">
-        <v>1098.0646017403</v>
+        <v>1098.0684371373</v>
       </c>
       <c r="O229" t="n">
-        <v>438127.7760943797</v>
+        <v>30745.9162398444</v>
       </c>
       <c r="P229" t="n">
         <v>1500</v>
       </c>
       <c r="Q229" t="n">
-        <v>598500</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="230">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="J263" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11514,19 +11514,19 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N263" t="n">
         <v>2804.33</v>
       </c>
       <c r="O263" t="n">
-        <v>1312426.44</v>
+        <v>1309622.11</v>
       </c>
       <c r="P263" t="n">
         <v>4900</v>
       </c>
       <c r="Q263" t="n">
-        <v>2293200</v>
+        <v>2288300</v>
       </c>
     </row>
     <row r="264">
@@ -11873,10 +11873,10 @@
         <v>123</v>
       </c>
       <c r="N271" t="n">
-        <v>2582.2549874182</v>
+        <v>2582.2549620637</v>
       </c>
       <c r="O271" t="n">
-        <v>317617.3634524386</v>
+        <v>317617.3603338351</v>
       </c>
       <c r="P271" t="n">
         <v>4500</v>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="J272" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -11916,19 +11916,19 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="N272" t="n">
         <v>10600</v>
       </c>
       <c r="O272" t="n">
-        <v>1325000</v>
+        <v>1134200</v>
       </c>
       <c r="P272" t="n">
         <v>17200</v>
       </c>
       <c r="Q272" t="n">
-        <v>2150000</v>
+        <v>1840400</v>
       </c>
     </row>
     <row r="273">
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -11962,19 +11962,19 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="N273" t="n">
-        <v>5216.8959284856</v>
+        <v>5216.8958877086</v>
       </c>
       <c r="O273" t="n">
-        <v>746016.1177734408</v>
+        <v>427785.4627921052</v>
       </c>
       <c r="P273" t="n">
         <v>8500</v>
       </c>
       <c r="Q273" t="n">
-        <v>1215500</v>
+        <v>697000</v>
       </c>
     </row>
     <row r="274">
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12218,19 +12218,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N279" t="n">
         <v>6713.08</v>
       </c>
       <c r="O279" t="n">
-        <v>429637.12</v>
+        <v>422924.04</v>
       </c>
       <c r="P279" t="n">
         <v>9900</v>
       </c>
       <c r="Q279" t="n">
-        <v>633600</v>
+        <v>623700</v>
       </c>
     </row>
     <row r="280">
@@ -12388,7 +12388,7 @@
         </is>
       </c>
       <c r="J283" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
@@ -12397,19 +12397,19 @@
         <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N283" t="n">
         <v>8214</v>
       </c>
       <c r="O283" t="n">
-        <v>648906</v>
+        <v>632478</v>
       </c>
       <c r="P283" t="n">
         <v>7900</v>
       </c>
       <c r="Q283" t="n">
-        <v>624100</v>
+        <v>608300</v>
       </c>
     </row>
     <row r="284">
@@ -12524,7 +12524,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12533,19 +12533,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="N286" t="n">
         <v>1480</v>
       </c>
       <c r="O286" t="n">
-        <v>1219520</v>
+        <v>1212120</v>
       </c>
       <c r="P286" t="n">
         <v>2600</v>
       </c>
       <c r="Q286" t="n">
-        <v>2142400</v>
+        <v>2129400</v>
       </c>
     </row>
     <row r="287">
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -12625,19 +12625,19 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="N288" t="n">
         <v>1337.34</v>
       </c>
       <c r="O288" t="n">
-        <v>938812.6799999999</v>
+        <v>932125.98</v>
       </c>
       <c r="P288" t="n">
         <v>2500</v>
       </c>
       <c r="Q288" t="n">
-        <v>1755000</v>
+        <v>1742500</v>
       </c>
     </row>
     <row r="289">
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -12712,19 +12712,19 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N290" t="n">
         <v>2742</v>
       </c>
       <c r="O290" t="n">
-        <v>13710</v>
+        <v>10968</v>
       </c>
       <c r="P290" t="n">
         <v>3500</v>
       </c>
       <c r="Q290" t="n">
-        <v>17500</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="291">
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -12758,19 +12758,19 @@
         <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="N291" t="n">
         <v>1026.13</v>
       </c>
       <c r="O291" t="n">
-        <v>466889.15</v>
+        <v>440209.77</v>
       </c>
       <c r="P291" t="n">
         <v>1900</v>
       </c>
       <c r="Q291" t="n">
-        <v>864500</v>
+        <v>815100</v>
       </c>
     </row>
     <row r="292">
@@ -12841,7 +12841,7 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>3145</v>
+        <v>3105</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -12850,19 +12850,19 @@
         <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>3145</v>
+        <v>3105</v>
       </c>
       <c r="N293" t="n">
         <v>156.25</v>
       </c>
       <c r="O293" t="n">
-        <v>491406.25</v>
+        <v>485156.25</v>
       </c>
       <c r="P293" t="n">
         <v>250</v>
       </c>
       <c r="Q293" t="n">
-        <v>786250</v>
+        <v>776250</v>
       </c>
     </row>
     <row r="294">
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13219,19 +13219,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="N301" t="n">
         <v>4357.55</v>
       </c>
       <c r="O301" t="n">
-        <v>793074.1</v>
+        <v>549051.3</v>
       </c>
       <c r="P301" t="n">
         <v>7500</v>
       </c>
       <c r="Q301" t="n">
-        <v>1365000</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="302">
@@ -13343,7 +13343,7 @@
         </is>
       </c>
       <c r="J304" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K304" t="n">
         <v>0</v>
@@ -13352,19 +13352,19 @@
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N304" t="n">
-        <v>4890.9300530504</v>
+        <v>4890.9300534045</v>
       </c>
       <c r="O304" t="n">
-        <v>381492.5441379312</v>
+        <v>376601.6141121465</v>
       </c>
       <c r="P304" t="n">
         <v>8200</v>
       </c>
       <c r="Q304" t="n">
-        <v>639600</v>
+        <v>631400</v>
       </c>
     </row>
     <row r="305">
@@ -13438,7 +13438,7 @@
         </is>
       </c>
       <c r="J306" t="n">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="K306" t="n">
         <v>0</v>
@@ -13447,19 +13447,19 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>955</v>
+        <v>917</v>
       </c>
       <c r="N306" t="n">
         <v>1203.38</v>
       </c>
       <c r="O306" t="n">
-        <v>1149227.9</v>
+        <v>1103499.46</v>
       </c>
       <c r="P306" t="n">
         <v>1900</v>
       </c>
       <c r="Q306" t="n">
-        <v>1814500</v>
+        <v>1742300</v>
       </c>
     </row>
     <row r="307">
@@ -13484,7 +13484,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13493,19 +13493,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N307" t="n">
         <v>3472</v>
       </c>
       <c r="O307" t="n">
-        <v>774256</v>
+        <v>767312</v>
       </c>
       <c r="P307" t="n">
         <v>4800</v>
       </c>
       <c r="Q307" t="n">
-        <v>1070400</v>
+        <v>1060800</v>
       </c>
     </row>
     <row r="308">
@@ -13530,7 +13530,7 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -13539,19 +13539,19 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="N308" t="n">
         <v>5888</v>
       </c>
       <c r="O308" t="n">
-        <v>288512</v>
+        <v>488704</v>
       </c>
       <c r="P308" t="n">
         <v>9500</v>
       </c>
       <c r="Q308" t="n">
-        <v>465500</v>
+        <v>788500</v>
       </c>
     </row>
     <row r="309">
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>1519</v>
+        <v>1507</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -13672,19 +13672,19 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>1519</v>
+        <v>1507</v>
       </c>
       <c r="N311" t="n">
-        <v>2267.0481021898</v>
+        <v>2267.0480923608</v>
       </c>
       <c r="O311" t="n">
-        <v>3443646.067226306</v>
+        <v>3416441.475187726</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
       </c>
       <c r="Q311" t="n">
-        <v>5924100</v>
+        <v>5877300</v>
       </c>
     </row>
     <row r="312">
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14192,19 +14192,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N323" t="n">
-        <v>3594.2530785869</v>
+        <v>3594.2530181818</v>
       </c>
       <c r="O323" t="n">
-        <v>255191.9685796699</v>
+        <v>240814.9522181806</v>
       </c>
       <c r="P323" t="n">
         <v>6500</v>
       </c>
       <c r="Q323" t="n">
-        <v>461500</v>
+        <v>435500</v>
       </c>
     </row>
     <row r="324">
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -14320,19 +14320,19 @@
         <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="N326" t="n">
         <v>2953.73</v>
       </c>
       <c r="O326" t="n">
-        <v>484411.72</v>
+        <v>404661.01</v>
       </c>
       <c r="P326" t="n">
         <v>4900</v>
       </c>
       <c r="Q326" t="n">
-        <v>803600</v>
+        <v>671300</v>
       </c>
     </row>
     <row r="327">
@@ -14352,7 +14352,7 @@
         </is>
       </c>
       <c r="J327" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -14361,19 +14361,19 @@
         <v>0</v>
       </c>
       <c r="M327" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N327" t="n">
-        <v>3240.8500514139</v>
+        <v>3240.8500533333</v>
       </c>
       <c r="O327" t="n">
-        <v>272231.4043187676</v>
+        <v>262508.8543199973</v>
       </c>
       <c r="P327" t="n">
         <v>5200</v>
       </c>
       <c r="Q327" t="n">
-        <v>436800</v>
+        <v>421200</v>
       </c>
     </row>
     <row r="328">
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="J331" t="n">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="K331" t="n">
         <v>0</v>
@@ -14543,19 +14543,19 @@
         <v>0</v>
       </c>
       <c r="M331" t="n">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="N331" t="n">
-        <v>616.01871807046</v>
+        <v>616.01871794872</v>
       </c>
       <c r="O331" t="n">
-        <v>1004726.52917292</v>
+        <v>1003494.491538465</v>
       </c>
       <c r="P331" t="n">
         <v>800</v>
       </c>
       <c r="Q331" t="n">
-        <v>1304800</v>
+        <v>1303200</v>
       </c>
     </row>
     <row r="332">
@@ -14675,10 +14675,10 @@
         <v>314</v>
       </c>
       <c r="N334" t="n">
-        <v>5191.4800283688</v>
+        <v>5191.4800284495</v>
       </c>
       <c r="O334" t="n">
-        <v>1630124.728907803</v>
+        <v>1630124.728933143</v>
       </c>
       <c r="P334" t="n">
         <v>9100</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="J335" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -14716,19 +14716,19 @@
         <v>0</v>
       </c>
       <c r="M335" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N335" t="n">
-        <v>381.16028283297</v>
+        <v>381.16028289855</v>
       </c>
       <c r="O335" t="n">
-        <v>83092.94165758745</v>
+        <v>82330.62110608681</v>
       </c>
       <c r="P335" t="n">
         <v>500</v>
       </c>
       <c r="Q335" t="n">
-        <v>109000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="336">
@@ -14751,7 +14751,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -14760,19 +14760,19 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N336" t="n">
         <v>2665.4</v>
       </c>
       <c r="O336" t="n">
-        <v>79962</v>
+        <v>69300.40000000001</v>
       </c>
       <c r="P336" t="n">
         <v>20900</v>
       </c>
       <c r="Q336" t="n">
-        <v>627000</v>
+        <v>543400</v>
       </c>
     </row>
     <row r="337">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14806,19 +14806,19 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N337" t="n">
-        <v>12422.462948052</v>
+        <v>12422.462959583</v>
       </c>
       <c r="O337" t="n">
-        <v>596278.221506496</v>
+        <v>546588.370221652</v>
       </c>
       <c r="P337" t="n">
         <v>19900</v>
       </c>
       <c r="Q337" t="n">
-        <v>955200</v>
+        <v>875600</v>
       </c>
     </row>
     <row r="338">
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14855,19 +14855,19 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N338" t="n">
         <v>1381.75</v>
       </c>
       <c r="O338" t="n">
-        <v>652186</v>
+        <v>645277.25</v>
       </c>
       <c r="P338" t="n">
         <v>2500</v>
       </c>
       <c r="Q338" t="n">
-        <v>1180000</v>
+        <v>1167500</v>
       </c>
     </row>
     <row r="339">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="J341" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K341" t="n">
         <v>0</v>
@@ -14986,19 +14986,19 @@
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="N341" t="n">
-        <v>3472.2761978447</v>
+        <v>3472.2762167406</v>
       </c>
       <c r="O341" t="n">
-        <v>597231.5060292884</v>
+        <v>576397.8519789396</v>
       </c>
       <c r="P341" t="n">
         <v>5900</v>
       </c>
       <c r="Q341" t="n">
-        <v>1014800</v>
+        <v>979400</v>
       </c>
     </row>
     <row r="342">
@@ -15254,10 +15254,10 @@
         <v>195</v>
       </c>
       <c r="N347" t="n">
-        <v>4371.1712628708</v>
+        <v>4371.1712629569</v>
       </c>
       <c r="O347" t="n">
-        <v>852378.396259806</v>
+        <v>852378.3962765955</v>
       </c>
       <c r="P347" t="n">
         <v>8900</v>
@@ -15414,7 +15414,7 @@
         </is>
       </c>
       <c r="J351" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -15423,19 +15423,19 @@
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N351" t="n">
         <v>3655.96</v>
       </c>
       <c r="O351" t="n">
-        <v>588609.5600000001</v>
+        <v>573985.72</v>
       </c>
       <c r="P351" t="n">
         <v>5500</v>
       </c>
       <c r="Q351" t="n">
-        <v>885500</v>
+        <v>863500</v>
       </c>
     </row>
     <row r="352">
@@ -15550,7 +15550,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -15559,19 +15559,19 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N354" t="n">
         <v>6446.04</v>
       </c>
       <c r="O354" t="n">
-        <v>206273.28</v>
+        <v>186935.16</v>
       </c>
       <c r="P354" t="n">
         <v>5300</v>
       </c>
       <c r="Q354" t="n">
-        <v>169600</v>
+        <v>153700</v>
       </c>
     </row>
     <row r="355">
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>423</v>
+        <v>313</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15867,19 +15867,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>423</v>
+        <v>313</v>
       </c>
       <c r="N361" t="n">
         <v>4648.6</v>
       </c>
       <c r="O361" t="n">
-        <v>1966357.8</v>
+        <v>1455011.8</v>
       </c>
       <c r="P361" t="n">
         <v>8900</v>
       </c>
       <c r="Q361" t="n">
-        <v>3764700</v>
+        <v>2785700</v>
       </c>
     </row>
     <row r="362">
@@ -15990,7 +15990,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -15999,19 +15999,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N364" t="n">
         <v>1312.43</v>
       </c>
       <c r="O364" t="n">
-        <v>1051256.43</v>
+        <v>1049944</v>
       </c>
       <c r="P364" t="n">
         <v>2300</v>
       </c>
       <c r="Q364" t="n">
-        <v>1842300</v>
+        <v>1840000</v>
       </c>
     </row>
     <row r="365">
@@ -16116,7 +16116,7 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
@@ -16125,19 +16125,19 @@
         <v>0</v>
       </c>
       <c r="M367" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N367" t="n">
         <v>17472.91</v>
       </c>
       <c r="O367" t="n">
-        <v>4508010.78</v>
+        <v>4455592.05</v>
       </c>
       <c r="P367" t="n">
         <v>2900</v>
       </c>
       <c r="Q367" t="n">
-        <v>748200</v>
+        <v>739500</v>
       </c>
     </row>
     <row r="368">
@@ -16160,7 +16160,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16169,19 +16169,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="N368" t="n">
         <v>1343.77</v>
       </c>
       <c r="O368" t="n">
-        <v>368192.98</v>
+        <v>364161.67</v>
       </c>
       <c r="P368" t="n">
         <v>2500</v>
       </c>
       <c r="Q368" t="n">
-        <v>685000</v>
+        <v>677500</v>
       </c>
     </row>
     <row r="369">
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="J371" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K371" t="n">
         <v>0</v>
@@ -16301,19 +16301,19 @@
         <v>0</v>
       </c>
       <c r="M371" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N371" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O371" t="n">
-        <v>536615.6699999999</v>
+        <v>517787.05</v>
       </c>
       <c r="P371" t="n">
         <v>16900</v>
       </c>
       <c r="Q371" t="n">
-        <v>963300</v>
+        <v>929500</v>
       </c>
     </row>
     <row r="372">
@@ -16336,7 +16336,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -16345,19 +16345,19 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="N372" t="n">
         <v>1387.55</v>
       </c>
       <c r="O372" t="n">
-        <v>740951.7</v>
+        <v>717363.35</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
       </c>
       <c r="Q372" t="n">
-        <v>1228200</v>
+        <v>1189100</v>
       </c>
     </row>
     <row r="373">
@@ -16462,7 +16462,7 @@
         </is>
       </c>
       <c r="J375" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -16471,19 +16471,19 @@
         <v>0</v>
       </c>
       <c r="M375" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="N375" t="n">
-        <v>2021.7211313869</v>
+        <v>2021.7211355311</v>
       </c>
       <c r="O375" t="n">
-        <v>363909.803649642</v>
+        <v>351779.4775824114</v>
       </c>
       <c r="P375" t="n">
         <v>2400</v>
       </c>
       <c r="Q375" t="n">
-        <v>432000</v>
+        <v>417600</v>
       </c>
     </row>
     <row r="376">
@@ -16821,7 +16821,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16830,19 +16830,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N383" t="n">
         <v>45945</v>
       </c>
       <c r="O383" t="n">
-        <v>689175</v>
+        <v>643230</v>
       </c>
       <c r="P383" t="n">
         <v>73900</v>
       </c>
       <c r="Q383" t="n">
-        <v>1108500</v>
+        <v>1034600</v>
       </c>
     </row>
     <row r="384">
@@ -16872,7 +16872,7 @@
         </is>
       </c>
       <c r="J384" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K384" t="n">
         <v>0</v>
@@ -16881,19 +16881,19 @@
         <v>0</v>
       </c>
       <c r="M384" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N384" t="n">
         <v>11921.4</v>
       </c>
       <c r="O384" t="n">
-        <v>1037161.8</v>
+        <v>953712</v>
       </c>
       <c r="P384" t="n">
         <v>19900</v>
       </c>
       <c r="Q384" t="n">
-        <v>1731300</v>
+        <v>1592000</v>
       </c>
     </row>
     <row r="385">
@@ -17353,7 +17353,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>614</v>
+        <v>582</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -17362,19 +17362,19 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>614</v>
+        <v>582</v>
       </c>
       <c r="N395" t="n">
-        <v>1630.924511587</v>
+        <v>1630.9246047904</v>
       </c>
       <c r="O395" t="n">
-        <v>1001387.650114418</v>
+        <v>949198.1199880128</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
       </c>
       <c r="Q395" t="n">
-        <v>1535000</v>
+        <v>1455000</v>
       </c>
     </row>
     <row r="396">
@@ -17440,7 +17440,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -17449,19 +17449,19 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="N397" t="n">
-        <v>1467.3113333333</v>
+        <v>1467.3067164179</v>
       </c>
       <c r="O397" t="n">
-        <v>180479.2939999959</v>
+        <v>157001.8186567153</v>
       </c>
       <c r="P397" t="n">
         <v>2500</v>
       </c>
       <c r="Q397" t="n">
-        <v>307500</v>
+        <v>267500</v>
       </c>
     </row>
     <row r="398">
@@ -17486,7 +17486,7 @@
         </is>
       </c>
       <c r="J398" t="n">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="K398" t="n">
         <v>0</v>
@@ -17495,19 +17495,19 @@
         <v>0</v>
       </c>
       <c r="M398" t="n">
-        <v>513</v>
+        <v>486</v>
       </c>
       <c r="N398" t="n">
-        <v>1690.5810573248</v>
+        <v>1690.5796701847</v>
       </c>
       <c r="O398" t="n">
-        <v>867268.0824076224</v>
+        <v>821621.7197097642</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
       </c>
       <c r="Q398" t="n">
-        <v>1487700</v>
+        <v>1409400</v>
       </c>
     </row>
     <row r="399">
@@ -17532,7 +17532,7 @@
         </is>
       </c>
       <c r="J399" t="n">
-        <v>1961</v>
+        <v>1913</v>
       </c>
       <c r="K399" t="n">
         <v>0</v>
@@ -17541,19 +17541,19 @@
         <v>0</v>
       </c>
       <c r="M399" t="n">
-        <v>1961</v>
+        <v>1913</v>
       </c>
       <c r="N399" t="n">
-        <v>1550.1946099379</v>
+        <v>1550.1946673374</v>
       </c>
       <c r="O399" t="n">
-        <v>3039931.630088222</v>
+        <v>2965522.398616446</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
       </c>
       <c r="Q399" t="n">
-        <v>4902500</v>
+        <v>4782500</v>
       </c>
     </row>
     <row r="400">
@@ -17590,10 +17590,10 @@
         <v>3</v>
       </c>
       <c r="N400" t="n">
-        <v>1579.3838288288</v>
+        <v>1579.3828229665</v>
       </c>
       <c r="O400" t="n">
-        <v>4738.1514864864</v>
+        <v>4738.148468899501</v>
       </c>
       <c r="P400" t="n">
         <v>2900</v>
@@ -17624,7 +17624,7 @@
         </is>
       </c>
       <c r="J401" t="n">
-        <v>1134</v>
+        <v>1092</v>
       </c>
       <c r="K401" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="M401" t="n">
-        <v>1134</v>
+        <v>1092</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.5197991712</v>
+        <v>2403.5202775057</v>
       </c>
       <c r="O401" t="n">
-        <v>2725591.452260141</v>
+        <v>2624644.143036224</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
       </c>
       <c r="Q401" t="n">
-        <v>3969000</v>
+        <v>3822000</v>
       </c>
     </row>
     <row r="402">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="J402" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K402" t="n">
         <v>0</v>
@@ -17677,19 +17677,19 @@
         <v>0</v>
       </c>
       <c r="M402" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N402" t="n">
         <v>24267.77</v>
       </c>
       <c r="O402" t="n">
-        <v>825104.1800000001</v>
+        <v>752300.87</v>
       </c>
       <c r="P402" t="n">
         <v>33400</v>
       </c>
       <c r="Q402" t="n">
-        <v>1135600</v>
+        <v>1035400</v>
       </c>
     </row>
     <row r="403">
@@ -17753,7 +17753,7 @@
         </is>
       </c>
       <c r="J404" t="n">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="K404" t="n">
         <v>0</v>
@@ -17762,19 +17762,19 @@
         <v>0</v>
       </c>
       <c r="M404" t="n">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="N404" t="n">
         <v>1000</v>
       </c>
       <c r="O404" t="n">
-        <v>822000</v>
+        <v>820000</v>
       </c>
       <c r="P404" t="n">
         <v>1300</v>
       </c>
       <c r="Q404" t="n">
-        <v>1068600</v>
+        <v>1066000</v>
       </c>
     </row>
     <row r="405">
@@ -18092,7 +18092,7 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -18101,19 +18101,19 @@
         <v>0</v>
       </c>
       <c r="M412" t="n">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="N412" t="n">
         <v>1307.69</v>
       </c>
       <c r="O412" t="n">
-        <v>1043536.62</v>
+        <v>1038305.86</v>
       </c>
       <c r="P412" t="n">
         <v>1700</v>
       </c>
       <c r="Q412" t="n">
-        <v>1356600</v>
+        <v>1349800</v>
       </c>
     </row>
     <row r="413">
@@ -18365,10 +18365,10 @@
         <v>43</v>
       </c>
       <c r="N418" t="n">
-        <v>1301.3994036697</v>
+        <v>1302.8935476464</v>
       </c>
       <c r="O418" t="n">
-        <v>55960.1743577971</v>
+        <v>56024.42254879521</v>
       </c>
       <c r="P418" t="n">
         <v>2000</v>
@@ -18853,7 +18853,7 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K429" t="n">
         <v>0</v>
@@ -18862,19 +18862,19 @@
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N429" t="n">
         <v>1965</v>
       </c>
       <c r="O429" t="n">
-        <v>27510</v>
+        <v>17685</v>
       </c>
       <c r="P429" t="n">
         <v>3700</v>
       </c>
       <c r="Q429" t="n">
-        <v>51800</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="430">
@@ -18986,7 +18986,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -18995,19 +18995,19 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="N432" t="n">
         <v>3253</v>
       </c>
       <c r="O432" t="n">
-        <v>936864</v>
+        <v>920599</v>
       </c>
       <c r="P432" t="n">
         <v>3900</v>
       </c>
       <c r="Q432" t="n">
-        <v>1123200</v>
+        <v>1103700</v>
       </c>
     </row>
     <row r="433">
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="J441" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="K441" t="n">
         <v>0</v>
@@ -19387,19 +19387,19 @@
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="N441" t="n">
         <v>3253</v>
       </c>
       <c r="O441" t="n">
-        <v>663612</v>
+        <v>653853</v>
       </c>
       <c r="P441" t="n">
         <v>3900</v>
       </c>
       <c r="Q441" t="n">
-        <v>795600</v>
+        <v>783900</v>
       </c>
     </row>
     <row r="442">
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
@@ -20242,19 +20242,19 @@
         <v>0</v>
       </c>
       <c r="M461" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N461" t="n">
         <v>4231</v>
       </c>
       <c r="O461" t="n">
-        <v>194626</v>
+        <v>186164</v>
       </c>
       <c r="P461" t="n">
         <v>6900</v>
       </c>
       <c r="Q461" t="n">
-        <v>317400</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="462">
@@ -20369,7 +20369,7 @@
         </is>
       </c>
       <c r="J464" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K464" t="n">
         <v>0</v>
@@ -20378,19 +20378,19 @@
         <v>0</v>
       </c>
       <c r="M464" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="N464" t="n">
         <v>9338</v>
       </c>
       <c r="O464" t="n">
-        <v>270802</v>
+        <v>233450</v>
       </c>
       <c r="P464" t="n">
         <v>15500</v>
       </c>
       <c r="Q464" t="n">
-        <v>449500</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="465">
@@ -20905,7 +20905,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -20914,19 +20914,19 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="N477" t="n">
         <v>2081</v>
       </c>
       <c r="O477" t="n">
-        <v>149832</v>
+        <v>118617</v>
       </c>
       <c r="P477" t="n">
         <v>3200</v>
       </c>
       <c r="Q477" t="n">
-        <v>230400</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="478">
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="J479" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K479" t="n">
         <v>0</v>
@@ -20996,19 +20996,19 @@
         <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N479" t="n">
         <v>2286.55</v>
       </c>
       <c r="O479" t="n">
-        <v>86888.90000000001</v>
+        <v>75456.15000000001</v>
       </c>
       <c r="P479" t="n">
         <v>3200</v>
       </c>
       <c r="Q479" t="n">
-        <v>121600</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="480">
@@ -21156,7 +21156,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -21165,19 +21165,19 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N483" t="n">
         <v>2567</v>
       </c>
       <c r="O483" t="n">
-        <v>821440</v>
+        <v>818873</v>
       </c>
       <c r="P483" t="n">
         <v>4500</v>
       </c>
       <c r="Q483" t="n">
-        <v>1440000</v>
+        <v>1435500</v>
       </c>
     </row>
     <row r="484">
@@ -21197,7 +21197,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -21206,19 +21206,19 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N484" t="n">
         <v>5519</v>
       </c>
       <c r="O484" t="n">
-        <v>22076</v>
+        <v>16557</v>
       </c>
       <c r="P484" t="n">
         <v>8300</v>
       </c>
       <c r="Q484" t="n">
-        <v>33200</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="485">
@@ -21279,7 +21279,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -21288,19 +21288,19 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N486" t="n">
         <v>6652</v>
       </c>
       <c r="O486" t="n">
-        <v>359208</v>
+        <v>345904</v>
       </c>
       <c r="P486" t="n">
         <v>5900</v>
       </c>
       <c r="Q486" t="n">
-        <v>318600</v>
+        <v>306800</v>
       </c>
     </row>
     <row r="487">
@@ -21525,7 +21525,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -21534,19 +21534,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="N492" t="n">
-        <v>2029.8741413584</v>
+        <v>2029.8741689828</v>
       </c>
       <c r="O492" t="n">
-        <v>856606.8876532448</v>
+        <v>834278.2834519309</v>
       </c>
       <c r="P492" t="n">
         <v>3600</v>
       </c>
       <c r="Q492" t="n">
-        <v>1519200</v>
+        <v>1479600</v>
       </c>
     </row>
     <row r="493">
@@ -21853,7 +21853,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -21862,19 +21862,19 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="N500" t="n">
         <v>1866.74</v>
       </c>
       <c r="O500" t="n">
-        <v>1204047.3</v>
+        <v>1198447.08</v>
       </c>
       <c r="P500" t="n">
         <v>2900</v>
       </c>
       <c r="Q500" t="n">
-        <v>1870500</v>
+        <v>1861800</v>
       </c>
     </row>
     <row r="501">
@@ -22066,7 +22066,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -22075,19 +22075,19 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N505" t="n">
-        <v>2680.7396939413</v>
+        <v>2680.7396933667</v>
       </c>
       <c r="O505" t="n">
-        <v>391387.9953154298</v>
+        <v>388707.2555381715</v>
       </c>
       <c r="P505" t="n">
         <v>4900</v>
       </c>
       <c r="Q505" t="n">
-        <v>715400</v>
+        <v>710500</v>
       </c>
     </row>
     <row r="506">
@@ -22119,10 +22119,10 @@
         <v>1306</v>
       </c>
       <c r="N506" t="n">
-        <v>880.32982103457</v>
+        <v>880.32985728346</v>
       </c>
       <c r="O506" t="n">
-        <v>1149710.746271149</v>
+        <v>1149710.793612199</v>
       </c>
       <c r="P506" t="n">
         <v>1200</v>
@@ -23018,10 +23018,10 @@
         <v>267</v>
       </c>
       <c r="N527" t="n">
-        <v>4285.1963341646</v>
+        <v>4285.1963420724</v>
       </c>
       <c r="O527" t="n">
-        <v>1144147.421221948</v>
+        <v>1144147.423333331</v>
       </c>
       <c r="P527" t="n">
         <v>6900</v>
@@ -23685,7 +23685,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -23694,19 +23694,19 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="N543" t="n">
         <v>3591.13</v>
       </c>
       <c r="O543" t="n">
-        <v>470438.03</v>
+        <v>398615.43</v>
       </c>
       <c r="P543" t="n">
         <v>6300</v>
       </c>
       <c r="Q543" t="n">
-        <v>825300</v>
+        <v>699300</v>
       </c>
     </row>
     <row r="544">
@@ -24161,7 +24161,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -24170,19 +24170,19 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N554" t="n">
         <v>881</v>
       </c>
       <c r="O554" t="n">
-        <v>59027</v>
+        <v>55503</v>
       </c>
       <c r="P554" t="n">
         <v>1500</v>
       </c>
       <c r="Q554" t="n">
-        <v>100500</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="555">
@@ -25519,10 +25519,10 @@
         <v>18</v>
       </c>
       <c r="N585" t="n">
-        <v>1561.0050819672</v>
+        <v>1561.0051173709</v>
       </c>
       <c r="O585" t="n">
-        <v>28098.0914754096</v>
+        <v>28098.0921126762</v>
       </c>
       <c r="P585" t="n">
         <v>2900</v>
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="J588" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K588" t="n">
         <v>0</v>
@@ -25649,19 +25649,19 @@
         <v>0</v>
       </c>
       <c r="M588" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N588" t="n">
         <v>5668</v>
       </c>
       <c r="O588" t="n">
-        <v>96356</v>
+        <v>90688</v>
       </c>
       <c r="P588" t="n">
         <v>9900</v>
       </c>
       <c r="Q588" t="n">
-        <v>168300</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="589">
@@ -25822,7 +25822,7 @@
         </is>
       </c>
       <c r="J592" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K592" t="n">
         <v>0</v>
@@ -25831,19 +25831,19 @@
         <v>0</v>
       </c>
       <c r="M592" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N592" t="n">
-        <v>7969.9501697531</v>
+        <v>7969.9501704105</v>
       </c>
       <c r="O592" t="n">
-        <v>1004213.721388891</v>
+        <v>996243.7713013125</v>
       </c>
       <c r="P592" t="n">
         <v>12900</v>
       </c>
       <c r="Q592" t="n">
-        <v>1625400</v>
+        <v>1612500</v>
       </c>
     </row>
     <row r="593">
@@ -26155,7 +26155,7 @@
         </is>
       </c>
       <c r="J600" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K600" t="n">
         <v>0</v>
@@ -26164,19 +26164,19 @@
         <v>0</v>
       </c>
       <c r="M600" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N600" t="n">
         <v>14954</v>
       </c>
       <c r="O600" t="n">
-        <v>613114</v>
+        <v>598160</v>
       </c>
       <c r="P600" t="n">
         <v>25500</v>
       </c>
       <c r="Q600" t="n">
-        <v>1045500</v>
+        <v>1020000</v>
       </c>
     </row>
     <row r="601">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -28158,19 +28158,19 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="N645" t="n">
-        <v>1664.3380609418</v>
+        <v>1664.3366763006</v>
       </c>
       <c r="O645" t="n">
-        <v>565874.9407202119</v>
+        <v>540909.419797695</v>
       </c>
       <c r="P645" t="n">
         <v>2900</v>
       </c>
       <c r="Q645" t="n">
-        <v>986000</v>
+        <v>942500</v>
       </c>
     </row>
     <row r="646">
@@ -28707,7 +28707,7 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
@@ -28716,19 +28716,19 @@
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N657" t="n">
         <v>3646</v>
       </c>
       <c r="O657" t="n">
-        <v>291680</v>
+        <v>277096</v>
       </c>
       <c r="P657" t="n">
         <v>6900</v>
       </c>
       <c r="Q657" t="n">
-        <v>552000</v>
+        <v>524400</v>
       </c>
     </row>
     <row r="658">
@@ -28845,7 +28845,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -28854,19 +28854,19 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="N660" t="n">
-        <v>1778.4728348758</v>
+        <v>1778.4728413344</v>
       </c>
       <c r="O660" t="n">
-        <v>2247989.663283011</v>
+        <v>2233761.888716007</v>
       </c>
       <c r="P660" t="n">
         <v>4900</v>
       </c>
       <c r="Q660" t="n">
-        <v>6193600</v>
+        <v>6154400</v>
       </c>
     </row>
     <row r="661">
@@ -29855,7 +29855,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -29864,19 +29864,19 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N682" t="n">
         <v>1817</v>
       </c>
       <c r="O682" t="n">
-        <v>270733</v>
+        <v>268916</v>
       </c>
       <c r="P682" t="n">
         <v>3100</v>
       </c>
       <c r="Q682" t="n">
-        <v>461900</v>
+        <v>458800</v>
       </c>
     </row>
     <row r="683">
@@ -30967,7 +30967,7 @@
         </is>
       </c>
       <c r="J706" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K706" t="n">
         <v>0</v>
@@ -30976,19 +30976,19 @@
         <v>0</v>
       </c>
       <c r="M706" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N706" t="n">
         <v>8858.16</v>
       </c>
       <c r="O706" t="n">
-        <v>2382845.04</v>
+        <v>2373986.88</v>
       </c>
       <c r="P706" t="n">
         <v>15500</v>
       </c>
       <c r="Q706" t="n">
-        <v>4169500</v>
+        <v>4154000</v>
       </c>
     </row>
     <row r="707">
@@ -31289,7 +31289,7 @@
         </is>
       </c>
       <c r="J713" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K713" t="n">
         <v>0</v>
@@ -31298,19 +31298,19 @@
         <v>0</v>
       </c>
       <c r="M713" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N713" t="n">
         <v>5014</v>
       </c>
       <c r="O713" t="n">
-        <v>200560</v>
+        <v>190532</v>
       </c>
       <c r="P713" t="n">
         <v>8200</v>
       </c>
       <c r="Q713" t="n">
-        <v>328000</v>
+        <v>311600</v>
       </c>
     </row>
     <row r="714">
@@ -31621,10 +31621,10 @@
         <v>664</v>
       </c>
       <c r="N720" t="n">
-        <v>2328.1186615921</v>
+        <v>2328.118659892</v>
       </c>
       <c r="O720" t="n">
-        <v>1545870.791297155</v>
+        <v>1545870.790168288</v>
       </c>
       <c r="P720" t="n">
         <v>4500</v>
@@ -32069,7 +32069,7 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
@@ -32078,19 +32078,19 @@
         <v>0</v>
       </c>
       <c r="M730" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N730" t="n">
         <v>9003</v>
       </c>
       <c r="O730" t="n">
-        <v>468156</v>
+        <v>459153</v>
       </c>
       <c r="P730" t="n">
         <v>14900</v>
       </c>
       <c r="Q730" t="n">
-        <v>774800</v>
+        <v>759900</v>
       </c>
     </row>
     <row r="731">
@@ -32115,7 +32115,7 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
@@ -32124,19 +32124,19 @@
         <v>0</v>
       </c>
       <c r="M731" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N731" t="n">
         <v>9178</v>
       </c>
       <c r="O731" t="n">
-        <v>605748</v>
+        <v>596570</v>
       </c>
       <c r="P731" t="n">
         <v>14900</v>
       </c>
       <c r="Q731" t="n">
-        <v>983400</v>
+        <v>968500</v>
       </c>
     </row>
     <row r="732">
@@ -32161,7 +32161,7 @@
         </is>
       </c>
       <c r="J732" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K732" t="n">
         <v>0</v>
@@ -32170,19 +32170,19 @@
         <v>0</v>
       </c>
       <c r="M732" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N732" t="n">
         <v>4544</v>
       </c>
       <c r="O732" t="n">
-        <v>1676736</v>
+        <v>1658560</v>
       </c>
       <c r="P732" t="n">
         <v>7900</v>
       </c>
       <c r="Q732" t="n">
-        <v>2915100</v>
+        <v>2883500</v>
       </c>
     </row>
     <row r="733">
@@ -32253,7 +32253,7 @@
         </is>
       </c>
       <c r="J734" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K734" t="n">
         <v>0</v>
@@ -32262,19 +32262,19 @@
         <v>0</v>
       </c>
       <c r="M734" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N734" t="n">
         <v>13922</v>
       </c>
       <c r="O734" t="n">
-        <v>306284</v>
+        <v>264518</v>
       </c>
       <c r="P734" t="n">
         <v>22900</v>
       </c>
       <c r="Q734" t="n">
-        <v>503800</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="735">
@@ -32345,7 +32345,7 @@
         </is>
       </c>
       <c r="J736" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K736" t="n">
         <v>0</v>
@@ -32354,19 +32354,19 @@
         <v>0</v>
       </c>
       <c r="M736" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N736" t="n">
         <v>25076</v>
       </c>
       <c r="O736" t="n">
-        <v>526596</v>
+        <v>501520</v>
       </c>
       <c r="P736" t="n">
         <v>40900</v>
       </c>
       <c r="Q736" t="n">
-        <v>858900</v>
+        <v>818000</v>
       </c>
     </row>
     <row r="737">
@@ -32403,10 +32403,10 @@
         <v>10</v>
       </c>
       <c r="N737" t="n">
-        <v>4907.8226736842</v>
+        <v>4907.822690678</v>
       </c>
       <c r="O737" t="n">
-        <v>49078.226736842</v>
+        <v>49078.22690678</v>
       </c>
       <c r="P737" t="n">
         <v>8200</v>
@@ -32437,7 +32437,7 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
@@ -32446,19 +32446,19 @@
         <v>0</v>
       </c>
       <c r="M738" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="N738" t="n">
         <v>6414</v>
       </c>
       <c r="O738" t="n">
-        <v>1180176</v>
+        <v>1167348</v>
       </c>
       <c r="P738" t="n">
         <v>10900</v>
       </c>
       <c r="Q738" t="n">
-        <v>2005600</v>
+        <v>1983800</v>
       </c>
     </row>
     <row r="739">
@@ -32483,7 +32483,7 @@
         </is>
       </c>
       <c r="J739" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K739" t="n">
         <v>0</v>
@@ -32492,19 +32492,19 @@
         <v>0</v>
       </c>
       <c r="M739" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="N739" t="n">
         <v>13210</v>
       </c>
       <c r="O739" t="n">
-        <v>2404220</v>
+        <v>2311750</v>
       </c>
       <c r="P739" t="n">
         <v>23900</v>
       </c>
       <c r="Q739" t="n">
-        <v>4349800</v>
+        <v>4182500</v>
       </c>
     </row>
     <row r="740">
@@ -32667,7 +32667,7 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
@@ -32676,19 +32676,19 @@
         <v>0</v>
       </c>
       <c r="M743" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="N743" t="n">
-        <v>3903.7392422907</v>
+        <v>3903.7394479074</v>
       </c>
       <c r="O743" t="n">
-        <v>136630.8734801745</v>
+        <v>109304.7045414072</v>
       </c>
       <c r="P743" t="n">
         <v>7500</v>
       </c>
       <c r="Q743" t="n">
-        <v>262500</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="744">
@@ -32938,7 +32938,7 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
@@ -32947,19 +32947,19 @@
         <v>0</v>
       </c>
       <c r="M749" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N749" t="n">
         <v>4202</v>
       </c>
       <c r="O749" t="n">
-        <v>247918</v>
+        <v>239514</v>
       </c>
       <c r="P749" t="n">
         <v>7900</v>
       </c>
       <c r="Q749" t="n">
-        <v>466100</v>
+        <v>450300</v>
       </c>
     </row>
     <row r="750">
@@ -33168,7 +33168,7 @@
         </is>
       </c>
       <c r="J754" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K754" t="n">
         <v>0</v>
@@ -33177,19 +33177,19 @@
         <v>0</v>
       </c>
       <c r="M754" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="N754" t="n">
         <v>2629</v>
       </c>
       <c r="O754" t="n">
-        <v>233981</v>
+        <v>223465</v>
       </c>
       <c r="P754" t="n">
         <v>4500</v>
       </c>
       <c r="Q754" t="n">
-        <v>400500</v>
+        <v>382500</v>
       </c>
     </row>
     <row r="755">
@@ -33214,7 +33214,7 @@
         </is>
       </c>
       <c r="J755" t="n">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="K755" t="n">
         <v>0</v>
@@ -33223,19 +33223,19 @@
         <v>0</v>
       </c>
       <c r="M755" t="n">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="N755" t="n">
-        <v>5869.1725284974</v>
+        <v>5869.172402529</v>
       </c>
       <c r="O755" t="n">
-        <v>2776118.60597927</v>
+        <v>2682211.787955753</v>
       </c>
       <c r="P755" t="n">
         <v>9500</v>
       </c>
       <c r="Q755" t="n">
-        <v>4493500</v>
+        <v>4341500</v>
       </c>
     </row>
     <row r="756">
@@ -33306,7 +33306,7 @@
         </is>
       </c>
       <c r="J757" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K757" t="n">
         <v>0</v>
@@ -33315,19 +33315,19 @@
         <v>0</v>
       </c>
       <c r="M757" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="N757" t="n">
         <v>4984</v>
       </c>
       <c r="O757" t="n">
-        <v>134568</v>
+        <v>54824</v>
       </c>
       <c r="P757" t="n">
         <v>7900</v>
       </c>
       <c r="Q757" t="n">
-        <v>213300</v>
+        <v>86900</v>
       </c>
     </row>
     <row r="758">
@@ -33352,7 +33352,7 @@
         </is>
       </c>
       <c r="J758" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="K758" t="n">
         <v>0</v>
@@ -33361,19 +33361,19 @@
         <v>0</v>
       </c>
       <c r="M758" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="N758" t="n">
         <v>5772</v>
       </c>
       <c r="O758" t="n">
-        <v>571428</v>
+        <v>484848</v>
       </c>
       <c r="P758" t="n">
         <v>9900</v>
       </c>
       <c r="Q758" t="n">
-        <v>980100</v>
+        <v>831600</v>
       </c>
     </row>
     <row r="759">
@@ -33398,7 +33398,7 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
@@ -33407,19 +33407,19 @@
         <v>0</v>
       </c>
       <c r="M759" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="N759" t="n">
         <v>6268</v>
       </c>
       <c r="O759" t="n">
-        <v>626800</v>
+        <v>520244</v>
       </c>
       <c r="P759" t="n">
         <v>10900</v>
       </c>
       <c r="Q759" t="n">
-        <v>1090000</v>
+        <v>904700</v>
       </c>
     </row>
     <row r="760">
@@ -33490,7 +33490,7 @@
         </is>
       </c>
       <c r="J761" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="K761" t="n">
         <v>0</v>
@@ -33499,19 +33499,19 @@
         <v>0</v>
       </c>
       <c r="M761" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="N761" t="n">
         <v>6645</v>
       </c>
       <c r="O761" t="n">
-        <v>1488480</v>
+        <v>1408740</v>
       </c>
       <c r="P761" t="n">
         <v>10900</v>
       </c>
       <c r="Q761" t="n">
-        <v>2441600</v>
+        <v>2310800</v>
       </c>
     </row>
     <row r="762">
@@ -33674,7 +33674,7 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
@@ -33683,19 +33683,19 @@
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N765" t="n">
         <v>7562</v>
       </c>
       <c r="O765" t="n">
-        <v>264670</v>
+        <v>249546</v>
       </c>
       <c r="P765" t="n">
         <v>12900</v>
       </c>
       <c r="Q765" t="n">
-        <v>451500</v>
+        <v>425700</v>
       </c>
     </row>
     <row r="766">
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="J773" t="n">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="K773" t="n">
         <v>0</v>
@@ -34054,19 +34054,19 @@
         <v>0</v>
       </c>
       <c r="M773" t="n">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N773" t="n">
         <v>753</v>
       </c>
       <c r="O773" t="n">
-        <v>381018</v>
+        <v>371982</v>
       </c>
       <c r="P773" t="n">
         <v>1600</v>
       </c>
       <c r="Q773" t="n">
-        <v>809600</v>
+        <v>790400</v>
       </c>
     </row>
     <row r="774">
@@ -34229,7 +34229,7 @@
         </is>
       </c>
       <c r="J777" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K777" t="n">
         <v>0</v>
@@ -34238,19 +34238,19 @@
         <v>0</v>
       </c>
       <c r="M777" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N777" t="n">
-        <v>17075.989518828</v>
+        <v>17075.989518156</v>
       </c>
       <c r="O777" t="n">
-        <v>2834614.260125448</v>
+        <v>2800462.280977584</v>
       </c>
       <c r="P777" t="n">
         <v>27500</v>
       </c>
       <c r="Q777" t="n">
-        <v>4565000</v>
+        <v>4510000</v>
       </c>
     </row>
     <row r="778">
@@ -34917,7 +34917,7 @@
         </is>
       </c>
       <c r="J792" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="K792" t="n">
         <v>0</v>
@@ -34926,19 +34926,19 @@
         <v>0</v>
       </c>
       <c r="M792" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="N792" t="n">
-        <v>4268.7110240964</v>
+        <v>4268.712516129</v>
       </c>
       <c r="O792" t="n">
-        <v>128061.330722892</v>
+        <v>81105.53780645099</v>
       </c>
       <c r="P792" t="n">
         <v>6900</v>
       </c>
       <c r="Q792" t="n">
-        <v>207000</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="793">
@@ -34963,7 +34963,7 @@
         </is>
       </c>
       <c r="J793" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K793" t="n">
         <v>0</v>
@@ -34972,19 +34972,19 @@
         <v>0</v>
       </c>
       <c r="M793" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N793" t="n">
         <v>5215</v>
       </c>
       <c r="O793" t="n">
-        <v>265965</v>
+        <v>245105</v>
       </c>
       <c r="P793" t="n">
         <v>8900</v>
       </c>
       <c r="Q793" t="n">
-        <v>453900</v>
+        <v>418300</v>
       </c>
     </row>
     <row r="794">
@@ -35009,7 +35009,7 @@
         </is>
       </c>
       <c r="J794" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K794" t="n">
         <v>0</v>
@@ -35018,19 +35018,19 @@
         <v>0</v>
       </c>
       <c r="M794" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N794" t="n">
         <v>29835</v>
       </c>
       <c r="O794" t="n">
-        <v>805545</v>
+        <v>775710</v>
       </c>
       <c r="P794" t="n">
         <v>47900</v>
       </c>
       <c r="Q794" t="n">
-        <v>1293300</v>
+        <v>1245400</v>
       </c>
     </row>
     <row r="795">
@@ -35239,7 +35239,7 @@
         </is>
       </c>
       <c r="J799" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="K799" t="n">
         <v>0</v>
@@ -35248,19 +35248,19 @@
         <v>0</v>
       </c>
       <c r="M799" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N799" t="n">
         <v>8700</v>
       </c>
       <c r="O799" t="n">
-        <v>556800</v>
+        <v>495900</v>
       </c>
       <c r="P799" t="n">
         <v>14900</v>
       </c>
       <c r="Q799" t="n">
-        <v>953600</v>
+        <v>849300</v>
       </c>
     </row>
     <row r="800">
@@ -35285,7 +35285,7 @@
         </is>
       </c>
       <c r="J800" t="n">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="K800" t="n">
         <v>0</v>
@@ -35294,19 +35294,19 @@
         <v>0</v>
       </c>
       <c r="M800" t="n">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="N800" t="n">
         <v>1326</v>
       </c>
       <c r="O800" t="n">
-        <v>1363128</v>
+        <v>1343238</v>
       </c>
       <c r="P800" t="n">
         <v>2500</v>
       </c>
       <c r="Q800" t="n">
-        <v>2570000</v>
+        <v>2532500</v>
       </c>
     </row>
     <row r="801">
@@ -35377,7 +35377,7 @@
         </is>
       </c>
       <c r="J802" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K802" t="n">
         <v>0</v>
@@ -35386,19 +35386,19 @@
         <v>0</v>
       </c>
       <c r="M802" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N802" t="n">
         <v>21762</v>
       </c>
       <c r="O802" t="n">
-        <v>391716</v>
+        <v>348192</v>
       </c>
       <c r="P802" t="n">
         <v>35900</v>
       </c>
       <c r="Q802" t="n">
-        <v>646200</v>
+        <v>574400</v>
       </c>
     </row>
     <row r="803">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="J804" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K804" t="n">
         <v>0</v>
@@ -35478,19 +35478,19 @@
         <v>0</v>
       </c>
       <c r="M804" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N804" t="n">
         <v>15472</v>
       </c>
       <c r="O804" t="n">
-        <v>108304</v>
+        <v>92832</v>
       </c>
       <c r="P804" t="n">
         <v>25900</v>
       </c>
       <c r="Q804" t="n">
-        <v>181300</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="805">
@@ -35515,7 +35515,7 @@
         </is>
       </c>
       <c r="J805" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K805" t="n">
         <v>0</v>
@@ -35524,13 +35524,13 @@
         <v>0</v>
       </c>
       <c r="M805" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N805" t="n">
         <v>10982.15</v>
       </c>
       <c r="O805" t="n">
-        <v>32946.45</v>
+        <v>21964.3</v>
       </c>
       <c r="P805" t="n">
         <v>0</v>
@@ -35561,7 +35561,7 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
@@ -35570,19 +35570,19 @@
         <v>0</v>
       </c>
       <c r="M806" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N806" t="n">
         <v>7253</v>
       </c>
       <c r="O806" t="n">
-        <v>108795</v>
+        <v>94289</v>
       </c>
       <c r="P806" t="n">
         <v>11900</v>
       </c>
       <c r="Q806" t="n">
-        <v>178500</v>
+        <v>154700</v>
       </c>
     </row>
     <row r="807">
@@ -35653,7 +35653,7 @@
         </is>
       </c>
       <c r="J808" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="K808" t="n">
         <v>0</v>
@@ -35662,19 +35662,19 @@
         <v>0</v>
       </c>
       <c r="M808" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="N808" t="n">
         <v>5476</v>
       </c>
       <c r="O808" t="n">
-        <v>2245160</v>
+        <v>2223256</v>
       </c>
       <c r="P808" t="n">
         <v>8900</v>
       </c>
       <c r="Q808" t="n">
-        <v>3649000</v>
+        <v>3613400</v>
       </c>
     </row>
     <row r="809">
@@ -35840,7 +35840,7 @@
         </is>
       </c>
       <c r="J812" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K812" t="n">
         <v>0</v>
@@ -35849,19 +35849,19 @@
         <v>0</v>
       </c>
       <c r="M812" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N812" t="n">
         <v>64612</v>
       </c>
       <c r="O812" t="n">
-        <v>2778316</v>
+        <v>2649092</v>
       </c>
       <c r="P812" t="n">
         <v>103900</v>
       </c>
       <c r="Q812" t="n">
-        <v>4467700</v>
+        <v>4259900</v>
       </c>
     </row>
     <row r="813">
@@ -35932,7 +35932,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -35941,19 +35941,19 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N814" t="n">
-        <v>1516.0387397625</v>
+        <v>1516.0387386003</v>
       </c>
       <c r="O814" t="n">
-        <v>626123.9995219125</v>
+        <v>618543.8053489224</v>
       </c>
       <c r="P814" t="n">
         <v>2300</v>
       </c>
       <c r="Q814" t="n">
-        <v>949900</v>
+        <v>938400</v>
       </c>
     </row>
     <row r="815">
@@ -36068,7 +36068,7 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
@@ -36077,19 +36077,19 @@
         <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="N817" t="n">
-        <v>2458.5124991023</v>
+        <v>2458.5124311594</v>
       </c>
       <c r="O817" t="n">
-        <v>2684695.649019712</v>
+        <v>2682237.062394905</v>
       </c>
       <c r="P817" t="n">
         <v>3500</v>
       </c>
       <c r="Q817" t="n">
-        <v>3822000</v>
+        <v>3818500</v>
       </c>
     </row>
     <row r="818">
@@ -36126,10 +36126,10 @@
         <v>321</v>
       </c>
       <c r="N818" t="n">
-        <v>1907.3924654378</v>
+        <v>1907.3924393064</v>
       </c>
       <c r="O818" t="n">
-        <v>612272.9814055337</v>
+        <v>612272.9730173544</v>
       </c>
       <c r="P818" t="n">
         <v>2500</v>
@@ -36172,10 +36172,10 @@
         <v>462</v>
       </c>
       <c r="N819" t="n">
-        <v>1771.0893598234</v>
+        <v>1771.0893441415</v>
       </c>
       <c r="O819" t="n">
-        <v>818243.2842384108</v>
+        <v>818243.2769933731</v>
       </c>
       <c r="P819" t="n">
         <v>2500</v>
@@ -36206,7 +36206,7 @@
         </is>
       </c>
       <c r="J820" t="n">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="K820" t="n">
         <v>0</v>
@@ -36215,19 +36215,19 @@
         <v>0</v>
       </c>
       <c r="M820" t="n">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N820" t="n">
-        <v>2079.3833133433</v>
+        <v>2079.3832881866</v>
       </c>
       <c r="O820" t="n">
-        <v>1201883.555112427</v>
+        <v>1189407.240842735</v>
       </c>
       <c r="P820" t="n">
         <v>2900</v>
       </c>
       <c r="Q820" t="n">
-        <v>1676200</v>
+        <v>1658800</v>
       </c>
     </row>
     <row r="821">
@@ -36264,10 +36264,10 @@
         <v>928</v>
       </c>
       <c r="N821" t="n">
-        <v>1803.0169552729</v>
+        <v>1803.0169781803</v>
       </c>
       <c r="O821" t="n">
-        <v>1673199.734493251</v>
+        <v>1673199.755751318</v>
       </c>
       <c r="P821" t="n">
         <v>2500</v>
@@ -36402,10 +36402,10 @@
         <v>548</v>
       </c>
       <c r="N824" t="n">
-        <v>2108.7969844358</v>
+        <v>2108.7971008815</v>
       </c>
       <c r="O824" t="n">
-        <v>1155620.747470818</v>
+        <v>1155620.811283062</v>
       </c>
       <c r="P824" t="n">
         <v>2900</v>
@@ -36436,7 +36436,7 @@
         </is>
       </c>
       <c r="J825" t="n">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="K825" t="n">
         <v>0</v>
@@ -36445,19 +36445,19 @@
         <v>0</v>
       </c>
       <c r="M825" t="n">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="N825" t="n">
-        <v>2056.0821161192</v>
+        <v>2056.0820030996</v>
       </c>
       <c r="O825" t="n">
-        <v>2037577.377074127</v>
+        <v>1988231.296997313</v>
       </c>
       <c r="P825" t="n">
         <v>2900</v>
       </c>
       <c r="Q825" t="n">
-        <v>2873900</v>
+        <v>2804300</v>
       </c>
     </row>
     <row r="826">
@@ -36482,7 +36482,7 @@
         </is>
       </c>
       <c r="J826" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K826" t="n">
         <v>0</v>
@@ -36491,19 +36491,19 @@
         <v>0</v>
       </c>
       <c r="M826" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N826" t="n">
-        <v>3224.5697707424</v>
+        <v>3224.5698459846</v>
       </c>
       <c r="O826" t="n">
-        <v>554626.0005676928</v>
+        <v>548176.873817382</v>
       </c>
       <c r="P826" t="n">
         <v>4500</v>
       </c>
       <c r="Q826" t="n">
-        <v>774000</v>
+        <v>765000</v>
       </c>
     </row>
     <row r="827">
@@ -36528,7 +36528,7 @@
         </is>
       </c>
       <c r="J827" t="n">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="K827" t="n">
         <v>0</v>
@@ -36537,19 +36537,19 @@
         <v>0</v>
       </c>
       <c r="M827" t="n">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="N827" t="n">
-        <v>1655.9292163743</v>
+        <v>1655.9292037471</v>
       </c>
       <c r="O827" t="n">
-        <v>930632.2196023567</v>
+        <v>927320.354098376</v>
       </c>
       <c r="P827" t="n">
         <v>2500</v>
       </c>
       <c r="Q827" t="n">
-        <v>1405000</v>
+        <v>1400000</v>
       </c>
     </row>
     <row r="828">
@@ -36669,7 +36669,7 @@
         </is>
       </c>
       <c r="J830" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K830" t="n">
         <v>0</v>
@@ -36678,19 +36678,19 @@
         <v>0</v>
       </c>
       <c r="M830" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N830" t="n">
         <v>3684</v>
       </c>
       <c r="O830" t="n">
-        <v>206304</v>
+        <v>191568</v>
       </c>
       <c r="P830" t="n">
         <v>6500</v>
       </c>
       <c r="Q830" t="n">
-        <v>364000</v>
+        <v>338000</v>
       </c>
     </row>
     <row r="831">
@@ -36897,7 +36897,7 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
@@ -36906,19 +36906,19 @@
         <v>0</v>
       </c>
       <c r="M835" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N835" t="n">
         <v>5347.73</v>
       </c>
       <c r="O835" t="n">
-        <v>197866.01</v>
+        <v>181822.82</v>
       </c>
       <c r="P835" t="n">
         <v>9500</v>
       </c>
       <c r="Q835" t="n">
-        <v>351500</v>
+        <v>323000</v>
       </c>
     </row>
     <row r="836">
@@ -36955,10 +36955,10 @@
         <v>2</v>
       </c>
       <c r="N836" t="n">
-        <v>1906.1725581395</v>
+        <v>1906.17</v>
       </c>
       <c r="O836" t="n">
-        <v>3812.345116279</v>
+        <v>3812.34</v>
       </c>
       <c r="P836" t="n">
         <v>2900</v>
@@ -36989,7 +36989,7 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K837" t="n">
         <v>0</v>
@@ -36998,19 +36998,19 @@
         <v>0</v>
       </c>
       <c r="M837" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="N837" t="n">
-        <v>2060.1585714286</v>
+        <v>2060.1584104628</v>
       </c>
       <c r="O837" t="n">
-        <v>129789.9900000018</v>
+        <v>115368.8709859168</v>
       </c>
       <c r="P837" t="n">
         <v>2900</v>
       </c>
       <c r="Q837" t="n">
-        <v>182700</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="838">
@@ -37035,7 +37035,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37044,19 +37044,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N838" t="n">
-        <v>2546.9801388889</v>
+        <v>2546.979929078</v>
       </c>
       <c r="O838" t="n">
-        <v>68768.4637500003</v>
+        <v>53486.57851063801</v>
       </c>
       <c r="P838" t="n">
         <v>3900</v>
       </c>
       <c r="Q838" t="n">
-        <v>105300</v>
+        <v>81900</v>
       </c>
     </row>
     <row r="839">
@@ -37081,7 +37081,7 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
@@ -37090,19 +37090,19 @@
         <v>0</v>
       </c>
       <c r="M839" t="n">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="N839" t="n">
-        <v>1259.274867406</v>
+        <v>1259.2749291992</v>
       </c>
       <c r="O839" t="n">
-        <v>289633.21950338</v>
+        <v>235484.4117602504</v>
       </c>
       <c r="P839" t="n">
         <v>1900</v>
       </c>
       <c r="Q839" t="n">
-        <v>437000</v>
+        <v>355300</v>
       </c>
     </row>
     <row r="840">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="J841" t="n">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="K841" t="n">
         <v>0</v>
@@ -37182,19 +37182,19 @@
         <v>0</v>
       </c>
       <c r="M841" t="n">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="N841" t="n">
         <v>1801</v>
       </c>
       <c r="O841" t="n">
-        <v>1113018</v>
+        <v>1098610</v>
       </c>
       <c r="P841" t="n">
         <v>2900</v>
       </c>
       <c r="Q841" t="n">
-        <v>1792200</v>
+        <v>1769000</v>
       </c>
     </row>
     <row r="842">
@@ -37217,7 +37217,7 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
@@ -37226,19 +37226,19 @@
         <v>0</v>
       </c>
       <c r="M842" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N842" t="n">
-        <v>692.1524140338601</v>
+        <v>692.15241910093</v>
       </c>
       <c r="O842" t="n">
-        <v>58832.95519287811</v>
+        <v>50527.1265943679</v>
       </c>
       <c r="P842" t="n">
         <v>1200</v>
       </c>
       <c r="Q842" t="n">
-        <v>102000</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="843">
@@ -37690,7 +37690,7 @@
         </is>
       </c>
       <c r="J852" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="K852" t="n">
         <v>0</v>
@@ -37699,19 +37699,19 @@
         <v>0</v>
       </c>
       <c r="M852" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="N852" t="n">
         <v>5215</v>
       </c>
       <c r="O852" t="n">
-        <v>599725</v>
+        <v>495425</v>
       </c>
       <c r="P852" t="n">
         <v>8900</v>
       </c>
       <c r="Q852" t="n">
-        <v>1023500</v>
+        <v>845500</v>
       </c>
     </row>
     <row r="853">
@@ -38568,7 +38568,7 @@
         </is>
       </c>
       <c r="J871" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="K871" t="n">
         <v>0</v>
@@ -38577,19 +38577,19 @@
         <v>0</v>
       </c>
       <c r="M871" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N871" t="n">
-        <v>1530.4499182339</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O871" t="n">
-        <v>564736.0198283091</v>
+        <v>557083.7701761696</v>
       </c>
       <c r="P871" t="n">
         <v>2600</v>
       </c>
       <c r="Q871" t="n">
-        <v>959400</v>
+        <v>946400</v>
       </c>
     </row>
     <row r="872">
@@ -38748,7 +38748,7 @@
         </is>
       </c>
       <c r="J875" t="n">
-        <v>3757</v>
+        <v>3745</v>
       </c>
       <c r="K875" t="n">
         <v>0</v>
@@ -38757,19 +38757,19 @@
         <v>0</v>
       </c>
       <c r="M875" t="n">
-        <v>3757</v>
+        <v>3745</v>
       </c>
       <c r="N875" t="n">
-        <v>574.67195050559</v>
+        <v>574.67195362473</v>
       </c>
       <c r="O875" t="n">
-        <v>2159042.518049501</v>
+        <v>2152146.466324614</v>
       </c>
       <c r="P875" t="n">
         <v>800</v>
       </c>
       <c r="Q875" t="n">
-        <v>3005600</v>
+        <v>2996000</v>
       </c>
     </row>
     <row r="876">
@@ -39020,7 +39020,7 @@
         </is>
       </c>
       <c r="J881" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="K881" t="n">
         <v>0</v>
@@ -39029,19 +39029,19 @@
         <v>0</v>
       </c>
       <c r="M881" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N881" t="n">
         <v>1828.64</v>
       </c>
       <c r="O881" t="n">
-        <v>1931043.84</v>
+        <v>1929215.2</v>
       </c>
       <c r="P881" t="n">
         <v>2000</v>
       </c>
       <c r="Q881" t="n">
-        <v>2112000</v>
+        <v>2110000</v>
       </c>
     </row>
     <row r="882">
@@ -39304,7 +39304,7 @@
         </is>
       </c>
       <c r="J887" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K887" t="n">
         <v>0</v>
@@ -39313,19 +39313,19 @@
         <v>0</v>
       </c>
       <c r="M887" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N887" t="n">
         <v>8702.219999999999</v>
       </c>
       <c r="O887" t="n">
-        <v>661368.72</v>
+        <v>652666.5</v>
       </c>
       <c r="P887" t="n">
         <v>8900</v>
       </c>
       <c r="Q887" t="n">
-        <v>676400</v>
+        <v>667500</v>
       </c>
     </row>
     <row r="888">
@@ -39360,10 +39360,10 @@
         <v>309</v>
       </c>
       <c r="N888" t="n">
-        <v>345.55838597724</v>
+        <v>345.55838583542</v>
       </c>
       <c r="O888" t="n">
-        <v>106777.5412669672</v>
+        <v>106777.5412231448</v>
       </c>
       <c r="P888" t="n">
         <v>600</v>
@@ -39404,10 +39404,10 @@
         <v>1443</v>
       </c>
       <c r="N889" t="n">
-        <v>711.33664519481</v>
+        <v>711.33664496242</v>
       </c>
       <c r="O889" t="n">
-        <v>1026458.779016111</v>
+        <v>1026458.778680772</v>
       </c>
       <c r="P889" t="n">
         <v>900</v>
@@ -39652,7 +39652,7 @@
         </is>
       </c>
       <c r="J895" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K895" t="n">
         <v>0</v>
@@ -39661,19 +39661,19 @@
         <v>0</v>
       </c>
       <c r="M895" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N895" t="n">
         <v>6213.51</v>
       </c>
       <c r="O895" t="n">
-        <v>310675.5</v>
+        <v>304461.99</v>
       </c>
       <c r="P895" t="n">
         <v>10300</v>
       </c>
       <c r="Q895" t="n">
-        <v>515000</v>
+        <v>504700</v>
       </c>
     </row>
     <row r="896">
@@ -39872,7 +39872,7 @@
         </is>
       </c>
       <c r="J900" t="n">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K900" t="n">
         <v>0</v>
@@ -39881,19 +39881,19 @@
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="N900" t="n">
-        <v>211.29233722871</v>
+        <v>211.29219798658</v>
       </c>
       <c r="O900" t="n">
-        <v>126564.1099999973</v>
+        <v>125930.1500000017</v>
       </c>
       <c r="P900" t="n">
         <v>400</v>
       </c>
       <c r="Q900" t="n">
-        <v>239600</v>
+        <v>238400</v>
       </c>
     </row>
     <row r="901">
@@ -40089,7 +40089,7 @@
         </is>
       </c>
       <c r="J905" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K905" t="n">
         <v>0</v>
@@ -40098,19 +40098,19 @@
         <v>0</v>
       </c>
       <c r="M905" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N905" t="n">
         <v>4243.87</v>
       </c>
       <c r="O905" t="n">
-        <v>216437.37</v>
+        <v>207949.63</v>
       </c>
       <c r="P905" t="n">
         <v>5900</v>
       </c>
       <c r="Q905" t="n">
-        <v>300900</v>
+        <v>289100</v>
       </c>
     </row>
     <row r="906">
@@ -40358,7 +40358,7 @@
         </is>
       </c>
       <c r="J911" t="n">
-        <v>3353</v>
+        <v>3228</v>
       </c>
       <c r="K911" t="n">
         <v>0</v>
@@ -40367,19 +40367,19 @@
         <v>0</v>
       </c>
       <c r="M911" t="n">
-        <v>3353</v>
+        <v>3228</v>
       </c>
       <c r="N911" t="n">
-        <v>517.29485088253</v>
+        <v>517.2950312417501</v>
       </c>
       <c r="O911" t="n">
-        <v>1734489.635009123</v>
+        <v>1669828.360848369</v>
       </c>
       <c r="P911" t="n">
         <v>900</v>
       </c>
       <c r="Q911" t="n">
-        <v>3017700</v>
+        <v>2905200</v>
       </c>
     </row>
     <row r="912">
@@ -40584,7 +40584,7 @@
         </is>
       </c>
       <c r="J916" t="n">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="K916" t="n">
         <v>0</v>
@@ -40593,19 +40593,19 @@
         <v>0</v>
       </c>
       <c r="M916" t="n">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="N916" t="n">
-        <v>3110.837275018</v>
+        <v>3110.8368831169</v>
       </c>
       <c r="O916" t="n">
-        <v>1486980.217458604</v>
+        <v>1315884.001558449</v>
       </c>
       <c r="P916" t="n">
         <v>4500</v>
       </c>
       <c r="Q916" t="n">
-        <v>2151000</v>
+        <v>1903500</v>
       </c>
     </row>
     <row r="917">
@@ -40818,10 +40818,10 @@
         <v>1225</v>
       </c>
       <c r="N921" t="n">
-        <v>703.7947515264</v>
+        <v>703.7947376286299</v>
       </c>
       <c r="O921" t="n">
-        <v>862148.5706198399</v>
+        <v>862148.5535950717</v>
       </c>
       <c r="P921" t="n">
         <v>900</v>
@@ -40899,7 +40899,7 @@
         </is>
       </c>
       <c r="J923" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K923" t="n">
         <v>0</v>
@@ -40908,19 +40908,19 @@
         <v>0</v>
       </c>
       <c r="M923" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N923" t="n">
-        <v>3182.2511299435</v>
+        <v>3182.2511320755</v>
       </c>
       <c r="O923" t="n">
-        <v>70009.52485875699</v>
+        <v>66827.2737735855</v>
       </c>
       <c r="P923" t="n">
         <v>6900</v>
       </c>
       <c r="Q923" t="n">
-        <v>151800</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="924">
@@ -41091,10 +41091,10 @@
         <v>3</v>
       </c>
       <c r="N927" t="n">
-        <v>2501.3844329897</v>
+        <v>2501.3844041451</v>
       </c>
       <c r="O927" t="n">
-        <v>7504.1532989691</v>
+        <v>7504.1532124353</v>
       </c>
       <c r="P927" t="n">
         <v>4100</v>
@@ -41562,7 +41562,7 @@
         </is>
       </c>
       <c r="J938" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="K938" t="n">
         <v>0</v>
@@ -41571,19 +41571,19 @@
         <v>0</v>
       </c>
       <c r="M938" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="N938" t="n">
-        <v>2717.1178965517</v>
+        <v>2717.1178819444</v>
       </c>
       <c r="O938" t="n">
-        <v>760793.011034476</v>
+        <v>755358.7711805431</v>
       </c>
       <c r="P938" t="n">
         <v>3500</v>
       </c>
       <c r="Q938" t="n">
-        <v>980000</v>
+        <v>973000</v>
       </c>
     </row>
     <row r="939">
@@ -41603,7 +41603,7 @@
         </is>
       </c>
       <c r="J939" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K939" t="n">
         <v>0</v>
@@ -41612,19 +41612,19 @@
         <v>0</v>
       </c>
       <c r="M939" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N939" t="n">
-        <v>2077.4948312883</v>
+        <v>2077.4948461538</v>
       </c>
       <c r="O939" t="n">
-        <v>496521.2646779037</v>
+        <v>492366.2785384507</v>
       </c>
       <c r="P939" t="n">
         <v>2900</v>
       </c>
       <c r="Q939" t="n">
-        <v>693100</v>
+        <v>687300</v>
       </c>
     </row>
     <row r="940">
@@ -41647,7 +41647,7 @@
         </is>
       </c>
       <c r="J940" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K940" t="n">
         <v>0</v>
@@ -41656,19 +41656,19 @@
         <v>0</v>
       </c>
       <c r="M940" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N940" t="n">
-        <v>3629.7160212766</v>
+        <v>3629.7160042735</v>
       </c>
       <c r="O940" t="n">
-        <v>61705.1723617022</v>
+        <v>54445.7400641025</v>
       </c>
       <c r="P940" t="n">
         <v>4900</v>
       </c>
       <c r="Q940" t="n">
-        <v>83300</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="941">
@@ -41688,7 +41688,7 @@
         </is>
       </c>
       <c r="J941" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="K941" t="n">
         <v>0</v>
@@ -41697,19 +41697,19 @@
         <v>0</v>
       </c>
       <c r="M941" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N941" t="n">
         <v>1000</v>
       </c>
       <c r="O941" t="n">
-        <v>248000</v>
+        <v>246000</v>
       </c>
       <c r="P941" t="n">
         <v>1300</v>
       </c>
       <c r="Q941" t="n">
-        <v>322400</v>
+        <v>319800</v>
       </c>
     </row>
     <row r="942">
@@ -41909,7 +41909,7 @@
         </is>
       </c>
       <c r="J946" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K946" t="n">
         <v>0</v>
@@ -41918,19 +41918,19 @@
         <v>0</v>
       </c>
       <c r="M946" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N946" t="n">
         <v>1567.02</v>
       </c>
       <c r="O946" t="n">
-        <v>272661.48</v>
+        <v>269527.44</v>
       </c>
       <c r="P946" t="n">
         <v>2900</v>
       </c>
       <c r="Q946" t="n">
-        <v>504600</v>
+        <v>498800</v>
       </c>
     </row>
     <row r="947">
@@ -42002,7 +42002,7 @@
         </is>
       </c>
       <c r="J948" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K948" t="n">
         <v>0</v>
@@ -42011,19 +42011,19 @@
         <v>0</v>
       </c>
       <c r="M948" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N948" t="n">
-        <v>6078.9925962596</v>
+        <v>6078.9926048565</v>
       </c>
       <c r="O948" t="n">
-        <v>267475.6742354224</v>
+        <v>249238.6967991165</v>
       </c>
       <c r="P948" t="n">
         <v>18500</v>
       </c>
       <c r="Q948" t="n">
-        <v>814000</v>
+        <v>758500</v>
       </c>
     </row>
     <row r="949">
@@ -42868,7 +42868,7 @@
         </is>
       </c>
       <c r="J966" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K966" t="n">
         <v>0</v>
@@ -42877,19 +42877,19 @@
         <v>0</v>
       </c>
       <c r="M966" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N966" t="n">
         <v>6773.85</v>
       </c>
       <c r="O966" t="n">
-        <v>81286.20000000001</v>
+        <v>74512.35000000001</v>
       </c>
       <c r="P966" t="n">
         <v>9500</v>
       </c>
       <c r="Q966" t="n">
-        <v>114000</v>
+        <v>104500</v>
       </c>
     </row>
     <row r="967">
@@ -42914,7 +42914,7 @@
         </is>
       </c>
       <c r="J967" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K967" t="n">
         <v>0</v>
@@ -42923,19 +42923,19 @@
         <v>0</v>
       </c>
       <c r="M967" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N967" t="n">
-        <v>1322.925</v>
+        <v>1322.9241666667</v>
       </c>
       <c r="O967" t="n">
-        <v>19843.875</v>
+        <v>9260.4691666669</v>
       </c>
       <c r="P967" t="n">
         <v>7900</v>
       </c>
       <c r="Q967" t="n">
-        <v>118500</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="968">
@@ -43004,7 +43004,7 @@
         </is>
       </c>
       <c r="J969" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K969" t="n">
         <v>0</v>
@@ -43013,19 +43013,19 @@
         <v>0</v>
       </c>
       <c r="M969" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N969" t="n">
-        <v>3414.5660313725</v>
+        <v>3414.5660188828</v>
       </c>
       <c r="O969" t="n">
-        <v>54633.05650196</v>
+        <v>40974.7922265936</v>
       </c>
       <c r="P969" t="n">
         <v>3500</v>
       </c>
       <c r="Q969" t="n">
-        <v>56000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="970">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="J971" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K971" t="n">
         <v>0</v>
@@ -43103,19 +43103,19 @@
         <v>0</v>
       </c>
       <c r="M971" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N971" t="n">
         <v>1230.77</v>
       </c>
       <c r="O971" t="n">
-        <v>354461.76</v>
+        <v>352000.22</v>
       </c>
       <c r="P971" t="n">
         <v>1600</v>
       </c>
       <c r="Q971" t="n">
-        <v>460800</v>
+        <v>457600</v>
       </c>
     </row>
     <row r="972">
@@ -43240,10 +43240,10 @@
         <v>1</v>
       </c>
       <c r="N974" t="n">
-        <v>1783.7988731104</v>
+        <v>1783.7988700046</v>
       </c>
       <c r="O974" t="n">
-        <v>1783.7988731104</v>
+        <v>1783.7988700046</v>
       </c>
       <c r="P974" t="n">
         <v>1500</v>
@@ -43272,7 +43272,7 @@
         </is>
       </c>
       <c r="J975" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K975" t="n">
         <v>0</v>
@@ -43281,19 +43281,19 @@
         <v>0</v>
       </c>
       <c r="M975" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="N975" t="n">
-        <v>460.04140858356</v>
+        <v>460.04140924819</v>
       </c>
       <c r="O975" t="n">
-        <v>166074.9484986652</v>
+        <v>164694.824510852</v>
       </c>
       <c r="P975" t="n">
         <v>600</v>
       </c>
       <c r="Q975" t="n">
-        <v>216600</v>
+        <v>214800</v>
       </c>
     </row>
     <row r="976">
@@ -44306,7 +44306,7 @@
         </is>
       </c>
       <c r="J997" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K997" t="n">
         <v>0</v>
@@ -44315,19 +44315,19 @@
         <v>0</v>
       </c>
       <c r="M997" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="N997" t="n">
-        <v>7046.9398269522</v>
+        <v>7046.9398267273</v>
       </c>
       <c r="O997" t="n">
-        <v>1261402.229024444</v>
+        <v>1226167.52985055</v>
       </c>
       <c r="P997" t="n">
         <v>9900</v>
       </c>
       <c r="Q997" t="n">
-        <v>1772100</v>
+        <v>1722600</v>
       </c>
     </row>
     <row r="998">
@@ -44352,7 +44352,7 @@
         </is>
       </c>
       <c r="J998" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K998" t="n">
         <v>0</v>
@@ -44361,19 +44361,19 @@
         <v>0</v>
       </c>
       <c r="M998" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N998" t="n">
         <v>24338.47</v>
       </c>
       <c r="O998" t="n">
-        <v>1874062.19</v>
+        <v>1825385.25</v>
       </c>
       <c r="P998" t="n">
         <v>27900</v>
       </c>
       <c r="Q998" t="n">
-        <v>2148300</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="999">
@@ -44396,7 +44396,7 @@
         </is>
       </c>
       <c r="J999" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K999" t="n">
         <v>0</v>
@@ -44405,19 +44405,19 @@
         <v>0</v>
       </c>
       <c r="M999" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N999" t="n">
         <v>10197</v>
       </c>
       <c r="O999" t="n">
-        <v>203940</v>
+        <v>101970</v>
       </c>
       <c r="P999" t="n">
         <v>14300</v>
       </c>
       <c r="Q999" t="n">
-        <v>286000</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="1000">
@@ -44544,10 +44544,10 @@
         <v>10</v>
       </c>
       <c r="N1002" t="n">
-        <v>44113.604171779</v>
+        <v>44113.604197531</v>
       </c>
       <c r="O1002" t="n">
-        <v>441136.04171779</v>
+        <v>441136.04197531</v>
       </c>
       <c r="P1002" t="n">
         <v>71900</v>
@@ -44581,7 +44581,7 @@
         </is>
       </c>
       <c r="J1003" t="n">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="K1003" t="n">
         <v>0</v>
@@ -44590,19 +44590,19 @@
         <v>0</v>
       </c>
       <c r="M1003" t="n">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="N1003" t="n">
         <v>1080.18</v>
       </c>
       <c r="O1003" t="n">
-        <v>651348.54</v>
+        <v>638386.38</v>
       </c>
       <c r="P1003" t="n">
         <v>4900</v>
       </c>
       <c r="Q1003" t="n">
-        <v>2954700</v>
+        <v>2895900</v>
       </c>
     </row>
     <row r="1004">
@@ -45075,10 +45075,10 @@
         <v>186</v>
       </c>
       <c r="N1013" t="n">
-        <v>430.60997550521</v>
+        <v>430.60997530864</v>
       </c>
       <c r="O1013" t="n">
-        <v>80093.45544396905</v>
+        <v>80093.45540740705</v>
       </c>
       <c r="P1013" t="n">
         <v>2200</v>
@@ -45161,7 +45161,7 @@
         </is>
       </c>
       <c r="J1015" t="n">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="K1015" t="n">
         <v>0</v>
@@ -45170,7 +45170,7 @@
         <v>0</v>
       </c>
       <c r="M1015" t="n">
-        <v>2367</v>
+        <v>2363</v>
       </c>
       <c r="N1015" t="n">
         <v>0</v>
@@ -45182,7 +45182,7 @@
         <v>6500</v>
       </c>
       <c r="Q1015" t="n">
-        <v>15385500</v>
+        <v>15359500</v>
       </c>
     </row>
     <row r="1016">
@@ -45498,7 +45498,7 @@
         </is>
       </c>
       <c r="J1023" t="n">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="K1023" t="n">
         <v>0</v>
@@ -45507,19 +45507,19 @@
         <v>0</v>
       </c>
       <c r="M1023" t="n">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="N1023" t="n">
-        <v>704.89694272446</v>
+        <v>704.89696969697</v>
       </c>
       <c r="O1023" t="n">
-        <v>271385.3229489171</v>
+        <v>264336.3636363638</v>
       </c>
       <c r="P1023" t="n">
         <v>900</v>
       </c>
       <c r="Q1023" t="n">
-        <v>346500</v>
+        <v>337500</v>
       </c>
     </row>
     <row r="1024">
@@ -45539,7 +45539,7 @@
         </is>
       </c>
       <c r="J1024" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="K1024" t="n">
         <v>0</v>
@@ -45548,19 +45548,19 @@
         <v>0</v>
       </c>
       <c r="M1024" t="n">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="N1024" t="n">
         <v>1153.85</v>
       </c>
       <c r="O1024" t="n">
-        <v>874618.2999999999</v>
+        <v>872310.6</v>
       </c>
       <c r="P1024" t="n">
         <v>1500</v>
       </c>
       <c r="Q1024" t="n">
-        <v>1137000</v>
+        <v>1134000</v>
       </c>
     </row>
     <row r="1025">
@@ -45794,7 +45794,7 @@
         </is>
       </c>
       <c r="J1030" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="K1030" t="n">
         <v>0</v>
@@ -45803,19 +45803,19 @@
         <v>0</v>
       </c>
       <c r="M1030" t="n">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N1030" t="n">
         <v>6761.25</v>
       </c>
       <c r="O1030" t="n">
-        <v>3353580</v>
+        <v>3346818.75</v>
       </c>
       <c r="P1030" t="n">
         <v>5200</v>
       </c>
       <c r="Q1030" t="n">
-        <v>2579200</v>
+        <v>2574000</v>
       </c>
     </row>
     <row r="1031">
@@ -46869,7 +46869,7 @@
         </is>
       </c>
       <c r="J1055" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="K1055" t="n">
         <v>0</v>
@@ -46878,19 +46878,19 @@
         <v>0</v>
       </c>
       <c r="M1055" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="N1055" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1055" t="n">
-        <v>948206.2000000001</v>
+        <v>900477.7000000001</v>
       </c>
       <c r="P1055" t="n">
         <v>5100</v>
       </c>
       <c r="Q1055" t="n">
-        <v>1519800</v>
+        <v>1443300</v>
       </c>
     </row>
     <row r="1056">
@@ -47171,7 +47171,7 @@
         </is>
       </c>
       <c r="J1062" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="K1062" t="n">
         <v>0</v>
@@ -47180,19 +47180,19 @@
         <v>0</v>
       </c>
       <c r="M1062" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N1062" t="n">
-        <v>2830.2251796407</v>
+        <v>2830.2252424242</v>
       </c>
       <c r="O1062" t="n">
-        <v>260380.7165269444</v>
+        <v>249059.8213333296</v>
       </c>
       <c r="P1062" t="n">
         <v>2400</v>
       </c>
       <c r="Q1062" t="n">
-        <v>220800</v>
+        <v>211200</v>
       </c>
     </row>
     <row r="1063">
@@ -47359,10 +47359,10 @@
         <v>29</v>
       </c>
       <c r="N1066" t="n">
-        <v>2523.3377368123</v>
+        <v>2523.3377355278</v>
       </c>
       <c r="O1066" t="n">
-        <v>73176.79436755671</v>
+        <v>73176.79433030619</v>
       </c>
       <c r="P1066" t="n">
         <v>2800</v>
@@ -47637,7 +47637,7 @@
         </is>
       </c>
       <c r="J1073" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K1073" t="n">
         <v>0</v>
@@ -47646,19 +47646,19 @@
         <v>0</v>
       </c>
       <c r="M1073" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N1073" t="n">
         <v>4538.46</v>
       </c>
       <c r="O1073" t="n">
-        <v>372153.72</v>
+        <v>363076.8</v>
       </c>
       <c r="P1073" t="n">
         <v>5900</v>
       </c>
       <c r="Q1073" t="n">
-        <v>483800</v>
+        <v>472000</v>
       </c>
     </row>
     <row r="1074">
@@ -48023,7 +48023,7 @@
         </is>
       </c>
       <c r="J1082" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="K1082" t="n">
         <v>0</v>
@@ -48032,19 +48032,19 @@
         <v>0</v>
       </c>
       <c r="M1082" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N1082" t="n">
         <v>5077</v>
       </c>
       <c r="O1082" t="n">
-        <v>228465</v>
+        <v>203080</v>
       </c>
       <c r="P1082" t="n">
         <v>8500</v>
       </c>
       <c r="Q1082" t="n">
-        <v>382500</v>
+        <v>340000</v>
       </c>
     </row>
     <row r="1083">
@@ -48064,7 +48064,7 @@
         </is>
       </c>
       <c r="J1083" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="K1083" t="n">
         <v>0</v>
@@ -48073,19 +48073,19 @@
         <v>0</v>
       </c>
       <c r="M1083" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="N1083" t="n">
         <v>923.08</v>
       </c>
       <c r="O1083" t="n">
-        <v>176308.28</v>
+        <v>172615.96</v>
       </c>
       <c r="P1083" t="n">
         <v>1200</v>
       </c>
       <c r="Q1083" t="n">
-        <v>229200</v>
+        <v>224400</v>
       </c>
     </row>
     <row r="1084">
@@ -48209,10 +48209,10 @@
         <v>67</v>
       </c>
       <c r="N1086" t="n">
-        <v>4985.4070588235</v>
+        <v>4985.4075471698</v>
       </c>
       <c r="O1086" t="n">
-        <v>334022.2729411745</v>
+        <v>334022.3056603766</v>
       </c>
       <c r="P1086" t="n">
         <v>7900</v>
@@ -48558,7 +48558,7 @@
         </is>
       </c>
       <c r="J1094" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K1094" t="n">
         <v>0</v>
@@ -48567,19 +48567,19 @@
         <v>0</v>
       </c>
       <c r="M1094" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N1094" t="n">
         <v>2500</v>
       </c>
       <c r="O1094" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="P1094" t="n">
         <v>3000</v>
       </c>
       <c r="Q1094" t="n">
-        <v>24000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1095">
@@ -48926,7 +48926,7 @@
         </is>
       </c>
       <c r="J1102" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K1102" t="n">
         <v>0</v>
@@ -48935,19 +48935,19 @@
         <v>0</v>
       </c>
       <c r="M1102" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N1102" t="n">
-        <v>1160.1556923077</v>
+        <v>1160.1569811321</v>
       </c>
       <c r="O1102" t="n">
-        <v>33644.5150769233</v>
+        <v>19722.6686792457</v>
       </c>
       <c r="P1102" t="n">
         <v>1600</v>
       </c>
       <c r="Q1102" t="n">
-        <v>46400</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="1103">
@@ -49156,7 +49156,7 @@
         </is>
       </c>
       <c r="J1107" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K1107" t="n">
         <v>0</v>
@@ -49165,19 +49165,19 @@
         <v>0</v>
       </c>
       <c r="M1107" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="N1107" t="n">
         <v>3872</v>
       </c>
       <c r="O1107" t="n">
-        <v>325248</v>
+        <v>313632</v>
       </c>
       <c r="P1107" t="n">
         <v>4900</v>
       </c>
       <c r="Q1107" t="n">
-        <v>411600</v>
+        <v>396900</v>
       </c>
     </row>
     <row r="1108">
@@ -49202,7 +49202,7 @@
         </is>
       </c>
       <c r="J1108" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K1108" t="n">
         <v>0</v>
@@ -49211,19 +49211,19 @@
         <v>0</v>
       </c>
       <c r="M1108" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N1108" t="n">
         <v>4400</v>
       </c>
       <c r="O1108" t="n">
-        <v>228800</v>
+        <v>224400</v>
       </c>
       <c r="P1108" t="n">
         <v>5900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>306800</v>
+        <v>300900</v>
       </c>
     </row>
     <row r="1109">
@@ -49248,7 +49248,7 @@
         </is>
       </c>
       <c r="J1109" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K1109" t="n">
         <v>0</v>
@@ -49257,19 +49257,19 @@
         <v>0</v>
       </c>
       <c r="M1109" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N1109" t="n">
         <v>6160</v>
       </c>
       <c r="O1109" t="n">
-        <v>1774080</v>
+        <v>1767920</v>
       </c>
       <c r="P1109" t="n">
         <v>7500</v>
       </c>
       <c r="Q1109" t="n">
-        <v>2160000</v>
+        <v>2152500</v>
       </c>
     </row>
     <row r="1110">
@@ -49297,7 +49297,7 @@
         </is>
       </c>
       <c r="J1110" t="n">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="K1110" t="n">
         <v>0</v>
@@ -49306,19 +49306,19 @@
         <v>0</v>
       </c>
       <c r="M1110" t="n">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="N1110" t="n">
         <v>1056</v>
       </c>
       <c r="O1110" t="n">
-        <v>1221792</v>
+        <v>1209120</v>
       </c>
       <c r="P1110" t="n">
         <v>1400</v>
       </c>
       <c r="Q1110" t="n">
-        <v>1619800</v>
+        <v>1603000</v>
       </c>
     </row>
     <row r="1111">
@@ -49346,7 +49346,7 @@
         </is>
       </c>
       <c r="J1111" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K1111" t="n">
         <v>0</v>
@@ -49355,19 +49355,19 @@
         <v>0</v>
       </c>
       <c r="M1111" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N1111" t="n">
         <v>7920</v>
       </c>
       <c r="O1111" t="n">
-        <v>1124640</v>
+        <v>1100880</v>
       </c>
       <c r="P1111" t="n">
         <v>10500</v>
       </c>
       <c r="Q1111" t="n">
-        <v>1491000</v>
+        <v>1459500</v>
       </c>
     </row>
     <row r="1112">
@@ -49395,7 +49395,7 @@
         </is>
       </c>
       <c r="J1112" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="K1112" t="n">
         <v>0</v>
@@ -49404,19 +49404,19 @@
         <v>0</v>
       </c>
       <c r="M1112" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="N1112" t="n">
         <v>7920</v>
       </c>
       <c r="O1112" t="n">
-        <v>966240</v>
+        <v>863280</v>
       </c>
       <c r="P1112" t="n">
         <v>10500</v>
       </c>
       <c r="Q1112" t="n">
-        <v>1281000</v>
+        <v>1144500</v>
       </c>
     </row>
     <row r="1113">
@@ -49533,7 +49533,7 @@
         </is>
       </c>
       <c r="J1115" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="K1115" t="n">
         <v>0</v>
@@ -49542,19 +49542,19 @@
         <v>0</v>
       </c>
       <c r="M1115" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="N1115" t="n">
         <v>9240</v>
       </c>
       <c r="O1115" t="n">
-        <v>2328480</v>
+        <v>2254560</v>
       </c>
       <c r="P1115" t="n">
         <v>11500</v>
       </c>
       <c r="Q1115" t="n">
-        <v>2898000</v>
+        <v>2806000</v>
       </c>
     </row>
     <row r="1116">
@@ -49579,7 +49579,7 @@
         </is>
       </c>
       <c r="J1116" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K1116" t="n">
         <v>0</v>
@@ -49588,19 +49588,19 @@
         <v>0</v>
       </c>
       <c r="M1116" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N1116" t="n">
         <v>2288</v>
       </c>
       <c r="O1116" t="n">
-        <v>107536</v>
+        <v>96096</v>
       </c>
       <c r="P1116" t="n">
         <v>2900</v>
       </c>
       <c r="Q1116" t="n">
-        <v>136300</v>
+        <v>121800</v>
       </c>
     </row>
     <row r="1117">
@@ -49625,7 +49625,7 @@
         </is>
       </c>
       <c r="J1117" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="K1117" t="n">
         <v>0</v>
@@ -49634,19 +49634,19 @@
         <v>0</v>
       </c>
       <c r="M1117" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="N1117" t="n">
         <v>4576</v>
       </c>
       <c r="O1117" t="n">
-        <v>228800</v>
+        <v>109824</v>
       </c>
       <c r="P1117" t="n">
         <v>5900</v>
       </c>
       <c r="Q1117" t="n">
-        <v>295000</v>
+        <v>141600</v>
       </c>
     </row>
     <row r="1118">
@@ -49855,7 +49855,7 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
@@ -49864,19 +49864,19 @@
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1122" t="n">
         <v>9500</v>
       </c>
       <c r="O1122" t="n">
-        <v>19000</v>
+        <v>9500</v>
       </c>
       <c r="P1122" t="n">
         <v>11400</v>
       </c>
       <c r="Q1122" t="n">
-        <v>22800</v>
+        <v>11400</v>
       </c>
     </row>
     <row r="1123">
@@ -50085,7 +50085,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -50094,19 +50094,19 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N1127" t="n">
         <v>2900</v>
       </c>
       <c r="O1127" t="n">
-        <v>110200</v>
+        <v>104400</v>
       </c>
       <c r="P1127" t="n">
         <v>3500</v>
       </c>
       <c r="Q1127" t="n">
-        <v>133000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1128">
@@ -50131,7 +50131,7 @@
         </is>
       </c>
       <c r="J1128" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K1128" t="n">
         <v>0</v>
@@ -50140,19 +50140,19 @@
         <v>0</v>
       </c>
       <c r="M1128" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N1128" t="n">
         <v>1000</v>
       </c>
       <c r="O1128" t="n">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="P1128" t="n">
         <v>1200</v>
       </c>
       <c r="Q1128" t="n">
-        <v>34800</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="1129">
@@ -50269,7 +50269,7 @@
         </is>
       </c>
       <c r="J1131" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K1131" t="n">
         <v>0</v>
@@ -50278,19 +50278,19 @@
         <v>0</v>
       </c>
       <c r="M1131" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N1131" t="n">
         <v>4500</v>
       </c>
       <c r="O1131" t="n">
-        <v>58500</v>
+        <v>49500</v>
       </c>
       <c r="P1131" t="n">
         <v>5400</v>
       </c>
       <c r="Q1131" t="n">
-        <v>70200</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="1132">
@@ -50315,7 +50315,7 @@
         </is>
       </c>
       <c r="J1132" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K1132" t="n">
         <v>0</v>
@@ -50324,19 +50324,19 @@
         <v>0</v>
       </c>
       <c r="M1132" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N1132" t="n">
         <v>2700</v>
       </c>
       <c r="O1132" t="n">
-        <v>145800</v>
+        <v>143100</v>
       </c>
       <c r="P1132" t="n">
         <v>3300</v>
       </c>
       <c r="Q1132" t="n">
-        <v>178200</v>
+        <v>174900</v>
       </c>
     </row>
     <row r="1133">
@@ -50816,7 +50816,7 @@
         </is>
       </c>
       <c r="J1143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K1143" t="n">
         <v>0</v>
@@ -50825,30 +50825,30 @@
         <v>0</v>
       </c>
       <c r="M1143" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1143" t="n">
         <v>6500</v>
       </c>
       <c r="O1143" t="n">
-        <v>39000</v>
+        <v>26000</v>
       </c>
       <c r="P1143" t="n">
         <v>7800</v>
       </c>
       <c r="Q1143" t="n">
-        <v>46800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>MC121206-E</t>
+          <t>MC121212</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>SET DE LAPICES CON BORRADOR  MC121206-E</t>
+          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
         </is>
       </c>
       <c r="E1144" t="inlineStr">
@@ -50862,7 +50862,7 @@
         </is>
       </c>
       <c r="J1144" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K1144" t="n">
         <v>0</v>
@@ -50871,35 +50871,35 @@
         <v>0</v>
       </c>
       <c r="M1144" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N1144" t="n">
         <v>6500</v>
       </c>
       <c r="O1144" t="n">
-        <v>32500</v>
+        <v>78000</v>
       </c>
       <c r="P1144" t="n">
         <v>7800</v>
       </c>
       <c r="Q1144" t="n">
-        <v>39000</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>MC121212</t>
+          <t>MG21714</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>SET LAPIZ CON BORRADOR Y TAJALAPIZ ROBOT MC121212</t>
+          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
         </is>
       </c>
       <c r="E1145" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECO</t>
         </is>
       </c>
       <c r="I1145" t="inlineStr">
@@ -50908,7 +50908,7 @@
         </is>
       </c>
       <c r="J1145" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1145" t="n">
         <v>0</v>
@@ -50917,35 +50917,35 @@
         <v>0</v>
       </c>
       <c r="M1145" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N1145" t="n">
-        <v>6500</v>
+        <v>576.58</v>
       </c>
       <c r="O1145" t="n">
-        <v>104000</v>
+        <v>9801.860000000001</v>
       </c>
       <c r="P1145" t="n">
-        <v>7800</v>
+        <v>5900</v>
       </c>
       <c r="Q1145" t="n">
-        <v>124800</v>
+        <v>100300</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>MG21714</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t>SET MILITAR CON MOTO BOLSA PVC MED MG21714</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E1146" t="inlineStr">
         <is>
-          <t>MUÑECO</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1146" t="inlineStr">
@@ -50954,7 +50954,7 @@
         </is>
       </c>
       <c r="J1146" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K1146" t="n">
         <v>0</v>
@@ -50963,35 +50963,40 @@
         <v>0</v>
       </c>
       <c r="M1146" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N1146" t="n">
-        <v>576.58</v>
+        <v>8174.05</v>
       </c>
       <c r="O1146" t="n">
-        <v>9801.860000000001</v>
+        <v>8174.05</v>
       </c>
       <c r="P1146" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q1146" t="n">
-        <v>100300</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E1147" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I1147" t="inlineStr">
@@ -51012,37 +51017,32 @@
         <v>1</v>
       </c>
       <c r="N1147" t="n">
-        <v>8174.05</v>
+        <v>751.45</v>
       </c>
       <c r="O1147" t="n">
-        <v>8174.05</v>
+        <v>751.45</v>
       </c>
       <c r="P1147" t="n">
-        <v>8900</v>
+        <v>2500</v>
       </c>
       <c r="Q1147" t="n">
-        <v>8900</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B1148" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG40207</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>SONAJERO DOBLE HELICE MG40207</t>
         </is>
       </c>
       <c r="E1148" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1148" t="inlineStr">
@@ -51063,32 +51063,32 @@
         <v>1</v>
       </c>
       <c r="N1148" t="n">
-        <v>751.45</v>
+        <v>323.9775</v>
       </c>
       <c r="O1148" t="n">
-        <v>751.45</v>
+        <v>323.9775</v>
       </c>
       <c r="P1148" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="Q1148" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>MG40207</t>
+          <t>MG40226</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>SONAJERO DOBLE HELICE MG40207</t>
+          <t>ATARY COCODRILO MG40226</t>
         </is>
       </c>
       <c r="E1149" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1149" t="inlineStr">
@@ -51097,7 +51097,7 @@
         </is>
       </c>
       <c r="J1149" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1149" t="n">
         <v>0</v>
@@ -51106,35 +51106,35 @@
         <v>0</v>
       </c>
       <c r="M1149" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N1149" t="n">
-        <v>323.9775</v>
+        <v>310.4175</v>
       </c>
       <c r="O1149" t="n">
-        <v>323.9775</v>
+        <v>1862.505</v>
       </c>
       <c r="P1149" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="Q1149" t="n">
-        <v>1500</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>MG40226</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>ATARY COCODRILO MG40226</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1150" t="inlineStr">
@@ -51143,7 +51143,7 @@
         </is>
       </c>
       <c r="J1150" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="K1150" t="n">
         <v>0</v>
@@ -51152,35 +51152,35 @@
         <v>0</v>
       </c>
       <c r="M1150" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="N1150" t="n">
-        <v>310.4175</v>
+        <v>227.41614285714</v>
       </c>
       <c r="O1150" t="n">
-        <v>1862.505</v>
+        <v>17965.87528571406</v>
       </c>
       <c r="P1150" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="Q1150" t="n">
-        <v>10800</v>
+        <v>94800</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40836</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MUÑECO GUERRERO BOLSA MG40836</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MUÑECOS</t>
         </is>
       </c>
       <c r="I1151" t="inlineStr">
@@ -51189,7 +51189,7 @@
         </is>
       </c>
       <c r="J1151" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K1151" t="n">
         <v>0</v>
@@ -51198,35 +51198,40 @@
         <v>0</v>
       </c>
       <c r="M1151" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N1151" t="n">
-        <v>227.41614285714</v>
+        <v>1441.78</v>
       </c>
       <c r="O1151" t="n">
-        <v>17965.87528571406</v>
+        <v>116784.18</v>
       </c>
       <c r="P1151" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="Q1151" t="n">
-        <v>94800</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>MG40836</t>
+          <t>MG40952</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>MG40952</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>MUÑECO GUERRERO BOLSA MG40836</t>
+          <t>CAMIONETA BLACK MG40952</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
         <is>
-          <t>MUÑECOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1152" t="inlineStr">
@@ -51235,7 +51240,7 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -51244,45 +51249,35 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="N1152" t="n">
-        <v>1441.78</v>
+        <v>38043.57</v>
       </c>
       <c r="O1152" t="n">
-        <v>116784.18</v>
+        <v>38043.57</v>
       </c>
       <c r="P1152" t="n">
-        <v>2400</v>
+        <v>70900</v>
       </c>
       <c r="Q1152" t="n">
-        <v>194400</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>MG40952</t>
-        </is>
-      </c>
-      <c r="B1153" t="inlineStr">
-        <is>
-          <t>MG40952</t>
+          <t>P155</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>CAMIONETA BLACK MG40952</t>
-        </is>
-      </c>
-      <c r="E1153" t="inlineStr">
-        <is>
-          <t>CARROS</t>
+          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
         </is>
       </c>
       <c r="I1153" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1153" t="n">
@@ -51298,27 +51293,27 @@
         <v>1</v>
       </c>
       <c r="N1153" t="n">
-        <v>38043.57</v>
+        <v>1461.53</v>
       </c>
       <c r="O1153" t="n">
-        <v>38043.57</v>
+        <v>1461.53</v>
       </c>
       <c r="P1153" t="n">
-        <v>70900</v>
+        <v>1900</v>
       </c>
       <c r="Q1153" t="n">
-        <v>70900</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>P155</t>
+          <t>P214</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
+          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
         </is>
       </c>
       <c r="I1154" t="inlineStr">
@@ -51339,27 +51334,27 @@
         <v>1</v>
       </c>
       <c r="N1154" t="n">
-        <v>1461.53</v>
+        <v>3153.85</v>
       </c>
       <c r="O1154" t="n">
-        <v>1461.53</v>
+        <v>3153.85</v>
       </c>
       <c r="P1154" t="n">
-        <v>1900</v>
+        <v>4100</v>
       </c>
       <c r="Q1154" t="n">
-        <v>1900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>P214</t>
+          <t>P458</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
+          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
         </is>
       </c>
       <c r="I1155" t="inlineStr">
@@ -51368,7 +51363,7 @@
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
@@ -51377,39 +51372,44 @@
         <v>0</v>
       </c>
       <c r="M1155" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N1155" t="n">
-        <v>3153.85</v>
+        <v>1230.76</v>
       </c>
       <c r="O1155" t="n">
-        <v>3153.85</v>
+        <v>39384.32</v>
       </c>
       <c r="P1155" t="n">
-        <v>4100</v>
+        <v>1600</v>
       </c>
       <c r="Q1155" t="n">
-        <v>4100</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>P458</t>
+          <t>PT14026</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
+          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1156" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1156" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K1156" t="n">
         <v>0</v>
@@ -51418,44 +51418,39 @@
         <v>0</v>
       </c>
       <c r="M1156" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N1156" t="n">
-        <v>1230.76</v>
+        <v>2690.69</v>
       </c>
       <c r="O1156" t="n">
-        <v>39384.32</v>
+        <v>2690.69</v>
       </c>
       <c r="P1156" t="n">
-        <v>1600</v>
+        <v>5900</v>
       </c>
       <c r="Q1156" t="n">
-        <v>51200</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>PT14026</t>
+          <t>Q1241</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
-        </is>
-      </c>
-      <c r="E1157" t="inlineStr">
-        <is>
-          <t>DIDACTICOS</t>
+          <t>RESALTADOR BOTELLA</t>
         </is>
       </c>
       <c r="I1157" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -51464,39 +51459,44 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1157" t="n">
-        <v>2690.69</v>
+        <v>5000</v>
       </c>
       <c r="O1157" t="n">
-        <v>2690.69</v>
+        <v>15000</v>
       </c>
       <c r="P1157" t="n">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="Q1157" t="n">
-        <v>5900</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>Q1241</t>
+          <t>QH-8308</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>RESALTADOR BOTELLA</t>
+          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1158" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
@@ -51505,30 +51505,30 @@
         <v>0</v>
       </c>
       <c r="M1158" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N1158" t="n">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="O1158" t="n">
-        <v>15000</v>
+        <v>26400</v>
       </c>
       <c r="P1158" t="n">
-        <v>6000</v>
+        <v>2700</v>
       </c>
       <c r="Q1158" t="n">
-        <v>18000</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>QH-8308</t>
+          <t>QH-8311</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+          <t>SET BORRADORES ANIMALES QH-8311</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
@@ -51542,7 +51542,7 @@
         </is>
       </c>
       <c r="J1159" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K1159" t="n">
         <v>0</v>
@@ -51551,30 +51551,30 @@
         <v>0</v>
       </c>
       <c r="M1159" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N1159" t="n">
         <v>2200</v>
       </c>
       <c r="O1159" t="n">
-        <v>26400</v>
+        <v>19800</v>
       </c>
       <c r="P1159" t="n">
         <v>2700</v>
       </c>
       <c r="Q1159" t="n">
-        <v>32400</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>QH-8311</t>
+          <t>QH-8314</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>SET BORRADORES ANIMALES QH-8311</t>
+          <t>SET BORRADORES DEPORTES QH-8314</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
@@ -51588,7 +51588,7 @@
         </is>
       </c>
       <c r="J1160" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K1160" t="n">
         <v>0</v>
@@ -51597,30 +51597,30 @@
         <v>0</v>
       </c>
       <c r="M1160" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N1160" t="n">
         <v>2200</v>
       </c>
       <c r="O1160" t="n">
-        <v>24200</v>
+        <v>35200</v>
       </c>
       <c r="P1160" t="n">
         <v>2700</v>
       </c>
       <c r="Q1160" t="n">
-        <v>29700</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>QH-8314</t>
+          <t>QH-8317</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>SET BORRADORES DEPORTES QH-8314</t>
+          <t>SET BORRADORES POSTRES QH-8317</t>
         </is>
       </c>
       <c r="E1161" t="inlineStr">
@@ -51634,7 +51634,7 @@
         </is>
       </c>
       <c r="J1161" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K1161" t="n">
         <v>0</v>
@@ -51643,30 +51643,30 @@
         <v>0</v>
       </c>
       <c r="M1161" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N1161" t="n">
         <v>2200</v>
       </c>
       <c r="O1161" t="n">
-        <v>39600</v>
+        <v>15400</v>
       </c>
       <c r="P1161" t="n">
         <v>2700</v>
       </c>
       <c r="Q1161" t="n">
-        <v>48600</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>QH-8317</t>
+          <t>QH-8385</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>SET BORRADORES POSTRES QH-8317</t>
+          <t>SET BORRADORES ESPACIAL QH-8385</t>
         </is>
       </c>
       <c r="E1162" t="inlineStr">
@@ -51680,7 +51680,7 @@
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51689,30 +51689,30 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N1162" t="n">
         <v>2200</v>
       </c>
       <c r="O1162" t="n">
-        <v>19800</v>
+        <v>4400</v>
       </c>
       <c r="P1162" t="n">
         <v>2700</v>
       </c>
       <c r="Q1162" t="n">
-        <v>24300</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>QH-8385</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>SET BORRADORES ESPACIAL QH-8385</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
@@ -51726,7 +51726,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51735,30 +51735,30 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="N1163" t="n">
         <v>2200</v>
       </c>
       <c r="O1163" t="n">
-        <v>4400</v>
+        <v>158400</v>
       </c>
       <c r="P1163" t="n">
         <v>2700</v>
       </c>
       <c r="Q1163" t="n">
-        <v>5400</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QQ-1503</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
@@ -51772,7 +51772,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51781,30 +51781,30 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N1164" t="n">
         <v>2200</v>
       </c>
       <c r="O1164" t="n">
-        <v>158400</v>
+        <v>151800</v>
       </c>
       <c r="P1164" t="n">
         <v>2700</v>
       </c>
       <c r="Q1164" t="n">
-        <v>194400</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>QQ-1525</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
@@ -51818,7 +51818,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51827,30 +51827,30 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N1165" t="n">
         <v>2200</v>
       </c>
       <c r="O1165" t="n">
-        <v>151800</v>
+        <v>154000</v>
       </c>
       <c r="P1165" t="n">
         <v>2700</v>
       </c>
       <c r="Q1165" t="n">
-        <v>186300</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
@@ -51864,7 +51864,7 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -51873,30 +51873,30 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="N1166" t="n">
-        <v>2200</v>
+        <v>5026.665826087</v>
       </c>
       <c r="O1166" t="n">
-        <v>154000</v>
+        <v>70373.32156521799</v>
       </c>
       <c r="P1166" t="n">
-        <v>2700</v>
+        <v>6300</v>
       </c>
       <c r="Q1166" t="n">
-        <v>189000</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
@@ -51910,7 +51910,7 @@
         </is>
       </c>
       <c r="J1167" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K1167" t="n">
         <v>0</v>
@@ -51919,30 +51919,30 @@
         <v>0</v>
       </c>
       <c r="M1167" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N1167" t="n">
-        <v>5026.665826087</v>
+        <v>5200</v>
       </c>
       <c r="O1167" t="n">
-        <v>70373.32156521799</v>
+        <v>78000</v>
       </c>
       <c r="P1167" t="n">
         <v>6300</v>
       </c>
       <c r="Q1167" t="n">
-        <v>88200</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>QT512452-E</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
@@ -51956,7 +51956,7 @@
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -51965,30 +51965,30 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N1168" t="n">
-        <v>5200</v>
+        <v>8800</v>
       </c>
       <c r="O1168" t="n">
-        <v>78000</v>
+        <v>149600</v>
       </c>
       <c r="P1168" t="n">
-        <v>6300</v>
+        <v>10600</v>
       </c>
       <c r="Q1168" t="n">
-        <v>94500</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>QT512452-E</t>
+          <t>QT512453-E</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
@@ -52029,26 +52029,21 @@
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>S145</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
-        </is>
-      </c>
-      <c r="E1170" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -52057,39 +52052,44 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N1170" t="n">
-        <v>8800</v>
+        <v>11538.4</v>
       </c>
       <c r="O1170" t="n">
-        <v>149600</v>
+        <v>11538.4</v>
       </c>
       <c r="P1170" t="n">
-        <v>10600</v>
+        <v>15000</v>
       </c>
       <c r="Q1170" t="n">
-        <v>180200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>S145</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1171" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -52098,30 +52098,30 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="N1171" t="n">
-        <v>11538.4</v>
+        <v>4550</v>
       </c>
       <c r="O1171" t="n">
-        <v>11538.4</v>
+        <v>1160250</v>
       </c>
       <c r="P1171" t="n">
-        <v>15000</v>
+        <v>5500</v>
       </c>
       <c r="Q1171" t="n">
-        <v>15000</v>
+        <v>1402500</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
@@ -52135,7 +52135,7 @@
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -52144,44 +52144,39 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>255</v>
+        <v>8</v>
       </c>
       <c r="N1172" t="n">
-        <v>4550</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O1172" t="n">
-        <v>1160250</v>
+        <v>8473.4781818184</v>
       </c>
       <c r="P1172" t="n">
-        <v>5500</v>
+        <v>9500</v>
       </c>
       <c r="Q1172" t="n">
-        <v>1402500</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>SY-661-A08</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
-        </is>
-      </c>
-      <c r="E1173" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RESALTADOR SUPER HEROES</t>
         </is>
       </c>
       <c r="I1173" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
@@ -52190,30 +52185,30 @@
         <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N1173" t="n">
-        <v>1059.1847727273</v>
+        <v>7500</v>
       </c>
       <c r="O1173" t="n">
-        <v>8473.4781818184</v>
+        <v>45000</v>
       </c>
       <c r="P1173" t="n">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>76000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>SY-661-A08</t>
+          <t>SY-661-A09</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER HEROES</t>
+          <t>RESALTADOR SUPER MARIO</t>
         </is>
       </c>
       <c r="I1174" t="inlineStr">
@@ -52222,7 +52217,7 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
@@ -52231,39 +52226,44 @@
         <v>0</v>
       </c>
       <c r="M1174" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N1174" t="n">
         <v>7500</v>
       </c>
       <c r="O1174" t="n">
-        <v>45000</v>
+        <v>105000</v>
       </c>
       <c r="P1174" t="n">
         <v>9000</v>
       </c>
       <c r="Q1174" t="n">
-        <v>54000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>SY-661-A09</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER MARIO</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1175" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K1175" t="n">
         <v>0</v>
@@ -52272,30 +52272,30 @@
         <v>0</v>
       </c>
       <c r="M1175" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N1175" t="n">
-        <v>7500</v>
+        <v>12392.16</v>
       </c>
       <c r="O1175" t="n">
-        <v>105000</v>
+        <v>24784.32</v>
       </c>
       <c r="P1175" t="n">
-        <v>9000</v>
+        <v>15900</v>
       </c>
       <c r="Q1175" t="n">
-        <v>126000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
@@ -52321,27 +52321,27 @@
         <v>2</v>
       </c>
       <c r="N1176" t="n">
-        <v>12392.16</v>
+        <v>5186.45</v>
       </c>
       <c r="O1176" t="n">
-        <v>24784.32</v>
+        <v>10372.9</v>
       </c>
       <c r="P1176" t="n">
-        <v>15900</v>
+        <v>7200</v>
       </c>
       <c r="Q1176" t="n">
-        <v>31800</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T219</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
@@ -52355,7 +52355,7 @@
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
@@ -52364,44 +52364,39 @@
         <v>0</v>
       </c>
       <c r="M1177" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N1177" t="n">
-        <v>5186.45</v>
+        <v>8746.92</v>
       </c>
       <c r="O1177" t="n">
-        <v>10372.9</v>
+        <v>87469.2</v>
       </c>
       <c r="P1177" t="n">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="Q1177" t="n">
-        <v>14400</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>T219</t>
+          <t>WT-E170</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
-        </is>
-      </c>
-      <c r="E1178" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
         </is>
       </c>
       <c r="I1178" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
@@ -52410,39 +52405,44 @@
         <v>0</v>
       </c>
       <c r="M1178" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N1178" t="n">
-        <v>8746.92</v>
+        <v>73405.77</v>
       </c>
       <c r="O1178" t="n">
-        <v>87469.2</v>
+        <v>367028.85</v>
       </c>
       <c r="P1178" t="n">
-        <v>11000</v>
+        <v>77900</v>
       </c>
       <c r="Q1178" t="n">
-        <v>110000</v>
+        <v>389500</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>WT-E170</t>
+          <t>XP-2984</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
+          <t>BORRADOR RETRACTIL XP-2984</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1179" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
@@ -52451,30 +52451,30 @@
         <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="N1179" t="n">
-        <v>73405.77</v>
+        <v>2403.9768595041</v>
       </c>
       <c r="O1179" t="n">
-        <v>367028.85</v>
+        <v>88947.14380165171</v>
       </c>
       <c r="P1179" t="n">
-        <v>77900</v>
+        <v>3000</v>
       </c>
       <c r="Q1179" t="n">
-        <v>389500</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>XP-2984</t>
+          <t>XP-2986</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL XP-2984</t>
+          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
@@ -52500,10 +52500,10 @@
         <v>43</v>
       </c>
       <c r="N1180" t="n">
-        <v>2403.977007874</v>
+        <v>2402.6741007194</v>
       </c>
       <c r="O1180" t="n">
-        <v>103371.011338582</v>
+        <v>103314.9863309342</v>
       </c>
       <c r="P1180" t="n">
         <v>3000</v>
@@ -52515,26 +52515,21 @@
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>XP-2986</t>
+          <t>YOYO2001</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
-        </is>
-      </c>
-      <c r="E1181" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ZET LAPIZ</t>
         </is>
       </c>
       <c r="I1181" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
@@ -52543,59 +52538,18 @@
         <v>0</v>
       </c>
       <c r="M1181" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1181" t="n">
-        <v>2402.6741007194</v>
+        <v>6000</v>
       </c>
       <c r="O1181" t="n">
-        <v>103314.9863309342</v>
+        <v>246000</v>
       </c>
       <c r="P1181" t="n">
-        <v>3000</v>
+        <v>7200</v>
       </c>
       <c r="Q1181" t="n">
-        <v>129000</v>
-      </c>
-    </row>
-    <row r="1182">
-      <c r="A1182" t="inlineStr">
-        <is>
-          <t>YOYO2001</t>
-        </is>
-      </c>
-      <c r="C1182" t="inlineStr">
-        <is>
-          <t>ZET LAPIZ</t>
-        </is>
-      </c>
-      <c r="I1182" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J1182" t="n">
-        <v>41</v>
-      </c>
-      <c r="K1182" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1182" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1182" t="n">
-        <v>41</v>
-      </c>
-      <c r="N1182" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O1182" t="n">
-        <v>246000</v>
-      </c>
-      <c r="P1182" t="n">
-        <v>7200</v>
-      </c>
-      <c r="Q1182" t="n">
         <v>295200</v>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -18365,10 +18365,10 @@
         <v>43</v>
       </c>
       <c r="N418" t="n">
-        <v>1302.8935476464</v>
+        <v>1301.3994029851</v>
       </c>
       <c r="O418" t="n">
-        <v>56024.42254879521</v>
+        <v>55960.1743283593</v>
       </c>
       <c r="P418" t="n">
         <v>2000</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1301,22 +1301,22 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="O22" t="n">
-        <v>537958.8893276532</v>
+        <v>525453.6249190893</v>
       </c>
       <c r="P22" t="n">
         <v>2600</v>
       </c>
       <c r="Q22" t="n">
-        <v>772200</v>
+        <v>746200</v>
       </c>
     </row>
     <row r="23">
@@ -2840,10 +2840,10 @@
         <v>35</v>
       </c>
       <c r="N60" t="n">
-        <v>6272.8551705566</v>
+        <v>6272.8551798561</v>
       </c>
       <c r="O60" t="n">
-        <v>219549.930969481</v>
+        <v>219549.9312949635</v>
       </c>
       <c r="P60" t="n">
         <v>7900</v>
@@ -3703,22 +3703,22 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M82" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N82" t="n">
         <v>31409.32</v>
       </c>
       <c r="O82" t="n">
-        <v>565367.76</v>
+        <v>471139.8</v>
       </c>
       <c r="P82" t="n">
         <v>45500</v>
       </c>
       <c r="Q82" t="n">
-        <v>819000</v>
+        <v>682500</v>
       </c>
     </row>
     <row r="83">
@@ -4891,22 +4891,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N109" t="n">
         <v>36762.36</v>
       </c>
       <c r="O109" t="n">
-        <v>294098.88</v>
+        <v>257336.52</v>
       </c>
       <c r="P109" t="n">
         <v>57100</v>
       </c>
       <c r="Q109" t="n">
-        <v>456800</v>
+        <v>399700</v>
       </c>
     </row>
     <row r="110">
@@ -4980,22 +4980,22 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N111" t="n">
-        <v>9392.0756666667</v>
+        <v>9392.075964912299</v>
       </c>
       <c r="O111" t="n">
-        <v>103312.8323333337</v>
+        <v>75136.60771929839</v>
       </c>
       <c r="P111" t="n">
         <v>18500</v>
       </c>
       <c r="Q111" t="n">
-        <v>203500</v>
+        <v>148000</v>
       </c>
     </row>
     <row r="112">
@@ -5269,22 +5269,22 @@
         <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N118" t="n">
         <v>20195.32</v>
       </c>
       <c r="O118" t="n">
-        <v>282734.48</v>
+        <v>262539.16</v>
       </c>
       <c r="P118" t="n">
         <v>45900</v>
       </c>
       <c r="Q118" t="n">
-        <v>642600</v>
+        <v>596700</v>
       </c>
     </row>
     <row r="119">
@@ -6542,22 +6542,22 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M147" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N147" t="n">
         <v>27000</v>
       </c>
       <c r="O147" t="n">
-        <v>216000</v>
+        <v>162000</v>
       </c>
       <c r="P147" t="n">
         <v>20000</v>
       </c>
       <c r="Q147" t="n">
-        <v>160000</v>
+        <v>120000</v>
       </c>
     </row>
     <row r="148">
@@ -6900,22 +6900,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N156" t="n">
         <v>29510.75</v>
       </c>
       <c r="O156" t="n">
-        <v>295107.5</v>
+        <v>236086</v>
       </c>
       <c r="P156" t="n">
         <v>58000</v>
       </c>
       <c r="Q156" t="n">
-        <v>580000</v>
+        <v>464000</v>
       </c>
     </row>
     <row r="157">
@@ -10071,10 +10071,10 @@
         <v>28</v>
       </c>
       <c r="N229" t="n">
-        <v>1098.0684371373</v>
+        <v>1098.0685808709</v>
       </c>
       <c r="O229" t="n">
-        <v>30745.9162398444</v>
+        <v>30745.9202643852</v>
       </c>
       <c r="P229" t="n">
         <v>1500</v>
@@ -10480,22 +10480,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M239" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="N239" t="n">
         <v>1332</v>
       </c>
       <c r="O239" t="n">
-        <v>102564</v>
+        <v>86580</v>
       </c>
       <c r="P239" t="n">
         <v>2000</v>
       </c>
       <c r="Q239" t="n">
-        <v>154000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="240">
@@ -11873,10 +11873,10 @@
         <v>123</v>
       </c>
       <c r="N271" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O271" t="n">
-        <v>317617.3603338351</v>
+        <v>317617.3601770839</v>
       </c>
       <c r="P271" t="n">
         <v>4500</v>
@@ -11965,10 +11965,10 @@
         <v>82</v>
       </c>
       <c r="N273" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O273" t="n">
-        <v>427785.4627921052</v>
+        <v>427785.4626385274</v>
       </c>
       <c r="P273" t="n">
         <v>8500</v>
@@ -12215,22 +12215,22 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M279" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N279" t="n">
         <v>6713.08</v>
       </c>
       <c r="O279" t="n">
-        <v>422924.04</v>
+        <v>409497.88</v>
       </c>
       <c r="P279" t="n">
         <v>9900</v>
       </c>
       <c r="Q279" t="n">
-        <v>623700</v>
+        <v>603900</v>
       </c>
     </row>
     <row r="280">
@@ -12267,10 +12267,10 @@
         <v>575</v>
       </c>
       <c r="N280" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O280" t="n">
-        <v>1816344.982527465</v>
+        <v>1816344.9825515</v>
       </c>
       <c r="P280" t="n">
         <v>5600</v>
@@ -12893,22 +12893,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N294" t="n">
         <v>7507.39</v>
       </c>
       <c r="O294" t="n">
-        <v>1013497.65</v>
+        <v>998482.87</v>
       </c>
       <c r="P294" t="n">
         <v>13500</v>
       </c>
       <c r="Q294" t="n">
-        <v>1822500</v>
+        <v>1795500</v>
       </c>
     </row>
     <row r="295">
@@ -12942,22 +12942,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M295" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="N295" t="n">
         <v>8796</v>
       </c>
       <c r="O295" t="n">
-        <v>1345788</v>
+        <v>1293012</v>
       </c>
       <c r="P295" t="n">
         <v>14900</v>
       </c>
       <c r="Q295" t="n">
-        <v>2279700</v>
+        <v>2190300</v>
       </c>
     </row>
     <row r="296">
@@ -13089,10 +13089,10 @@
         <v>282</v>
       </c>
       <c r="N298" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O298" t="n">
-        <v>1070390.222148163</v>
+        <v>1070390.222149799</v>
       </c>
       <c r="P298" t="n">
         <v>6200</v>
@@ -13355,10 +13355,10 @@
         <v>77</v>
       </c>
       <c r="N304" t="n">
-        <v>4890.9300534045</v>
+        <v>4890.9300534402</v>
       </c>
       <c r="O304" t="n">
-        <v>376601.6141121465</v>
+        <v>376601.6141148954</v>
       </c>
       <c r="P304" t="n">
         <v>8200</v>
@@ -13669,22 +13669,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M311" t="n">
-        <v>1507</v>
+        <v>1499</v>
       </c>
       <c r="N311" t="n">
-        <v>2267.0480923608</v>
+        <v>2267.0480857514</v>
       </c>
       <c r="O311" t="n">
-        <v>3416441.475187726</v>
+        <v>3398305.080541349</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
       </c>
       <c r="Q311" t="n">
-        <v>5877300</v>
+        <v>5846100</v>
       </c>
     </row>
     <row r="312">
@@ -13843,22 +13843,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="M315" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N315" t="n">
         <v>156</v>
       </c>
       <c r="O315" t="n">
-        <v>156000</v>
+        <v>78000</v>
       </c>
       <c r="P315" t="n">
         <v>195</v>
       </c>
       <c r="Q315" t="n">
-        <v>195000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="316">
@@ -14189,22 +14189,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M323" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N323" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O323" t="n">
-        <v>240814.9522181806</v>
+        <v>226437.9388621434</v>
       </c>
       <c r="P323" t="n">
         <v>6500</v>
       </c>
       <c r="Q323" t="n">
-        <v>435500</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="324">
@@ -14989,10 +14989,10 @@
         <v>166</v>
       </c>
       <c r="N341" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O341" t="n">
-        <v>576397.8519789396</v>
+        <v>576397.853267664</v>
       </c>
       <c r="P341" t="n">
         <v>5900</v>
@@ -15167,10 +15167,10 @@
         <v>419</v>
       </c>
       <c r="N345" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O345" t="n">
-        <v>1274455.545943264</v>
+        <v>1274455.545947496</v>
       </c>
       <c r="P345" t="n">
         <v>5500</v>
@@ -15248,22 +15248,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M347" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N347" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O347" t="n">
-        <v>852378.3962765955</v>
+        <v>843751.1316464313</v>
       </c>
       <c r="P347" t="n">
         <v>8900</v>
       </c>
       <c r="Q347" t="n">
-        <v>1735500</v>
+        <v>1717700</v>
       </c>
     </row>
     <row r="348">
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M351" t="n">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="N351" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O351" t="n">
-        <v>573985.72</v>
+        <v>520895.8582610606</v>
       </c>
       <c r="P351" t="n">
         <v>5500</v>
       </c>
       <c r="Q351" t="n">
-        <v>863500</v>
+        <v>781000</v>
       </c>
     </row>
     <row r="352">
@@ -15864,22 +15864,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M361" t="n">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="N361" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O361" t="n">
-        <v>1455011.8</v>
+        <v>1445967.479937035</v>
       </c>
       <c r="P361" t="n">
         <v>8900</v>
       </c>
       <c r="Q361" t="n">
-        <v>2785700</v>
+        <v>2767900</v>
       </c>
     </row>
     <row r="362">
@@ -17365,10 +17365,10 @@
         <v>582</v>
       </c>
       <c r="N395" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O395" t="n">
-        <v>949198.1199880128</v>
+        <v>949198.1215937508</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
@@ -17400,22 +17400,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M396" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N396" t="n">
         <v>27634</v>
       </c>
       <c r="O396" t="n">
-        <v>386876</v>
+        <v>359242</v>
       </c>
       <c r="P396" t="n">
         <v>31900</v>
       </c>
       <c r="Q396" t="n">
-        <v>446600</v>
+        <v>414700</v>
       </c>
     </row>
     <row r="397">
@@ -17492,22 +17492,22 @@
         <v>0</v>
       </c>
       <c r="L398" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M398" t="n">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="N398" t="n">
-        <v>1690.5796701847</v>
+        <v>1699.5482625995</v>
       </c>
       <c r="O398" t="n">
-        <v>821621.7197097642</v>
+        <v>819182.2625729591</v>
       </c>
       <c r="P398" t="n">
         <v>2900</v>
       </c>
       <c r="Q398" t="n">
-        <v>1409400</v>
+        <v>1397800</v>
       </c>
     </row>
     <row r="399">
@@ -17538,22 +17538,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M399" t="n">
-        <v>1913</v>
+        <v>1907</v>
       </c>
       <c r="N399" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O399" t="n">
-        <v>2965522.398616446</v>
+        <v>2958456.28699981</v>
       </c>
       <c r="P399" t="n">
         <v>2500</v>
       </c>
       <c r="Q399" t="n">
-        <v>4782500</v>
+        <v>4767500</v>
       </c>
     </row>
     <row r="400">
@@ -17630,22 +17630,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M401" t="n">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.5202775057</v>
+        <v>2407.4618268285</v>
       </c>
       <c r="O401" t="n">
-        <v>2624644.143036224</v>
+        <v>2616911.005762579</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
       </c>
       <c r="Q401" t="n">
-        <v>3822000</v>
+        <v>3804500</v>
       </c>
     </row>
     <row r="402">
@@ -18403,22 +18403,22 @@
         <v>0</v>
       </c>
       <c r="L419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M419" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N419" t="n">
         <v>59081.6</v>
       </c>
       <c r="O419" t="n">
-        <v>472652.8</v>
+        <v>354489.6</v>
       </c>
       <c r="P419" t="n">
         <v>40000</v>
       </c>
       <c r="Q419" t="n">
-        <v>320000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="420">
@@ -19038,22 +19038,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M433" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N433" t="n">
         <v>17328</v>
       </c>
       <c r="O433" t="n">
-        <v>571824</v>
+        <v>519840</v>
       </c>
       <c r="P433" t="n">
         <v>32900</v>
       </c>
       <c r="Q433" t="n">
-        <v>1085700</v>
+        <v>987000</v>
       </c>
     </row>
     <row r="434">
@@ -20747,22 +20747,22 @@
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M473" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N473" t="n">
-        <v>2661.82</v>
+        <v>2668.524836272</v>
       </c>
       <c r="O473" t="n">
-        <v>513731.26</v>
+        <v>512356.768564224</v>
       </c>
       <c r="P473" t="n">
         <v>3200</v>
       </c>
       <c r="Q473" t="n">
-        <v>617600</v>
+        <v>614400</v>
       </c>
     </row>
     <row r="474">
@@ -20870,22 +20870,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N476" t="n">
-        <v>2610</v>
+        <v>2613.8724035608</v>
       </c>
       <c r="O476" t="n">
-        <v>234900</v>
+        <v>232634.6439169112</v>
       </c>
       <c r="P476" t="n">
         <v>3200</v>
       </c>
       <c r="Q476" t="n">
-        <v>288000</v>
+        <v>284800</v>
       </c>
     </row>
     <row r="477">
@@ -20911,22 +20911,22 @@
         <v>0</v>
       </c>
       <c r="L477" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M477" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N477" t="n">
-        <v>2081</v>
+        <v>2086.0024038462</v>
       </c>
       <c r="O477" t="n">
-        <v>118617</v>
+        <v>116816.1346153872</v>
       </c>
       <c r="P477" t="n">
         <v>3200</v>
       </c>
       <c r="Q477" t="n">
-        <v>182400</v>
+        <v>179200</v>
       </c>
     </row>
     <row r="478">
@@ -21408,22 +21408,22 @@
         <v>0</v>
       </c>
       <c r="L489" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M489" t="n">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="N489" t="n">
-        <v>2517.22</v>
+        <v>2545.636406397</v>
       </c>
       <c r="O489" t="n">
-        <v>855854.7999999999</v>
+        <v>834968.741298216</v>
       </c>
       <c r="P489" t="n">
         <v>4200</v>
       </c>
       <c r="Q489" t="n">
-        <v>1428000</v>
+        <v>1377600</v>
       </c>
     </row>
     <row r="490">
@@ -21996,10 +21996,10 @@
         <v>42</v>
       </c>
       <c r="N503" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O503" t="n">
-        <v>1030596.84</v>
+        <v>1068591.193548396</v>
       </c>
       <c r="P503" t="n">
         <v>52900</v>
@@ -22963,22 +22963,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M526" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N526" t="n">
         <v>3049.52</v>
       </c>
       <c r="O526" t="n">
-        <v>15247.6</v>
+        <v>0</v>
       </c>
       <c r="P526" t="n">
         <v>3000</v>
       </c>
       <c r="Q526" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
@@ -23018,10 +23018,10 @@
         <v>267</v>
       </c>
       <c r="N527" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O527" t="n">
-        <v>1144147.423333331</v>
+        <v>1144147.433969836</v>
       </c>
       <c r="P527" t="n">
         <v>6900</v>
@@ -23102,22 +23102,22 @@
         <v>0</v>
       </c>
       <c r="L529" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M529" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N529" t="n">
         <v>9776.99</v>
       </c>
       <c r="O529" t="n">
-        <v>1984728.97</v>
+        <v>1965174.99</v>
       </c>
       <c r="P529" t="n">
         <v>15900</v>
       </c>
       <c r="Q529" t="n">
-        <v>3227700</v>
+        <v>3195900</v>
       </c>
     </row>
     <row r="530">
@@ -23266,22 +23266,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M533" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N533" t="n">
         <v>8963</v>
       </c>
       <c r="O533" t="n">
-        <v>179260</v>
+        <v>125482</v>
       </c>
       <c r="P533" t="n">
         <v>15200</v>
       </c>
       <c r="Q533" t="n">
-        <v>304000</v>
+        <v>212800</v>
       </c>
     </row>
     <row r="534">
@@ -25345,10 +25345,10 @@
         <v>33</v>
       </c>
       <c r="N581" t="n">
-        <v>4100.45</v>
+        <v>4107.6818342152</v>
       </c>
       <c r="O581" t="n">
-        <v>135314.85</v>
+        <v>135553.5005291016</v>
       </c>
       <c r="P581" t="n">
         <v>26900</v>
@@ -25519,10 +25519,10 @@
         <v>18</v>
       </c>
       <c r="N585" t="n">
-        <v>1561.0051173709</v>
+        <v>1600.4118322476</v>
       </c>
       <c r="O585" t="n">
-        <v>28098.0921126762</v>
+        <v>28807.4129804568</v>
       </c>
       <c r="P585" t="n">
         <v>2900</v>
@@ -25559,22 +25559,22 @@
         <v>0</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M586" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N586" t="n">
         <v>3487.53</v>
       </c>
       <c r="O586" t="n">
-        <v>474304.08</v>
+        <v>460353.96</v>
       </c>
       <c r="P586" t="n">
         <v>6500</v>
       </c>
       <c r="Q586" t="n">
-        <v>884000</v>
+        <v>858000</v>
       </c>
     </row>
     <row r="587">
@@ -25834,10 +25834,10 @@
         <v>125</v>
       </c>
       <c r="N592" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O592" t="n">
-        <v>996243.7713013125</v>
+        <v>996243.7713343624</v>
       </c>
       <c r="P592" t="n">
         <v>12900</v>
@@ -28161,10 +28161,10 @@
         <v>325</v>
       </c>
       <c r="N645" t="n">
-        <v>1664.3366763006</v>
+        <v>1664.3365797101</v>
       </c>
       <c r="O645" t="n">
-        <v>540909.419797695</v>
+        <v>540909.3884057825</v>
       </c>
       <c r="P645" t="n">
         <v>2900</v>
@@ -28345,22 +28345,22 @@
         <v>0</v>
       </c>
       <c r="L649" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M649" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N649" t="n">
         <v>10174</v>
       </c>
       <c r="O649" t="n">
-        <v>61044</v>
+        <v>20348</v>
       </c>
       <c r="P649" t="n">
         <v>16900</v>
       </c>
       <c r="Q649" t="n">
-        <v>101400</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="650">
@@ -28437,22 +28437,22 @@
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M651" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N651" t="n">
         <v>38469</v>
       </c>
       <c r="O651" t="n">
-        <v>76938</v>
+        <v>38469</v>
       </c>
       <c r="P651" t="n">
         <v>62900</v>
       </c>
       <c r="Q651" t="n">
-        <v>125800</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="652">
@@ -28575,22 +28575,22 @@
         <v>0</v>
       </c>
       <c r="L654" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M654" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N654" t="n">
         <v>55139</v>
       </c>
       <c r="O654" t="n">
-        <v>827085</v>
+        <v>771946</v>
       </c>
       <c r="P654" t="n">
         <v>89900</v>
       </c>
       <c r="Q654" t="n">
-        <v>1348500</v>
+        <v>1258600</v>
       </c>
     </row>
     <row r="655">
@@ -28857,10 +28857,10 @@
         <v>1256</v>
       </c>
       <c r="N660" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O660" t="n">
-        <v>2233761.888716007</v>
+        <v>2233761.898032261</v>
       </c>
       <c r="P660" t="n">
         <v>4900</v>
@@ -28989,22 +28989,22 @@
         <v>0</v>
       </c>
       <c r="L663" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M663" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N663" t="n">
         <v>22739</v>
       </c>
       <c r="O663" t="n">
-        <v>522997</v>
+        <v>500258</v>
       </c>
       <c r="P663" t="n">
         <v>36900</v>
       </c>
       <c r="Q663" t="n">
-        <v>848700</v>
+        <v>811800</v>
       </c>
     </row>
     <row r="664">
@@ -29081,22 +29081,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M665" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N665" t="n">
         <v>16058</v>
       </c>
       <c r="O665" t="n">
-        <v>867132</v>
+        <v>835016</v>
       </c>
       <c r="P665" t="n">
         <v>25900</v>
       </c>
       <c r="Q665" t="n">
-        <v>1398600</v>
+        <v>1346800</v>
       </c>
     </row>
     <row r="666">
@@ -29682,22 +29682,22 @@
         <v>0</v>
       </c>
       <c r="L678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M678" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="N678" t="n">
         <v>5200</v>
       </c>
       <c r="O678" t="n">
-        <v>353600</v>
+        <v>348400</v>
       </c>
       <c r="P678" t="n">
         <v>8500</v>
       </c>
       <c r="Q678" t="n">
-        <v>578000</v>
+        <v>569500</v>
       </c>
     </row>
     <row r="679">
@@ -30004,22 +30004,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M685" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N685" t="n">
         <v>1870</v>
       </c>
       <c r="O685" t="n">
-        <v>69190</v>
+        <v>63580</v>
       </c>
       <c r="P685" t="n">
         <v>3000</v>
       </c>
       <c r="Q685" t="n">
-        <v>111000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="686">
@@ -30188,22 +30188,22 @@
         <v>0</v>
       </c>
       <c r="L689" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M689" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N689" t="n">
         <v>1840</v>
       </c>
       <c r="O689" t="n">
-        <v>58880</v>
+        <v>57040</v>
       </c>
       <c r="P689" t="n">
         <v>3000</v>
       </c>
       <c r="Q689" t="n">
-        <v>96000</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="690">
@@ -31249,22 +31249,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M712" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N712" t="n">
         <v>11376</v>
       </c>
       <c r="O712" t="n">
-        <v>261648</v>
+        <v>238896</v>
       </c>
       <c r="P712" t="n">
         <v>18500</v>
       </c>
       <c r="Q712" t="n">
-        <v>425500</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="713">
@@ -31937,22 +31937,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M727" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N727" t="n">
         <v>34912</v>
       </c>
       <c r="O727" t="n">
-        <v>1082272</v>
+        <v>1012448</v>
       </c>
       <c r="P727" t="n">
         <v>56900</v>
       </c>
       <c r="Q727" t="n">
-        <v>1763900</v>
+        <v>1650100</v>
       </c>
     </row>
     <row r="728">
@@ -32443,22 +32443,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M738" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N738" t="n">
-        <v>6414</v>
+        <v>6426.9445005045</v>
       </c>
       <c r="O738" t="n">
-        <v>1167348</v>
+        <v>1156850.01009081</v>
       </c>
       <c r="P738" t="n">
         <v>10900</v>
       </c>
       <c r="Q738" t="n">
-        <v>1983800</v>
+        <v>1962000</v>
       </c>
     </row>
     <row r="739">
@@ -32679,10 +32679,10 @@
         <v>28</v>
       </c>
       <c r="N743" t="n">
-        <v>3903.7394479074</v>
+        <v>3903.7394652406</v>
       </c>
       <c r="O743" t="n">
-        <v>109304.7045414072</v>
+        <v>109304.7050267368</v>
       </c>
       <c r="P743" t="n">
         <v>7500</v>
@@ -33174,22 +33174,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M754" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N754" t="n">
         <v>2629</v>
       </c>
       <c r="O754" t="n">
-        <v>223465</v>
+        <v>191917</v>
       </c>
       <c r="P754" t="n">
         <v>4500</v>
       </c>
       <c r="Q754" t="n">
-        <v>382500</v>
+        <v>328500</v>
       </c>
     </row>
     <row r="755">
@@ -33496,22 +33496,22 @@
         <v>0</v>
       </c>
       <c r="L761" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M761" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="N761" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O761" t="n">
-        <v>1408740</v>
+        <v>1396229.145728634</v>
       </c>
       <c r="P761" t="n">
         <v>10900</v>
       </c>
       <c r="Q761" t="n">
-        <v>2310800</v>
+        <v>2289000</v>
       </c>
     </row>
     <row r="762">
@@ -33726,22 +33726,22 @@
         <v>0</v>
       </c>
       <c r="L766" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M766" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N766" t="n">
-        <v>3898</v>
+        <v>3904.464344942</v>
       </c>
       <c r="O766" t="n">
-        <v>966704</v>
+        <v>960498.228855732</v>
       </c>
       <c r="P766" t="n">
         <v>6900</v>
       </c>
       <c r="Q766" t="n">
-        <v>1711200</v>
+        <v>1697400</v>
       </c>
     </row>
     <row r="767">
@@ -34002,22 +34002,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M772" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N772" t="n">
         <v>19008</v>
       </c>
       <c r="O772" t="n">
-        <v>532224</v>
+        <v>494208</v>
       </c>
       <c r="P772" t="n">
         <v>30900</v>
       </c>
       <c r="Q772" t="n">
-        <v>865200</v>
+        <v>803400</v>
       </c>
     </row>
     <row r="773">
@@ -34552,22 +34552,22 @@
         <v>0</v>
       </c>
       <c r="L784" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M784" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N784" t="n">
         <v>21346</v>
       </c>
       <c r="O784" t="n">
-        <v>64038</v>
+        <v>21346</v>
       </c>
       <c r="P784" t="n">
         <v>34900</v>
       </c>
       <c r="Q784" t="n">
-        <v>104700</v>
+        <v>34900</v>
       </c>
     </row>
     <row r="785">
@@ -34693,22 +34693,22 @@
         <v>0</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M787" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N787" t="n">
         <v>10755</v>
       </c>
       <c r="O787" t="n">
-        <v>924930</v>
+        <v>881910</v>
       </c>
       <c r="P787" t="n">
         <v>17900</v>
       </c>
       <c r="Q787" t="n">
-        <v>1539400</v>
+        <v>1467800</v>
       </c>
     </row>
     <row r="788">
@@ -34969,22 +34969,22 @@
         <v>0</v>
       </c>
       <c r="L793" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M793" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="N793" t="n">
         <v>5215</v>
       </c>
       <c r="O793" t="n">
-        <v>245105</v>
+        <v>182525</v>
       </c>
       <c r="P793" t="n">
         <v>8900</v>
       </c>
       <c r="Q793" t="n">
-        <v>418300</v>
+        <v>311500</v>
       </c>
     </row>
     <row r="794">
@@ -35846,22 +35846,22 @@
         <v>0</v>
       </c>
       <c r="L812" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M812" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N812" t="n">
         <v>64612</v>
       </c>
       <c r="O812" t="n">
-        <v>2649092</v>
+        <v>2519868</v>
       </c>
       <c r="P812" t="n">
         <v>103900</v>
       </c>
       <c r="Q812" t="n">
-        <v>4259900</v>
+        <v>4052100</v>
       </c>
     </row>
     <row r="813">
@@ -36080,10 +36080,10 @@
         <v>1091</v>
       </c>
       <c r="N817" t="n">
-        <v>2458.5124311594</v>
+        <v>2458.5124201742</v>
       </c>
       <c r="O817" t="n">
-        <v>2682237.062394905</v>
+        <v>2682237.050410052</v>
       </c>
       <c r="P817" t="n">
         <v>3500</v>
@@ -36172,10 +36172,10 @@
         <v>462</v>
       </c>
       <c r="N819" t="n">
-        <v>1771.0893441415</v>
+        <v>1771.0893205318</v>
       </c>
       <c r="O819" t="n">
-        <v>818243.2769933731</v>
+        <v>818243.2660856916</v>
       </c>
       <c r="P819" t="n">
         <v>2500</v>
@@ -36264,10 +36264,10 @@
         <v>928</v>
       </c>
       <c r="N821" t="n">
-        <v>1803.0169781803</v>
+        <v>1803.0169868096</v>
       </c>
       <c r="O821" t="n">
-        <v>1673199.755751318</v>
+        <v>1673199.763759309</v>
       </c>
       <c r="P821" t="n">
         <v>2500</v>
@@ -37087,22 +37087,22 @@
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M839" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="N839" t="n">
-        <v>1259.2749291992</v>
+        <v>1262.9750514202</v>
       </c>
       <c r="O839" t="n">
-        <v>235484.4117602504</v>
+        <v>221020.633998535</v>
       </c>
       <c r="P839" t="n">
         <v>1900</v>
       </c>
       <c r="Q839" t="n">
-        <v>355300</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="840">
@@ -37696,22 +37696,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M852" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N852" t="n">
         <v>5215</v>
       </c>
       <c r="O852" t="n">
-        <v>495425</v>
+        <v>458920</v>
       </c>
       <c r="P852" t="n">
         <v>8900</v>
       </c>
       <c r="Q852" t="n">
-        <v>845500</v>
+        <v>783200</v>
       </c>
     </row>
     <row r="853">
@@ -38207,22 +38207,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M863" t="n">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="N863" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O863" t="n">
-        <v>2477870.26</v>
+        <v>2433143.36</v>
       </c>
       <c r="P863" t="n">
         <v>14900</v>
       </c>
       <c r="Q863" t="n">
-        <v>4127300</v>
+        <v>4052800</v>
       </c>
     </row>
     <row r="864">
@@ -38574,22 +38574,22 @@
         <v>0</v>
       </c>
       <c r="L871" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M871" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="N871" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O871" t="n">
-        <v>557083.7701761696</v>
+        <v>541379.8040345728</v>
       </c>
       <c r="P871" t="n">
         <v>2600</v>
       </c>
       <c r="Q871" t="n">
-        <v>946400</v>
+        <v>915200</v>
       </c>
     </row>
     <row r="872">
@@ -39570,22 +39570,22 @@
         <v>0</v>
       </c>
       <c r="L893" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M893" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="N893" t="n">
         <v>5050</v>
       </c>
       <c r="O893" t="n">
-        <v>409050</v>
+        <v>388850</v>
       </c>
       <c r="P893" t="n">
         <v>2000</v>
       </c>
       <c r="Q893" t="n">
-        <v>162000</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="894">
@@ -40370,10 +40370,10 @@
         <v>3228</v>
       </c>
       <c r="N911" t="n">
-        <v>517.2950312417501</v>
+        <v>517.29511103247</v>
       </c>
       <c r="O911" t="n">
-        <v>1669828.360848369</v>
+        <v>1669828.618412813</v>
       </c>
       <c r="P911" t="n">
         <v>900</v>
@@ -40590,22 +40590,22 @@
         <v>0</v>
       </c>
       <c r="L916" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M916" t="n">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="N916" t="n">
-        <v>3110.8368831169</v>
+        <v>3110.8366754617</v>
       </c>
       <c r="O916" t="n">
-        <v>1315884.001558449</v>
+        <v>1222558.813456448</v>
       </c>
       <c r="P916" t="n">
         <v>4500</v>
       </c>
       <c r="Q916" t="n">
-        <v>1903500</v>
+        <v>1768500</v>
       </c>
     </row>
     <row r="917">
@@ -40818,10 +40818,10 @@
         <v>1225</v>
       </c>
       <c r="N921" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O921" t="n">
-        <v>862148.5535950717</v>
+        <v>862148.549536316</v>
       </c>
       <c r="P921" t="n">
         <v>900</v>
@@ -43568,10 +43568,10 @@
         <v>1</v>
       </c>
       <c r="N981" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="O981" t="n">
-        <v>10737.525714286</v>
+        <v>10737.525609756</v>
       </c>
       <c r="P981" t="n">
         <v>18900</v>
@@ -44775,22 +44775,22 @@
         <v>0</v>
       </c>
       <c r="L1007" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1007" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N1007" t="n">
         <v>7811.9</v>
       </c>
       <c r="O1007" t="n">
-        <v>1070230.3</v>
+        <v>1054606.5</v>
       </c>
       <c r="P1007" t="n">
         <v>13900</v>
       </c>
       <c r="Q1007" t="n">
-        <v>1904300</v>
+        <v>1876500</v>
       </c>
     </row>
     <row r="1008">
@@ -45020,22 +45020,22 @@
         <v>0</v>
       </c>
       <c r="L1012" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1012" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N1012" t="n">
         <v>426.1</v>
       </c>
       <c r="O1012" t="n">
-        <v>27270.4</v>
+        <v>25566</v>
       </c>
       <c r="P1012" t="n">
         <v>2900</v>
       </c>
       <c r="Q1012" t="n">
-        <v>185600</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="1013">
@@ -45069,22 +45069,22 @@
         <v>0</v>
       </c>
       <c r="L1013" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M1013" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="N1013" t="n">
-        <v>430.60997530864</v>
+        <v>430.60997520149</v>
       </c>
       <c r="O1013" t="n">
-        <v>80093.45540740705</v>
+        <v>77079.18556106671</v>
       </c>
       <c r="P1013" t="n">
         <v>2200</v>
       </c>
       <c r="Q1013" t="n">
-        <v>409200</v>
+        <v>393800</v>
       </c>
     </row>
     <row r="1014">
@@ -47265,22 +47265,22 @@
         <v>0</v>
       </c>
       <c r="L1064" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1064" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="N1064" t="n">
-        <v>1464</v>
+        <v>1752</v>
       </c>
       <c r="O1064" t="n">
-        <v>98088</v>
+        <v>96360</v>
       </c>
       <c r="P1064" t="n">
         <v>1500</v>
       </c>
       <c r="Q1064" t="n">
-        <v>100500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="1065">
@@ -48029,22 +48029,22 @@
         <v>0</v>
       </c>
       <c r="L1082" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1082" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N1082" t="n">
         <v>5077</v>
       </c>
       <c r="O1082" t="n">
-        <v>203080</v>
+        <v>182772</v>
       </c>
       <c r="P1082" t="n">
         <v>8500</v>
       </c>
       <c r="Q1082" t="n">
-        <v>340000</v>
+        <v>306000</v>
       </c>
     </row>
     <row r="1083">
@@ -49208,22 +49208,22 @@
         <v>0</v>
       </c>
       <c r="L1108" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1108" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="N1108" t="n">
         <v>4400</v>
       </c>
       <c r="O1108" t="n">
-        <v>224400</v>
+        <v>171600</v>
       </c>
       <c r="P1108" t="n">
         <v>5900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>300900</v>
+        <v>230100</v>
       </c>
     </row>
     <row r="1109">
@@ -49254,22 +49254,22 @@
         <v>0</v>
       </c>
       <c r="L1109" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1109" t="n">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="N1109" t="n">
-        <v>6160</v>
+        <v>6202.5414364641</v>
       </c>
       <c r="O1109" t="n">
-        <v>1767920</v>
+        <v>1705698.895027627</v>
       </c>
       <c r="P1109" t="n">
         <v>7500</v>
       </c>
       <c r="Q1109" t="n">
-        <v>2152500</v>
+        <v>2062500</v>
       </c>
     </row>
     <row r="1110">
@@ -52141,22 +52141,22 @@
         <v>0</v>
       </c>
       <c r="L1172" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1172" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N1172" t="n">
-        <v>1059.1847727273</v>
+        <v>1059.1855263158</v>
       </c>
       <c r="O1172" t="n">
-        <v>8473.4781818184</v>
+        <v>2118.3710526316</v>
       </c>
       <c r="P1172" t="n">
         <v>9500</v>
       </c>
       <c r="Q1172" t="n">
-        <v>76000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="1173">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -12749,13 +12749,13 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M291" t="n">
         <v>369</v>
@@ -12841,13 +12841,13 @@
         </is>
       </c>
       <c r="J293" t="n">
-        <v>2755</v>
+        <v>2795</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M293" t="n">
         <v>2755</v>
@@ -14809,10 +14809,10 @@
         <v>44</v>
       </c>
       <c r="N337" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O337" t="n">
-        <v>546588.370221652</v>
+        <v>546588.37027828</v>
       </c>
       <c r="P337" t="n">
         <v>19900</v>
@@ -17636,10 +17636,10 @@
         <v>1062</v>
       </c>
       <c r="N401" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O401" t="n">
-        <v>2552539.001607778</v>
+        <v>2552539.016295026</v>
       </c>
       <c r="P401" t="n">
         <v>3500</v>
@@ -35891,13 +35891,13 @@
         </is>
       </c>
       <c r="J813" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K813" t="n">
         <v>0</v>
       </c>
       <c r="L813" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M813" t="n">
         <v>403</v>
@@ -49492,28 +49492,28 @@
         </is>
       </c>
       <c r="J1114" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K1114" t="n">
         <v>0</v>
       </c>
       <c r="L1114" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M1114" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N1114" t="n">
         <v>9240</v>
       </c>
       <c r="O1114" t="n">
-        <v>2032800</v>
+        <v>2005080</v>
       </c>
       <c r="P1114" t="n">
         <v>11500</v>
       </c>
       <c r="Q1114" t="n">
-        <v>2530000</v>
+        <v>2495500</v>
       </c>
     </row>
     <row r="1115">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -2757,10 +2757,10 @@
         <v>35</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.855198556</v>
+        <v>6272.8552079566</v>
       </c>
       <c r="O58" t="n">
-        <v>219549.93194946</v>
+        <v>219549.932278481</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
@@ -3314,10 +3314,10 @@
         <v>167</v>
       </c>
       <c r="N72" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O72" t="n">
-        <v>620627.1428524571</v>
+        <v>620627.142906398</v>
       </c>
       <c r="P72" t="n">
         <v>9500</v>
@@ -14073,10 +14073,10 @@
         <v>53</v>
       </c>
       <c r="N320" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O320" t="n">
-        <v>190495.4053313718</v>
+        <v>190495.4050552683</v>
       </c>
       <c r="P320" t="n">
         <v>6500</v>
@@ -14687,10 +14687,10 @@
         <v>44</v>
       </c>
       <c r="N334" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O334" t="n">
-        <v>546588.371421048</v>
+        <v>546588.371594188</v>
       </c>
       <c r="P334" t="n">
         <v>19900</v>
@@ -15045,10 +15045,10 @@
         <v>419</v>
       </c>
       <c r="N342" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O342" t="n">
-        <v>1274455.54621201</v>
+        <v>1274455.546221228</v>
       </c>
       <c r="P342" t="n">
         <v>5500</v>
@@ -17243,10 +17243,10 @@
         <v>548</v>
       </c>
       <c r="N392" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O392" t="n">
-        <v>893746.7248935048</v>
+        <v>893746.7342944448</v>
       </c>
       <c r="P392" t="n">
         <v>2500</v>
@@ -22809,10 +22809,10 @@
         <v>267</v>
       </c>
       <c r="N522" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O522" t="n">
-        <v>1144147.442575754</v>
+        <v>1144147.44691138</v>
       </c>
       <c r="P522" t="n">
         <v>6900</v>
@@ -35689,10 +35689,10 @@
         <v>397</v>
       </c>
       <c r="N808" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O808" t="n">
-        <v>601867.3780412988</v>
+        <v>601867.3761783367</v>
       </c>
       <c r="P808" t="n">
         <v>2300</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -1268,10 +1268,10 @@
         <v>232</v>
       </c>
       <c r="N21" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O21" t="n">
-        <v>420224.0776699144</v>
+        <v>420224.1019607784</v>
       </c>
       <c r="P21" t="n">
         <v>2600</v>
@@ -9902,10 +9902,10 @@
         <v>27</v>
       </c>
       <c r="N225" t="n">
-        <v>1098.0691359493</v>
+        <v>1098.0698699716</v>
       </c>
       <c r="O225" t="n">
-        <v>29647.8666706311</v>
+        <v>29647.8864892332</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
@@ -12280,10 +12280,10 @@
         <v>11</v>
       </c>
       <c r="N280" t="n">
-        <v>3230.0661344538</v>
+        <v>3230.0661016949</v>
       </c>
       <c r="O280" t="n">
-        <v>35530.7274789918</v>
+        <v>35530.7271186439</v>
       </c>
       <c r="P280" t="n">
         <v>6200</v>
@@ -12920,10 +12920,10 @@
         <v>282</v>
       </c>
       <c r="N294" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O294" t="n">
-        <v>1070390.222152252</v>
+        <v>1070390.222153916</v>
       </c>
       <c r="P294" t="n">
         <v>6200</v>
@@ -13186,10 +13186,10 @@
         <v>76</v>
       </c>
       <c r="N300" t="n">
-        <v>4890.9300537634</v>
+        <v>4890.9300539811</v>
       </c>
       <c r="O300" t="n">
-        <v>371710.6840860184</v>
+        <v>371710.6841025636</v>
       </c>
       <c r="P300" t="n">
         <v>8200</v>
@@ -14241,10 +14241,10 @@
         <v>102</v>
       </c>
       <c r="N324" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O324" t="n">
-        <v>498882</v>
+        <v>500467.0103256564</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14820,10 +14820,10 @@
         <v>226</v>
       </c>
       <c r="N337" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O337" t="n">
-        <v>784734.4410330142</v>
+        <v>784734.4434271677</v>
       </c>
       <c r="P337" t="n">
         <v>5900</v>
@@ -15085,10 +15085,10 @@
         <v>193</v>
       </c>
       <c r="N343" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O343" t="n">
-        <v>843636.053833826</v>
+        <v>843636.053933665</v>
       </c>
       <c r="P343" t="n">
         <v>8900</v>
@@ -17196,10 +17196,10 @@
         <v>530</v>
       </c>
       <c r="N391" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O391" t="n">
-        <v>864390.0904980371</v>
+        <v>864390.093545431</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
@@ -17467,10 +17467,10 @@
         <v>1021</v>
       </c>
       <c r="N397" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O397" t="n">
-        <v>2453995.143109196</v>
+        <v>2453995.157892765</v>
       </c>
       <c r="P397" t="n">
         <v>3500</v>
@@ -22544,10 +22544,10 @@
         <v>1</v>
       </c>
       <c r="N516" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O516" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="P516" t="n">
         <v>9900</v>
@@ -23441,10 +23441,10 @@
         <v>109</v>
       </c>
       <c r="N537" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O537" t="n">
-        <v>391433.17</v>
+        <v>391851.0701814928</v>
       </c>
       <c r="P537" t="n">
         <v>6300</v>
@@ -25706,10 +25706,10 @@
         <v>1</v>
       </c>
       <c r="N589" t="n">
-        <v>9627.34</v>
+        <v>9808.987924528299</v>
       </c>
       <c r="O589" t="n">
-        <v>9627.34</v>
+        <v>9808.987924528299</v>
       </c>
       <c r="P589" t="n">
         <v>15900</v>
@@ -30723,10 +30723,10 @@
         <v>315</v>
       </c>
       <c r="N700" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O700" t="n">
-        <v>2790320.4</v>
+        <v>2795044.418735877</v>
       </c>
       <c r="P700" t="n">
         <v>15500</v>
@@ -33016,10 +33016,10 @@
         <v>90</v>
       </c>
       <c r="N750" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O750" t="n">
-        <v>616428</v>
+        <v>617609.6511182099</v>
       </c>
       <c r="P750" t="n">
         <v>11500</v>
@@ -35642,10 +35642,10 @@
         <v>390</v>
       </c>
       <c r="N807" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O807" t="n">
-        <v>591255.1036290211</v>
+        <v>591255.103526373</v>
       </c>
       <c r="P807" t="n">
         <v>2300</v>
@@ -35870,10 +35870,10 @@
         <v>462</v>
       </c>
       <c r="N812" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O812" t="n">
-        <v>818243.2660856916</v>
+        <v>818243.1770526089</v>
       </c>
       <c r="P812" t="n">
         <v>2500</v>
@@ -36192,10 +36192,10 @@
         <v>168</v>
       </c>
       <c r="N819" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O819" t="n">
-        <v>541727.7469623096</v>
+        <v>541727.7488124265</v>
       </c>
       <c r="P819" t="n">
         <v>4500</v>
@@ -36238,10 +36238,10 @@
         <v>560</v>
       </c>
       <c r="N820" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O820" t="n">
-        <v>927320.306530296</v>
+        <v>927320.248451128</v>
       </c>
       <c r="P820" t="n">
         <v>2500</v>
@@ -40294,10 +40294,10 @@
         <v>324</v>
       </c>
       <c r="N909" t="n">
-        <v>3110.8359666534</v>
+        <v>3110.8359331476</v>
       </c>
       <c r="O909" t="n">
-        <v>1007910.853195702</v>
+        <v>1007910.842339822</v>
       </c>
       <c r="P909" t="n">
         <v>4500</v>
@@ -40516,10 +40516,10 @@
         <v>1122</v>
       </c>
       <c r="N914" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O914" t="n">
-        <v>789657.6489690425</v>
+        <v>789657.6362041719</v>
       </c>
       <c r="P914" t="n">
         <v>900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1173"/>
+  <dimension ref="A1:Q1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -971,19 +971,19 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N14" t="n">
         <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>1053000</v>
+        <v>1026000</v>
       </c>
       <c r="P14" t="n">
         <v>20000</v>
       </c>
       <c r="Q14" t="n">
-        <v>780000</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="15">
@@ -1103,10 +1103,10 @@
         <v>78</v>
       </c>
       <c r="N17" t="n">
-        <v>988.39886486486</v>
+        <v>988.39849162011</v>
       </c>
       <c r="O17" t="n">
-        <v>77095.11145945908</v>
+        <v>77095.08234636858</v>
       </c>
       <c r="P17" t="n">
         <v>1200</v>
@@ -1385,10 +1385,10 @@
         <v>125</v>
       </c>
       <c r="N24" t="n">
-        <v>3376.7464001115</v>
+        <v>3376.746386014</v>
       </c>
       <c r="O24" t="n">
-        <v>422093.3000139375</v>
+        <v>422093.29825175</v>
       </c>
       <c r="P24" t="n">
         <v>4500</v>
@@ -2757,10 +2757,10 @@
         <v>35</v>
       </c>
       <c r="N58" t="n">
-        <v>6272.8552268603</v>
+        <v>6272.8552363636</v>
       </c>
       <c r="O58" t="n">
-        <v>219549.9329401105</v>
+        <v>219549.933272726</v>
       </c>
       <c r="P58" t="n">
         <v>7900</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2871,19 +2871,19 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N61" t="n">
-        <v>3926.8370772443</v>
+        <v>3926.8370726607</v>
       </c>
       <c r="O61" t="n">
-        <v>141366.1347807948</v>
+        <v>137439.2975431245</v>
       </c>
       <c r="P61" t="n">
         <v>4800</v>
       </c>
       <c r="Q61" t="n">
-        <v>172800</v>
+        <v>168000</v>
       </c>
     </row>
     <row r="62">
@@ -3431,10 +3431,10 @@
         <v>74</v>
       </c>
       <c r="N75" t="n">
-        <v>2681</v>
+        <v>2785.6243902439</v>
       </c>
       <c r="O75" t="n">
-        <v>198394</v>
+        <v>206136.2048780486</v>
       </c>
       <c r="P75" t="n">
         <v>3500</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3970,19 +3970,19 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="N88" t="n">
         <v>1800</v>
       </c>
       <c r="O88" t="n">
-        <v>129600</v>
+        <v>63000</v>
       </c>
       <c r="P88" t="n">
         <v>2200</v>
       </c>
       <c r="Q88" t="n">
-        <v>158400</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="89">
@@ -4775,10 +4775,10 @@
         <v>9</v>
       </c>
       <c r="N106" t="n">
-        <v>16486.406415094</v>
+        <v>16486.406019417</v>
       </c>
       <c r="O106" t="n">
-        <v>148377.657735846</v>
+        <v>148377.654174753</v>
       </c>
       <c r="P106" t="n">
         <v>30500</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4986,19 +4986,19 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="N111" t="n">
-        <v>7407.7300558659</v>
+        <v>7407.7300564972</v>
       </c>
       <c r="O111" t="n">
-        <v>570395.2143016743</v>
+        <v>540764.2941242956</v>
       </c>
       <c r="P111" t="n">
         <v>10900</v>
       </c>
       <c r="Q111" t="n">
-        <v>839300</v>
+        <v>795700</v>
       </c>
     </row>
     <row r="112">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5064,19 +5064,19 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N113" t="n">
         <v>6321.94</v>
       </c>
       <c r="O113" t="n">
-        <v>94829.09999999999</v>
+        <v>82185.22</v>
       </c>
       <c r="P113" t="n">
         <v>14100</v>
       </c>
       <c r="Q113" t="n">
-        <v>211500</v>
+        <v>183300</v>
       </c>
     </row>
     <row r="114">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5838,19 +5838,19 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N131" t="n">
-        <v>174389.98666667</v>
+        <v>174390.095</v>
       </c>
       <c r="O131" t="n">
-        <v>174389.98666667</v>
+        <v>348780.19</v>
       </c>
       <c r="P131" t="n">
         <v>368200</v>
       </c>
       <c r="Q131" t="n">
-        <v>368200</v>
+        <v>736400</v>
       </c>
     </row>
     <row r="132">
@@ -8015,10 +8015,10 @@
         <v>36</v>
       </c>
       <c r="N181" t="n">
-        <v>2572.67</v>
+        <v>2584.1380683507</v>
       </c>
       <c r="O181" t="n">
-        <v>92616.12</v>
+        <v>93028.97046062521</v>
       </c>
       <c r="P181" t="n">
         <v>4700</v>
@@ -8481,10 +8481,10 @@
         <v>3</v>
       </c>
       <c r="N192" t="n">
-        <v>1801.0181355932</v>
+        <v>1801.0185714286</v>
       </c>
       <c r="O192" t="n">
-        <v>5403.0544067796</v>
+        <v>5403.0557142858</v>
       </c>
       <c r="P192" t="n">
         <v>3200</v>
@@ -9187,10 +9187,10 @@
         <v>992</v>
       </c>
       <c r="N208" t="n">
-        <v>1950.2137275986</v>
+        <v>1950.2136708861</v>
       </c>
       <c r="O208" t="n">
-        <v>1934612.017777811</v>
+        <v>1934611.961519011</v>
       </c>
       <c r="P208" t="n">
         <v>2900</v>
@@ -9902,10 +9902,10 @@
         <v>27</v>
       </c>
       <c r="N225" t="n">
-        <v>1098.0698699716</v>
+        <v>1108.8838530981</v>
       </c>
       <c r="O225" t="n">
-        <v>29647.8864892332</v>
+        <v>29939.8640336487</v>
       </c>
       <c r="P225" t="n">
         <v>1500</v>
@@ -10030,10 +10030,10 @@
         <v>13</v>
       </c>
       <c r="N228" t="n">
-        <v>21084.771478495</v>
+        <v>21084.77148248</v>
       </c>
       <c r="O228" t="n">
-        <v>274102.029220435</v>
+        <v>274102.02927224</v>
       </c>
       <c r="P228" t="n">
         <v>30000</v>
@@ -10869,7 +10869,7 @@
         </is>
       </c>
       <c r="J248" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
@@ -10878,19 +10878,19 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N248" t="n">
         <v>9153.85</v>
       </c>
       <c r="O248" t="n">
-        <v>347846.3</v>
+        <v>338692.45</v>
       </c>
       <c r="P248" t="n">
         <v>11900</v>
       </c>
       <c r="Q248" t="n">
-        <v>452200</v>
+        <v>440300</v>
       </c>
     </row>
     <row r="249">
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
@@ -11255,19 +11255,19 @@
         <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="N257" t="n">
         <v>2913</v>
       </c>
       <c r="O257" t="n">
-        <v>209736</v>
+        <v>174780</v>
       </c>
       <c r="P257" t="n">
         <v>4950</v>
       </c>
       <c r="Q257" t="n">
-        <v>356400</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="258">
@@ -11336,7 +11336,7 @@
         </is>
       </c>
       <c r="J259" t="n">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11345,19 +11345,19 @@
         <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="N259" t="n">
         <v>2804.33</v>
       </c>
       <c r="O259" t="n">
-        <v>1309622.11</v>
+        <v>1242318.19</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
       </c>
       <c r="Q259" t="n">
-        <v>2288300</v>
+        <v>2170700</v>
       </c>
     </row>
     <row r="260">
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -11701,19 +11701,19 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="N267" t="n">
-        <v>2582.2549040675</v>
+        <v>2582.2548633316</v>
       </c>
       <c r="O267" t="n">
-        <v>286630.2943514925</v>
+        <v>255643.2314698284</v>
       </c>
       <c r="P267" t="n">
         <v>4500</v>
       </c>
       <c r="Q267" t="n">
-        <v>499500</v>
+        <v>445500</v>
       </c>
     </row>
     <row r="268">
@@ -11784,7 +11784,7 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -11793,19 +11793,19 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="N269" t="n">
-        <v>5216.8958410068</v>
+        <v>5216.8958275597</v>
       </c>
       <c r="O269" t="n">
-        <v>1236404.314318612</v>
+        <v>1205102.936166291</v>
       </c>
       <c r="P269" t="n">
         <v>8500</v>
       </c>
       <c r="Q269" t="n">
-        <v>2014500</v>
+        <v>1963500</v>
       </c>
     </row>
     <row r="270">
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="J280" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -12277,19 +12277,19 @@
         <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N280" t="n">
-        <v>3230.0661016949</v>
+        <v>3230.0658928571</v>
       </c>
       <c r="O280" t="n">
-        <v>35530.7271186439</v>
+        <v>29070.5930357139</v>
       </c>
       <c r="P280" t="n">
         <v>6200</v>
       </c>
       <c r="Q280" t="n">
-        <v>68200</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="281">
@@ -12367,10 +12367,10 @@
         <v>813</v>
       </c>
       <c r="N282" t="n">
-        <v>1480</v>
+        <v>1482.2572445348</v>
       </c>
       <c r="O282" t="n">
-        <v>1203240</v>
+        <v>1205075.139806792</v>
       </c>
       <c r="P282" t="n">
         <v>2600</v>
@@ -12580,7 +12580,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12589,19 +12589,19 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="N287" t="n">
         <v>1026.13</v>
       </c>
       <c r="O287" t="n">
-        <v>378641.97</v>
+        <v>374537.45</v>
       </c>
       <c r="P287" t="n">
         <v>1900</v>
       </c>
       <c r="Q287" t="n">
-        <v>701100</v>
+        <v>693500</v>
       </c>
     </row>
     <row r="288">
@@ -13186,10 +13186,10 @@
         <v>76</v>
       </c>
       <c r="N300" t="n">
-        <v>4890.9300539811</v>
+        <v>4890.9300540176</v>
       </c>
       <c r="O300" t="n">
-        <v>371710.6841025636</v>
+        <v>371710.6841053376</v>
       </c>
       <c r="P300" t="n">
         <v>8200</v>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="J302" t="n">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
@@ -13278,19 +13278,19 @@
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>899</v>
+        <v>874</v>
       </c>
       <c r="N302" t="n">
         <v>1203.38</v>
       </c>
       <c r="O302" t="n">
-        <v>1081838.62</v>
+        <v>1051754.12</v>
       </c>
       <c r="P302" t="n">
         <v>1900</v>
       </c>
       <c r="Q302" t="n">
-        <v>1708100</v>
+        <v>1660600</v>
       </c>
     </row>
     <row r="303">
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="J312" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13723,19 +13723,19 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N312" t="n">
         <v>8662</v>
       </c>
       <c r="O312" t="n">
-        <v>571692</v>
+        <v>537044</v>
       </c>
       <c r="P312" t="n">
         <v>14200</v>
       </c>
       <c r="Q312" t="n">
-        <v>937200</v>
+        <v>880400</v>
       </c>
     </row>
     <row r="313">
@@ -14026,10 +14026,10 @@
         <v>53</v>
       </c>
       <c r="N319" t="n">
-        <v>3594.252920354</v>
+        <v>3594.2528730512</v>
       </c>
       <c r="O319" t="n">
-        <v>190495.404778762</v>
+        <v>190495.4022717136</v>
       </c>
       <c r="P319" t="n">
         <v>6500</v>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="J323" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -14192,19 +14192,19 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="N323" t="n">
-        <v>3240.8500537634</v>
+        <v>3354.2325655977</v>
       </c>
       <c r="O323" t="n">
-        <v>262508.8543548354</v>
+        <v>231442.0470262413</v>
       </c>
       <c r="P323" t="n">
         <v>5200</v>
       </c>
       <c r="Q323" t="n">
-        <v>421200</v>
+        <v>358800</v>
       </c>
     </row>
     <row r="324">
@@ -14241,10 +14241,10 @@
         <v>102</v>
       </c>
       <c r="N324" t="n">
-        <v>4906.5393169182</v>
+        <v>4891</v>
       </c>
       <c r="O324" t="n">
-        <v>500467.0103256564</v>
+        <v>498882</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="J325" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -14284,19 +14284,19 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="N325" t="n">
         <v>8154</v>
       </c>
       <c r="O325" t="n">
-        <v>513702</v>
+        <v>497394</v>
       </c>
       <c r="P325" t="n">
         <v>13500</v>
       </c>
       <c r="Q325" t="n">
-        <v>850500</v>
+        <v>823500</v>
       </c>
     </row>
     <row r="326">
@@ -14333,10 +14333,10 @@
         <v>44</v>
       </c>
       <c r="N326" t="n">
-        <v>14822.378819914</v>
+        <v>14822.378817006</v>
       </c>
       <c r="O326" t="n">
-        <v>652184.668076216</v>
+        <v>652184.6679482639</v>
       </c>
       <c r="P326" t="n">
         <v>24900</v>
@@ -14421,10 +14421,10 @@
         <v>2</v>
       </c>
       <c r="N328" t="n">
-        <v>2090.85</v>
+        <v>2093.3158067369</v>
       </c>
       <c r="O328" t="n">
-        <v>4181.7</v>
+        <v>4186.6316134738</v>
       </c>
       <c r="P328" t="n">
         <v>2900</v>
@@ -14640,10 +14640,10 @@
         <v>44</v>
       </c>
       <c r="N333" t="n">
-        <v>12422.462992091</v>
+        <v>12422.463</v>
       </c>
       <c r="O333" t="n">
-        <v>546588.371652004</v>
+        <v>546588.372</v>
       </c>
       <c r="P333" t="n">
         <v>19900</v>
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="J334" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="K334" t="n">
         <v>0</v>
@@ -14686,19 +14686,19 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="N334" t="n">
         <v>1381.75</v>
       </c>
       <c r="O334" t="n">
-        <v>619024</v>
+        <v>610733.5</v>
       </c>
       <c r="P334" t="n">
         <v>2500</v>
       </c>
       <c r="Q334" t="n">
-        <v>1120000</v>
+        <v>1105000</v>
       </c>
     </row>
     <row r="335">
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="J337" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14817,19 +14817,19 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="N337" t="n">
-        <v>3472.2762983503</v>
+        <v>3472.276319645</v>
       </c>
       <c r="O337" t="n">
-        <v>784734.4434271677</v>
+        <v>763900.7903219</v>
       </c>
       <c r="P337" t="n">
         <v>5900</v>
       </c>
       <c r="Q337" t="n">
-        <v>1333400</v>
+        <v>1298000</v>
       </c>
     </row>
     <row r="338">
@@ -14998,10 +14998,10 @@
         <v>419</v>
       </c>
       <c r="N341" t="n">
-        <v>3041.6600148478</v>
+        <v>3041.6600148588</v>
       </c>
       <c r="O341" t="n">
-        <v>1274455.546221228</v>
+        <v>1274455.546225837</v>
       </c>
       <c r="P341" t="n">
         <v>5500</v>
@@ -15085,10 +15085,10 @@
         <v>193</v>
       </c>
       <c r="N343" t="n">
-        <v>4371.171263905</v>
+        <v>4371.1712639913</v>
       </c>
       <c r="O343" t="n">
-        <v>843636.053933665</v>
+        <v>843636.0539503209</v>
       </c>
       <c r="P343" t="n">
         <v>8900</v>
@@ -15211,10 +15211,10 @@
         <v>68</v>
       </c>
       <c r="N346" t="n">
-        <v>2224.56</v>
+        <v>2231.2604819277</v>
       </c>
       <c r="O346" t="n">
-        <v>151270.08</v>
+        <v>151725.7127710836</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
@@ -15245,7 +15245,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -15254,19 +15254,19 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="N347" t="n">
         <v>3655.96</v>
       </c>
       <c r="O347" t="n">
-        <v>446027.12</v>
+        <v>409467.52</v>
       </c>
       <c r="P347" t="n">
         <v>5500</v>
       </c>
       <c r="Q347" t="n">
-        <v>671000</v>
+        <v>616000</v>
       </c>
     </row>
     <row r="348">
@@ -15689,7 +15689,7 @@
         </is>
       </c>
       <c r="J357" t="n">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15698,19 +15698,19 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="N357" t="n">
         <v>4648.6</v>
       </c>
       <c r="O357" t="n">
-        <v>1850142.8</v>
+        <v>1682793.2</v>
       </c>
       <c r="P357" t="n">
         <v>8900</v>
       </c>
       <c r="Q357" t="n">
-        <v>3542200</v>
+        <v>3221800</v>
       </c>
     </row>
     <row r="358">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15956,19 +15956,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N363" t="n">
         <v>17472.91</v>
       </c>
       <c r="O363" t="n">
-        <v>4403173.32</v>
+        <v>4385700.41</v>
       </c>
       <c r="P363" t="n">
         <v>2900</v>
       </c>
       <c r="Q363" t="n">
-        <v>730800</v>
+        <v>727900</v>
       </c>
     </row>
     <row r="364">
@@ -16035,7 +16035,7 @@
         </is>
       </c>
       <c r="J365" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -16044,19 +16044,19 @@
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N365" t="n">
         <v>1530.63</v>
       </c>
       <c r="O365" t="n">
-        <v>535720.5</v>
+        <v>534189.87</v>
       </c>
       <c r="P365" t="n">
         <v>2900</v>
       </c>
       <c r="Q365" t="n">
-        <v>1015000</v>
+        <v>1012100</v>
       </c>
     </row>
     <row r="366">
@@ -16135,10 +16135,10 @@
         <v>48</v>
       </c>
       <c r="N367" t="n">
-        <v>9414.309999999999</v>
+        <v>9677.770167910399</v>
       </c>
       <c r="O367" t="n">
-        <v>451886.88</v>
+        <v>464532.9680596992</v>
       </c>
       <c r="P367" t="n">
         <v>16900</v>
@@ -16167,7 +16167,7 @@
         </is>
       </c>
       <c r="J368" t="n">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -16176,19 +16176,19 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="N368" t="n">
         <v>1387.55</v>
       </c>
       <c r="O368" t="n">
-        <v>659086.25</v>
+        <v>650760.95</v>
       </c>
       <c r="P368" t="n">
         <v>2300</v>
       </c>
       <c r="Q368" t="n">
-        <v>1092500</v>
+        <v>1078700</v>
       </c>
     </row>
     <row r="369">
@@ -16703,7 +16703,7 @@
         </is>
       </c>
       <c r="J380" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K380" t="n">
         <v>0</v>
@@ -16712,19 +16712,19 @@
         <v>0</v>
       </c>
       <c r="M380" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N380" t="n">
         <v>11921.4</v>
       </c>
       <c r="O380" t="n">
-        <v>953712</v>
+        <v>941790.6</v>
       </c>
       <c r="P380" t="n">
         <v>19900</v>
       </c>
       <c r="Q380" t="n">
-        <v>1592000</v>
+        <v>1572100</v>
       </c>
     </row>
     <row r="381">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="K388" t="n">
         <v>0</v>
@@ -17052,19 +17052,19 @@
         <v>0</v>
       </c>
       <c r="M388" t="n">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="N388" t="n">
         <v>3751</v>
       </c>
       <c r="O388" t="n">
-        <v>2993298</v>
+        <v>2985796</v>
       </c>
       <c r="P388" t="n">
         <v>6400</v>
       </c>
       <c r="Q388" t="n">
-        <v>5107200</v>
+        <v>5094400</v>
       </c>
     </row>
     <row r="389">
@@ -17092,7 +17092,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -17101,19 +17101,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N389" t="n">
         <v>9903</v>
       </c>
       <c r="O389" t="n">
-        <v>534762</v>
+        <v>505053</v>
       </c>
       <c r="P389" t="n">
         <v>15900</v>
       </c>
       <c r="Q389" t="n">
-        <v>858600</v>
+        <v>810900</v>
       </c>
     </row>
     <row r="390">
@@ -17184,7 +17184,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17193,19 +17193,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="N391" t="n">
-        <v>1630.9247048027</v>
+        <v>1630.9247235872</v>
       </c>
       <c r="O391" t="n">
-        <v>864390.093545431</v>
+        <v>859497.3293304545</v>
       </c>
       <c r="P391" t="n">
         <v>2500</v>
       </c>
       <c r="Q391" t="n">
-        <v>1325000</v>
+        <v>1317500</v>
       </c>
     </row>
     <row r="392">
@@ -17317,7 +17317,7 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
@@ -17326,19 +17326,19 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.5776592798</v>
+        <v>1690.5767609618</v>
       </c>
       <c r="O394" t="n">
-        <v>772593.9902908686</v>
+        <v>760759.5424328099</v>
       </c>
       <c r="P394" t="n">
         <v>2900</v>
       </c>
       <c r="Q394" t="n">
-        <v>1325300</v>
+        <v>1305000</v>
       </c>
     </row>
     <row r="395">
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="J395" t="n">
-        <v>2091</v>
+        <v>2065</v>
       </c>
       <c r="K395" t="n">
         <v>0</v>
@@ -17372,19 +17372,19 @@
         <v>0</v>
       </c>
       <c r="M395" t="n">
-        <v>2091</v>
+        <v>2065</v>
       </c>
       <c r="N395" t="n">
-        <v>1550.1947552537</v>
+        <v>1550.1948069948</v>
       </c>
       <c r="O395" t="n">
-        <v>3241457.233235486</v>
+        <v>3201152.276444262</v>
       </c>
       <c r="P395" t="n">
         <v>2500</v>
       </c>
       <c r="Q395" t="n">
-        <v>5227500</v>
+        <v>5162500</v>
       </c>
     </row>
     <row r="396">
@@ -17455,7 +17455,7 @@
         </is>
       </c>
       <c r="J397" t="n">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="K397" t="n">
         <v>0</v>
@@ -17464,19 +17464,19 @@
         <v>0</v>
       </c>
       <c r="M397" t="n">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="N397" t="n">
-        <v>2403.5212124317</v>
+        <v>2403.5218851304</v>
       </c>
       <c r="O397" t="n">
-        <v>2453995.157892765</v>
+        <v>2427557.103981704</v>
       </c>
       <c r="P397" t="n">
         <v>3500</v>
       </c>
       <c r="Q397" t="n">
-        <v>3573500</v>
+        <v>3535000</v>
       </c>
     </row>
     <row r="398">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="J459" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K459" t="n">
         <v>0</v>
@@ -20163,19 +20163,19 @@
         <v>0</v>
       </c>
       <c r="M459" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N459" t="n">
         <v>9338</v>
       </c>
       <c r="O459" t="n">
-        <v>214774</v>
+        <v>205436</v>
       </c>
       <c r="P459" t="n">
         <v>15500</v>
       </c>
       <c r="Q459" t="n">
-        <v>356500</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="460">
@@ -20854,7 +20854,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -20863,19 +20863,19 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N476" t="n">
         <v>8794.48</v>
       </c>
       <c r="O476" t="n">
-        <v>1266405.12</v>
+        <v>1248816.16</v>
       </c>
       <c r="P476" t="n">
         <v>14500</v>
       </c>
       <c r="Q476" t="n">
-        <v>2088000</v>
+        <v>2059000</v>
       </c>
     </row>
     <row r="477">
@@ -20941,7 +20941,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -20950,19 +20950,19 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="N478" t="n">
         <v>2567</v>
       </c>
       <c r="O478" t="n">
-        <v>777801</v>
+        <v>708492</v>
       </c>
       <c r="P478" t="n">
         <v>4500</v>
       </c>
       <c r="Q478" t="n">
-        <v>1363500</v>
+        <v>1242000</v>
       </c>
     </row>
     <row r="479">
@@ -21769,7 +21769,7 @@
         </is>
       </c>
       <c r="J498" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -21778,19 +21778,19 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N498" t="n">
         <v>24538.02</v>
       </c>
       <c r="O498" t="n">
-        <v>1030596.84</v>
+        <v>1006058.82</v>
       </c>
       <c r="P498" t="n">
         <v>52900</v>
       </c>
       <c r="Q498" t="n">
-        <v>2221800</v>
+        <v>2168900</v>
       </c>
     </row>
     <row r="499">
@@ -21863,10 +21863,10 @@
         <v>145</v>
       </c>
       <c r="N500" t="n">
-        <v>2680.7396933667</v>
+        <v>2680.7396931747</v>
       </c>
       <c r="O500" t="n">
-        <v>388707.2555381715</v>
+        <v>388707.2555103315</v>
       </c>
       <c r="P500" t="n">
         <v>4900</v>
@@ -21904,10 +21904,10 @@
         <v>1306</v>
       </c>
       <c r="N501" t="n">
-        <v>880.32985728346</v>
+        <v>880.3299232103</v>
       </c>
       <c r="O501" t="n">
-        <v>1149710.793612199</v>
+        <v>1149710.879712652</v>
       </c>
       <c r="P501" t="n">
         <v>1200</v>
@@ -22032,10 +22032,10 @@
         <v>17</v>
       </c>
       <c r="N504" t="n">
-        <v>11431.604691358</v>
+        <v>11431.604625</v>
       </c>
       <c r="O504" t="n">
-        <v>194337.279753086</v>
+        <v>194337.278625</v>
       </c>
       <c r="P504" t="n">
         <v>48900</v>
@@ -22184,7 +22184,7 @@
         </is>
       </c>
       <c r="J508" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -22193,19 +22193,19 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N508" t="n">
         <v>26595</v>
       </c>
       <c r="O508" t="n">
-        <v>132975</v>
+        <v>106380</v>
       </c>
       <c r="P508" t="n">
         <v>39900</v>
       </c>
       <c r="Q508" t="n">
-        <v>199500</v>
+        <v>159600</v>
       </c>
     </row>
     <row r="509">
@@ -22544,10 +22544,10 @@
         <v>1</v>
       </c>
       <c r="N516" t="n">
-        <v>6213.167301168</v>
+        <v>6207.988218663</v>
       </c>
       <c r="O516" t="n">
-        <v>6213.167301168</v>
+        <v>6207.988218663</v>
       </c>
       <c r="P516" t="n">
         <v>9900</v>
@@ -22762,10 +22762,10 @@
         <v>267</v>
       </c>
       <c r="N521" t="n">
-        <v>4285.1964303797</v>
+        <v>4285.1964713376</v>
       </c>
       <c r="O521" t="n">
-        <v>1144147.44691138</v>
+        <v>1144147.457847139</v>
       </c>
       <c r="P521" t="n">
         <v>6900</v>
@@ -23441,10 +23441,10 @@
         <v>109</v>
       </c>
       <c r="N537" t="n">
-        <v>3594.9639466192</v>
+        <v>3591.13</v>
       </c>
       <c r="O537" t="n">
-        <v>391851.0701814928</v>
+        <v>391433.17</v>
       </c>
       <c r="P537" t="n">
         <v>6300</v>
@@ -24294,7 +24294,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -24303,19 +24303,19 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N557" t="n">
         <v>21418.04</v>
       </c>
       <c r="O557" t="n">
-        <v>64254.12</v>
+        <v>42836.08</v>
       </c>
       <c r="P557" t="n">
         <v>34900</v>
       </c>
       <c r="Q557" t="n">
-        <v>104700</v>
+        <v>69800</v>
       </c>
     </row>
     <row r="558">
@@ -24787,10 +24787,10 @@
         <v>1</v>
       </c>
       <c r="N568" t="n">
-        <v>13515.55</v>
+        <v>14744.236363636</v>
       </c>
       <c r="O568" t="n">
-        <v>13515.55</v>
+        <v>14744.236363636</v>
       </c>
       <c r="P568" t="n">
         <v>30900</v>
@@ -25118,7 +25118,7 @@
         </is>
       </c>
       <c r="J576" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K576" t="n">
         <v>0</v>
@@ -25127,19 +25127,19 @@
         <v>0</v>
       </c>
       <c r="M576" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N576" t="n">
-        <v>31771.063781513</v>
+        <v>31771.063813559</v>
       </c>
       <c r="O576" t="n">
-        <v>889589.785882364</v>
+        <v>857818.722966093</v>
       </c>
       <c r="P576" t="n">
         <v>68900</v>
       </c>
       <c r="Q576" t="n">
-        <v>1929200</v>
+        <v>1860300</v>
       </c>
     </row>
     <row r="577">
@@ -25164,7 +25164,7 @@
         </is>
       </c>
       <c r="J577" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K577" t="n">
         <v>0</v>
@@ -25173,19 +25173,19 @@
         <v>0</v>
       </c>
       <c r="M577" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N577" t="n">
         <v>5431.12</v>
       </c>
       <c r="O577" t="n">
-        <v>619147.6799999999</v>
+        <v>613716.5599999999</v>
       </c>
       <c r="P577" t="n">
         <v>8900</v>
       </c>
       <c r="Q577" t="n">
-        <v>1014600</v>
+        <v>1005700</v>
       </c>
     </row>
     <row r="578">
@@ -25263,10 +25263,10 @@
         <v>18</v>
       </c>
       <c r="N579" t="n">
-        <v>1561.0057714286</v>
+        <v>1561.0061538462</v>
       </c>
       <c r="O579" t="n">
-        <v>28098.1038857148</v>
+        <v>28098.1107692316</v>
       </c>
       <c r="P579" t="n">
         <v>2900</v>
@@ -25578,10 +25578,10 @@
         <v>125</v>
       </c>
       <c r="N586" t="n">
-        <v>7969.9501716069</v>
+        <v>7969.9501717408</v>
       </c>
       <c r="O586" t="n">
-        <v>996243.7714508625</v>
+        <v>996243.7714676</v>
       </c>
       <c r="P586" t="n">
         <v>12900</v>
@@ -25706,10 +25706,10 @@
         <v>1</v>
       </c>
       <c r="N589" t="n">
-        <v>9808.987924528299</v>
+        <v>9627.34</v>
       </c>
       <c r="O589" t="n">
-        <v>9808.987924528299</v>
+        <v>9627.34</v>
       </c>
       <c r="P589" t="n">
         <v>15900</v>
@@ -26068,7 +26068,7 @@
         </is>
       </c>
       <c r="J598" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K598" t="n">
         <v>0</v>
@@ -26077,19 +26077,19 @@
         <v>0</v>
       </c>
       <c r="M598" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N598" t="n">
         <v>12981.59</v>
       </c>
       <c r="O598" t="n">
-        <v>298576.57</v>
+        <v>285594.98</v>
       </c>
       <c r="P598" t="n">
         <v>21900</v>
       </c>
       <c r="Q598" t="n">
-        <v>503700</v>
+        <v>481800</v>
       </c>
     </row>
     <row r="599">
@@ -26401,7 +26401,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -26410,19 +26410,19 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N606" t="n">
         <v>7836</v>
       </c>
       <c r="O606" t="n">
-        <v>15672</v>
+        <v>7836</v>
       </c>
       <c r="P606" t="n">
         <v>13400</v>
       </c>
       <c r="Q606" t="n">
-        <v>26800</v>
+        <v>13400</v>
       </c>
     </row>
     <row r="607">
@@ -26668,7 +26668,7 @@
         </is>
       </c>
       <c r="J612" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K612" t="n">
         <v>0</v>
@@ -26677,19 +26677,19 @@
         <v>0</v>
       </c>
       <c r="M612" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N612" t="n">
         <v>20504</v>
       </c>
       <c r="O612" t="n">
-        <v>512600</v>
+        <v>492096</v>
       </c>
       <c r="P612" t="n">
         <v>32900</v>
       </c>
       <c r="Q612" t="n">
-        <v>822500</v>
+        <v>789600</v>
       </c>
     </row>
     <row r="613">
@@ -27399,10 +27399,10 @@
         <v>20</v>
       </c>
       <c r="N628" t="n">
-        <v>5218.1705835544</v>
+        <v>5218.1705843293</v>
       </c>
       <c r="O628" t="n">
-        <v>104363.411671088</v>
+        <v>104363.411686586</v>
       </c>
       <c r="P628" t="n">
         <v>8500</v>
@@ -27525,7 +27525,7 @@
         </is>
       </c>
       <c r="J631" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K631" t="n">
         <v>0</v>
@@ -27534,19 +27534,19 @@
         <v>0</v>
       </c>
       <c r="M631" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N631" t="n">
         <v>5194</v>
       </c>
       <c r="O631" t="n">
-        <v>93492</v>
+        <v>88298</v>
       </c>
       <c r="P631" t="n">
         <v>9000</v>
       </c>
       <c r="Q631" t="n">
-        <v>162000</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="632">
@@ -27893,7 +27893,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -27902,19 +27902,19 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N639" t="n">
-        <v>1664.3303780069</v>
+        <v>1664.3295438596</v>
       </c>
       <c r="O639" t="n">
-        <v>456026.5235738906</v>
+        <v>446040.3177543728</v>
       </c>
       <c r="P639" t="n">
         <v>2900</v>
       </c>
       <c r="Q639" t="n">
-        <v>794600</v>
+        <v>777200</v>
       </c>
     </row>
     <row r="640">
@@ -28601,10 +28601,10 @@
         <v>1240</v>
       </c>
       <c r="N654" t="n">
-        <v>1778.4728622951</v>
+        <v>1778.4728660538</v>
       </c>
       <c r="O654" t="n">
-        <v>2205306.349245924</v>
+        <v>2205306.353906712</v>
       </c>
       <c r="P654" t="n">
         <v>4900</v>
@@ -28972,10 +28972,10 @@
         <v>4</v>
       </c>
       <c r="N662" t="n">
-        <v>5148</v>
+        <v>5188.8571428571</v>
       </c>
       <c r="O662" t="n">
-        <v>20592</v>
+        <v>20755.4285714284</v>
       </c>
       <c r="P662" t="n">
         <v>8600</v>
@@ -30527,7 +30527,7 @@
         </is>
       </c>
       <c r="J696" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K696" t="n">
         <v>0</v>
@@ -30536,19 +30536,19 @@
         <v>0</v>
       </c>
       <c r="M696" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N696" t="n">
         <v>28116</v>
       </c>
       <c r="O696" t="n">
-        <v>899712</v>
+        <v>871596</v>
       </c>
       <c r="P696" t="n">
         <v>45900</v>
       </c>
       <c r="Q696" t="n">
-        <v>1468800</v>
+        <v>1422900</v>
       </c>
     </row>
     <row r="697">
@@ -30723,10 +30723,10 @@
         <v>315</v>
       </c>
       <c r="N700" t="n">
-        <v>8873.1568848758</v>
+        <v>8858.16</v>
       </c>
       <c r="O700" t="n">
-        <v>2795044.418735877</v>
+        <v>2790320.4</v>
       </c>
       <c r="P700" t="n">
         <v>15500</v>
@@ -30815,10 +30815,10 @@
         <v>5</v>
       </c>
       <c r="N702" t="n">
-        <v>10411</v>
+        <v>10448.721014493</v>
       </c>
       <c r="O702" t="n">
-        <v>52055</v>
+        <v>52243.605072465</v>
       </c>
       <c r="P702" t="n">
         <v>16900</v>
@@ -32147,10 +32147,10 @@
         <v>9</v>
       </c>
       <c r="N731" t="n">
-        <v>4907.8227078891</v>
+        <v>4907.8227311828</v>
       </c>
       <c r="O731" t="n">
-        <v>44170.4043710019</v>
+        <v>44170.4045806452</v>
       </c>
       <c r="P731" t="n">
         <v>8200</v>
@@ -32227,7 +32227,7 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
@@ -32236,19 +32236,19 @@
         <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="N733" t="n">
         <v>13210</v>
       </c>
       <c r="O733" t="n">
-        <v>2311750</v>
+        <v>2258910</v>
       </c>
       <c r="P733" t="n">
         <v>23900</v>
       </c>
       <c r="Q733" t="n">
-        <v>4182500</v>
+        <v>4086900</v>
       </c>
     </row>
     <row r="734">
@@ -32319,7 +32319,7 @@
         </is>
       </c>
       <c r="J735" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K735" t="n">
         <v>0</v>
@@ -32328,19 +32328,19 @@
         <v>0</v>
       </c>
       <c r="M735" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N735" t="n">
         <v>76839</v>
       </c>
       <c r="O735" t="n">
-        <v>922068</v>
+        <v>845229</v>
       </c>
       <c r="P735" t="n">
         <v>122900</v>
       </c>
       <c r="Q735" t="n">
-        <v>1474800</v>
+        <v>1351900</v>
       </c>
     </row>
     <row r="736">
@@ -32423,10 +32423,10 @@
         <v>22</v>
       </c>
       <c r="N737" t="n">
-        <v>3903.7398185118</v>
+        <v>3903.7398545455</v>
       </c>
       <c r="O737" t="n">
-        <v>85882.2760072596</v>
+        <v>85882.276800001</v>
       </c>
       <c r="P737" t="n">
         <v>7500</v>
@@ -32682,7 +32682,7 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
@@ -32691,19 +32691,19 @@
         <v>0</v>
       </c>
       <c r="M743" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N743" t="n">
         <v>4202</v>
       </c>
       <c r="O743" t="n">
-        <v>239514</v>
+        <v>235312</v>
       </c>
       <c r="P743" t="n">
         <v>7900</v>
       </c>
       <c r="Q743" t="n">
-        <v>450300</v>
+        <v>442400</v>
       </c>
     </row>
     <row r="744">
@@ -32774,7 +32774,7 @@
         </is>
       </c>
       <c r="J745" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K745" t="n">
         <v>0</v>
@@ -32783,19 +32783,19 @@
         <v>0</v>
       </c>
       <c r="M745" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N745" t="n">
         <v>16469</v>
       </c>
       <c r="O745" t="n">
-        <v>1021078</v>
+        <v>988140</v>
       </c>
       <c r="P745" t="n">
         <v>26900</v>
       </c>
       <c r="Q745" t="n">
-        <v>1667800</v>
+        <v>1614000</v>
       </c>
     </row>
     <row r="746">
@@ -32924,10 +32924,10 @@
         <v>73</v>
       </c>
       <c r="N748" t="n">
-        <v>2629</v>
+        <v>2636.2357798165</v>
       </c>
       <c r="O748" t="n">
-        <v>191917</v>
+        <v>192445.2119266045</v>
       </c>
       <c r="P748" t="n">
         <v>4500</v>
@@ -32970,10 +32970,10 @@
         <v>456</v>
       </c>
       <c r="N749" t="n">
-        <v>5869.1723297872</v>
+        <v>5869.1723216187</v>
       </c>
       <c r="O749" t="n">
-        <v>2676342.582382964</v>
+        <v>2676342.578658127</v>
       </c>
       <c r="P749" t="n">
         <v>9500</v>
@@ -33016,10 +33016,10 @@
         <v>90</v>
       </c>
       <c r="N750" t="n">
-        <v>6862.329456869</v>
+        <v>6849.2</v>
       </c>
       <c r="O750" t="n">
-        <v>617609.6511182099</v>
+        <v>616428</v>
       </c>
       <c r="P750" t="n">
         <v>11500</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
@@ -33151,19 +33151,19 @@
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N753" t="n">
         <v>6268</v>
       </c>
       <c r="O753" t="n">
-        <v>507708</v>
+        <v>501440</v>
       </c>
       <c r="P753" t="n">
         <v>10900</v>
       </c>
       <c r="Q753" t="n">
-        <v>882900</v>
+        <v>872000</v>
       </c>
     </row>
     <row r="754">
@@ -33246,10 +33246,10 @@
         <v>210</v>
       </c>
       <c r="N755" t="n">
-        <v>6645</v>
+        <v>6650.5777839955</v>
       </c>
       <c r="O755" t="n">
-        <v>1395450</v>
+        <v>1396621.334639055</v>
       </c>
       <c r="P755" t="n">
         <v>10900</v>
@@ -33280,7 +33280,7 @@
         </is>
       </c>
       <c r="J756" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K756" t="n">
         <v>0</v>
@@ -33289,19 +33289,19 @@
         <v>0</v>
       </c>
       <c r="M756" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N756" t="n">
         <v>13098</v>
       </c>
       <c r="O756" t="n">
-        <v>982350</v>
+        <v>956154</v>
       </c>
       <c r="P756" t="n">
         <v>21200</v>
       </c>
       <c r="Q756" t="n">
-        <v>1590000</v>
+        <v>1547600</v>
       </c>
     </row>
     <row r="757">
@@ -33418,7 +33418,7 @@
         </is>
       </c>
       <c r="J759" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K759" t="n">
         <v>0</v>
@@ -33427,19 +33427,19 @@
         <v>0</v>
       </c>
       <c r="M759" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N759" t="n">
         <v>7562</v>
       </c>
       <c r="O759" t="n">
-        <v>249546</v>
+        <v>226860</v>
       </c>
       <c r="P759" t="n">
         <v>12900</v>
       </c>
       <c r="Q759" t="n">
-        <v>425700</v>
+        <v>387000</v>
       </c>
     </row>
     <row r="760">
@@ -33510,7 +33510,7 @@
         </is>
       </c>
       <c r="J761" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K761" t="n">
         <v>0</v>
@@ -33519,19 +33519,19 @@
         <v>0</v>
       </c>
       <c r="M761" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N761" t="n">
         <v>13565</v>
       </c>
       <c r="O761" t="n">
-        <v>1275110</v>
+        <v>1261545</v>
       </c>
       <c r="P761" t="n">
         <v>22500</v>
       </c>
       <c r="Q761" t="n">
-        <v>2115000</v>
+        <v>2092500</v>
       </c>
     </row>
     <row r="762">
@@ -33648,7 +33648,7 @@
         </is>
       </c>
       <c r="J764" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K764" t="n">
         <v>0</v>
@@ -33657,19 +33657,19 @@
         <v>0</v>
       </c>
       <c r="M764" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N764" t="n">
         <v>5438</v>
       </c>
       <c r="O764" t="n">
-        <v>21752</v>
+        <v>16314</v>
       </c>
       <c r="P764" t="n">
         <v>8900</v>
       </c>
       <c r="Q764" t="n">
-        <v>35600</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="765">
@@ -33789,7 +33789,7 @@
         </is>
       </c>
       <c r="J767" t="n">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="K767" t="n">
         <v>0</v>
@@ -33798,19 +33798,19 @@
         <v>0</v>
       </c>
       <c r="M767" t="n">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="N767" t="n">
         <v>753</v>
       </c>
       <c r="O767" t="n">
-        <v>370476</v>
+        <v>361440</v>
       </c>
       <c r="P767" t="n">
         <v>1600</v>
       </c>
       <c r="Q767" t="n">
-        <v>787200</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="768">
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="J768" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K768" t="n">
         <v>0</v>
@@ -33844,19 +33844,19 @@
         <v>0</v>
       </c>
       <c r="M768" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N768" t="n">
         <v>11302</v>
       </c>
       <c r="O768" t="n">
-        <v>1265824</v>
+        <v>1243220</v>
       </c>
       <c r="P768" t="n">
         <v>18900</v>
       </c>
       <c r="Q768" t="n">
-        <v>2116800</v>
+        <v>2079000</v>
       </c>
     </row>
     <row r="769">
@@ -33881,7 +33881,7 @@
         </is>
       </c>
       <c r="J769" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K769" t="n">
         <v>0</v>
@@ -33890,19 +33890,19 @@
         <v>0</v>
       </c>
       <c r="M769" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="N769" t="n">
         <v>17992</v>
       </c>
       <c r="O769" t="n">
-        <v>1979120</v>
+        <v>1907152</v>
       </c>
       <c r="P769" t="n">
         <v>28900</v>
       </c>
       <c r="Q769" t="n">
-        <v>3179000</v>
+        <v>3063400</v>
       </c>
     </row>
     <row r="770">
@@ -33973,7 +33973,7 @@
         </is>
       </c>
       <c r="J771" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K771" t="n">
         <v>0</v>
@@ -33982,19 +33982,19 @@
         <v>0</v>
       </c>
       <c r="M771" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N771" t="n">
-        <v>17075.98951782</v>
+        <v>17075.989516129</v>
       </c>
       <c r="O771" t="n">
-        <v>2800462.28092248</v>
+        <v>2749234.312096769</v>
       </c>
       <c r="P771" t="n">
         <v>27500</v>
       </c>
       <c r="Q771" t="n">
-        <v>4510000</v>
+        <v>4427500</v>
       </c>
     </row>
     <row r="772">
@@ -34348,10 +34348,10 @@
         <v>25</v>
       </c>
       <c r="N779" t="n">
-        <v>18001</v>
+        <v>18170.288401254</v>
       </c>
       <c r="O779" t="n">
-        <v>450025</v>
+        <v>454257.21003135</v>
       </c>
       <c r="P779" t="n">
         <v>28900</v>
@@ -35075,7 +35075,7 @@
         </is>
       </c>
       <c r="J795" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
@@ -35084,19 +35084,19 @@
         <v>0</v>
       </c>
       <c r="M795" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N795" t="n">
         <v>21762</v>
       </c>
       <c r="O795" t="n">
-        <v>609336</v>
+        <v>587574</v>
       </c>
       <c r="P795" t="n">
         <v>35900</v>
       </c>
       <c r="Q795" t="n">
-        <v>1005200</v>
+        <v>969300</v>
       </c>
     </row>
     <row r="796">
@@ -35167,7 +35167,7 @@
         </is>
       </c>
       <c r="J797" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K797" t="n">
         <v>0</v>
@@ -35176,19 +35176,19 @@
         <v>0</v>
       </c>
       <c r="M797" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N797" t="n">
         <v>15472</v>
       </c>
       <c r="O797" t="n">
-        <v>92832</v>
+        <v>46416</v>
       </c>
       <c r="P797" t="n">
         <v>25900</v>
       </c>
       <c r="Q797" t="n">
-        <v>155400</v>
+        <v>77700</v>
       </c>
     </row>
     <row r="798">
@@ -35630,7 +35630,7 @@
         </is>
       </c>
       <c r="J807" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="K807" t="n">
         <v>0</v>
@@ -35639,19 +35639,19 @@
         <v>0</v>
       </c>
       <c r="M807" t="n">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="N807" t="n">
-        <v>1516.0387269907</v>
+        <v>1516.0387131507</v>
       </c>
       <c r="O807" t="n">
-        <v>591255.103526373</v>
+        <v>530613.549602745</v>
       </c>
       <c r="P807" t="n">
         <v>2300</v>
       </c>
       <c r="Q807" t="n">
-        <v>897000</v>
+        <v>805000</v>
       </c>
     </row>
     <row r="808">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="J810" t="n">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="K810" t="n">
         <v>0</v>
@@ -35775,19 +35775,19 @@
         <v>0</v>
       </c>
       <c r="M810" t="n">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="N810" t="n">
-        <v>2458.5123113728</v>
+        <v>2458.5122801183</v>
       </c>
       <c r="O810" t="n">
-        <v>2682236.931707725</v>
+        <v>2677319.873048829</v>
       </c>
       <c r="P810" t="n">
         <v>3500</v>
       </c>
       <c r="Q810" t="n">
-        <v>3818500</v>
+        <v>3811500</v>
       </c>
     </row>
     <row r="811">
@@ -35870,10 +35870,10 @@
         <v>462</v>
       </c>
       <c r="N812" t="n">
-        <v>1771.0891278195</v>
+        <v>1771.0889280245</v>
       </c>
       <c r="O812" t="n">
-        <v>818243.1770526089</v>
+        <v>818243.084747319</v>
       </c>
       <c r="P812" t="n">
         <v>2500</v>
@@ -35904,7 +35904,7 @@
         </is>
       </c>
       <c r="J813" t="n">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="K813" t="n">
         <v>0</v>
@@ -35913,19 +35913,19 @@
         <v>0</v>
       </c>
       <c r="M813" t="n">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N813" t="n">
-        <v>2079.3832653832</v>
+        <v>2079.383244983</v>
       </c>
       <c r="O813" t="n">
-        <v>1189407.22779919</v>
+        <v>1185248.44964031</v>
       </c>
       <c r="P813" t="n">
         <v>2900</v>
       </c>
       <c r="Q813" t="n">
-        <v>1658800</v>
+        <v>1653000</v>
       </c>
     </row>
     <row r="814">
@@ -35950,7 +35950,7 @@
         </is>
       </c>
       <c r="J814" t="n">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="K814" t="n">
         <v>0</v>
@@ -35959,19 +35959,19 @@
         <v>0</v>
       </c>
       <c r="M814" t="n">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="N814" t="n">
-        <v>1803.0172653236</v>
+        <v>1803.0173791902</v>
       </c>
       <c r="O814" t="n">
-        <v>1669593.987689654</v>
+        <v>1665988.058371745</v>
       </c>
       <c r="P814" t="n">
         <v>2500</v>
       </c>
       <c r="Q814" t="n">
-        <v>2315000</v>
+        <v>2310000</v>
       </c>
     </row>
     <row r="815">
@@ -36008,10 +36008,10 @@
         <v>143</v>
       </c>
       <c r="N815" t="n">
-        <v>3306.5943925234</v>
+        <v>3306.5943307087</v>
       </c>
       <c r="O815" t="n">
-        <v>472842.9981308462</v>
+        <v>472842.9892913441</v>
       </c>
       <c r="P815" t="n">
         <v>4900</v>
@@ -36042,7 +36042,7 @@
         </is>
       </c>
       <c r="J816" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K816" t="n">
         <v>0</v>
@@ -36051,19 +36051,19 @@
         <v>0</v>
       </c>
       <c r="M816" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="N816" t="n">
-        <v>2122.1634734735</v>
+        <v>2122.1634691152</v>
       </c>
       <c r="O816" t="n">
-        <v>797933.466026036</v>
+        <v>793689.1374490848</v>
       </c>
       <c r="P816" t="n">
         <v>2900</v>
       </c>
       <c r="Q816" t="n">
-        <v>1090400</v>
+        <v>1084600</v>
       </c>
     </row>
     <row r="817">
@@ -36088,7 +36088,7 @@
         </is>
       </c>
       <c r="J817" t="n">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="K817" t="n">
         <v>0</v>
@@ -36097,19 +36097,19 @@
         <v>0</v>
       </c>
       <c r="M817" t="n">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="N817" t="n">
-        <v>2108.7974425574</v>
+        <v>2108.7985744681</v>
       </c>
       <c r="O817" t="n">
-        <v>1147185.808751225</v>
+        <v>1138751.230212774</v>
       </c>
       <c r="P817" t="n">
         <v>2900</v>
       </c>
       <c r="Q817" t="n">
-        <v>1577600</v>
+        <v>1566000</v>
       </c>
     </row>
     <row r="818">
@@ -36146,10 +36146,10 @@
         <v>967</v>
       </c>
       <c r="N818" t="n">
-        <v>2056.0819217221</v>
+        <v>2056.081835443</v>
       </c>
       <c r="O818" t="n">
-        <v>1988231.218305271</v>
+        <v>1988231.134873381</v>
       </c>
       <c r="P818" t="n">
         <v>2900</v>
@@ -36238,10 +36238,10 @@
         <v>560</v>
       </c>
       <c r="N820" t="n">
-        <v>1655.9290150913</v>
+        <v>1655.9289976134</v>
       </c>
       <c r="O820" t="n">
-        <v>927320.248451128</v>
+        <v>927320.238663504</v>
       </c>
       <c r="P820" t="n">
         <v>2500</v>
@@ -36459,7 +36459,7 @@
         </is>
       </c>
       <c r="J825" t="n">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="K825" t="n">
         <v>0</v>
@@ -36468,19 +36468,19 @@
         <v>0</v>
       </c>
       <c r="M825" t="n">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="N825" t="n">
         <v>1662</v>
       </c>
       <c r="O825" t="n">
-        <v>837648</v>
+        <v>812718</v>
       </c>
       <c r="P825" t="n">
         <v>2900</v>
       </c>
       <c r="Q825" t="n">
-        <v>1461600</v>
+        <v>1418100</v>
       </c>
     </row>
     <row r="826">
@@ -36505,7 +36505,7 @@
         </is>
       </c>
       <c r="J826" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="K826" t="n">
         <v>0</v>
@@ -36514,19 +36514,19 @@
         <v>0</v>
       </c>
       <c r="M826" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="N826" t="n">
         <v>2003</v>
       </c>
       <c r="O826" t="n">
-        <v>328492</v>
+        <v>296444</v>
       </c>
       <c r="P826" t="n">
         <v>3900</v>
       </c>
       <c r="Q826" t="n">
-        <v>639600</v>
+        <v>577200</v>
       </c>
     </row>
     <row r="827">
@@ -36595,7 +36595,7 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
@@ -36604,19 +36604,19 @@
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N828" t="n">
         <v>5347.73</v>
       </c>
       <c r="O828" t="n">
-        <v>181822.82</v>
+        <v>176475.09</v>
       </c>
       <c r="P828" t="n">
         <v>9500</v>
       </c>
       <c r="Q828" t="n">
-        <v>323000</v>
+        <v>313500</v>
       </c>
     </row>
     <row r="829">
@@ -36699,10 +36699,10 @@
         <v>56</v>
       </c>
       <c r="N830" t="n">
-        <v>2060.158340081</v>
+        <v>2072.7973006135</v>
       </c>
       <c r="O830" t="n">
-        <v>115368.867044536</v>
+        <v>116076.648834356</v>
       </c>
       <c r="P830" t="n">
         <v>2900</v>
@@ -36745,10 +36745,10 @@
         <v>21</v>
       </c>
       <c r="N831" t="n">
-        <v>2546.9795970696</v>
+        <v>2546.9788188976</v>
       </c>
       <c r="O831" t="n">
-        <v>53486.5715384616</v>
+        <v>53486.5551968496</v>
       </c>
       <c r="P831" t="n">
         <v>3900</v>
@@ -36791,10 +36791,10 @@
         <v>175</v>
       </c>
       <c r="N832" t="n">
-        <v>1259.2750273904</v>
+        <v>1259.2751217656</v>
       </c>
       <c r="O832" t="n">
-        <v>220373.12979332</v>
+        <v>220373.14630898</v>
       </c>
       <c r="P832" t="n">
         <v>1900</v>
@@ -36871,7 +36871,7 @@
         </is>
       </c>
       <c r="J834" t="n">
-        <v>802</v>
+        <v>722</v>
       </c>
       <c r="K834" t="n">
         <v>0</v>
@@ -36880,19 +36880,19 @@
         <v>0</v>
       </c>
       <c r="M834" t="n">
-        <v>802</v>
+        <v>722</v>
       </c>
       <c r="N834" t="n">
         <v>1801</v>
       </c>
       <c r="O834" t="n">
-        <v>1444402</v>
+        <v>1300322</v>
       </c>
       <c r="P834" t="n">
         <v>2900</v>
       </c>
       <c r="Q834" t="n">
-        <v>2325800</v>
+        <v>2093800</v>
       </c>
     </row>
     <row r="835">
@@ -36927,10 +36927,10 @@
         <v>13</v>
       </c>
       <c r="N835" t="n">
-        <v>692.1524551748601</v>
+        <v>692.15249234096</v>
       </c>
       <c r="O835" t="n">
-        <v>8997.98191727318</v>
+        <v>8997.98240043248</v>
       </c>
       <c r="P835" t="n">
         <v>1200</v>
@@ -37241,7 +37241,7 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
@@ -37250,19 +37250,19 @@
         <v>0</v>
       </c>
       <c r="M842" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N842" t="n">
         <v>13518</v>
       </c>
       <c r="O842" t="n">
-        <v>594792</v>
+        <v>567756</v>
       </c>
       <c r="P842" t="n">
         <v>21900</v>
       </c>
       <c r="Q842" t="n">
-        <v>963600</v>
+        <v>919800</v>
       </c>
     </row>
     <row r="843">
@@ -37388,7 +37388,7 @@
         </is>
       </c>
       <c r="J845" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="K845" t="n">
         <v>0</v>
@@ -37397,19 +37397,19 @@
         <v>0</v>
       </c>
       <c r="M845" t="n">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="N845" t="n">
         <v>5215</v>
       </c>
       <c r="O845" t="n">
-        <v>657090</v>
+        <v>458920</v>
       </c>
       <c r="P845" t="n">
         <v>8900</v>
       </c>
       <c r="Q845" t="n">
-        <v>1121400</v>
+        <v>783200</v>
       </c>
     </row>
     <row r="846">
@@ -38686,10 +38686,10 @@
         <v>1071</v>
       </c>
       <c r="N873" t="n">
-        <v>628</v>
+        <v>631.09868421053</v>
       </c>
       <c r="O873" t="n">
-        <v>672588</v>
+        <v>675906.6907894777</v>
       </c>
       <c r="P873" t="n">
         <v>1400</v>
@@ -38823,10 +38823,10 @@
         <v>561</v>
       </c>
       <c r="N876" t="n">
-        <v>481.48790873239</v>
+        <v>481.48790068997</v>
       </c>
       <c r="O876" t="n">
-        <v>270114.7167988708</v>
+        <v>270114.7122870731</v>
       </c>
       <c r="P876" t="n">
         <v>650</v>
@@ -38916,10 +38916,10 @@
         <v>575</v>
       </c>
       <c r="N878" t="n">
-        <v>872.15418687873</v>
+        <v>872.15420863309</v>
       </c>
       <c r="O878" t="n">
-        <v>501488.6574552698</v>
+        <v>501488.6699640267</v>
       </c>
       <c r="P878" t="n">
         <v>1200</v>
@@ -40056,7 +40056,7 @@
         </is>
       </c>
       <c r="J904" t="n">
-        <v>2876</v>
+        <v>2716</v>
       </c>
       <c r="K904" t="n">
         <v>0</v>
@@ -40065,19 +40065,19 @@
         <v>0</v>
       </c>
       <c r="M904" t="n">
-        <v>2876</v>
+        <v>2716</v>
       </c>
       <c r="N904" t="n">
-        <v>517.29583827893</v>
+        <v>517.29622957051</v>
       </c>
       <c r="O904" t="n">
-        <v>1487742.830890203</v>
+        <v>1404976.559513505</v>
       </c>
       <c r="P904" t="n">
         <v>900</v>
       </c>
       <c r="Q904" t="n">
-        <v>2588400</v>
+        <v>2444400</v>
       </c>
     </row>
     <row r="905">
@@ -40282,7 +40282,7 @@
         </is>
       </c>
       <c r="J909" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K909" t="n">
         <v>0</v>
@@ -40291,19 +40291,19 @@
         <v>0</v>
       </c>
       <c r="M909" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="N909" t="n">
-        <v>3110.8359331476</v>
+        <v>3110.8357056207</v>
       </c>
       <c r="O909" t="n">
-        <v>1007910.842339822</v>
+        <v>967469.9044480377</v>
       </c>
       <c r="P909" t="n">
         <v>4500</v>
       </c>
       <c r="Q909" t="n">
-        <v>1458000</v>
+        <v>1399500</v>
       </c>
     </row>
     <row r="910">
@@ -40504,7 +40504,7 @@
         </is>
       </c>
       <c r="J914" t="n">
-        <v>1122</v>
+        <v>1050</v>
       </c>
       <c r="K914" t="n">
         <v>0</v>
@@ -40513,19 +40513,19 @@
         <v>0</v>
       </c>
       <c r="M914" t="n">
-        <v>1122</v>
+        <v>1050</v>
       </c>
       <c r="N914" t="n">
-        <v>703.79468467395</v>
+        <v>703.79465893216</v>
       </c>
       <c r="O914" t="n">
-        <v>789657.6362041719</v>
+        <v>738984.391878768</v>
       </c>
       <c r="P914" t="n">
         <v>900</v>
       </c>
       <c r="Q914" t="n">
-        <v>1009800</v>
+        <v>945000</v>
       </c>
     </row>
     <row r="915">
@@ -40745,10 +40745,10 @@
         <v>3</v>
       </c>
       <c r="N919" t="n">
-        <v>2501.3843455497</v>
+        <v>2501.3841304348</v>
       </c>
       <c r="O919" t="n">
-        <v>7504.1530366491</v>
+        <v>7504.1523913044</v>
       </c>
       <c r="P919" t="n">
         <v>4100</v>
@@ -42089,7 +42089,7 @@
         </is>
       </c>
       <c r="J949" t="n">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="K949" t="n">
         <v>0</v>
@@ -42098,19 +42098,19 @@
         <v>0</v>
       </c>
       <c r="M949" t="n">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N949" t="n">
         <v>1669.6</v>
       </c>
       <c r="O949" t="n">
-        <v>873200.7999999999</v>
+        <v>868192</v>
       </c>
       <c r="P949" t="n">
         <v>2900</v>
       </c>
       <c r="Q949" t="n">
-        <v>1516700</v>
+        <v>1508000</v>
       </c>
     </row>
     <row r="950">
@@ -42670,10 +42670,10 @@
         <v>12</v>
       </c>
       <c r="N961" t="n">
-        <v>3414.5660094637</v>
+        <v>3414.5659584665</v>
       </c>
       <c r="O961" t="n">
-        <v>40974.7921135644</v>
+        <v>40974.791501598</v>
       </c>
       <c r="P961" t="n">
         <v>3500</v>
@@ -42719,10 +42719,10 @@
         <v>54</v>
       </c>
       <c r="N962" t="n">
-        <v>3067.0906185567</v>
+        <v>3099.0394791667</v>
       </c>
       <c r="O962" t="n">
-        <v>165622.8934020618</v>
+        <v>167348.1318750018</v>
       </c>
       <c r="P962" t="n">
         <v>7200</v>
@@ -43593,10 +43593,10 @@
         <v>2</v>
       </c>
       <c r="N981" t="n">
-        <v>2000.7273195876</v>
+        <v>2000.7364130435</v>
       </c>
       <c r="O981" t="n">
-        <v>4001.4546391752</v>
+        <v>4001.472826087</v>
       </c>
       <c r="P981" t="n">
         <v>2000</v>
@@ -43972,10 +43972,10 @@
         <v>174</v>
       </c>
       <c r="N989" t="n">
-        <v>7046.9398265771</v>
+        <v>7046.9398263889</v>
       </c>
       <c r="O989" t="n">
-        <v>1226167.529824415</v>
+        <v>1226167.529791669</v>
       </c>
       <c r="P989" t="n">
         <v>9900</v>
@@ -45076,10 +45076,10 @@
         <v>289</v>
       </c>
       <c r="N1013" t="n">
-        <v>2703.2000014449</v>
+        <v>2703.2000014451</v>
       </c>
       <c r="O1013" t="n">
-        <v>781224.8004175761</v>
+        <v>781224.800417634</v>
       </c>
       <c r="P1013" t="n">
         <v>4500</v>
@@ -45448,7 +45448,7 @@
         </is>
       </c>
       <c r="J1022" t="n">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="K1022" t="n">
         <v>0</v>
@@ -45457,19 +45457,19 @@
         <v>0</v>
       </c>
       <c r="M1022" t="n">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="N1022" t="n">
         <v>6761.25</v>
       </c>
       <c r="O1022" t="n">
-        <v>3346818.75</v>
+        <v>3265683.75</v>
       </c>
       <c r="P1022" t="n">
         <v>5200</v>
       </c>
       <c r="Q1022" t="n">
-        <v>2574000</v>
+        <v>2511600</v>
       </c>
     </row>
     <row r="1023">
@@ -45799,10 +45799,10 @@
         <v>88</v>
       </c>
       <c r="N1030" t="n">
-        <v>2738.6959359606</v>
+        <v>2738.6958015267</v>
       </c>
       <c r="O1030" t="n">
-        <v>241005.2423645328</v>
+        <v>241005.2305343496</v>
       </c>
       <c r="P1030" t="n">
         <v>2800</v>
@@ -46362,10 +46362,10 @@
         <v>1</v>
       </c>
       <c r="N1043" t="n">
-        <v>2988.7998653199</v>
+        <v>2988.7998648649</v>
       </c>
       <c r="O1043" t="n">
-        <v>2988.7998653199</v>
+        <v>2988.7998648649</v>
       </c>
       <c r="P1043" t="n">
         <v>3800</v>
@@ -46523,7 +46523,7 @@
         </is>
       </c>
       <c r="J1047" t="n">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="K1047" t="n">
         <v>0</v>
@@ -46532,19 +46532,19 @@
         <v>0</v>
       </c>
       <c r="M1047" t="n">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="N1047" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1047" t="n">
-        <v>763656</v>
+        <v>677744.7000000001</v>
       </c>
       <c r="P1047" t="n">
         <v>5100</v>
       </c>
       <c r="Q1047" t="n">
-        <v>1224000</v>
+        <v>1086300</v>
       </c>
     </row>
     <row r="1048">
@@ -46661,10 +46661,10 @@
         <v>165</v>
       </c>
       <c r="N1050" t="n">
-        <v>1794.2879574714</v>
+        <v>1794.2879512478</v>
       </c>
       <c r="O1050" t="n">
-        <v>296057.512982781</v>
+        <v>296057.511955887</v>
       </c>
       <c r="P1050" t="n">
         <v>1600</v>
@@ -47013,10 +47013,10 @@
         <v>29</v>
       </c>
       <c r="N1058" t="n">
-        <v>2523.3377355278</v>
+        <v>2523.3377277904</v>
       </c>
       <c r="O1058" t="n">
-        <v>73176.79433030619</v>
+        <v>73176.79410592161</v>
       </c>
       <c r="P1058" t="n">
         <v>2800</v>
@@ -47177,10 +47177,10 @@
         <v>18</v>
       </c>
       <c r="N1062" t="n">
-        <v>2271.5972749591</v>
+        <v>2271.5972682527</v>
       </c>
       <c r="O1062" t="n">
-        <v>40888.75094926381</v>
+        <v>40888.7508285486</v>
       </c>
       <c r="P1062" t="n">
         <v>2900</v>
@@ -47914,10 +47914,10 @@
         <v>7</v>
       </c>
       <c r="N1079" t="n">
-        <v>1757.3206220096</v>
+        <v>1757.3206341463</v>
       </c>
       <c r="O1079" t="n">
-        <v>12301.2443540672</v>
+        <v>12301.2444390241</v>
       </c>
       <c r="P1079" t="n">
         <v>2000</v>
@@ -48055,10 +48055,10 @@
         <v>57</v>
       </c>
       <c r="N1082" t="n">
-        <v>2367.6159558824</v>
+        <v>2367.6159259259</v>
       </c>
       <c r="O1082" t="n">
-        <v>134954.1094852968</v>
+        <v>134954.1077777763</v>
       </c>
       <c r="P1082" t="n">
         <v>2900</v>
@@ -48951,7 +48951,7 @@
         </is>
       </c>
       <c r="J1102" t="n">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="K1102" t="n">
         <v>0</v>
@@ -48960,19 +48960,19 @@
         <v>0</v>
       </c>
       <c r="M1102" t="n">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="N1102" t="n">
         <v>1056</v>
       </c>
       <c r="O1102" t="n">
-        <v>1194336</v>
+        <v>1181664</v>
       </c>
       <c r="P1102" t="n">
         <v>1400</v>
       </c>
       <c r="Q1102" t="n">
-        <v>1583400</v>
+        <v>1566600</v>
       </c>
     </row>
     <row r="1103">
@@ -49000,7 +49000,7 @@
         </is>
       </c>
       <c r="J1103" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K1103" t="n">
         <v>0</v>
@@ -49009,19 +49009,19 @@
         <v>0</v>
       </c>
       <c r="M1103" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="N1103" t="n">
         <v>7920</v>
       </c>
       <c r="O1103" t="n">
-        <v>1029600</v>
+        <v>982080</v>
       </c>
       <c r="P1103" t="n">
         <v>10500</v>
       </c>
       <c r="Q1103" t="n">
-        <v>1365000</v>
+        <v>1302000</v>
       </c>
     </row>
     <row r="1104">
@@ -49049,7 +49049,7 @@
         </is>
       </c>
       <c r="J1104" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K1104" t="n">
         <v>0</v>
@@ -49058,19 +49058,19 @@
         <v>0</v>
       </c>
       <c r="M1104" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N1104" t="n">
         <v>7920</v>
       </c>
       <c r="O1104" t="n">
-        <v>681120</v>
+        <v>633600</v>
       </c>
       <c r="P1104" t="n">
         <v>10500</v>
       </c>
       <c r="Q1104" t="n">
-        <v>903000</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="1105">
@@ -50870,27 +50870,17 @@
     <row r="1144">
       <c r="A1144" t="inlineStr">
         <is>
-          <t>MG40952</t>
-        </is>
-      </c>
-      <c r="B1144" t="inlineStr">
-        <is>
-          <t>MG40952</t>
+          <t>P155</t>
         </is>
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>CAMIONETA BLACK MG40952</t>
-        </is>
-      </c>
-      <c r="E1144" t="inlineStr">
-        <is>
-          <t>CARROS</t>
+          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
         </is>
       </c>
       <c r="I1144" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1144" t="n">
@@ -50906,27 +50896,27 @@
         <v>1</v>
       </c>
       <c r="N1144" t="n">
-        <v>38043.57</v>
+        <v>1461.53</v>
       </c>
       <c r="O1144" t="n">
-        <v>38043.57</v>
+        <v>1461.53</v>
       </c>
       <c r="P1144" t="n">
-        <v>70900</v>
+        <v>1900</v>
       </c>
       <c r="Q1144" t="n">
-        <v>70900</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="inlineStr">
         <is>
-          <t>P155</t>
+          <t>P214</t>
         </is>
       </c>
       <c r="C1145" t="inlineStr">
         <is>
-          <t>BT-3002 LAPIZ PORTAMINAS CONEJO</t>
+          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
         </is>
       </c>
       <c r="I1145" t="inlineStr">
@@ -50947,27 +50937,27 @@
         <v>1</v>
       </c>
       <c r="N1145" t="n">
-        <v>1461.53</v>
+        <v>3153.85</v>
       </c>
       <c r="O1145" t="n">
-        <v>1461.53</v>
+        <v>3153.85</v>
       </c>
       <c r="P1145" t="n">
-        <v>1900</v>
+        <v>4100</v>
       </c>
       <c r="Q1145" t="n">
-        <v>1900</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="1146">
       <c r="A1146" t="inlineStr">
         <is>
-          <t>P214</t>
+          <t>P458</t>
         </is>
       </c>
       <c r="C1146" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLOBO FELIZ CUMPLEAÑOS COLORES VIVOS </t>
+          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
         </is>
       </c>
       <c r="I1146" t="inlineStr">
@@ -50976,7 +50966,7 @@
         </is>
       </c>
       <c r="J1146" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="K1146" t="n">
         <v>0</v>
@@ -50985,39 +50975,44 @@
         <v>0</v>
       </c>
       <c r="M1146" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="N1146" t="n">
-        <v>3153.85</v>
+        <v>1230.76</v>
       </c>
       <c r="O1146" t="n">
-        <v>3153.85</v>
+        <v>39384.32</v>
       </c>
       <c r="P1146" t="n">
-        <v>4100</v>
+        <v>1600</v>
       </c>
       <c r="Q1146" t="n">
-        <v>4100</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147" t="inlineStr">
         <is>
-          <t>P458</t>
+          <t>PT14026</t>
         </is>
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>IF2826 VELAS COLRES SURTIDOSX6 P548</t>
+          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1147" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1147" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K1147" t="n">
         <v>0</v>
@@ -51026,44 +51021,39 @@
         <v>0</v>
       </c>
       <c r="M1147" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="N1147" t="n">
-        <v>1230.76</v>
+        <v>2690.69</v>
       </c>
       <c r="O1147" t="n">
-        <v>39384.32</v>
+        <v>2690.69</v>
       </c>
       <c r="P1147" t="n">
-        <v>1600</v>
+        <v>5900</v>
       </c>
       <c r="Q1147" t="n">
-        <v>51200</v>
+        <v>5900</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148" t="inlineStr">
         <is>
-          <t>PT14026</t>
+          <t>Q1241</t>
         </is>
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
-        </is>
-      </c>
-      <c r="E1148" t="inlineStr">
-        <is>
-          <t>DIDACTICOS</t>
+          <t>RESALTADOR BOTELLA</t>
         </is>
       </c>
       <c r="I1148" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1148" t="n">
         <v>0</v>
@@ -51072,39 +51062,44 @@
         <v>0</v>
       </c>
       <c r="M1148" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1148" t="n">
-        <v>2690.69</v>
+        <v>5000</v>
       </c>
       <c r="O1148" t="n">
-        <v>2690.69</v>
+        <v>15000</v>
       </c>
       <c r="P1148" t="n">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="Q1148" t="n">
-        <v>5900</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149" t="inlineStr">
         <is>
-          <t>Q1241</t>
+          <t>QH-8308</t>
         </is>
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>RESALTADOR BOTELLA</t>
+          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1149" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1149" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K1149" t="n">
         <v>0</v>
@@ -51113,30 +51108,30 @@
         <v>0</v>
       </c>
       <c r="M1149" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N1149" t="n">
-        <v>5000</v>
+        <v>2200</v>
       </c>
       <c r="O1149" t="n">
-        <v>15000</v>
+        <v>26400</v>
       </c>
       <c r="P1149" t="n">
-        <v>6000</v>
+        <v>2700</v>
       </c>
       <c r="Q1149" t="n">
-        <v>18000</v>
+        <v>32400</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150" t="inlineStr">
         <is>
-          <t>QH-8308</t>
+          <t>QH-8311</t>
         </is>
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+          <t>SET BORRADORES ANIMALES QH-8311</t>
         </is>
       </c>
       <c r="E1150" t="inlineStr">
@@ -51150,7 +51145,7 @@
         </is>
       </c>
       <c r="J1150" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K1150" t="n">
         <v>0</v>
@@ -51159,30 +51154,30 @@
         <v>0</v>
       </c>
       <c r="M1150" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N1150" t="n">
         <v>2200</v>
       </c>
       <c r="O1150" t="n">
-        <v>26400</v>
+        <v>19800</v>
       </c>
       <c r="P1150" t="n">
         <v>2700</v>
       </c>
       <c r="Q1150" t="n">
-        <v>32400</v>
+        <v>24300</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
-          <t>QH-8311</t>
+          <t>QH-8314</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>SET BORRADORES ANIMALES QH-8311</t>
+          <t>SET BORRADORES DEPORTES QH-8314</t>
         </is>
       </c>
       <c r="E1151" t="inlineStr">
@@ -51196,7 +51191,7 @@
         </is>
       </c>
       <c r="J1151" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K1151" t="n">
         <v>0</v>
@@ -51205,30 +51200,30 @@
         <v>0</v>
       </c>
       <c r="M1151" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N1151" t="n">
         <v>2200</v>
       </c>
       <c r="O1151" t="n">
-        <v>19800</v>
+        <v>35200</v>
       </c>
       <c r="P1151" t="n">
         <v>2700</v>
       </c>
       <c r="Q1151" t="n">
-        <v>24300</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152" t="inlineStr">
         <is>
-          <t>QH-8314</t>
+          <t>QH-8317</t>
         </is>
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>SET BORRADORES DEPORTES QH-8314</t>
+          <t>SET BORRADORES POSTRES QH-8317</t>
         </is>
       </c>
       <c r="E1152" t="inlineStr">
@@ -51242,7 +51237,7 @@
         </is>
       </c>
       <c r="J1152" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K1152" t="n">
         <v>0</v>
@@ -51251,30 +51246,30 @@
         <v>0</v>
       </c>
       <c r="M1152" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="N1152" t="n">
         <v>2200</v>
       </c>
       <c r="O1152" t="n">
-        <v>35200</v>
+        <v>15400</v>
       </c>
       <c r="P1152" t="n">
         <v>2700</v>
       </c>
       <c r="Q1152" t="n">
-        <v>43200</v>
+        <v>18900</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153" t="inlineStr">
         <is>
-          <t>QH-8317</t>
+          <t>QH-8385</t>
         </is>
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>SET BORRADORES POSTRES QH-8317</t>
+          <t>SET BORRADORES ESPACIAL QH-8385</t>
         </is>
       </c>
       <c r="E1153" t="inlineStr">
@@ -51288,7 +51283,7 @@
         </is>
       </c>
       <c r="J1153" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K1153" t="n">
         <v>0</v>
@@ -51297,30 +51292,30 @@
         <v>0</v>
       </c>
       <c r="M1153" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N1153" t="n">
         <v>2200</v>
       </c>
       <c r="O1153" t="n">
-        <v>15400</v>
+        <v>4400</v>
       </c>
       <c r="P1153" t="n">
         <v>2700</v>
       </c>
       <c r="Q1153" t="n">
-        <v>18900</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154" t="inlineStr">
         <is>
-          <t>QH-8385</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C1154" t="inlineStr">
         <is>
-          <t>SET BORRADORES ESPACIAL QH-8385</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E1154" t="inlineStr">
@@ -51334,7 +51329,7 @@
         </is>
       </c>
       <c r="J1154" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="K1154" t="n">
         <v>0</v>
@@ -51343,30 +51338,30 @@
         <v>0</v>
       </c>
       <c r="M1154" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="N1154" t="n">
         <v>2200</v>
       </c>
       <c r="O1154" t="n">
-        <v>4400</v>
+        <v>158400</v>
       </c>
       <c r="P1154" t="n">
         <v>2700</v>
       </c>
       <c r="Q1154" t="n">
-        <v>5400</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QQ-1503</t>
         </is>
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
         </is>
       </c>
       <c r="E1155" t="inlineStr">
@@ -51380,7 +51375,7 @@
         </is>
       </c>
       <c r="J1155" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K1155" t="n">
         <v>0</v>
@@ -51389,30 +51384,30 @@
         <v>0</v>
       </c>
       <c r="M1155" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N1155" t="n">
         <v>2200</v>
       </c>
       <c r="O1155" t="n">
-        <v>158400</v>
+        <v>151800</v>
       </c>
       <c r="P1155" t="n">
         <v>2700</v>
       </c>
       <c r="Q1155" t="n">
-        <v>194400</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
         <is>
-          <t>QQ-1503</t>
+          <t>QQ-1525</t>
         </is>
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CARRITO QQ-1503</t>
+          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
         </is>
       </c>
       <c r="E1156" t="inlineStr">
@@ -51426,7 +51421,7 @@
         </is>
       </c>
       <c r="J1156" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K1156" t="n">
         <v>0</v>
@@ -51435,30 +51430,30 @@
         <v>0</v>
       </c>
       <c r="M1156" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N1156" t="n">
         <v>2200</v>
       </c>
       <c r="O1156" t="n">
-        <v>151800</v>
+        <v>147400</v>
       </c>
       <c r="P1156" t="n">
         <v>2700</v>
       </c>
       <c r="Q1156" t="n">
-        <v>186300</v>
+        <v>180900</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157" t="inlineStr">
         <is>
-          <t>QQ-1525</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO RETRACTIL CAPOBARA QQ-1525</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E1157" t="inlineStr">
@@ -51472,7 +51467,7 @@
         </is>
       </c>
       <c r="J1157" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="K1157" t="n">
         <v>0</v>
@@ -51481,30 +51476,30 @@
         <v>0</v>
       </c>
       <c r="M1157" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="N1157" t="n">
-        <v>2200</v>
+        <v>5026.665826087</v>
       </c>
       <c r="O1157" t="n">
-        <v>154000</v>
+        <v>70373.32156521799</v>
       </c>
       <c r="P1157" t="n">
-        <v>2700</v>
+        <v>6300</v>
       </c>
       <c r="Q1157" t="n">
-        <v>189000</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E1158" t="inlineStr">
@@ -51518,7 +51513,7 @@
         </is>
       </c>
       <c r="J1158" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K1158" t="n">
         <v>0</v>
@@ -51527,30 +51522,30 @@
         <v>0</v>
       </c>
       <c r="M1158" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N1158" t="n">
-        <v>5026.665826087</v>
+        <v>5200</v>
       </c>
       <c r="O1158" t="n">
-        <v>70373.32156521799</v>
+        <v>78000</v>
       </c>
       <c r="P1158" t="n">
         <v>6300</v>
       </c>
       <c r="Q1158" t="n">
-        <v>88200</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>QT512452-E</t>
         </is>
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
         </is>
       </c>
       <c r="E1159" t="inlineStr">
@@ -51564,7 +51559,7 @@
         </is>
       </c>
       <c r="J1159" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K1159" t="n">
         <v>0</v>
@@ -51573,30 +51568,30 @@
         <v>0</v>
       </c>
       <c r="M1159" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N1159" t="n">
-        <v>5200</v>
+        <v>8800</v>
       </c>
       <c r="O1159" t="n">
-        <v>78000</v>
+        <v>149600</v>
       </c>
       <c r="P1159" t="n">
-        <v>6300</v>
+        <v>10600</v>
       </c>
       <c r="Q1159" t="n">
-        <v>94500</v>
+        <v>180200</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>QT512452-E</t>
+          <t>QT512453-E</t>
         </is>
       </c>
       <c r="C1160" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
         </is>
       </c>
       <c r="E1160" t="inlineStr">
@@ -51637,26 +51632,21 @@
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>S145</t>
         </is>
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
-        </is>
-      </c>
-      <c r="E1161" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
         </is>
       </c>
       <c r="I1161" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1161" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K1161" t="n">
         <v>0</v>
@@ -51665,39 +51655,44 @@
         <v>0</v>
       </c>
       <c r="M1161" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N1161" t="n">
-        <v>8800</v>
+        <v>11538.4</v>
       </c>
       <c r="O1161" t="n">
-        <v>149600</v>
+        <v>11538.4</v>
       </c>
       <c r="P1161" t="n">
-        <v>10600</v>
+        <v>15000</v>
       </c>
       <c r="Q1161" t="n">
-        <v>180200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
         <is>
-          <t>S145</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR SIN CAJA MEDIANAS</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1162" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1162" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="K1162" t="n">
         <v>0</v>
@@ -51706,30 +51701,30 @@
         <v>0</v>
       </c>
       <c r="M1162" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="N1162" t="n">
-        <v>11538.4</v>
+        <v>4550</v>
       </c>
       <c r="O1162" t="n">
-        <v>11538.4</v>
+        <v>1101100</v>
       </c>
       <c r="P1162" t="n">
-        <v>15000</v>
+        <v>5500</v>
       </c>
       <c r="Q1162" t="n">
-        <v>15000</v>
+        <v>1331000</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
@@ -51743,7 +51738,7 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="K1163" t="n">
         <v>0</v>
@@ -51752,44 +51747,39 @@
         <v>0</v>
       </c>
       <c r="M1163" t="n">
-        <v>242</v>
+        <v>2</v>
       </c>
       <c r="N1163" t="n">
-        <v>4550</v>
+        <v>1059.1855263158</v>
       </c>
       <c r="O1163" t="n">
-        <v>1101100</v>
+        <v>2118.3710526316</v>
       </c>
       <c r="P1163" t="n">
-        <v>5500</v>
+        <v>9500</v>
       </c>
       <c r="Q1163" t="n">
-        <v>1331000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>SY-661-A08</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
-        </is>
-      </c>
-      <c r="E1164" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>RESALTADOR SUPER HEROES</t>
         </is>
       </c>
       <c r="I1164" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -51798,30 +51788,30 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N1164" t="n">
-        <v>1059.1855263158</v>
+        <v>7500</v>
       </c>
       <c r="O1164" t="n">
-        <v>2118.3710526316</v>
+        <v>45000</v>
       </c>
       <c r="P1164" t="n">
-        <v>9500</v>
+        <v>9000</v>
       </c>
       <c r="Q1164" t="n">
-        <v>19000</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>SY-661-A08</t>
+          <t>SY-661-A09</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER HEROES</t>
+          <t>RESALTADOR SUPER MARIO</t>
         </is>
       </c>
       <c r="I1165" t="inlineStr">
@@ -51830,7 +51820,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -51839,39 +51829,44 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N1165" t="n">
         <v>7500</v>
       </c>
       <c r="O1165" t="n">
-        <v>45000</v>
+        <v>105000</v>
       </c>
       <c r="P1165" t="n">
         <v>9000</v>
       </c>
       <c r="Q1165" t="n">
-        <v>54000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>SY-661-A09</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>RESALTADOR SUPER MARIO</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1166" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -51880,30 +51875,30 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="N1166" t="n">
-        <v>7500</v>
+        <v>12392.16</v>
       </c>
       <c r="O1166" t="n">
-        <v>105000</v>
+        <v>24784.32</v>
       </c>
       <c r="P1166" t="n">
-        <v>9000</v>
+        <v>15900</v>
       </c>
       <c r="Q1166" t="n">
-        <v>126000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
@@ -51929,27 +51924,27 @@
         <v>2</v>
       </c>
       <c r="N1167" t="n">
-        <v>12392.16</v>
+        <v>5186.45</v>
       </c>
       <c r="O1167" t="n">
-        <v>24784.32</v>
+        <v>10372.9</v>
       </c>
       <c r="P1167" t="n">
-        <v>15900</v>
+        <v>7200</v>
       </c>
       <c r="Q1167" t="n">
-        <v>31800</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T219</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
@@ -51963,7 +51958,7 @@
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -51972,44 +51967,39 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N1168" t="n">
-        <v>5186.45</v>
+        <v>8746.92</v>
       </c>
       <c r="O1168" t="n">
-        <v>10372.9</v>
+        <v>87469.2</v>
       </c>
       <c r="P1168" t="n">
-        <v>7200</v>
+        <v>11000</v>
       </c>
       <c r="Q1168" t="n">
-        <v>14400</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>T219</t>
+          <t>WT-E170</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
-        </is>
-      </c>
-      <c r="E1169" t="inlineStr">
-        <is>
-          <t>PELUCHES</t>
+          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
         </is>
       </c>
       <c r="I1169" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -52018,39 +52008,44 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N1169" t="n">
-        <v>8746.92</v>
+        <v>73405.77</v>
       </c>
       <c r="O1169" t="n">
-        <v>87469.2</v>
+        <v>367028.85</v>
       </c>
       <c r="P1169" t="n">
-        <v>11000</v>
+        <v>77900</v>
       </c>
       <c r="Q1169" t="n">
-        <v>110000</v>
+        <v>389500</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>WT-E170</t>
+          <t>XP-2984</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>WT-E170 RODILLO PARA ABDOMINALES</t>
+          <t>BORRADOR RETRACTIL XP-2984</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -52059,30 +52054,30 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="N1170" t="n">
-        <v>73405.77</v>
+        <v>2403.9768595041</v>
       </c>
       <c r="O1170" t="n">
-        <v>367028.85</v>
+        <v>88947.14380165171</v>
       </c>
       <c r="P1170" t="n">
-        <v>77900</v>
+        <v>3000</v>
       </c>
       <c r="Q1170" t="n">
-        <v>389500</v>
+        <v>111000</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>XP-2984</t>
+          <t>XP-2986</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL XP-2984</t>
+          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
@@ -52096,7 +52091,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -52105,44 +52100,39 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N1171" t="n">
-        <v>2403.9768595041</v>
+        <v>2402.674057971</v>
       </c>
       <c r="O1171" t="n">
-        <v>88947.14380165171</v>
+        <v>103314.984492753</v>
       </c>
       <c r="P1171" t="n">
         <v>3000</v>
       </c>
       <c r="Q1171" t="n">
-        <v>111000</v>
+        <v>129000</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>XP-2986</t>
+          <t>YOYO2001</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>BORRADOR RETRACTIL COHETE XP-2986</t>
-        </is>
-      </c>
-      <c r="E1172" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>ZET LAPIZ</t>
         </is>
       </c>
       <c r="I1172" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -52151,59 +52141,18 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1172" t="n">
-        <v>2402.6741007194</v>
+        <v>6000</v>
       </c>
       <c r="O1172" t="n">
-        <v>103314.9863309342</v>
+        <v>246000</v>
       </c>
       <c r="P1172" t="n">
-        <v>3000</v>
+        <v>7200</v>
       </c>
       <c r="Q1172" t="n">
-        <v>129000</v>
-      </c>
-    </row>
-    <row r="1173">
-      <c r="A1173" t="inlineStr">
-        <is>
-          <t>YOYO2001</t>
-        </is>
-      </c>
-      <c r="C1173" t="inlineStr">
-        <is>
-          <t>ZET LAPIZ</t>
-        </is>
-      </c>
-      <c r="I1173" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-      <c r="J1173" t="n">
-        <v>41</v>
-      </c>
-      <c r="K1173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1173" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1173" t="n">
-        <v>41</v>
-      </c>
-      <c r="N1173" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O1173" t="n">
-        <v>246000</v>
-      </c>
-      <c r="P1173" t="n">
-        <v>7200</v>
-      </c>
-      <c r="Q1173" t="n">
         <v>295200</v>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -12639,22 +12639,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M288" t="n">
-        <v>2635</v>
+        <v>2595</v>
       </c>
       <c r="N288" t="n">
         <v>156.25</v>
       </c>
       <c r="O288" t="n">
-        <v>411718.75</v>
+        <v>405468.75</v>
       </c>
       <c r="P288" t="n">
         <v>250</v>
       </c>
       <c r="Q288" t="n">
-        <v>658750</v>
+        <v>648750</v>
       </c>
     </row>
     <row r="289">
@@ -34327,10 +34327,10 @@
         <v>75</v>
       </c>
       <c r="N778" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O778" t="n">
-        <v>806625</v>
+        <v>809680.3977272999</v>
       </c>
       <c r="P778" t="n">
         <v>17900</v>
@@ -36761,22 +36761,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M831" t="n">
-        <v>701</v>
+        <v>677</v>
       </c>
       <c r="N831" t="n">
         <v>1801</v>
       </c>
       <c r="O831" t="n">
-        <v>1262501</v>
+        <v>1219277</v>
       </c>
       <c r="P831" t="n">
         <v>2900</v>
       </c>
       <c r="Q831" t="n">
-        <v>2032900</v>
+        <v>1963300</v>
       </c>
     </row>
     <row r="832">
@@ -40394,22 +40394,22 @@
         <v>0</v>
       </c>
       <c r="L911" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M911" t="n">
-        <v>996</v>
+        <v>972</v>
       </c>
       <c r="N911" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O911" t="n">
-        <v>700979.4587640568</v>
+        <v>684088.3857968334</v>
       </c>
       <c r="P911" t="n">
         <v>900</v>
       </c>
       <c r="Q911" t="n">
-        <v>896400</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="912">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -556,10 +556,10 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27065.693430657</v>
       </c>
       <c r="O4" t="n">
-        <v>405000</v>
+        <v>405985.401459855</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -935,10 +935,10 @@
         <v>38</v>
       </c>
       <c r="N13" t="n">
-        <v>27000</v>
+        <v>27109.756097561</v>
       </c>
       <c r="O13" t="n">
-        <v>1026000</v>
+        <v>1030170.731707318</v>
       </c>
       <c r="P13" t="n">
         <v>20000</v>
@@ -2598,10 +2598,10 @@
         <v>19</v>
       </c>
       <c r="N54" t="n">
-        <v>27000</v>
+        <v>27151.898734177</v>
       </c>
       <c r="O54" t="n">
-        <v>513000</v>
+        <v>515886.075949363</v>
       </c>
       <c r="P54" t="n">
         <v>20000</v>
@@ -2835,10 +2835,10 @@
         <v>35</v>
       </c>
       <c r="N60" t="n">
-        <v>3926.8370711297</v>
+        <v>3926.837066527</v>
       </c>
       <c r="O60" t="n">
-        <v>137439.2974895395</v>
+        <v>137439.297328445</v>
       </c>
       <c r="P60" t="n">
         <v>4800</v>
@@ -3275,10 +3275,10 @@
         <v>167</v>
       </c>
       <c r="N71" t="n">
-        <v>3716.3301970443</v>
+        <v>3716.3301973684</v>
       </c>
       <c r="O71" t="n">
-        <v>620627.142906398</v>
+        <v>620627.1429605228</v>
       </c>
       <c r="P71" t="n">
         <v>9500</v>
@@ -6340,10 +6340,10 @@
         <v>20</v>
       </c>
       <c r="N142" t="n">
-        <v>27000</v>
+        <v>27352.173913043</v>
       </c>
       <c r="O142" t="n">
-        <v>540000</v>
+        <v>547043.47826086</v>
       </c>
       <c r="P142" t="n">
         <v>20000</v>
@@ -9785,10 +9785,10 @@
         <v>27</v>
       </c>
       <c r="N222" t="n">
-        <v>1098.072297891</v>
+        <v>1098.0725121628</v>
       </c>
       <c r="O222" t="n">
-        <v>29647.952043057</v>
+        <v>29647.9578283956</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
@@ -11587,10 +11587,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2582.2548125</v>
+        <v>2582.2547989556</v>
       </c>
       <c r="O264" t="n">
-        <v>219491.6590625</v>
+        <v>219491.657911226</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -11633,10 +11633,10 @@
         <v>207</v>
       </c>
       <c r="N265" t="n">
-        <v>10600</v>
+        <v>10614.851138354</v>
       </c>
       <c r="O265" t="n">
-        <v>2194200</v>
+        <v>2197274.185639278</v>
       </c>
       <c r="P265" t="n">
         <v>17200</v>
@@ -12163,10 +12163,10 @@
         <v>3</v>
       </c>
       <c r="N277" t="n">
-        <v>3230.0657538462</v>
+        <v>3230.0657009346</v>
       </c>
       <c r="O277" t="n">
-        <v>9690.1972615386</v>
+        <v>9690.197102803801</v>
       </c>
       <c r="P277" t="n">
         <v>6200</v>
@@ -13069,10 +13069,10 @@
         <v>70</v>
       </c>
       <c r="N297" t="n">
-        <v>4890.9300552868</v>
+        <v>4890.930055517</v>
       </c>
       <c r="O297" t="n">
-        <v>342365.103870076</v>
+        <v>342365.10388619</v>
       </c>
       <c r="P297" t="n">
         <v>8200</v>
@@ -13600,25 +13600,25 @@
         <v>56</v>
       </c>
       <c r="K309" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="N309" t="n">
         <v>8662</v>
       </c>
       <c r="O309" t="n">
-        <v>485072</v>
+        <v>874862</v>
       </c>
       <c r="P309" t="n">
         <v>14200</v>
       </c>
       <c r="Q309" t="n">
-        <v>795200</v>
+        <v>1434200</v>
       </c>
     </row>
     <row r="310">
@@ -14120,25 +14120,25 @@
         <v>59</v>
       </c>
       <c r="K321" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
       </c>
       <c r="M321" t="n">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="N321" t="n">
         <v>8154</v>
       </c>
       <c r="O321" t="n">
-        <v>481086</v>
+        <v>872478</v>
       </c>
       <c r="P321" t="n">
         <v>13500</v>
       </c>
       <c r="Q321" t="n">
-        <v>796500</v>
+        <v>1444500</v>
       </c>
     </row>
     <row r="322">
@@ -14175,10 +14175,10 @@
         <v>44</v>
       </c>
       <c r="N322" t="n">
-        <v>14822.378817006</v>
+        <v>14822.378814083</v>
       </c>
       <c r="O322" t="n">
-        <v>652184.6679482639</v>
+        <v>652184.667819652</v>
       </c>
       <c r="P322" t="n">
         <v>24900</v>
@@ -14482,10 +14482,10 @@
         <v>89</v>
       </c>
       <c r="N329" t="n">
-        <v>12422.463007951</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O329" t="n">
-        <v>1105599.207707639</v>
+        <v>1105599.208181386</v>
       </c>
       <c r="P329" t="n">
         <v>19900</v>
@@ -14662,10 +14662,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.2763500602</v>
+        <v>3472.2763717066</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.933321552</v>
+        <v>1243074.941070963</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -14796,10 +14796,10 @@
         <v>419</v>
       </c>
       <c r="N336" t="n">
-        <v>3041.6600149925</v>
+        <v>3041.660015015</v>
       </c>
       <c r="O336" t="n">
-        <v>1274455.546281857</v>
+        <v>1274455.546291285</v>
       </c>
       <c r="P336" t="n">
         <v>5500</v>
@@ -14883,10 +14883,10 @@
         <v>185</v>
       </c>
       <c r="N338" t="n">
-        <v>4371.1729689003</v>
+        <v>4371.1729703288</v>
       </c>
       <c r="O338" t="n">
-        <v>808666.9992465554</v>
+        <v>808666.9995108281</v>
       </c>
       <c r="P338" t="n">
         <v>8900</v>
@@ -14918,25 +14918,25 @@
         <v>12</v>
       </c>
       <c r="K339" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="N339" t="n">
         <v>6441.03</v>
       </c>
       <c r="O339" t="n">
-        <v>77292.36</v>
+        <v>283405.32</v>
       </c>
       <c r="P339" t="n">
         <v>10500</v>
       </c>
       <c r="Q339" t="n">
-        <v>126000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="340">
@@ -16985,25 +16985,25 @@
         <v>448</v>
       </c>
       <c r="K386" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>448</v>
+        <v>832</v>
       </c>
       <c r="N386" t="n">
-        <v>1630.9249342316</v>
+        <v>1630.925009772</v>
       </c>
       <c r="O386" t="n">
-        <v>730654.3705357568</v>
+        <v>1356929.608130304</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
       </c>
       <c r="Q386" t="n">
-        <v>1120000</v>
+        <v>2080000</v>
       </c>
     </row>
     <row r="387">
@@ -17127,10 +17127,10 @@
         <v>427</v>
       </c>
       <c r="N389" t="n">
-        <v>1690.5739608434</v>
+        <v>1690.5736115326</v>
       </c>
       <c r="O389" t="n">
-        <v>721875.0812801318</v>
+        <v>721874.9321244202</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17164,25 +17164,25 @@
         <v>1920</v>
       </c>
       <c r="K390" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>1920</v>
+        <v>2305</v>
       </c>
       <c r="N390" t="n">
-        <v>1550.1949322169</v>
+        <v>1550.1949414115</v>
       </c>
       <c r="O390" t="n">
-        <v>2976374.269856448</v>
+        <v>3573199.339953507</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>4800000</v>
+        <v>5762500</v>
       </c>
     </row>
     <row r="391">
@@ -17265,10 +17265,10 @@
         <v>991</v>
       </c>
       <c r="N392" t="n">
-        <v>2403.5224548084</v>
+        <v>2403.5228513613</v>
       </c>
       <c r="O392" t="n">
-        <v>2381890.752715125</v>
+        <v>2381891.145699048</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
@@ -18627,10 +18627,10 @@
         <v>30</v>
       </c>
       <c r="N423" t="n">
-        <v>17328</v>
+        <v>17991.272727273</v>
       </c>
       <c r="O423" t="n">
-        <v>519840</v>
+        <v>539738.18181819</v>
       </c>
       <c r="P423" t="n">
         <v>32900</v>
@@ -18879,25 +18879,25 @@
         <v>109</v>
       </c>
       <c r="K429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
       </c>
       <c r="M429" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N429" t="n">
         <v>7028</v>
       </c>
       <c r="O429" t="n">
-        <v>766052</v>
+        <v>773080</v>
       </c>
       <c r="P429" t="n">
         <v>15900</v>
       </c>
       <c r="Q429" t="n">
-        <v>1733100</v>
+        <v>1749000</v>
       </c>
     </row>
     <row r="430">
@@ -21120,10 +21120,10 @@
         <v>396</v>
       </c>
       <c r="N482" t="n">
-        <v>2029.8742253521</v>
+        <v>2029.8742541123</v>
       </c>
       <c r="O482" t="n">
-        <v>803830.1932394316</v>
+        <v>803830.2046284708</v>
       </c>
       <c r="P482" t="n">
         <v>3600</v>
@@ -21661,10 +21661,10 @@
         <v>145</v>
       </c>
       <c r="N495" t="n">
-        <v>2680.7396931747</v>
+        <v>2680.7396929825</v>
       </c>
       <c r="O495" t="n">
-        <v>388707.2555103315</v>
+        <v>388707.2554824625</v>
       </c>
       <c r="P495" t="n">
         <v>4900</v>
@@ -21830,10 +21830,10 @@
         <v>17</v>
       </c>
       <c r="N499" t="n">
-        <v>11431.604625</v>
+        <v>11724.722692308</v>
       </c>
       <c r="O499" t="n">
-        <v>194337.278625</v>
+        <v>199320.285769236</v>
       </c>
       <c r="P499" t="n">
         <v>48900</v>
@@ -22122,10 +22122,10 @@
         <v>52</v>
       </c>
       <c r="N506" t="n">
-        <v>30611</v>
+        <v>30745.062773723</v>
       </c>
       <c r="O506" t="n">
-        <v>1591772</v>
+        <v>1598743.264233596</v>
       </c>
       <c r="P506" t="n">
         <v>38900</v>
@@ -22250,10 +22250,10 @@
         <v>91</v>
       </c>
       <c r="N509" t="n">
-        <v>1651</v>
+        <v>3271.8447488584</v>
       </c>
       <c r="O509" t="n">
-        <v>150241</v>
+        <v>297737.8721461144</v>
       </c>
       <c r="P509" t="n">
         <v>2500</v>
@@ -22333,25 +22333,25 @@
         <v>121</v>
       </c>
       <c r="K511" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>121</v>
+        <v>209</v>
       </c>
       <c r="N511" t="n">
-        <v>6207.9882021366</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O511" t="n">
-        <v>751166.5724585287</v>
+        <v>1297469.534088023</v>
       </c>
       <c r="P511" t="n">
         <v>9900</v>
       </c>
       <c r="Q511" t="n">
-        <v>1197900</v>
+        <v>2069100</v>
       </c>
     </row>
     <row r="512">
@@ -22560,10 +22560,10 @@
         <v>267</v>
       </c>
       <c r="N516" t="n">
-        <v>4285.1965633075</v>
+        <v>4285.1966145833</v>
       </c>
       <c r="O516" t="n">
-        <v>1144147.482403102</v>
+        <v>1144147.496093741</v>
       </c>
       <c r="P516" t="n">
         <v>6900</v>
@@ -22846,25 +22846,25 @@
         <v>9</v>
       </c>
       <c r="K523" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="N523" t="n">
         <v>16275</v>
       </c>
       <c r="O523" t="n">
-        <v>146475</v>
+        <v>585900</v>
       </c>
       <c r="P523" t="n">
         <v>27600</v>
       </c>
       <c r="Q523" t="n">
-        <v>248400</v>
+        <v>993600</v>
       </c>
     </row>
     <row r="524">
@@ -22988,10 +22988,10 @@
         <v>556</v>
       </c>
       <c r="N526" t="n">
-        <v>1106</v>
+        <v>1111.1642023346</v>
       </c>
       <c r="O526" t="n">
-        <v>614936</v>
+        <v>617807.2964980376</v>
       </c>
       <c r="P526" t="n">
         <v>2100</v>
@@ -23029,10 +23029,10 @@
         <v>21</v>
       </c>
       <c r="N527" t="n">
-        <v>1430.38</v>
+        <v>1447.7706382979</v>
       </c>
       <c r="O527" t="n">
-        <v>30037.98</v>
+        <v>30403.1834042559</v>
       </c>
       <c r="P527" t="n">
         <v>4000</v>
@@ -23244,10 +23244,10 @@
         <v>165</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633769677</v>
+        <v>4814.2633736737</v>
       </c>
       <c r="O532" t="n">
-        <v>794353.4571996706</v>
+        <v>794353.4566561604</v>
       </c>
       <c r="P532" t="n">
         <v>9900</v>
@@ -23377,10 +23377,10 @@
         <v>48</v>
       </c>
       <c r="N535" t="n">
-        <v>11562.038395415</v>
+        <v>11562.038381503</v>
       </c>
       <c r="O535" t="n">
-        <v>554977.84297992</v>
+        <v>554977.842312144</v>
       </c>
       <c r="P535" t="n">
         <v>18500</v>
@@ -23423,10 +23423,10 @@
         <v>49</v>
       </c>
       <c r="N536" t="n">
-        <v>13513.643534483</v>
+        <v>13513.643727273</v>
       </c>
       <c r="O536" t="n">
-        <v>662168.533189667</v>
+        <v>662168.542636377</v>
       </c>
       <c r="P536" t="n">
         <v>21900</v>
@@ -23469,10 +23469,10 @@
         <v>53</v>
       </c>
       <c r="N537" t="n">
-        <v>12005.159823009</v>
+        <v>12005.159821429</v>
       </c>
       <c r="O537" t="n">
-        <v>636273.470619477</v>
+        <v>636273.470535737</v>
       </c>
       <c r="P537" t="n">
         <v>19500</v>
@@ -24682,10 +24682,10 @@
         <v>29</v>
       </c>
       <c r="N565" t="n">
-        <v>27123.764688797</v>
+        <v>27123.764610526</v>
       </c>
       <c r="O565" t="n">
-        <v>786589.1759751131</v>
+        <v>786589.173705254</v>
       </c>
       <c r="P565" t="n">
         <v>44500</v>
@@ -25066,10 +25066,10 @@
         <v>18</v>
       </c>
       <c r="N574" t="n">
-        <v>1561.0066122098</v>
+        <v>1561.0072654155</v>
       </c>
       <c r="O574" t="n">
-        <v>28098.1190197764</v>
+        <v>28098.130777479</v>
       </c>
       <c r="P574" t="n">
         <v>2900</v>
@@ -25245,10 +25245,10 @@
         <v>31</v>
       </c>
       <c r="N578" t="n">
-        <v>26854</v>
+        <v>27080.935211268</v>
       </c>
       <c r="O578" t="n">
-        <v>832474</v>
+        <v>839508.9915493079</v>
       </c>
       <c r="P578" t="n">
         <v>43900</v>
@@ -26701,10 +26701,10 @@
         <v>1</v>
       </c>
       <c r="N612" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="O612" t="n">
-        <v>7700</v>
+        <v>7738.024691358</v>
       </c>
       <c r="P612" t="n">
         <v>13900</v>
@@ -28078,25 +28078,25 @@
         <v>14</v>
       </c>
       <c r="K642" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N642" t="n">
         <v>55139</v>
       </c>
       <c r="O642" t="n">
-        <v>771946</v>
+        <v>1047641</v>
       </c>
       <c r="P642" t="n">
         <v>89900</v>
       </c>
       <c r="Q642" t="n">
-        <v>1258600</v>
+        <v>1708100</v>
       </c>
     </row>
     <row r="643">
@@ -28271,10 +28271,10 @@
         <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>23521.622708333</v>
+        <v>23521.621666667</v>
       </c>
       <c r="O646" t="n">
-        <v>94086.49083333201</v>
+        <v>94086.486666668</v>
       </c>
       <c r="P646" t="n">
         <v>39000</v>
@@ -28363,10 +28363,10 @@
         <v>1208</v>
       </c>
       <c r="N648" t="n">
-        <v>1778.4728840436</v>
+        <v>1778.4728878597</v>
       </c>
       <c r="O648" t="n">
-        <v>2148395.243924669</v>
+        <v>2148395.248534517</v>
       </c>
       <c r="P648" t="n">
         <v>4900</v>
@@ -28501,10 +28501,10 @@
         <v>22</v>
       </c>
       <c r="N651" t="n">
-        <v>22739</v>
+        <v>22935.194995686</v>
       </c>
       <c r="O651" t="n">
-        <v>500258</v>
+        <v>504574.289905092</v>
       </c>
       <c r="P651" t="n">
         <v>36900</v>
@@ -28593,10 +28593,10 @@
         <v>38</v>
       </c>
       <c r="N653" t="n">
-        <v>16058</v>
+        <v>16177.301634473</v>
       </c>
       <c r="O653" t="n">
-        <v>610204</v>
+        <v>614737.462109974</v>
       </c>
       <c r="P653" t="n">
         <v>25900</v>
@@ -30301,10 +30301,10 @@
         <v>31</v>
       </c>
       <c r="N690" t="n">
-        <v>28116</v>
+        <v>28661.941747573</v>
       </c>
       <c r="O690" t="n">
-        <v>871596</v>
+        <v>888520.194174763</v>
       </c>
       <c r="P690" t="n">
         <v>45900</v>
@@ -31495,10 +31495,10 @@
         <v>222</v>
       </c>
       <c r="N716" t="n">
-        <v>3519</v>
+        <v>4129.9375</v>
       </c>
       <c r="O716" t="n">
-        <v>781218</v>
+        <v>916846.125</v>
       </c>
       <c r="P716" t="n">
         <v>5900</v>
@@ -31909,10 +31909,10 @@
         <v>9</v>
       </c>
       <c r="N725" t="n">
-        <v>4907.8227973568</v>
+        <v>4907.8228159645</v>
       </c>
       <c r="O725" t="n">
-        <v>44170.4051762112</v>
+        <v>44170.4053436805</v>
       </c>
       <c r="P725" t="n">
         <v>8200</v>
@@ -32226,10 +32226,10 @@
         <v>49</v>
       </c>
       <c r="N732" t="n">
-        <v>20726</v>
+        <v>21286.162162162</v>
       </c>
       <c r="O732" t="n">
-        <v>1015574</v>
+        <v>1043021.945945938</v>
       </c>
       <c r="P732" t="n">
         <v>33900</v>
@@ -32272,10 +32272,10 @@
         <v>15</v>
       </c>
       <c r="N733" t="n">
-        <v>20731</v>
+        <v>21767.55</v>
       </c>
       <c r="O733" t="n">
-        <v>310965</v>
+        <v>326513.25</v>
       </c>
       <c r="P733" t="n">
         <v>33900</v>
@@ -33284,10 +33284,10 @@
         <v>93</v>
       </c>
       <c r="N755" t="n">
-        <v>13565</v>
+        <v>13585.998452012</v>
       </c>
       <c r="O755" t="n">
-        <v>1261545</v>
+        <v>1263497.856037116</v>
       </c>
       <c r="P755" t="n">
         <v>22500</v>
@@ -33468,10 +33468,10 @@
         <v>1</v>
       </c>
       <c r="N759" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="O759" t="n">
-        <v>23439</v>
+        <v>24040</v>
       </c>
       <c r="P759" t="n">
         <v>37900</v>
@@ -33514,10 +33514,10 @@
         <v>56</v>
       </c>
       <c r="N760" t="n">
-        <v>19008</v>
+        <v>19059.165545087</v>
       </c>
       <c r="O760" t="n">
-        <v>1064448</v>
+        <v>1067313.270524872</v>
       </c>
       <c r="P760" t="n">
         <v>30900</v>
@@ -33655,10 +33655,10 @@
         <v>106</v>
       </c>
       <c r="N763" t="n">
-        <v>17992</v>
+        <v>18038.854166667</v>
       </c>
       <c r="O763" t="n">
-        <v>1907152</v>
+        <v>1912118.541666702</v>
       </c>
       <c r="P763" t="n">
         <v>28900</v>
@@ -33747,10 +33747,10 @@
         <v>161</v>
       </c>
       <c r="N765" t="n">
-        <v>17075.989515789</v>
+        <v>17112.014810127</v>
       </c>
       <c r="O765" t="n">
-        <v>2749234.312042029</v>
+        <v>2755034.384430447</v>
       </c>
       <c r="P765" t="n">
         <v>27500</v>
@@ -34941,10 +34941,10 @@
         <v>39</v>
       </c>
       <c r="N791" t="n">
-        <v>15472</v>
+        <v>15602.016806723</v>
       </c>
       <c r="O791" t="n">
-        <v>603408</v>
+        <v>608478.655462197</v>
       </c>
       <c r="P791" t="n">
         <v>25900</v>
@@ -35770,10 +35770,10 @@
         <v>143</v>
       </c>
       <c r="N809" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942583732</v>
       </c>
       <c r="O809" t="n">
-        <v>472842.9802547737</v>
+        <v>472842.9789473676</v>
       </c>
       <c r="P809" t="n">
         <v>4900</v>
@@ -35908,10 +35908,10 @@
         <v>955</v>
       </c>
       <c r="N812" t="n">
-        <v>2056.0812616427</v>
+        <v>2056.081010453</v>
       </c>
       <c r="O812" t="n">
-        <v>1963557.604868779</v>
+        <v>1963557.364982615</v>
       </c>
       <c r="P812" t="n">
         <v>2900</v>
@@ -36000,10 +36000,10 @@
         <v>560</v>
       </c>
       <c r="N814" t="n">
-        <v>1655.9287880016</v>
+        <v>1655.9287789047</v>
       </c>
       <c r="O814" t="n">
-        <v>927320.121280896</v>
+        <v>927320.1161866321</v>
       </c>
       <c r="P814" t="n">
         <v>2500</v>
@@ -36689,10 +36689,10 @@
         <v>13</v>
       </c>
       <c r="N829" t="n">
-        <v>692.15251958462</v>
+        <v>692.1525362185999</v>
       </c>
       <c r="O829" t="n">
-        <v>8997.98275460006</v>
+        <v>8997.9829708418</v>
       </c>
       <c r="P829" t="n">
         <v>1200</v>
@@ -36957,25 +36957,25 @@
         <v>102</v>
       </c>
       <c r="K835" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L835" t="n">
         <v>0</v>
       </c>
       <c r="M835" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="N835" t="n">
         <v>11690</v>
       </c>
       <c r="O835" t="n">
-        <v>1192380</v>
+        <v>1414490</v>
       </c>
       <c r="P835" t="n">
         <v>18900</v>
       </c>
       <c r="Q835" t="n">
-        <v>1927800</v>
+        <v>2286900</v>
       </c>
     </row>
     <row r="836">
@@ -37055,25 +37055,25 @@
         <v>101</v>
       </c>
       <c r="K837" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L837" t="n">
         <v>0</v>
       </c>
       <c r="M837" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="N837" t="n">
         <v>9736</v>
       </c>
       <c r="O837" t="n">
-        <v>983336</v>
+        <v>1139112</v>
       </c>
       <c r="P837" t="n">
         <v>15900</v>
       </c>
       <c r="Q837" t="n">
-        <v>1605900</v>
+        <v>1860300</v>
       </c>
     </row>
     <row r="838">
@@ -37153,25 +37153,25 @@
         <v>251</v>
       </c>
       <c r="K839" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L839" t="n">
         <v>0</v>
       </c>
       <c r="M839" t="n">
-        <v>251</v>
+        <v>421</v>
       </c>
       <c r="N839" t="n">
         <v>5215</v>
       </c>
       <c r="O839" t="n">
-        <v>1308965</v>
+        <v>2195515</v>
       </c>
       <c r="P839" t="n">
         <v>8900</v>
       </c>
       <c r="Q839" t="n">
-        <v>2233900</v>
+        <v>3746900</v>
       </c>
     </row>
     <row r="840">
@@ -39821,25 +39821,25 @@
         <v>2644</v>
       </c>
       <c r="K898" t="n">
-        <v>0</v>
+        <v>1728</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>2644</v>
+        <v>4372</v>
       </c>
       <c r="N898" t="n">
-        <v>517.29656001551</v>
+        <v>517.29673853391</v>
       </c>
       <c r="O898" t="n">
-        <v>1367732.104681008</v>
+        <v>2261621.340870255</v>
       </c>
       <c r="P898" t="n">
         <v>900</v>
       </c>
       <c r="Q898" t="n">
-        <v>2379600</v>
+        <v>3934800</v>
       </c>
     </row>
     <row r="899">
@@ -40056,10 +40056,10 @@
         <v>267</v>
       </c>
       <c r="N903" t="n">
-        <v>3110.8352523988</v>
+        <v>3110.8351781971</v>
       </c>
       <c r="O903" t="n">
-        <v>830593.0123904797</v>
+        <v>830592.9925786257</v>
       </c>
       <c r="P903" t="n">
         <v>4500</v>
@@ -40278,10 +40278,10 @@
         <v>2652</v>
       </c>
       <c r="N908" t="n">
-        <v>703.79459507493</v>
+        <v>703.79459259958</v>
       </c>
       <c r="O908" t="n">
-        <v>1866463.266138715</v>
+        <v>1866463.259574086</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
@@ -40507,10 +40507,10 @@
         <v>3</v>
       </c>
       <c r="N913" t="n">
-        <v>2501.384</v>
+        <v>2501.3837931034</v>
       </c>
       <c r="O913" t="n">
-        <v>7504.152</v>
+        <v>7504.1513793102</v>
       </c>
       <c r="P913" t="n">
         <v>4100</v>
@@ -41721,10 +41721,10 @@
         <v>4</v>
       </c>
       <c r="N940" t="n">
-        <v>16041.19</v>
+        <v>19605.898888889</v>
       </c>
       <c r="O940" t="n">
-        <v>64164.76</v>
+        <v>78423.59555555601</v>
       </c>
       <c r="P940" t="n">
         <v>40000</v>
@@ -42481,10 +42481,10 @@
         <v>54</v>
       </c>
       <c r="N956" t="n">
-        <v>3067.0906293706</v>
+        <v>3099.6039575972</v>
       </c>
       <c r="O956" t="n">
-        <v>165622.8939860124</v>
+        <v>167378.6137102488</v>
       </c>
       <c r="P956" t="n">
         <v>7200</v>
@@ -42984,10 +42984,10 @@
         <v>1</v>
       </c>
       <c r="N967" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="O967" t="n">
-        <v>10737.5255</v>
+        <v>10737.525384615</v>
       </c>
       <c r="P967" t="n">
         <v>18900</v>
@@ -43401,10 +43401,10 @@
         <v>8</v>
       </c>
       <c r="N976" t="n">
-        <v>5216.9</v>
+        <v>5254.1635714286</v>
       </c>
       <c r="O976" t="n">
-        <v>41735.2</v>
+        <v>42033.3085714288</v>
       </c>
       <c r="P976" t="n">
         <v>20500</v>
@@ -43780,10 +43780,10 @@
         <v>98</v>
       </c>
       <c r="N984" t="n">
-        <v>24338.47</v>
+        <v>24856.309787234</v>
       </c>
       <c r="O984" t="n">
-        <v>2385170.06</v>
+        <v>2435918.359148932</v>
       </c>
       <c r="P984" t="n">
         <v>27900</v>
@@ -44491,10 +44491,10 @@
         <v>179</v>
       </c>
       <c r="N999" t="n">
-        <v>430.60997520149</v>
+        <v>430.6099751861</v>
       </c>
       <c r="O999" t="n">
-        <v>77079.18556106671</v>
+        <v>77079.18555831189</v>
       </c>
       <c r="P999" t="n">
         <v>2200</v>
@@ -48961,10 +48961,10 @@
         <v>171</v>
       </c>
       <c r="N1101" t="n">
-        <v>9240</v>
+        <v>9401.162790697699</v>
       </c>
       <c r="O1101" t="n">
-        <v>1580040</v>
+        <v>1607598.837209307</v>
       </c>
       <c r="P1101" t="n">
         <v>11500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>27065.693430657</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>405985.401459855</v>
+        <v>405000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>232</v>
+        <v>382</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1226,19 +1226,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>232</v>
+        <v>382</v>
       </c>
       <c r="N20" t="n">
-        <v>1811.3108641975</v>
+        <v>1811.3112820513</v>
       </c>
       <c r="O20" t="n">
-        <v>420224.12049382</v>
+        <v>691920.9097435966</v>
       </c>
       <c r="P20" t="n">
         <v>2600</v>
       </c>
       <c r="Q20" t="n">
-        <v>603200</v>
+        <v>993200</v>
       </c>
     </row>
     <row r="21">
@@ -1346,10 +1346,10 @@
         <v>122</v>
       </c>
       <c r="N23" t="n">
-        <v>3376.7463799384</v>
+        <v>3376.7463585118</v>
       </c>
       <c r="O23" t="n">
-        <v>411963.0583524848</v>
+        <v>411963.0557384396</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -2598,10 +2598,10 @@
         <v>19</v>
       </c>
       <c r="N54" t="n">
-        <v>27151.898734177</v>
+        <v>27000</v>
       </c>
       <c r="O54" t="n">
-        <v>515886.075949363</v>
+        <v>513000</v>
       </c>
       <c r="P54" t="n">
         <v>20000</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2832,19 +2832,19 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N60" t="n">
-        <v>3926.837066527</v>
+        <v>3926.837057278</v>
       </c>
       <c r="O60" t="n">
-        <v>137439.297328445</v>
+        <v>113878.274661062</v>
       </c>
       <c r="P60" t="n">
         <v>4800</v>
       </c>
       <c r="Q60" t="n">
-        <v>168000</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="61">
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4947,19 +4947,19 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N110" t="n">
-        <v>7407.7300571429</v>
+        <v>7407.7300576369</v>
       </c>
       <c r="O110" t="n">
-        <v>518541.104000003</v>
+        <v>496317.9138616723</v>
       </c>
       <c r="P110" t="n">
         <v>10900</v>
       </c>
       <c r="Q110" t="n">
-        <v>763000</v>
+        <v>730300</v>
       </c>
     </row>
     <row r="111">
@@ -5718,10 +5718,10 @@
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>141416.88465116</v>
+        <v>141416.88463576</v>
       </c>
       <c r="O128" t="n">
-        <v>282833.76930232</v>
+        <v>282833.76927152</v>
       </c>
       <c r="P128" t="n">
         <v>251900</v>
@@ -6340,10 +6340,10 @@
         <v>20</v>
       </c>
       <c r="N142" t="n">
-        <v>27352.173913043</v>
+        <v>27000</v>
       </c>
       <c r="O142" t="n">
-        <v>547043.47826086</v>
+        <v>540000</v>
       </c>
       <c r="P142" t="n">
         <v>20000</v>
@@ -6659,10 +6659,10 @@
         <v>4</v>
       </c>
       <c r="N150" t="n">
-        <v>61666.874389535</v>
+        <v>61666.874467456</v>
       </c>
       <c r="O150" t="n">
-        <v>246667.49755814</v>
+        <v>246667.497869824</v>
       </c>
       <c r="P150" t="n">
         <v>98900</v>
@@ -9321,10 +9321,10 @@
         <v>123</v>
       </c>
       <c r="N211" t="n">
-        <v>4937.310173913</v>
+        <v>4937.3101888412</v>
       </c>
       <c r="O211" t="n">
-        <v>607289.151391299</v>
+        <v>607289.1532274677</v>
       </c>
       <c r="P211" t="n">
         <v>7500</v>
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -9782,19 +9782,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="N222" t="n">
-        <v>1098.0725121628</v>
+        <v>1098.0729937163</v>
       </c>
       <c r="O222" t="n">
-        <v>29647.9578283956</v>
+        <v>26353.7518491912</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
       </c>
       <c r="Q222" t="n">
-        <v>40500</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="223">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10492,19 +10492,19 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="N239" t="n">
         <v>2613</v>
       </c>
       <c r="O239" t="n">
-        <v>334464</v>
+        <v>216879</v>
       </c>
       <c r="P239" t="n">
         <v>5100</v>
       </c>
       <c r="Q239" t="n">
-        <v>652800</v>
+        <v>423300</v>
       </c>
     </row>
     <row r="240">
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11228,19 +11228,19 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="N256" t="n">
         <v>2804.33</v>
       </c>
       <c r="O256" t="n">
-        <v>1231100.87</v>
+        <v>1197448.91</v>
       </c>
       <c r="P256" t="n">
         <v>4900</v>
       </c>
       <c r="Q256" t="n">
-        <v>2151100</v>
+        <v>2092300</v>
       </c>
     </row>
     <row r="257">
@@ -11587,10 +11587,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2582.2547989556</v>
+        <v>2582.25476203</v>
       </c>
       <c r="O264" t="n">
-        <v>219491.657911226</v>
+        <v>219491.65477255</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -11633,10 +11633,10 @@
         <v>207</v>
       </c>
       <c r="N265" t="n">
-        <v>10614.851138354</v>
+        <v>10600</v>
       </c>
       <c r="O265" t="n">
-        <v>2197274.185639278</v>
+        <v>2194200</v>
       </c>
       <c r="P265" t="n">
         <v>17200</v>
@@ -11679,10 +11679,10 @@
         <v>231</v>
       </c>
       <c r="N266" t="n">
-        <v>5216.895823058</v>
+        <v>5216.8958101422</v>
       </c>
       <c r="O266" t="n">
-        <v>1205102.935126398</v>
+        <v>1205102.932142848</v>
       </c>
       <c r="P266" t="n">
         <v>8500</v>
@@ -11981,10 +11981,10 @@
         <v>560</v>
       </c>
       <c r="N273" t="n">
-        <v>3158.8608423208</v>
+        <v>3158.8608436687</v>
       </c>
       <c r="O273" t="n">
-        <v>1768962.071699648</v>
+        <v>1768962.072454472</v>
       </c>
       <c r="P273" t="n">
         <v>5600</v>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12024,19 +12024,19 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="N274" t="n">
         <v>1903</v>
       </c>
       <c r="O274" t="n">
-        <v>808775</v>
+        <v>763103</v>
       </c>
       <c r="P274" t="n">
         <v>3200</v>
       </c>
       <c r="Q274" t="n">
-        <v>1360000</v>
+        <v>1283200</v>
       </c>
     </row>
     <row r="275">
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="J279" t="n">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12247,19 +12247,19 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="N279" t="n">
         <v>1480</v>
       </c>
       <c r="O279" t="n">
-        <v>1198800</v>
+        <v>1181040</v>
       </c>
       <c r="P279" t="n">
         <v>2600</v>
       </c>
       <c r="Q279" t="n">
-        <v>2106000</v>
+        <v>2074800</v>
       </c>
     </row>
     <row r="280">
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="J284" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="K284" t="n">
         <v>0</v>
@@ -12472,19 +12472,19 @@
         <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="N284" t="n">
         <v>1026.13</v>
       </c>
       <c r="O284" t="n">
-        <v>356067.11</v>
+        <v>343753.55</v>
       </c>
       <c r="P284" t="n">
         <v>1900</v>
       </c>
       <c r="Q284" t="n">
-        <v>659300</v>
+        <v>636500</v>
       </c>
     </row>
     <row r="285">
@@ -13069,10 +13069,10 @@
         <v>70</v>
       </c>
       <c r="N297" t="n">
-        <v>4890.930055517</v>
+        <v>4890.9300565371</v>
       </c>
       <c r="O297" t="n">
-        <v>342365.10388619</v>
+        <v>342365.103957597</v>
       </c>
       <c r="P297" t="n">
         <v>8200</v>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>856</v>
+        <v>820</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13161,19 +13161,19 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>856</v>
+        <v>820</v>
       </c>
       <c r="N299" t="n">
         <v>1203.38</v>
       </c>
       <c r="O299" t="n">
-        <v>1030093.28</v>
+        <v>986771.6000000001</v>
       </c>
       <c r="P299" t="n">
         <v>1900</v>
       </c>
       <c r="Q299" t="n">
-        <v>1626400</v>
+        <v>1558000</v>
       </c>
     </row>
     <row r="300">
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13207,19 +13207,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N300" t="n">
         <v>3472</v>
       </c>
       <c r="O300" t="n">
-        <v>739536</v>
+        <v>725648</v>
       </c>
       <c r="P300" t="n">
         <v>4800</v>
       </c>
       <c r="Q300" t="n">
-        <v>1022400</v>
+        <v>1003200</v>
       </c>
     </row>
     <row r="301">
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13253,19 +13253,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="N301" t="n">
         <v>5888</v>
       </c>
       <c r="O301" t="n">
-        <v>471040</v>
+        <v>453376</v>
       </c>
       <c r="P301" t="n">
         <v>9500</v>
       </c>
       <c r="Q301" t="n">
-        <v>760000</v>
+        <v>731500</v>
       </c>
     </row>
     <row r="302">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13514,19 +13514,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N307" t="n">
         <v>5667.94</v>
       </c>
       <c r="O307" t="n">
-        <v>606469.58</v>
+        <v>595133.7</v>
       </c>
       <c r="P307" t="n">
         <v>9500</v>
       </c>
       <c r="Q307" t="n">
-        <v>1016500</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="308">
@@ -13597,28 +13597,28 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="K309" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N309" t="n">
         <v>8662</v>
       </c>
       <c r="O309" t="n">
-        <v>874862</v>
+        <v>866200</v>
       </c>
       <c r="P309" t="n">
         <v>14200</v>
       </c>
       <c r="Q309" t="n">
-        <v>1434200</v>
+        <v>1420000</v>
       </c>
     </row>
     <row r="310">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -13993,19 +13993,19 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N318" t="n">
         <v>2953.73</v>
       </c>
       <c r="O318" t="n">
-        <v>398753.55</v>
+        <v>363308.79</v>
       </c>
       <c r="P318" t="n">
         <v>4900</v>
       </c>
       <c r="Q318" t="n">
-        <v>661500</v>
+        <v>602700</v>
       </c>
     </row>
     <row r="319">
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="K321" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -14433,19 +14433,19 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N328" t="n">
         <v>2665.4</v>
       </c>
       <c r="O328" t="n">
-        <v>122608.4</v>
+        <v>117277.6</v>
       </c>
       <c r="P328" t="n">
         <v>20900</v>
       </c>
       <c r="Q328" t="n">
-        <v>961400</v>
+        <v>919600</v>
       </c>
     </row>
     <row r="329">
@@ -14482,10 +14482,10 @@
         <v>89</v>
       </c>
       <c r="N329" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46300928</v>
       </c>
       <c r="O329" t="n">
-        <v>1105599.208181386</v>
+        <v>1105599.20782592</v>
       </c>
       <c r="P329" t="n">
         <v>19900</v>
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -14528,19 +14528,19 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="N330" t="n">
         <v>1381.75</v>
       </c>
       <c r="O330" t="n">
-        <v>610733.5</v>
+        <v>555463.5</v>
       </c>
       <c r="P330" t="n">
         <v>2500</v>
       </c>
       <c r="Q330" t="n">
-        <v>1105000</v>
+        <v>1005000</v>
       </c>
     </row>
     <row r="331">
@@ -14662,10 +14662,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.2763717066</v>
+        <v>3472.2763744227</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.941070963</v>
+        <v>1243074.942043327</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -14784,7 +14784,7 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
@@ -14793,19 +14793,19 @@
         <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="N336" t="n">
-        <v>3041.660015015</v>
+        <v>3041.6600151515</v>
       </c>
       <c r="O336" t="n">
-        <v>1274455.546291285</v>
+        <v>1237955.626166661</v>
       </c>
       <c r="P336" t="n">
         <v>5500</v>
       </c>
       <c r="Q336" t="n">
-        <v>2304500</v>
+        <v>2238500</v>
       </c>
     </row>
     <row r="337">
@@ -14883,10 +14883,10 @@
         <v>185</v>
       </c>
       <c r="N338" t="n">
-        <v>4371.1729703288</v>
+        <v>4371.1729731899</v>
       </c>
       <c r="O338" t="n">
-        <v>808666.9995108281</v>
+        <v>808667.0000401316</v>
       </c>
       <c r="P338" t="n">
         <v>8900</v>
@@ -14915,10 +14915,10 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="K339" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15886,19 +15886,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="N361" t="n">
         <v>1647.46</v>
       </c>
       <c r="O361" t="n">
-        <v>1238889.92</v>
+        <v>1219120.4</v>
       </c>
       <c r="P361" t="n">
         <v>2900</v>
       </c>
       <c r="Q361" t="n">
-        <v>2180800</v>
+        <v>2146000</v>
       </c>
     </row>
     <row r="362">
@@ -15965,7 +15965,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15974,19 +15974,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>443</v>
+        <v>409</v>
       </c>
       <c r="N363" t="n">
         <v>1387.55</v>
       </c>
       <c r="O363" t="n">
-        <v>614684.65</v>
+        <v>567507.95</v>
       </c>
       <c r="P363" t="n">
         <v>2300</v>
       </c>
       <c r="Q363" t="n">
-        <v>1018900</v>
+        <v>940700</v>
       </c>
     </row>
     <row r="364">
@@ -16103,10 +16103,10 @@
         <v>174</v>
       </c>
       <c r="N366" t="n">
-        <v>2021.7211355311</v>
+        <v>2021.7211369193</v>
       </c>
       <c r="O366" t="n">
-        <v>351779.4775824114</v>
+        <v>351779.4778239582</v>
       </c>
       <c r="P366" t="n">
         <v>2400</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -16374,19 +16374,19 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="N372" t="n">
         <v>3761.6</v>
       </c>
       <c r="O372" t="n">
-        <v>206888</v>
+        <v>176795.2</v>
       </c>
       <c r="P372" t="n">
         <v>6900</v>
       </c>
       <c r="Q372" t="n">
-        <v>379500</v>
+        <v>324300</v>
       </c>
     </row>
     <row r="373">
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16850,19 +16850,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="N383" t="n">
         <v>3751</v>
       </c>
       <c r="O383" t="n">
-        <v>2925780</v>
+        <v>2910776</v>
       </c>
       <c r="P383" t="n">
         <v>6400</v>
       </c>
       <c r="Q383" t="n">
-        <v>4992000</v>
+        <v>4966400</v>
       </c>
     </row>
     <row r="384">
@@ -16982,28 +16982,28 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>448</v>
+        <v>784</v>
       </c>
       <c r="K386" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>832</v>
+        <v>784</v>
       </c>
       <c r="N386" t="n">
-        <v>1630.925009772</v>
+        <v>1630.9251181364</v>
       </c>
       <c r="O386" t="n">
-        <v>1356929.608130304</v>
+        <v>1278645.292618938</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
       </c>
       <c r="Q386" t="n">
-        <v>2080000</v>
+        <v>1960000</v>
       </c>
     </row>
     <row r="387">
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="K388" t="n">
         <v>0</v>
@@ -17078,19 +17078,19 @@
         <v>0</v>
       </c>
       <c r="M388" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="N388" t="n">
-        <v>1467.3004273504</v>
+        <v>1467.2914141414</v>
       </c>
       <c r="O388" t="n">
-        <v>132057.038461536</v>
+        <v>105644.9818181808</v>
       </c>
       <c r="P388" t="n">
         <v>2500</v>
       </c>
       <c r="Q388" t="n">
-        <v>225000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="389">
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -17124,19 +17124,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="N389" t="n">
-        <v>1690.5736115326</v>
+        <v>1690.5719339623</v>
       </c>
       <c r="O389" t="n">
-        <v>721874.9321244202</v>
+        <v>706659.0683962414</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
       </c>
       <c r="Q389" t="n">
-        <v>1238300</v>
+        <v>1212200</v>
       </c>
     </row>
     <row r="390">
@@ -17161,28 +17161,28 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>1920</v>
+        <v>2225</v>
       </c>
       <c r="K390" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>2305</v>
+        <v>2225</v>
       </c>
       <c r="N390" t="n">
-        <v>1550.1949414115</v>
+        <v>1550.1950026961</v>
       </c>
       <c r="O390" t="n">
-        <v>3573199.339953507</v>
+        <v>3449183.880998822</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>5762500</v>
+        <v>5562500</v>
       </c>
     </row>
     <row r="391">
@@ -17219,10 +17219,10 @@
         <v>3</v>
       </c>
       <c r="N391" t="n">
-        <v>1579.3809042553</v>
+        <v>1579.380802139</v>
       </c>
       <c r="O391" t="n">
-        <v>4738.1427127659</v>
+        <v>4738.142406417001</v>
       </c>
       <c r="P391" t="n">
         <v>2900</v>
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -17262,19 +17262,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="N392" t="n">
-        <v>2403.5228513613</v>
+        <v>2403.522961183</v>
       </c>
       <c r="O392" t="n">
-        <v>2381891.145699048</v>
+        <v>2374680.685648804</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
       </c>
       <c r="Q392" t="n">
-        <v>3468500</v>
+        <v>3458000</v>
       </c>
     </row>
     <row r="393">
@@ -18876,10 +18876,10 @@
         </is>
       </c>
       <c r="J429" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
@@ -21366,10 +21366,10 @@
         <v>64</v>
       </c>
       <c r="N488" t="n">
-        <v>22485.695396419</v>
+        <v>22485.695378691</v>
       </c>
       <c r="O488" t="n">
-        <v>1439084.505370816</v>
+        <v>1439084.504236224</v>
       </c>
       <c r="P488" t="n">
         <v>36500</v>
@@ -21518,7 +21518,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -21527,19 +21527,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N492" t="n">
         <v>7103</v>
       </c>
       <c r="O492" t="n">
-        <v>866566</v>
+        <v>845257</v>
       </c>
       <c r="P492" t="n">
         <v>10700</v>
       </c>
       <c r="Q492" t="n">
-        <v>1305400</v>
+        <v>1273300</v>
       </c>
     </row>
     <row r="493">
@@ -22238,7 +22238,7 @@
         </is>
       </c>
       <c r="J509" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -22247,19 +22247,19 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N509" t="n">
-        <v>3271.8447488584</v>
+        <v>1651</v>
       </c>
       <c r="O509" t="n">
-        <v>297737.8721461144</v>
+        <v>145288</v>
       </c>
       <c r="P509" t="n">
         <v>2500</v>
       </c>
       <c r="Q509" t="n">
-        <v>227500</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="510">
@@ -22330,28 +22330,28 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="K511" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N511" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9882003658</v>
       </c>
       <c r="O511" t="n">
-        <v>1297469.534088023</v>
+        <v>1272637.581074989</v>
       </c>
       <c r="P511" t="n">
         <v>9900</v>
       </c>
       <c r="Q511" t="n">
-        <v>2069100</v>
+        <v>2029500</v>
       </c>
     </row>
     <row r="512">
@@ -22843,10 +22843,10 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="K523" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -22985,19 +22985,19 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="N526" t="n">
-        <v>1111.1642023346</v>
+        <v>1106</v>
       </c>
       <c r="O526" t="n">
-        <v>617807.2964980376</v>
+        <v>606088</v>
       </c>
       <c r="P526" t="n">
         <v>2100</v>
       </c>
       <c r="Q526" t="n">
-        <v>1167600</v>
+        <v>1150800</v>
       </c>
     </row>
     <row r="527">
@@ -23029,10 +23029,10 @@
         <v>21</v>
       </c>
       <c r="N527" t="n">
-        <v>1447.7706382979</v>
+        <v>1430.38</v>
       </c>
       <c r="O527" t="n">
-        <v>30403.1834042559</v>
+        <v>30037.98</v>
       </c>
       <c r="P527" t="n">
         <v>4000</v>
@@ -23198,10 +23198,10 @@
         <v>4</v>
       </c>
       <c r="N531" t="n">
-        <v>30244.600034965</v>
+        <v>30244.600034985</v>
       </c>
       <c r="O531" t="n">
-        <v>120978.40013986</v>
+        <v>120978.40013994</v>
       </c>
       <c r="P531" t="n">
         <v>48900</v>
@@ -23232,7 +23232,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -23241,19 +23241,19 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633736737</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O532" t="n">
-        <v>794353.4566561604</v>
+        <v>775096.3988997956</v>
       </c>
       <c r="P532" t="n">
         <v>9900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1633500</v>
+        <v>1593900</v>
       </c>
     </row>
     <row r="533">
@@ -23291,10 +23291,10 @@
         <v>384250.91</v>
       </c>
       <c r="P533" t="n">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="Q533" t="n">
-        <v>674100</v>
+        <v>738300</v>
       </c>
     </row>
     <row r="534">
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K570" t="n">
         <v>0</v>
@@ -24889,19 +24889,19 @@
         <v>0</v>
       </c>
       <c r="M570" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N570" t="n">
         <v>4100.45</v>
       </c>
       <c r="O570" t="n">
-        <v>135314.85</v>
+        <v>131214.4</v>
       </c>
       <c r="P570" t="n">
         <v>26900</v>
       </c>
       <c r="Q570" t="n">
-        <v>887700</v>
+        <v>860800</v>
       </c>
     </row>
     <row r="571">
@@ -24967,7 +24967,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -24976,19 +24976,19 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N572" t="n">
         <v>5431.12</v>
       </c>
       <c r="O572" t="n">
-        <v>613716.5599999999</v>
+        <v>597423.2</v>
       </c>
       <c r="P572" t="n">
         <v>8900</v>
       </c>
       <c r="Q572" t="n">
-        <v>1005700</v>
+        <v>979000</v>
       </c>
     </row>
     <row r="573">
@@ -25066,10 +25066,10 @@
         <v>18</v>
       </c>
       <c r="N574" t="n">
-        <v>1561.0072654155</v>
+        <v>1561.0074054054</v>
       </c>
       <c r="O574" t="n">
-        <v>28098.130777479</v>
+        <v>28098.1332972972</v>
       </c>
       <c r="P574" t="n">
         <v>2900</v>
@@ -26701,10 +26701,10 @@
         <v>1</v>
       </c>
       <c r="N612" t="n">
-        <v>7738.024691358</v>
+        <v>7700</v>
       </c>
       <c r="O612" t="n">
-        <v>7738.024691358</v>
+        <v>7700</v>
       </c>
       <c r="P612" t="n">
         <v>13900</v>
@@ -28075,10 +28075,10 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K642" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -28271,10 +28271,10 @@
         <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>23521.621666667</v>
+        <v>23521.621025641</v>
       </c>
       <c r="O646" t="n">
-        <v>94086.486666668</v>
+        <v>94086.48410256401</v>
       </c>
       <c r="P646" t="n">
         <v>39000</v>
@@ -28363,10 +28363,10 @@
         <v>1208</v>
       </c>
       <c r="N648" t="n">
-        <v>1778.4728878597</v>
+        <v>1778.4728955224</v>
       </c>
       <c r="O648" t="n">
-        <v>2148395.248534517</v>
+        <v>2148395.257791059</v>
       </c>
       <c r="P648" t="n">
         <v>4900</v>
@@ -28593,10 +28593,10 @@
         <v>38</v>
       </c>
       <c r="N653" t="n">
-        <v>16177.301634473</v>
+        <v>16058</v>
       </c>
       <c r="O653" t="n">
-        <v>614737.462109974</v>
+        <v>610204</v>
       </c>
       <c r="P653" t="n">
         <v>25900</v>
@@ -30243,7 +30243,7 @@
         </is>
       </c>
       <c r="J689" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K689" t="n">
         <v>0</v>
@@ -30252,19 +30252,19 @@
         <v>0</v>
       </c>
       <c r="M689" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N689" t="n">
         <v>7713</v>
       </c>
       <c r="O689" t="n">
-        <v>516771</v>
+        <v>485919</v>
       </c>
       <c r="P689" t="n">
         <v>12500</v>
       </c>
       <c r="Q689" t="n">
-        <v>837500</v>
+        <v>787500</v>
       </c>
     </row>
     <row r="690">
@@ -31495,10 +31495,10 @@
         <v>222</v>
       </c>
       <c r="N716" t="n">
-        <v>4129.9375</v>
+        <v>3519</v>
       </c>
       <c r="O716" t="n">
-        <v>916846.125</v>
+        <v>781218</v>
       </c>
       <c r="P716" t="n">
         <v>5900</v>
@@ -31897,7 +31897,7 @@
         </is>
       </c>
       <c r="J725" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K725" t="n">
         <v>0</v>
@@ -31906,19 +31906,19 @@
         <v>0</v>
       </c>
       <c r="M725" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N725" t="n">
-        <v>4907.8228159645</v>
+        <v>4907.8228222222</v>
       </c>
       <c r="O725" t="n">
-        <v>44170.4053436805</v>
+        <v>39262.5825777776</v>
       </c>
       <c r="P725" t="n">
         <v>8200</v>
       </c>
       <c r="Q725" t="n">
-        <v>73800</v>
+        <v>65600</v>
       </c>
     </row>
     <row r="726">
@@ -32185,10 +32185,10 @@
         <v>17</v>
       </c>
       <c r="N731" t="n">
-        <v>3903.7399452055</v>
+        <v>3903.7403351955</v>
       </c>
       <c r="O731" t="n">
-        <v>66363.57906849351</v>
+        <v>66363.5856983235</v>
       </c>
       <c r="P731" t="n">
         <v>7500</v>
@@ -32444,7 +32444,7 @@
         </is>
       </c>
       <c r="J737" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K737" t="n">
         <v>0</v>
@@ -32453,19 +32453,19 @@
         <v>0</v>
       </c>
       <c r="M737" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N737" t="n">
         <v>4202</v>
       </c>
       <c r="O737" t="n">
-        <v>235312</v>
+        <v>222706</v>
       </c>
       <c r="P737" t="n">
         <v>7900</v>
       </c>
       <c r="Q737" t="n">
-        <v>442400</v>
+        <v>418700</v>
       </c>
     </row>
     <row r="738">
@@ -33468,10 +33468,10 @@
         <v>1</v>
       </c>
       <c r="N759" t="n">
-        <v>24040</v>
+        <v>23439</v>
       </c>
       <c r="O759" t="n">
-        <v>24040</v>
+        <v>23439</v>
       </c>
       <c r="P759" t="n">
         <v>37900</v>
@@ -35392,7 +35392,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -35401,19 +35401,19 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="N801" t="n">
-        <v>1516.0387067969</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O801" t="n">
-        <v>526065.4312585243</v>
+        <v>507872.9636137575</v>
       </c>
       <c r="P801" t="n">
         <v>2300</v>
       </c>
       <c r="Q801" t="n">
-        <v>798100</v>
+        <v>770500</v>
       </c>
     </row>
     <row r="802">
@@ -35482,7 +35482,7 @@
         </is>
       </c>
       <c r="J803" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K803" t="n">
         <v>0</v>
@@ -35491,19 +35491,19 @@
         <v>0</v>
       </c>
       <c r="M803" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="N803" t="n">
         <v>508.51</v>
       </c>
       <c r="O803" t="n">
-        <v>39663.78</v>
+        <v>29493.58</v>
       </c>
       <c r="P803" t="n">
         <v>1200</v>
       </c>
       <c r="Q803" t="n">
-        <v>93600</v>
+        <v>69600</v>
       </c>
     </row>
     <row r="804">
@@ -35712,7 +35712,7 @@
         </is>
       </c>
       <c r="J808" t="n">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="K808" t="n">
         <v>0</v>
@@ -35721,19 +35721,19 @@
         <v>0</v>
       </c>
       <c r="M808" t="n">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="N808" t="n">
-        <v>1803.0175771122</v>
+        <v>1803.0176111361</v>
       </c>
       <c r="O808" t="n">
-        <v>1660579.188520336</v>
+        <v>1642549.043744987</v>
       </c>
       <c r="P808" t="n">
         <v>2500</v>
       </c>
       <c r="Q808" t="n">
-        <v>2302500</v>
+        <v>2277500</v>
       </c>
     </row>
     <row r="809">
@@ -35770,10 +35770,10 @@
         <v>143</v>
       </c>
       <c r="N809" t="n">
-        <v>3306.5942583732</v>
+        <v>3306.5942675159</v>
       </c>
       <c r="O809" t="n">
-        <v>472842.9789473676</v>
+        <v>472842.9802547737</v>
       </c>
       <c r="P809" t="n">
         <v>4900</v>
@@ -35862,10 +35862,10 @@
         <v>525</v>
       </c>
       <c r="N811" t="n">
-        <v>2108.7999087799</v>
+        <v>2108.8000229358</v>
       </c>
       <c r="O811" t="n">
-        <v>1107119.952109447</v>
+        <v>1107120.012041295</v>
       </c>
       <c r="P811" t="n">
         <v>2900</v>
@@ -36507,10 +36507,10 @@
         <v>21</v>
       </c>
       <c r="N825" t="n">
-        <v>2546.9780672269</v>
+        <v>2546.9779661017</v>
       </c>
       <c r="O825" t="n">
-        <v>53486.5394117649</v>
+        <v>53486.5372881357</v>
       </c>
       <c r="P825" t="n">
         <v>3900</v>
@@ -36541,7 +36541,7 @@
         </is>
       </c>
       <c r="J826" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K826" t="n">
         <v>0</v>
@@ -36550,19 +36550,19 @@
         <v>0</v>
       </c>
       <c r="M826" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="N826" t="n">
-        <v>1259.2751782508</v>
+        <v>1259.2752009274</v>
       </c>
       <c r="O826" t="n">
-        <v>220373.15619389</v>
+        <v>197706.2065456018</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
       </c>
       <c r="Q826" t="n">
-        <v>332500</v>
+        <v>298300</v>
       </c>
     </row>
     <row r="827">
@@ -36689,10 +36689,10 @@
         <v>13</v>
       </c>
       <c r="N829" t="n">
-        <v>692.1525362185999</v>
+        <v>692.1525418121701</v>
       </c>
       <c r="O829" t="n">
-        <v>8997.9829708418</v>
+        <v>8997.983043558212</v>
       </c>
       <c r="P829" t="n">
         <v>1200</v>
@@ -36954,28 +36954,28 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="K835" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L835" t="n">
         <v>0</v>
       </c>
       <c r="M835" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N835" t="n">
         <v>11690</v>
       </c>
       <c r="O835" t="n">
-        <v>1414490</v>
+        <v>1402800</v>
       </c>
       <c r="P835" t="n">
         <v>18900</v>
       </c>
       <c r="Q835" t="n">
-        <v>2286900</v>
+        <v>2268000</v>
       </c>
     </row>
     <row r="836">
@@ -37052,10 +37052,10 @@
         </is>
       </c>
       <c r="J837" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K837" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L837" t="n">
         <v>0</v>
@@ -37101,7 +37101,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37110,19 +37110,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N838" t="n">
         <v>44470</v>
       </c>
       <c r="O838" t="n">
-        <v>1156220</v>
+        <v>1111750</v>
       </c>
       <c r="P838" t="n">
         <v>71900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1869400</v>
+        <v>1797500</v>
       </c>
     </row>
     <row r="839">
@@ -37150,28 +37150,28 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>251</v>
+        <v>418</v>
       </c>
       <c r="K839" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="L839" t="n">
         <v>0</v>
       </c>
       <c r="M839" t="n">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N839" t="n">
         <v>5215</v>
       </c>
       <c r="O839" t="n">
-        <v>2195515</v>
+        <v>2179870</v>
       </c>
       <c r="P839" t="n">
         <v>8900</v>
       </c>
       <c r="Q839" t="n">
-        <v>3746900</v>
+        <v>3720200</v>
       </c>
     </row>
     <row r="840">
@@ -37612,7 +37612,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -37621,19 +37621,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="N849" t="n">
         <v>2857.22</v>
       </c>
       <c r="O849" t="n">
-        <v>1308606.76</v>
+        <v>1300035.1</v>
       </c>
       <c r="P849" t="n">
         <v>4900</v>
       </c>
       <c r="Q849" t="n">
-        <v>2244200</v>
+        <v>2229500</v>
       </c>
     </row>
     <row r="850">
@@ -38896,7 +38896,7 @@
         </is>
       </c>
       <c r="J877" t="n">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="K877" t="n">
         <v>0</v>
@@ -38905,19 +38905,19 @@
         <v>0</v>
       </c>
       <c r="M877" t="n">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="N877" t="n">
-        <v>2286.164453125</v>
+        <v>2286.1643873518</v>
       </c>
       <c r="O877" t="n">
-        <v>1312258.39609375</v>
+        <v>1284824.385691712</v>
       </c>
       <c r="P877" t="n">
         <v>3000</v>
       </c>
       <c r="Q877" t="n">
-        <v>1722000</v>
+        <v>1686000</v>
       </c>
     </row>
     <row r="878">
@@ -39024,7 +39024,7 @@
         </is>
       </c>
       <c r="J880" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K880" t="n">
         <v>0</v>
@@ -39033,19 +39033,19 @@
         <v>0</v>
       </c>
       <c r="M880" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="N880" t="n">
         <v>5050</v>
       </c>
       <c r="O880" t="n">
-        <v>318150</v>
+        <v>277750</v>
       </c>
       <c r="P880" t="n">
         <v>2000</v>
       </c>
       <c r="Q880" t="n">
-        <v>126000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="881">
@@ -39818,28 +39818,28 @@
         </is>
       </c>
       <c r="J898" t="n">
-        <v>2644</v>
+        <v>4318</v>
       </c>
       <c r="K898" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>4372</v>
+        <v>4318</v>
       </c>
       <c r="N898" t="n">
-        <v>517.29673853391</v>
+        <v>517.29691759113</v>
       </c>
       <c r="O898" t="n">
-        <v>2261621.340870255</v>
+        <v>2233688.090158499</v>
       </c>
       <c r="P898" t="n">
         <v>900</v>
       </c>
       <c r="Q898" t="n">
-        <v>3934800</v>
+        <v>3886200</v>
       </c>
     </row>
     <row r="899">
@@ -40056,10 +40056,10 @@
         <v>267</v>
       </c>
       <c r="N903" t="n">
-        <v>3110.8351781971</v>
+        <v>3110.8351657574</v>
       </c>
       <c r="O903" t="n">
-        <v>830592.9925786257</v>
+        <v>830592.9892572258</v>
       </c>
       <c r="P903" t="n">
         <v>4500</v>
@@ -40266,7 +40266,7 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>2652</v>
+        <v>2628</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
@@ -40275,19 +40275,19 @@
         <v>0</v>
       </c>
       <c r="M908" t="n">
-        <v>2652</v>
+        <v>2628</v>
       </c>
       <c r="N908" t="n">
-        <v>703.79459259958</v>
+        <v>703.79458866348</v>
       </c>
       <c r="O908" t="n">
-        <v>1866463.259574086</v>
+        <v>1849572.179007625</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
       </c>
       <c r="Q908" t="n">
-        <v>2386800</v>
+        <v>2365200</v>
       </c>
     </row>
     <row r="909">
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="J915" t="n">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="K915" t="n">
         <v>0</v>
@@ -40594,19 +40594,19 @@
         <v>0</v>
       </c>
       <c r="M915" t="n">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="N915" t="n">
         <v>2529.19</v>
       </c>
       <c r="O915" t="n">
-        <v>364203.36</v>
+        <v>250389.81</v>
       </c>
       <c r="P915" t="n">
         <v>5100</v>
       </c>
       <c r="Q915" t="n">
-        <v>734400</v>
+        <v>504900</v>
       </c>
     </row>
     <row r="916">
@@ -40762,7 +40762,7 @@
         </is>
       </c>
       <c r="J919" t="n">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="K919" t="n">
         <v>0</v>
@@ -40771,19 +40771,19 @@
         <v>0</v>
       </c>
       <c r="M919" t="n">
-        <v>10</v>
+        <v>235</v>
       </c>
       <c r="N919" t="n">
         <v>1300</v>
       </c>
       <c r="O919" t="n">
-        <v>13000</v>
+        <v>305500</v>
       </c>
       <c r="P919" t="n">
         <v>2200</v>
       </c>
       <c r="Q919" t="n">
-        <v>22000</v>
+        <v>517000</v>
       </c>
     </row>
     <row r="920">
@@ -42481,10 +42481,10 @@
         <v>54</v>
       </c>
       <c r="N956" t="n">
-        <v>3099.6039575972</v>
+        <v>3067.0906360424</v>
       </c>
       <c r="O956" t="n">
-        <v>167378.6137102488</v>
+        <v>165622.8943462896</v>
       </c>
       <c r="P956" t="n">
         <v>7200</v>
@@ -42879,7 +42879,7 @@
         </is>
       </c>
       <c r="J965" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="K965" t="n">
         <v>0</v>
@@ -42888,19 +42888,19 @@
         <v>0</v>
       </c>
       <c r="M965" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="N965" t="n">
         <v>1759.84</v>
       </c>
       <c r="O965" t="n">
-        <v>344928.64</v>
+        <v>337889.28</v>
       </c>
       <c r="P965" t="n">
         <v>3300</v>
       </c>
       <c r="Q965" t="n">
-        <v>646800</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="966">
@@ -43355,10 +43355,10 @@
         <v>2</v>
       </c>
       <c r="N975" t="n">
-        <v>2000.7364130435</v>
+        <v>2000.7487209302</v>
       </c>
       <c r="O975" t="n">
-        <v>4001.472826087</v>
+        <v>4001.4974418604</v>
       </c>
       <c r="P975" t="n">
         <v>2000</v>
@@ -43780,10 +43780,10 @@
         <v>98</v>
       </c>
       <c r="N984" t="n">
-        <v>24856.309787234</v>
+        <v>24338.47</v>
       </c>
       <c r="O984" t="n">
-        <v>2435918.359148932</v>
+        <v>2385170.06</v>
       </c>
       <c r="P984" t="n">
         <v>27900</v>
@@ -46675,7 +46675,7 @@
         </is>
       </c>
       <c r="J1050" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K1050" t="n">
         <v>0</v>
@@ -46684,19 +46684,19 @@
         <v>0</v>
       </c>
       <c r="M1050" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="N1050" t="n">
         <v>1464</v>
       </c>
       <c r="O1050" t="n">
-        <v>80520</v>
+        <v>36600</v>
       </c>
       <c r="P1050" t="n">
         <v>1500</v>
       </c>
       <c r="Q1050" t="n">
-        <v>82500</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="1051">
@@ -48961,10 +48961,10 @@
         <v>171</v>
       </c>
       <c r="N1101" t="n">
-        <v>9401.162790697699</v>
+        <v>9240</v>
       </c>
       <c r="O1101" t="n">
-        <v>1607598.837209307</v>
+        <v>1580040</v>
       </c>
       <c r="P1101" t="n">
         <v>11500</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -935,10 +935,10 @@
         <v>38</v>
       </c>
       <c r="N13" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O13" t="n">
-        <v>1030170.731707318</v>
+        <v>1026000</v>
       </c>
       <c r="P13" t="n">
         <v>20000</v>
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1226,19 +1226,19 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="N20" t="n">
-        <v>1811.3112820513</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O20" t="n">
-        <v>691920.9097435966</v>
+        <v>746260.07604937</v>
       </c>
       <c r="P20" t="n">
         <v>2600</v>
       </c>
       <c r="Q20" t="n">
-        <v>993200</v>
+        <v>1071200</v>
       </c>
     </row>
     <row r="21">
@@ -9773,7 +9773,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -9782,19 +9782,19 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N222" t="n">
-        <v>1098.0729937163</v>
+        <v>1098.0730382022</v>
       </c>
       <c r="O222" t="n">
-        <v>26353.7518491912</v>
+        <v>29647.9720314594</v>
       </c>
       <c r="P222" t="n">
         <v>1500</v>
       </c>
       <c r="Q222" t="n">
-        <v>36000</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="223">
@@ -11219,7 +11219,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11228,19 +11228,19 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="N256" t="n">
         <v>2804.33</v>
       </c>
       <c r="O256" t="n">
-        <v>1197448.91</v>
+        <v>1231100.87</v>
       </c>
       <c r="P256" t="n">
         <v>4900</v>
       </c>
       <c r="Q256" t="n">
-        <v>2092300</v>
+        <v>2151100</v>
       </c>
     </row>
     <row r="257">
@@ -11587,10 +11587,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O264" t="n">
-        <v>219491.65477255</v>
+        <v>219840.8826571215</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="K274" t="n">
         <v>0</v>
@@ -12024,19 +12024,19 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="N274" t="n">
         <v>1903</v>
       </c>
       <c r="O274" t="n">
-        <v>763103</v>
+        <v>808775</v>
       </c>
       <c r="P274" t="n">
         <v>3200</v>
       </c>
       <c r="Q274" t="n">
-        <v>1283200</v>
+        <v>1360000</v>
       </c>
     </row>
     <row r="275">
@@ -12163,10 +12163,10 @@
         <v>3</v>
       </c>
       <c r="N277" t="n">
-        <v>3230.0657009346</v>
+        <v>3230.0656603774</v>
       </c>
       <c r="O277" t="n">
-        <v>9690.197102803801</v>
+        <v>9690.1969811322</v>
       </c>
       <c r="P277" t="n">
         <v>6200</v>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="J299" t="n">
-        <v>820</v>
+        <v>844</v>
       </c>
       <c r="K299" t="n">
         <v>0</v>
@@ -13161,19 +13161,19 @@
         <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>820</v>
+        <v>844</v>
       </c>
       <c r="N299" t="n">
         <v>1203.38</v>
       </c>
       <c r="O299" t="n">
-        <v>986771.6000000001</v>
+        <v>1015652.72</v>
       </c>
       <c r="P299" t="n">
         <v>1900</v>
       </c>
       <c r="Q299" t="n">
-        <v>1558000</v>
+        <v>1603600</v>
       </c>
     </row>
     <row r="300">
@@ -13244,7 +13244,7 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -13253,19 +13253,19 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N301" t="n">
         <v>5888</v>
       </c>
       <c r="O301" t="n">
-        <v>453376</v>
+        <v>471040</v>
       </c>
       <c r="P301" t="n">
         <v>9500</v>
       </c>
       <c r="Q301" t="n">
-        <v>731500</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="302">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13514,19 +13514,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N307" t="n">
         <v>5667.94</v>
       </c>
       <c r="O307" t="n">
-        <v>595133.7</v>
+        <v>606469.58</v>
       </c>
       <c r="P307" t="n">
         <v>9500</v>
       </c>
       <c r="Q307" t="n">
-        <v>997500</v>
+        <v>1016500</v>
       </c>
     </row>
     <row r="308">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="J309" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K309" t="n">
         <v>0</v>
@@ -13606,19 +13606,19 @@
         <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N309" t="n">
         <v>8662</v>
       </c>
       <c r="O309" t="n">
-        <v>866200</v>
+        <v>874862</v>
       </c>
       <c r="P309" t="n">
         <v>14200</v>
       </c>
       <c r="Q309" t="n">
-        <v>1420000</v>
+        <v>1434200</v>
       </c>
     </row>
     <row r="310">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
@@ -13993,19 +13993,19 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="N318" t="n">
         <v>2953.73</v>
       </c>
       <c r="O318" t="n">
-        <v>363308.79</v>
+        <v>398753.55</v>
       </c>
       <c r="P318" t="n">
         <v>4900</v>
       </c>
       <c r="Q318" t="n">
-        <v>602700</v>
+        <v>661500</v>
       </c>
     </row>
     <row r="319">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="J328" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K328" t="n">
         <v>0</v>
@@ -14433,19 +14433,19 @@
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N328" t="n">
         <v>2665.4</v>
       </c>
       <c r="O328" t="n">
-        <v>117277.6</v>
+        <v>122608.4</v>
       </c>
       <c r="P328" t="n">
         <v>20900</v>
       </c>
       <c r="Q328" t="n">
-        <v>919600</v>
+        <v>961400</v>
       </c>
     </row>
     <row r="329">
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="J330" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="K330" t="n">
         <v>0</v>
@@ -14528,19 +14528,19 @@
         <v>0</v>
       </c>
       <c r="M330" t="n">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="N330" t="n">
         <v>1381.75</v>
       </c>
       <c r="O330" t="n">
-        <v>555463.5</v>
+        <v>594152.5</v>
       </c>
       <c r="P330" t="n">
         <v>2500</v>
       </c>
       <c r="Q330" t="n">
-        <v>1005000</v>
+        <v>1075000</v>
       </c>
     </row>
     <row r="331">
@@ -14662,10 +14662,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.942043327</v>
+        <v>1243074.943990596</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15886,19 +15886,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="N361" t="n">
         <v>1647.46</v>
       </c>
       <c r="O361" t="n">
-        <v>1219120.4</v>
+        <v>1238889.92</v>
       </c>
       <c r="P361" t="n">
         <v>2900</v>
       </c>
       <c r="Q361" t="n">
-        <v>2146000</v>
+        <v>2180800</v>
       </c>
     </row>
     <row r="362">
@@ -15965,7 +15965,7 @@
         </is>
       </c>
       <c r="J363" t="n">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15974,19 +15974,19 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>409</v>
+        <v>443</v>
       </c>
       <c r="N363" t="n">
         <v>1387.55</v>
       </c>
       <c r="O363" t="n">
-        <v>567507.95</v>
+        <v>614684.65</v>
       </c>
       <c r="P363" t="n">
         <v>2300</v>
       </c>
       <c r="Q363" t="n">
-        <v>940700</v>
+        <v>1018900</v>
       </c>
     </row>
     <row r="364">
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="J372" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -16374,19 +16374,19 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N372" t="n">
         <v>3761.6</v>
       </c>
       <c r="O372" t="n">
-        <v>176795.2</v>
+        <v>199364.8</v>
       </c>
       <c r="P372" t="n">
         <v>6900</v>
       </c>
       <c r="Q372" t="n">
-        <v>324300</v>
+        <v>365700</v>
       </c>
     </row>
     <row r="373">
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16850,19 +16850,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="N383" t="n">
         <v>3751</v>
       </c>
       <c r="O383" t="n">
-        <v>2910776</v>
+        <v>2922029</v>
       </c>
       <c r="P383" t="n">
         <v>6400</v>
       </c>
       <c r="Q383" t="n">
-        <v>4966400</v>
+        <v>4985600</v>
       </c>
     </row>
     <row r="384">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="J386" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="K386" t="n">
         <v>0</v>
@@ -16991,19 +16991,19 @@
         <v>0</v>
       </c>
       <c r="M386" t="n">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="N386" t="n">
         <v>1630.9251181364</v>
       </c>
       <c r="O386" t="n">
-        <v>1278645.292618938</v>
+        <v>1293323.618682165</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
       </c>
       <c r="Q386" t="n">
-        <v>1960000</v>
+        <v>1982500</v>
       </c>
     </row>
     <row r="387">
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="J388" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="K388" t="n">
         <v>0</v>
@@ -17078,19 +17078,19 @@
         <v>0</v>
       </c>
       <c r="M388" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="N388" t="n">
-        <v>1467.2914141414</v>
+        <v>1467.3004273504</v>
       </c>
       <c r="O388" t="n">
-        <v>105644.9818181808</v>
+        <v>132057.038461536</v>
       </c>
       <c r="P388" t="n">
         <v>2500</v>
       </c>
       <c r="Q388" t="n">
-        <v>180000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="389">
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="J389" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="K389" t="n">
         <v>0</v>
@@ -17124,19 +17124,19 @@
         <v>0</v>
       </c>
       <c r="M389" t="n">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="N389" t="n">
-        <v>1690.5719339623</v>
+        <v>1690.5726046512</v>
       </c>
       <c r="O389" t="n">
-        <v>706659.0683962414</v>
+        <v>721874.5021860624</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
       </c>
       <c r="Q389" t="n">
-        <v>1212200</v>
+        <v>1238300</v>
       </c>
     </row>
     <row r="390">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>2225</v>
+        <v>2285</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
@@ -17170,19 +17170,19 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>2225</v>
+        <v>2285</v>
       </c>
       <c r="N390" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O390" t="n">
-        <v>3449183.880998822</v>
+        <v>3542195.489442288</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
       </c>
       <c r="Q390" t="n">
-        <v>5562500</v>
+        <v>5712500</v>
       </c>
     </row>
     <row r="391">
@@ -17253,7 +17253,7 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
@@ -17262,19 +17262,19 @@
         <v>0</v>
       </c>
       <c r="M392" t="n">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="N392" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="O392" t="n">
-        <v>2374680.685648804</v>
+        <v>2381891.229324187</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
       </c>
       <c r="Q392" t="n">
-        <v>3458000</v>
+        <v>3468500</v>
       </c>
     </row>
     <row r="393">
@@ -18627,10 +18627,10 @@
         <v>30</v>
       </c>
       <c r="N423" t="n">
-        <v>17991.272727273</v>
+        <v>17328</v>
       </c>
       <c r="O423" t="n">
-        <v>539738.18181819</v>
+        <v>519840</v>
       </c>
       <c r="P423" t="n">
         <v>32900</v>
@@ -21120,10 +21120,10 @@
         <v>396</v>
       </c>
       <c r="N482" t="n">
-        <v>2029.8742541123</v>
+        <v>2029.8742613636</v>
       </c>
       <c r="O482" t="n">
-        <v>803830.2046284708</v>
+        <v>803830.2074999856</v>
       </c>
       <c r="P482" t="n">
         <v>3600</v>
@@ -21518,7 +21518,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -21527,19 +21527,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="N492" t="n">
         <v>7103</v>
       </c>
       <c r="O492" t="n">
-        <v>845257</v>
+        <v>866566</v>
       </c>
       <c r="P492" t="n">
         <v>10700</v>
       </c>
       <c r="Q492" t="n">
-        <v>1273300</v>
+        <v>1305400</v>
       </c>
     </row>
     <row r="493">
@@ -21830,10 +21830,10 @@
         <v>17</v>
       </c>
       <c r="N499" t="n">
-        <v>11724.722692308</v>
+        <v>11431.604487179</v>
       </c>
       <c r="O499" t="n">
-        <v>199320.285769236</v>
+        <v>194337.276282043</v>
       </c>
       <c r="P499" t="n">
         <v>48900</v>
@@ -22122,10 +22122,10 @@
         <v>52</v>
       </c>
       <c r="N506" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O506" t="n">
-        <v>1598743.264233596</v>
+        <v>1591772</v>
       </c>
       <c r="P506" t="n">
         <v>38900</v>
@@ -22330,7 +22330,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -22339,19 +22339,19 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="N511" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O511" t="n">
-        <v>1272637.581074989</v>
+        <v>1297469.534088023</v>
       </c>
       <c r="P511" t="n">
         <v>9900</v>
       </c>
       <c r="Q511" t="n">
-        <v>2029500</v>
+        <v>2069100</v>
       </c>
     </row>
     <row r="512">
@@ -23232,7 +23232,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -23241,19 +23241,19 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O532" t="n">
-        <v>775096.3988997956</v>
+        <v>794353.4530189666</v>
       </c>
       <c r="P532" t="n">
         <v>9900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1593900</v>
+        <v>1633500</v>
       </c>
     </row>
     <row r="533">
@@ -24682,10 +24682,10 @@
         <v>29</v>
       </c>
       <c r="N565" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O565" t="n">
-        <v>786589.173705254</v>
+        <v>786589.1730444019</v>
       </c>
       <c r="P565" t="n">
         <v>44500</v>
@@ -24880,7 +24880,7 @@
         </is>
       </c>
       <c r="J570" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K570" t="n">
         <v>0</v>
@@ -24889,19 +24889,19 @@
         <v>0</v>
       </c>
       <c r="M570" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N570" t="n">
         <v>4100.45</v>
       </c>
       <c r="O570" t="n">
-        <v>131214.4</v>
+        <v>135314.85</v>
       </c>
       <c r="P570" t="n">
         <v>26900</v>
       </c>
       <c r="Q570" t="n">
-        <v>860800</v>
+        <v>887700</v>
       </c>
     </row>
     <row r="571">
@@ -25245,10 +25245,10 @@
         <v>31</v>
       </c>
       <c r="N578" t="n">
-        <v>27080.935211268</v>
+        <v>26854</v>
       </c>
       <c r="O578" t="n">
-        <v>839508.9915493079</v>
+        <v>832474</v>
       </c>
       <c r="P578" t="n">
         <v>43900</v>
@@ -27762,10 +27762,10 @@
         <v>15</v>
       </c>
       <c r="N635" t="n">
-        <v>9188.98</v>
+        <v>9456.2957818182</v>
       </c>
       <c r="O635" t="n">
-        <v>137834.7</v>
+        <v>141844.436727273</v>
       </c>
       <c r="P635" t="n">
         <v>12900</v>
@@ -28271,10 +28271,10 @@
         <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>23521.621025641</v>
+        <v>23521.620277778</v>
       </c>
       <c r="O646" t="n">
-        <v>94086.48410256401</v>
+        <v>94086.48111111201</v>
       </c>
       <c r="P646" t="n">
         <v>39000</v>
@@ -28501,10 +28501,10 @@
         <v>22</v>
       </c>
       <c r="N651" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O651" t="n">
-        <v>504574.289905092</v>
+        <v>500258</v>
       </c>
       <c r="P651" t="n">
         <v>36900</v>
@@ -30301,10 +30301,10 @@
         <v>31</v>
       </c>
       <c r="N690" t="n">
-        <v>28661.941747573</v>
+        <v>28116</v>
       </c>
       <c r="O690" t="n">
-        <v>888520.194174763</v>
+        <v>871596</v>
       </c>
       <c r="P690" t="n">
         <v>45900</v>
@@ -30577,10 +30577,10 @@
         <v>5</v>
       </c>
       <c r="N696" t="n">
-        <v>10411</v>
+        <v>10642.355555556</v>
       </c>
       <c r="O696" t="n">
-        <v>52055</v>
+        <v>53211.77777778</v>
       </c>
       <c r="P696" t="n">
         <v>16900</v>
@@ -32226,10 +32226,10 @@
         <v>49</v>
       </c>
       <c r="N732" t="n">
-        <v>21286.162162162</v>
+        <v>20726</v>
       </c>
       <c r="O732" t="n">
-        <v>1043021.945945938</v>
+        <v>1015574</v>
       </c>
       <c r="P732" t="n">
         <v>33900</v>
@@ -32272,10 +32272,10 @@
         <v>15</v>
       </c>
       <c r="N733" t="n">
-        <v>21767.55</v>
+        <v>20731</v>
       </c>
       <c r="O733" t="n">
-        <v>326513.25</v>
+        <v>310965</v>
       </c>
       <c r="P733" t="n">
         <v>33900</v>
@@ -33284,10 +33284,10 @@
         <v>93</v>
       </c>
       <c r="N755" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O755" t="n">
-        <v>1263497.856037116</v>
+        <v>1261545</v>
       </c>
       <c r="P755" t="n">
         <v>22500</v>
@@ -33514,10 +33514,10 @@
         <v>56</v>
       </c>
       <c r="N760" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O760" t="n">
-        <v>1067313.270524872</v>
+        <v>1064448</v>
       </c>
       <c r="P760" t="n">
         <v>30900</v>
@@ -33655,10 +33655,10 @@
         <v>106</v>
       </c>
       <c r="N763" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O763" t="n">
-        <v>1912118.541666702</v>
+        <v>1907152</v>
       </c>
       <c r="P763" t="n">
         <v>28900</v>
@@ -33747,10 +33747,10 @@
         <v>161</v>
       </c>
       <c r="N765" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O765" t="n">
-        <v>2755034.384430447</v>
+        <v>2749234.311877648</v>
       </c>
       <c r="P765" t="n">
         <v>27500</v>
@@ -34941,10 +34941,10 @@
         <v>39</v>
       </c>
       <c r="N791" t="n">
-        <v>15602.016806723</v>
+        <v>15472</v>
       </c>
       <c r="O791" t="n">
-        <v>608478.655462197</v>
+        <v>603408</v>
       </c>
       <c r="P791" t="n">
         <v>25900</v>
@@ -35392,7 +35392,7 @@
         </is>
       </c>
       <c r="J801" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="K801" t="n">
         <v>0</v>
@@ -35401,19 +35401,19 @@
         <v>0</v>
       </c>
       <c r="M801" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="N801" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O801" t="n">
-        <v>507872.9636137575</v>
+        <v>526065.4285552902</v>
       </c>
       <c r="P801" t="n">
         <v>2300</v>
       </c>
       <c r="Q801" t="n">
-        <v>770500</v>
+        <v>798100</v>
       </c>
     </row>
     <row r="802">
@@ -35586,10 +35586,10 @@
         <v>321</v>
       </c>
       <c r="N805" t="n">
-        <v>1907.3924305556</v>
+        <v>1907.3922142857</v>
       </c>
       <c r="O805" t="n">
-        <v>612272.9702083475</v>
+        <v>612272.9007857097</v>
       </c>
       <c r="P805" t="n">
         <v>2500</v>
@@ -35724,10 +35724,10 @@
         <v>911</v>
       </c>
       <c r="N808" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O808" t="n">
-        <v>1642549.043744987</v>
+        <v>1642549.081309252</v>
       </c>
       <c r="P808" t="n">
         <v>2500</v>
@@ -35816,10 +35816,10 @@
         <v>374</v>
       </c>
       <c r="N810" t="n">
-        <v>2122.1634163581</v>
+        <v>2122.1634141414</v>
       </c>
       <c r="O810" t="n">
-        <v>793689.1177179295</v>
+        <v>793689.1168888836</v>
       </c>
       <c r="P810" t="n">
         <v>2900</v>
@@ -35954,10 +35954,10 @@
         <v>168</v>
       </c>
       <c r="N813" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O813" t="n">
-        <v>541727.7656502264</v>
+        <v>541727.7665956296</v>
       </c>
       <c r="P813" t="n">
         <v>4500</v>
@@ -36000,10 +36000,10 @@
         <v>560</v>
       </c>
       <c r="N814" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O814" t="n">
-        <v>927320.1161866321</v>
+        <v>927320.0230547681</v>
       </c>
       <c r="P814" t="n">
         <v>2500</v>
@@ -36415,10 +36415,10 @@
         <v>2</v>
       </c>
       <c r="N823" t="n">
-        <v>1906.1654098361</v>
+        <v>2153.2609259259</v>
       </c>
       <c r="O823" t="n">
-        <v>3812.3308196722</v>
+        <v>4306.5218518518</v>
       </c>
       <c r="P823" t="n">
         <v>2900</v>
@@ -36541,7 +36541,7 @@
         </is>
       </c>
       <c r="J826" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="K826" t="n">
         <v>0</v>
@@ -36550,19 +36550,19 @@
         <v>0</v>
       </c>
       <c r="M826" t="n">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="N826" t="n">
-        <v>1259.2752009274</v>
+        <v>1259.2751769231</v>
       </c>
       <c r="O826" t="n">
-        <v>197706.2065456018</v>
+        <v>220373.1559615425</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
       </c>
       <c r="Q826" t="n">
-        <v>298300</v>
+        <v>332500</v>
       </c>
     </row>
     <row r="827">
@@ -36689,10 +36689,10 @@
         <v>13</v>
       </c>
       <c r="N829" t="n">
-        <v>692.1525418121701</v>
+        <v>692.15254743047</v>
       </c>
       <c r="O829" t="n">
-        <v>8997.983043558212</v>
+        <v>8997.98311659611</v>
       </c>
       <c r="P829" t="n">
         <v>1200</v>
@@ -36954,7 +36954,7 @@
         </is>
       </c>
       <c r="J835" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K835" t="n">
         <v>0</v>
@@ -36963,19 +36963,19 @@
         <v>0</v>
       </c>
       <c r="M835" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N835" t="n">
         <v>11690</v>
       </c>
       <c r="O835" t="n">
-        <v>1402800</v>
+        <v>1414490</v>
       </c>
       <c r="P835" t="n">
         <v>18900</v>
       </c>
       <c r="Q835" t="n">
-        <v>2268000</v>
+        <v>2286900</v>
       </c>
     </row>
     <row r="836">
@@ -37101,7 +37101,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37110,19 +37110,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N838" t="n">
         <v>44470</v>
       </c>
       <c r="O838" t="n">
-        <v>1111750</v>
+        <v>1156220</v>
       </c>
       <c r="P838" t="n">
         <v>71900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1797500</v>
+        <v>1869400</v>
       </c>
     </row>
     <row r="839">
@@ -37150,7 +37150,7 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
@@ -37159,19 +37159,19 @@
         <v>0</v>
       </c>
       <c r="M839" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N839" t="n">
         <v>5215</v>
       </c>
       <c r="O839" t="n">
-        <v>2179870</v>
+        <v>2195515</v>
       </c>
       <c r="P839" t="n">
         <v>8900</v>
       </c>
       <c r="Q839" t="n">
-        <v>3720200</v>
+        <v>3746900</v>
       </c>
     </row>
     <row r="840">
@@ -37673,10 +37673,10 @@
         <v>272</v>
       </c>
       <c r="N850" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O850" t="n">
-        <v>2433143.36</v>
+        <v>2434240.193971446</v>
       </c>
       <c r="P850" t="n">
         <v>14900</v>
@@ -38896,7 +38896,7 @@
         </is>
       </c>
       <c r="J877" t="n">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="K877" t="n">
         <v>0</v>
@@ -38905,19 +38905,19 @@
         <v>0</v>
       </c>
       <c r="M877" t="n">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="N877" t="n">
-        <v>2286.1643873518</v>
+        <v>2286.164453125</v>
       </c>
       <c r="O877" t="n">
-        <v>1284824.385691712</v>
+        <v>1312258.39609375</v>
       </c>
       <c r="P877" t="n">
         <v>3000</v>
       </c>
       <c r="Q877" t="n">
-        <v>1686000</v>
+        <v>1722000</v>
       </c>
     </row>
     <row r="878">
@@ -39818,7 +39818,7 @@
         </is>
       </c>
       <c r="J898" t="n">
-        <v>4318</v>
+        <v>4348</v>
       </c>
       <c r="K898" t="n">
         <v>0</v>
@@ -39827,19 +39827,19 @@
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>4318</v>
+        <v>4348</v>
       </c>
       <c r="N898" t="n">
-        <v>517.29691759113</v>
+        <v>517.29686746988</v>
       </c>
       <c r="O898" t="n">
-        <v>2233688.090158499</v>
+        <v>2249206.779759038</v>
       </c>
       <c r="P898" t="n">
         <v>900</v>
       </c>
       <c r="Q898" t="n">
-        <v>3886200</v>
+        <v>3913200</v>
       </c>
     </row>
     <row r="899">
@@ -40266,7 +40266,7 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>2628</v>
+        <v>2652</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
@@ -40275,19 +40275,19 @@
         <v>0</v>
       </c>
       <c r="M908" t="n">
-        <v>2628</v>
+        <v>2652</v>
       </c>
       <c r="N908" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O908" t="n">
-        <v>1849572.179007625</v>
+        <v>1866463.253776761</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
       </c>
       <c r="Q908" t="n">
-        <v>2365200</v>
+        <v>2386800</v>
       </c>
     </row>
     <row r="909">
@@ -41721,10 +41721,10 @@
         <v>4</v>
       </c>
       <c r="N940" t="n">
-        <v>19605.898888889</v>
+        <v>16041.19</v>
       </c>
       <c r="O940" t="n">
-        <v>78423.59555555601</v>
+        <v>64164.76</v>
       </c>
       <c r="P940" t="n">
         <v>40000</v>
@@ -42879,7 +42879,7 @@
         </is>
       </c>
       <c r="J965" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="K965" t="n">
         <v>0</v>
@@ -42888,19 +42888,19 @@
         <v>0</v>
       </c>
       <c r="M965" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N965" t="n">
         <v>1759.84</v>
       </c>
       <c r="O965" t="n">
-        <v>337889.28</v>
+        <v>344928.64</v>
       </c>
       <c r="P965" t="n">
         <v>3300</v>
       </c>
       <c r="Q965" t="n">
-        <v>633600</v>
+        <v>646800</v>
       </c>
     </row>
     <row r="966">
@@ -42984,10 +42984,10 @@
         <v>1</v>
       </c>
       <c r="N967" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="O967" t="n">
-        <v>10737.525384615</v>
+        <v>19429.807619048</v>
       </c>
       <c r="P967" t="n">
         <v>18900</v>
@@ -43401,10 +43401,10 @@
         <v>8</v>
       </c>
       <c r="N976" t="n">
-        <v>5254.1635714286</v>
+        <v>5216.9</v>
       </c>
       <c r="O976" t="n">
-        <v>42033.3085714288</v>
+        <v>41735.2</v>
       </c>
       <c r="P976" t="n">
         <v>20500</v>
@@ -46675,7 +46675,7 @@
         </is>
       </c>
       <c r="J1050" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="K1050" t="n">
         <v>0</v>
@@ -46684,19 +46684,19 @@
         <v>0</v>
       </c>
       <c r="M1050" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="N1050" t="n">
         <v>1464</v>
       </c>
       <c r="O1050" t="n">
-        <v>36600</v>
+        <v>62952</v>
       </c>
       <c r="P1050" t="n">
         <v>1500</v>
       </c>
       <c r="Q1050" t="n">
-        <v>37500</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="1051">

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-29</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>10471</v>
-      </c>
-      <c r="B7" t="n">
-        <v>6941607380819</v>
+        <v>1051</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PISCINA ESTRUCTURAL 228X159X42cm</t>
+          <t>CARTUCHERA CON AGARRADERA MOTIVO SPORT 1051</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -679,7 +676,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -688,42 +685,37 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>96741.481428571</v>
+        <v>4400</v>
       </c>
       <c r="O7" t="n">
-        <v>290224.444285713</v>
+        <v>35200</v>
       </c>
       <c r="P7" t="n">
-        <v>188900</v>
+        <v>5300</v>
       </c>
       <c r="Q7" t="n">
-        <v>566700</v>
+        <v>42400</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1051</v>
+        <v>1100050</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CARTUCHERA CON AGARRADERA MOTIVO SPORT 1051</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>SERPENTOR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -732,37 +724,42 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4400</v>
+        <v>27000</v>
       </c>
       <c r="O8" t="n">
-        <v>35200</v>
+        <v>81000</v>
       </c>
       <c r="P8" t="n">
-        <v>5300</v>
+        <v>92000</v>
       </c>
       <c r="Q8" t="n">
-        <v>42400</v>
+        <v>276000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1100050</v>
+        <v>1456</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SERPENTOR</t>
+          <t>MORRAL INFANTIL MODELOS STD 1456</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -771,42 +768,37 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>27000</v>
+        <v>22900</v>
       </c>
       <c r="O9" t="n">
-        <v>81000</v>
+        <v>389300</v>
       </c>
       <c r="P9" t="n">
-        <v>92000</v>
+        <v>27500</v>
       </c>
       <c r="Q9" t="n">
-        <v>276000</v>
+        <v>467500</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1456</v>
+        <v>1600010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MORRAL INFANTIL MODELOS STD 1456</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MUNECA MALCRIADA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -815,28 +807,28 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>22900</v>
+        <v>37615.38</v>
       </c>
       <c r="O10" t="n">
-        <v>389300</v>
+        <v>37615.38</v>
       </c>
       <c r="P10" t="n">
-        <v>27500</v>
+        <v>48900</v>
       </c>
       <c r="Q10" t="n">
-        <v>467500</v>
+        <v>48900</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1600010</v>
+        <v>1600080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUNECA MALCRIADA</t>
+          <t>1600080 COSSETE BABY STEPS-2ASSORTED OUTFITS</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -845,7 +837,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -854,28 +846,28 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>37615.38</v>
+        <v>27000</v>
       </c>
       <c r="O11" t="n">
-        <v>37615.38</v>
+        <v>567000</v>
       </c>
       <c r="P11" t="n">
         <v>48900</v>
       </c>
       <c r="Q11" t="n">
-        <v>48900</v>
+        <v>1026900</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1600080</v>
+        <v>1600090</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1600080 COSSETE BABY STEPS-2ASSORTED OUTFITS</t>
+          <t>1600090 SYMPHONY TOWER</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -884,7 +876,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -893,28 +885,30 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="N12" t="n">
         <v>27000</v>
       </c>
       <c r="O12" t="n">
-        <v>432000</v>
+        <v>1026000</v>
       </c>
       <c r="P12" t="n">
-        <v>48900</v>
+        <v>20000</v>
       </c>
       <c r="Q12" t="n">
-        <v>782400</v>
+        <v>760000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>1600090</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>16722-7</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1600090 SYMPHONY TOWER</t>
+          <t>16722-7 PICATODO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -923,7 +917,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -932,39 +926,42 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N13" t="n">
-        <v>27000</v>
+        <v>8642.226428571401</v>
       </c>
       <c r="O13" t="n">
-        <v>1026000</v>
+        <v>276551.2457142848</v>
       </c>
       <c r="P13" t="n">
-        <v>20000</v>
+        <v>13900</v>
       </c>
       <c r="Q13" t="n">
-        <v>760000</v>
+        <v>444800</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>16722-7</t>
-        </is>
+      <c r="A14" t="n">
+        <v>16806</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16722-7 PICATODO</t>
+          <t>ESFERO COCNEJO  16806</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -973,28 +970,28 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="N14" t="n">
-        <v>8642.226428571401</v>
+        <v>900</v>
       </c>
       <c r="O14" t="n">
-        <v>276551.2457142848</v>
+        <v>71100</v>
       </c>
       <c r="P14" t="n">
-        <v>13900</v>
+        <v>1100</v>
       </c>
       <c r="Q14" t="n">
-        <v>444800</v>
+        <v>86900</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16806</v>
+        <v>1689</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ESFERO COCNEJO  16806</t>
+          <t>ESFERO CAPIBARA 1689</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1008,7 +1005,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1017,28 +1014,28 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N15" t="n">
-        <v>900</v>
+        <v>988.39849162011</v>
       </c>
       <c r="O15" t="n">
-        <v>71100</v>
+        <v>77095.08234636858</v>
       </c>
       <c r="P15" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="Q15" t="n">
-        <v>86900</v>
+        <v>93600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1689</v>
+        <v>16890</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ESFERO CAPIBARA 1689</t>
+          <t>ESFERO MOTO 16890</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1052,7 +1049,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1061,42 +1058,37 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="N16" t="n">
-        <v>988.39849162011</v>
+        <v>900</v>
       </c>
       <c r="O16" t="n">
-        <v>77095.08234636858</v>
+        <v>51300</v>
       </c>
       <c r="P16" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="Q16" t="n">
-        <v>93600</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16890</v>
+        <v>17269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ESFERO MOTO 16890</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>17269 EXPRIMIDOR</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1105,28 +1097,30 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="N17" t="n">
-        <v>900</v>
+        <v>28076.92</v>
       </c>
       <c r="O17" t="n">
-        <v>51300</v>
+        <v>56153.84</v>
       </c>
       <c r="P17" t="n">
-        <v>1100</v>
+        <v>36500</v>
       </c>
       <c r="Q17" t="n">
-        <v>62700</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>17269</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17269-3</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17269 EXPRIMIDOR</t>
+          <t>17269-3 CEPILLO ELECTRICO LIMPIADOR</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1135,7 +1129,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1144,39 +1138,39 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="N18" t="n">
-        <v>28076.92</v>
+        <v>14490.384892086</v>
       </c>
       <c r="O18" t="n">
-        <v>56153.84</v>
+        <v>304298.082733806</v>
       </c>
       <c r="P18" t="n">
-        <v>36500</v>
+        <v>23600</v>
       </c>
       <c r="Q18" t="n">
-        <v>73000</v>
+        <v>495600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17269-3</t>
+          <t>2038-2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17269-3 CEPILLO ELECTRICO LIMPIADOR</t>
+          <t>VARITA DE CONO CON LUZ</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1185,39 +1179,37 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="N19" t="n">
-        <v>14490.384892086</v>
+        <v>1811.3108641975</v>
       </c>
       <c r="O19" t="n">
-        <v>304298.082733806</v>
+        <v>746260.07604937</v>
       </c>
       <c r="P19" t="n">
-        <v>23600</v>
+        <v>2600</v>
       </c>
       <c r="Q19" t="n">
-        <v>495600</v>
+        <v>1071200</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2038-2</t>
-        </is>
+      <c r="A20" t="n">
+        <v>2100120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VARITA DE CONO CON LUZ</t>
+          <t>2100120 FABRICA DE GOMIQUITAS</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>412</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1226,28 +1218,28 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>412</v>
+        <v>26</v>
       </c>
       <c r="N20" t="n">
-        <v>1811.3108641975</v>
+        <v>27000</v>
       </c>
       <c r="O20" t="n">
-        <v>746260.07604937</v>
+        <v>702000</v>
       </c>
       <c r="P20" t="n">
-        <v>2600</v>
+        <v>30000</v>
       </c>
       <c r="Q20" t="n">
-        <v>1071200</v>
+        <v>780000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2100120</v>
+        <v>21002</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2100120 FABRICA DE GOMIQUITAS</t>
+          <t>GAFAS DE NATACION BESTWAY 24PCS</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1256,7 +1248,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1265,28 +1257,28 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N21" t="n">
-        <v>27000</v>
+        <v>1990.0433268102</v>
       </c>
       <c r="O21" t="n">
-        <v>702000</v>
+        <v>135322.9462230936</v>
       </c>
       <c r="P21" t="n">
-        <v>30000</v>
+        <v>4400</v>
       </c>
       <c r="Q21" t="n">
-        <v>780000</v>
+        <v>299200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21002</v>
+        <v>217</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAFAS DE NATACION BESTWAY 24PCS</t>
+          <t>217 CHIQUITIN EN PASTA BLANCO - NEGRO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1295,7 +1287,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1304,28 +1296,31 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="N22" t="n">
-        <v>1990.0433268102</v>
+        <v>3376.7463585118</v>
       </c>
       <c r="O22" t="n">
-        <v>135322.9462230936</v>
+        <v>411963.0557384396</v>
       </c>
       <c r="P22" t="n">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="Q22" t="n">
-        <v>299200</v>
+        <v>549000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>217</v>
+        <v>22040</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6941607331002</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>217 CHIQUITIN EN PASTA BLANCO - NEGRO</t>
+          <t>22040 CARETA NATACION  NIÑOS BESTWAY 12 PCS</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1334,7 +1329,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1343,31 +1338,28 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>3376.7463585118</v>
+        <v>7588.3731034483</v>
       </c>
       <c r="O23" t="n">
-        <v>411963.0557384396</v>
+        <v>7588.3731034483</v>
       </c>
       <c r="P23" t="n">
-        <v>4500</v>
+        <v>14900</v>
       </c>
       <c r="Q23" t="n">
-        <v>549000</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22040</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6941607331002</v>
+        <v>22044</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22040 CARETA NATACION  NIÑOS BESTWAY 12 PCS</t>
+          <t>22044 CARETA BESTWAY</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1376,7 +1368,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1385,28 +1377,28 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="N24" t="n">
-        <v>7588.3731034483</v>
+        <v>11291</v>
       </c>
       <c r="O24" t="n">
-        <v>7588.3731034483</v>
+        <v>327439</v>
       </c>
       <c r="P24" t="n">
-        <v>14900</v>
+        <v>19400</v>
       </c>
       <c r="Q24" t="n">
-        <v>14900</v>
+        <v>562600</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>22044</v>
+        <v>22057</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22044 CARETA BESTWAY</t>
+          <t>22057 CARETA NATACION NIÑOS BESTWAY</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1415,7 +1407,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1424,28 +1416,28 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>11291</v>
+        <v>6338</v>
       </c>
       <c r="O25" t="n">
-        <v>327439</v>
+        <v>25352</v>
       </c>
       <c r="P25" t="n">
-        <v>19400</v>
+        <v>10900</v>
       </c>
       <c r="Q25" t="n">
-        <v>562600</v>
+        <v>43600</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>22057</v>
+        <v>22064</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>22057 CARETA NATACION NIÑOS BESTWAY</t>
+          <t>22064 GAFA NATACION  INFANTIL BESTWAY</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1454,7 +1446,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1463,28 +1455,28 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="N26" t="n">
-        <v>6338</v>
+        <v>5758.9597767857</v>
       </c>
       <c r="O26" t="n">
-        <v>25352</v>
+        <v>316742.7877232135</v>
       </c>
       <c r="P26" t="n">
-        <v>10900</v>
+        <v>16900</v>
       </c>
       <c r="Q26" t="n">
-        <v>43600</v>
+        <v>929500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22064</v>
+        <v>22074</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22064 GAFA NATACION  INFANTIL BESTWAY</t>
+          <t>22074  CARETA BESTWAY</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1493,7 +1485,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1502,28 +1494,28 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="N27" t="n">
-        <v>5758.9597772829</v>
+        <v>17631.78</v>
       </c>
       <c r="O27" t="n">
-        <v>316742.7877505595</v>
+        <v>299740.26</v>
       </c>
       <c r="P27" t="n">
-        <v>16900</v>
+        <v>47600</v>
       </c>
       <c r="Q27" t="n">
-        <v>929500</v>
+        <v>809200</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22074</v>
+        <v>22075</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22074  CARETA BESTWAY</t>
+          <t>22075 CARETA NATACION ADULTO BESTWAY</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1532,7 +1524,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1541,28 +1533,28 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>17631.78</v>
+        <v>20165</v>
       </c>
       <c r="O28" t="n">
-        <v>299740.26</v>
+        <v>463795</v>
       </c>
       <c r="P28" t="n">
-        <v>47600</v>
+        <v>34900</v>
       </c>
       <c r="Q28" t="n">
-        <v>809200</v>
+        <v>802700</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>22075</v>
+        <v>222</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22075 CARETA NATACION ADULTO BESTWAY</t>
+          <t>222 BEBE DORMIDO PEQUENO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1571,7 +1563,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1580,28 +1572,28 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="N29" t="n">
-        <v>20165</v>
+        <v>4072</v>
       </c>
       <c r="O29" t="n">
-        <v>463795</v>
+        <v>399056</v>
       </c>
       <c r="P29" t="n">
-        <v>34900</v>
+        <v>7500</v>
       </c>
       <c r="Q29" t="n">
-        <v>802700</v>
+        <v>735000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>222 BEBE DORMIDO PEQUENO</t>
+          <t>BEBE RISITAS GRANDE BLANCO-NEGRO.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1610,7 +1602,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1619,28 +1611,28 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>4072</v>
+        <v>48710.1</v>
       </c>
       <c r="O30" t="n">
-        <v>399056</v>
+        <v>633231.2999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>7500</v>
+        <v>67900</v>
       </c>
       <c r="Q30" t="n">
-        <v>735000</v>
+        <v>882700</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BEBE RISITAS GRANDE BLANCO-NEGRO.</t>
+          <t>BEBE DORMIDO GRANDE</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1649,7 +1641,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1658,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N31" t="n">
-        <v>48710.1</v>
+        <v>37131</v>
       </c>
       <c r="O31" t="n">
-        <v>633231.2999999999</v>
+        <v>259917</v>
       </c>
       <c r="P31" t="n">
-        <v>67900</v>
+        <v>54600</v>
       </c>
       <c r="Q31" t="n">
-        <v>882700</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>230</v>
+        <v>24003</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BEBE DORMIDO GRANDE</t>
+          <t>SNORKER</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1688,7 +1680,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1697,28 +1689,28 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N32" t="n">
-        <v>37131</v>
+        <v>35775</v>
       </c>
       <c r="O32" t="n">
-        <v>259917</v>
+        <v>536625</v>
       </c>
       <c r="P32" t="n">
-        <v>54600</v>
+        <v>50500</v>
       </c>
       <c r="Q32" t="n">
-        <v>382200</v>
+        <v>757500</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>24003</v>
+        <v>24020</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SNORKER</t>
+          <t>HYDRO-SWIM SECRET BAY SNORKEL SET 6PCS</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1727,7 +1719,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1736,28 +1728,31 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>35775</v>
+        <v>17632.21</v>
       </c>
       <c r="O33" t="n">
-        <v>536625</v>
+        <v>405540.83</v>
       </c>
       <c r="P33" t="n">
-        <v>50500</v>
+        <v>34700</v>
       </c>
       <c r="Q33" t="n">
-        <v>757500</v>
+        <v>798100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>24020</v>
+        <v>24021</v>
+      </c>
+      <c r="B34" t="n">
+        <v>6941607331156</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HYDRO-SWIM SECRET BAY SNORKEL SET 6PCS</t>
+          <t>HYDRO-PRO BLACKSEA MASK  SNORKEL SET 6 PCS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1766,7 +1761,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1775,31 +1770,28 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>17632.21</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O34" t="n">
-        <v>405540.83</v>
+        <v>27815.961126761</v>
       </c>
       <c r="P34" t="n">
-        <v>34700</v>
+        <v>58600</v>
       </c>
       <c r="Q34" t="n">
-        <v>798100</v>
+        <v>58600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>24021</v>
-      </c>
-      <c r="B35" t="n">
-        <v>6941607331156</v>
+        <v>24023</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HYDRO-PRO BLACKSEA MASK  SNORKEL SET 6 PCS</t>
+          <t>CARETA SNORKER</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1808,7 +1800,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1817,24 +1809,24 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N35" t="n">
-        <v>27815.961126761</v>
+        <v>12785.78</v>
       </c>
       <c r="O35" t="n">
-        <v>27815.961126761</v>
+        <v>230144.04</v>
       </c>
       <c r="P35" t="n">
-        <v>58600</v>
+        <v>22900</v>
       </c>
       <c r="Q35" t="n">
-        <v>58600</v>
+        <v>412200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>24023</v>
+        <v>24025</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1847,7 +1839,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1856,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>12785.78</v>
+        <v>23481.71</v>
       </c>
       <c r="O36" t="n">
-        <v>230144.04</v>
+        <v>281780.52</v>
       </c>
       <c r="P36" t="n">
-        <v>22900</v>
+        <v>41500</v>
       </c>
       <c r="Q36" t="n">
-        <v>412200</v>
+        <v>498000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24025</v>
+        <v>24029</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CARETA SNORKER</t>
+          <t>HYDRO-SWIM BLACKSTRIPE SET</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -1886,7 +1878,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1895,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N37" t="n">
-        <v>23481.71</v>
+        <v>20826.6775</v>
       </c>
       <c r="O37" t="n">
-        <v>281780.52</v>
+        <v>270746.8075</v>
       </c>
       <c r="P37" t="n">
-        <v>41500</v>
+        <v>39100</v>
       </c>
       <c r="Q37" t="n">
-        <v>498000</v>
+        <v>508300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>24029</v>
+        <v>24032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HYDRO-SWIM BLACKSTRIPE SET</t>
+          <t>HYDRO-SWIM PIKE SET</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1925,7 +1917,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1934,37 +1926,45 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="N38" t="n">
-        <v>20826.6775</v>
+        <v>25246</v>
       </c>
       <c r="O38" t="n">
-        <v>270746.8075</v>
+        <v>126230</v>
       </c>
       <c r="P38" t="n">
-        <v>39100</v>
+        <v>35500</v>
       </c>
       <c r="Q38" t="n">
-        <v>508300</v>
+        <v>177500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>24032</v>
+        <v>24035</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6941607331217</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HYDRO-SWIM PIKE SET</t>
+          <t>Equipo de Buceo Bestway, Essential Freestyle, +7 Años, 35x13cm, 24035</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1973,31 +1973,31 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>25246</v>
+        <v>13386</v>
       </c>
       <c r="O39" t="n">
-        <v>126230</v>
+        <v>160632</v>
       </c>
       <c r="P39" t="n">
-        <v>35500</v>
+        <v>23900</v>
       </c>
       <c r="Q39" t="n">
-        <v>177500</v>
+        <v>286800</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>24035</v>
+        <v>24068</v>
       </c>
       <c r="B40" t="n">
-        <v>6941607331217</v>
+        <v>6941607331149</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Equipo de Buceo Bestway, Essential Freestyle, +7 Años, 35x13cm, 24035</t>
+          <t>Máscara de Buceo Snorkel +14 Bestway Spark Wave</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2020,45 +2020,40 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>13386</v>
+        <v>18934</v>
       </c>
       <c r="O40" t="n">
-        <v>160632</v>
+        <v>208274</v>
       </c>
       <c r="P40" t="n">
-        <v>23900</v>
+        <v>32900</v>
       </c>
       <c r="Q40" t="n">
-        <v>286800</v>
+        <v>361900</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>24068</v>
+        <v>24069</v>
       </c>
       <c r="B41" t="n">
-        <v>6941607331149</v>
+        <v>6941607331125</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Máscara de Buceo Snorkel +14 Bestway Spark Wave</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>24069 SET SNORKEL ADULTO BESTWAY</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2067,31 +2062,28 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>18934</v>
+        <v>30240.861395349</v>
       </c>
       <c r="O41" t="n">
-        <v>208274</v>
+        <v>90722.584186047</v>
       </c>
       <c r="P41" t="n">
-        <v>32900</v>
+        <v>56900</v>
       </c>
       <c r="Q41" t="n">
-        <v>361900</v>
+        <v>170700</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>24069</v>
-      </c>
-      <c r="B42" t="n">
-        <v>6941607331125</v>
+        <v>243</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>24069 SET SNORKEL ADULTO BESTWAY</t>
+          <t>243 MUNECOS DISFRAZADOS PEQUENOS</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2100,7 +2092,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2109,28 +2101,30 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="N42" t="n">
-        <v>30240.861395349</v>
+        <v>15238.01</v>
       </c>
       <c r="O42" t="n">
-        <v>90722.584186047</v>
+        <v>579044.38</v>
       </c>
       <c r="P42" t="n">
-        <v>56900</v>
+        <v>40400</v>
       </c>
       <c r="Q42" t="n">
-        <v>170700</v>
+        <v>1535200</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>243</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2432603-1</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>243 MUNECOS DISFRAZADOS PEQUENOS</t>
+          <t>SATENES EN ACERO INOX 3 CAPAS</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2139,7 +2133,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2148,30 +2142,30 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N43" t="n">
-        <v>15238.01</v>
+        <v>49275.947916667</v>
       </c>
       <c r="O43" t="n">
-        <v>579044.38</v>
+        <v>443483.531250003</v>
       </c>
       <c r="P43" t="n">
-        <v>40400</v>
+        <v>82900</v>
       </c>
       <c r="Q43" t="n">
-        <v>1535200</v>
+        <v>746100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2432603-1</t>
+          <t>2432603-2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SATENES EN ACERO INOX 3 CAPAS</t>
+          <t>SARTENES EN ACERO INOXIDABLE 3 CAPA</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2180,7 +2174,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2189,30 +2183,30 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
-        <v>49275.947916667</v>
+        <v>55900</v>
       </c>
       <c r="O44" t="n">
-        <v>443483.531250003</v>
+        <v>447200</v>
       </c>
       <c r="P44" t="n">
-        <v>82900</v>
+        <v>94900</v>
       </c>
       <c r="Q44" t="n">
-        <v>746100</v>
+        <v>759200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2432603-2</t>
+          <t>2432603-3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SARTENES EN ACERO INOXIDABLE 3 CAPA</t>
+          <t>SARTÉN EN ACERO INOXIDABLE 3 CAPAS</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2221,7 +2215,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2230,30 +2224,30 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>55900</v>
+        <v>78104.977647059</v>
       </c>
       <c r="O45" t="n">
-        <v>447200</v>
+        <v>390524.888235295</v>
       </c>
       <c r="P45" t="n">
-        <v>94900</v>
+        <v>119900</v>
       </c>
       <c r="Q45" t="n">
-        <v>759200</v>
+        <v>599500</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2432603-3</t>
+          <t>2440110-1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SARTÉN EN ACERO INOXIDABLE 3 CAPAS</t>
+          <t>EXTENDEDOR DE ROPA</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2262,7 +2256,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2271,30 +2265,30 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N46" t="n">
-        <v>78104.977647059</v>
+        <v>57762.968613861</v>
       </c>
       <c r="O46" t="n">
-        <v>390524.888235295</v>
+        <v>635392.654752471</v>
       </c>
       <c r="P46" t="n">
-        <v>119900</v>
+        <v>87343</v>
       </c>
       <c r="Q46" t="n">
-        <v>599500</v>
+        <v>960773</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2440110-1</t>
+          <t>2440202-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EXTENDEDOR DE ROPA</t>
+          <t>CAJA OGANIZADOR DE ALIMENTO PARA NEVERA （33.7*21.3*15cm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2303,7 +2297,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2312,30 +2306,30 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N47" t="n">
-        <v>57762.968613861</v>
+        <v>44675.413333333</v>
       </c>
       <c r="O47" t="n">
-        <v>635392.654752471</v>
+        <v>446754.13333333</v>
       </c>
       <c r="P47" t="n">
-        <v>87343</v>
+        <v>62900</v>
       </c>
       <c r="Q47" t="n">
-        <v>960773</v>
+        <v>629000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2440202-30</t>
+          <t>2440202-53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAJA OGANIZADOR DE ALIMENTO PARA NEVERA （33.7*21.3*15cm</t>
+          <t>Jabonera</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2344,7 +2338,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2353,30 +2347,30 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N48" t="n">
-        <v>44675.413333333</v>
+        <v>9994.7630973451</v>
       </c>
       <c r="O48" t="n">
-        <v>446754.13333333</v>
+        <v>209890.0250442471</v>
       </c>
       <c r="P48" t="n">
-        <v>62900</v>
+        <v>16500</v>
       </c>
       <c r="Q48" t="n">
-        <v>629000</v>
+        <v>346500</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2440202-53</t>
+          <t>2440202-54</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jabonera</t>
+          <t>tapete silicona</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2385,7 +2379,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2394,30 +2388,30 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N49" t="n">
-        <v>9994.7630973451</v>
+        <v>2700</v>
       </c>
       <c r="O49" t="n">
-        <v>209890.0250442471</v>
+        <v>148500</v>
       </c>
       <c r="P49" t="n">
-        <v>16500</v>
+        <v>3900</v>
       </c>
       <c r="Q49" t="n">
-        <v>346500</v>
+        <v>214500</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2440202-54</t>
+          <t>2440202-88</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tapete silicona</t>
+          <t>MÁSCARA PARA DOLOR DE CABEZA</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2426,7 +2420,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2435,30 +2429,30 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>2700</v>
+        <v>6200</v>
       </c>
       <c r="O50" t="n">
-        <v>148500</v>
+        <v>12400</v>
       </c>
       <c r="P50" t="n">
-        <v>3900</v>
+        <v>10500</v>
       </c>
       <c r="Q50" t="n">
-        <v>214500</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2440202-88</t>
+          <t>2440202-9</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MÁSCARA PARA DOLOR DE CABEZA</t>
+          <t>VENTILADOR PORTATIL CON UMIFICADOR CLIMATIZADOR</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2467,7 +2461,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2476,30 +2470,28 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="N51" t="n">
-        <v>6200</v>
+        <v>28242.901</v>
       </c>
       <c r="O51" t="n">
-        <v>12400</v>
+        <v>480129.317</v>
       </c>
       <c r="P51" t="n">
-        <v>10500</v>
+        <v>40900</v>
       </c>
       <c r="Q51" t="n">
-        <v>21000</v>
+        <v>695300</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2440202-9</t>
-        </is>
+      <c r="A52" t="n">
+        <v>266</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VENTILADOR PORTATIL CON UMIFICADOR CLIMATIZADOR</t>
+          <t>MUNECO DISFRAZADO GRANDE</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2508,7 +2500,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2517,19 +2509,19 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>28242.901</v>
+        <v>35831.14</v>
       </c>
       <c r="O52" t="n">
-        <v>480129.317</v>
+        <v>35831.14</v>
       </c>
       <c r="P52" t="n">
-        <v>40900</v>
+        <v>62900</v>
       </c>
       <c r="Q52" t="n">
-        <v>695300</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="53">
@@ -2963,10 +2955,10 @@
         <v>12</v>
       </c>
       <c r="N63" t="n">
-        <v>22510.483207547</v>
+        <v>22510.483076923</v>
       </c>
       <c r="O63" t="n">
-        <v>270125.798490564</v>
+        <v>270125.796923076</v>
       </c>
       <c r="P63" t="n">
         <v>44900</v>
@@ -3275,10 +3267,10 @@
         <v>167</v>
       </c>
       <c r="N71" t="n">
-        <v>3716.3301973684</v>
+        <v>3716.3301980198</v>
       </c>
       <c r="O71" t="n">
-        <v>620627.1429605228</v>
+        <v>620627.1430693066</v>
       </c>
       <c r="P71" t="n">
         <v>9500</v>
@@ -3973,10 +3965,10 @@
         <v>34</v>
       </c>
       <c r="N88" t="n">
-        <v>3910.6279262673</v>
+        <v>3910.6278971963</v>
       </c>
       <c r="O88" t="n">
-        <v>132961.3494930882</v>
+        <v>132961.3485046742</v>
       </c>
       <c r="P88" t="n">
         <v>9100</v>
@@ -5718,10 +5710,10 @@
         <v>2</v>
       </c>
       <c r="N128" t="n">
-        <v>141416.88463576</v>
+        <v>141416.88465116</v>
       </c>
       <c r="O128" t="n">
-        <v>282833.76927152</v>
+        <v>282833.76930232</v>
       </c>
       <c r="P128" t="n">
         <v>251900</v>
@@ -5896,10 +5888,10 @@
         <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>344599.17805556</v>
+        <v>344599.178</v>
       </c>
       <c r="O132" t="n">
-        <v>689198.35611112</v>
+        <v>689198.356</v>
       </c>
       <c r="P132" t="n">
         <v>532900</v>
@@ -11587,10 +11579,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2586.3633253779</v>
+        <v>2582.2547091633</v>
       </c>
       <c r="O264" t="n">
-        <v>219840.8826571215</v>
+        <v>219491.6502788805</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -11679,10 +11671,10 @@
         <v>231</v>
       </c>
       <c r="N266" t="n">
-        <v>5216.8958101422</v>
+        <v>5216.8958023544</v>
       </c>
       <c r="O266" t="n">
-        <v>1205102.932142848</v>
+        <v>1205102.930343866</v>
       </c>
       <c r="P266" t="n">
         <v>8500</v>
@@ -11981,10 +11973,10 @@
         <v>560</v>
       </c>
       <c r="N273" t="n">
-        <v>3158.8608436687</v>
+        <v>3158.8608437109</v>
       </c>
       <c r="O273" t="n">
-        <v>1768962.072454472</v>
+        <v>1768962.072478104</v>
       </c>
       <c r="P273" t="n">
         <v>5600</v>
@@ -12803,10 +12795,10 @@
         <v>282</v>
       </c>
       <c r="N291" t="n">
-        <v>3795.7100076453</v>
+        <v>3795.7100076628</v>
       </c>
       <c r="O291" t="n">
-        <v>1070390.222155974</v>
+        <v>1070390.22216091</v>
       </c>
       <c r="P291" t="n">
         <v>6200</v>
@@ -13075,10 +13067,10 @@
         <v>342365.103957597</v>
       </c>
       <c r="P297" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q297" t="n">
-        <v>574000</v>
+        <v>623000</v>
       </c>
     </row>
     <row r="298">
@@ -13505,7 +13497,7 @@
         </is>
       </c>
       <c r="J307" t="n">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13514,19 +13506,19 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>107</v>
+        <v>207</v>
       </c>
       <c r="N307" t="n">
         <v>5667.94</v>
       </c>
       <c r="O307" t="n">
-        <v>606469.58</v>
+        <v>1173263.58</v>
       </c>
       <c r="P307" t="n">
         <v>9500</v>
       </c>
       <c r="Q307" t="n">
-        <v>1016500</v>
+        <v>1966500</v>
       </c>
     </row>
     <row r="308">
@@ -13856,7 +13848,7 @@
         </is>
       </c>
       <c r="J315" t="n">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -13865,19 +13857,19 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>53</v>
+        <v>221</v>
       </c>
       <c r="N315" t="n">
         <v>3594.2527927928</v>
       </c>
       <c r="O315" t="n">
-        <v>190495.3980180184</v>
+        <v>794329.8672072088</v>
       </c>
       <c r="P315" t="n">
         <v>6500</v>
       </c>
       <c r="Q315" t="n">
-        <v>344500</v>
+        <v>1436500</v>
       </c>
     </row>
     <row r="316">
@@ -14071,7 +14063,7 @@
         </is>
       </c>
       <c r="J320" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="K320" t="n">
         <v>0</v>
@@ -14080,19 +14072,19 @@
         <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="N320" t="n">
         <v>4891</v>
       </c>
       <c r="O320" t="n">
-        <v>498882</v>
+        <v>577138</v>
       </c>
       <c r="P320" t="n">
-        <v>8200</v>
+        <v>8900</v>
       </c>
       <c r="Q320" t="n">
-        <v>836400</v>
+        <v>1050200</v>
       </c>
     </row>
     <row r="321">
@@ -14163,7 +14155,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14172,19 +14164,19 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="N322" t="n">
         <v>14822.378814083</v>
       </c>
       <c r="O322" t="n">
-        <v>652184.667819652</v>
+        <v>1022744.138171727</v>
       </c>
       <c r="P322" t="n">
         <v>24900</v>
       </c>
       <c r="Q322" t="n">
-        <v>1095600</v>
+        <v>1718100</v>
       </c>
     </row>
     <row r="323">
@@ -14348,10 +14340,10 @@
         <v>314</v>
       </c>
       <c r="N326" t="n">
-        <v>5191.4800286123</v>
+        <v>5191.4800286533</v>
       </c>
       <c r="O326" t="n">
-        <v>1630124.728984262</v>
+        <v>1630124.728997136</v>
       </c>
       <c r="P326" t="n">
         <v>9100</v>
@@ -14662,10 +14654,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.276379862</v>
+        <v>3472.276393501</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.943990596</v>
+        <v>1243074.948873358</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -14796,10 +14788,10 @@
         <v>407</v>
       </c>
       <c r="N336" t="n">
-        <v>3041.6600151515</v>
+        <v>3041.660015186</v>
       </c>
       <c r="O336" t="n">
-        <v>1237955.626166661</v>
+        <v>1237955.626180702</v>
       </c>
       <c r="P336" t="n">
         <v>5500</v>
@@ -15921,7 +15913,7 @@
         </is>
       </c>
       <c r="J362" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="K362" t="n">
         <v>0</v>
@@ -15930,19 +15922,19 @@
         <v>0</v>
       </c>
       <c r="M362" t="n">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="N362" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O362" t="n">
-        <v>724901.87</v>
+        <v>1007331.17</v>
       </c>
       <c r="P362" t="n">
         <v>16900</v>
       </c>
       <c r="Q362" t="n">
-        <v>1301300</v>
+        <v>1808300</v>
       </c>
     </row>
     <row r="363">
@@ -16994,10 +16986,10 @@
         <v>793</v>
       </c>
       <c r="N386" t="n">
-        <v>1630.9251181364</v>
+        <v>1630.9251335113</v>
       </c>
       <c r="O386" t="n">
-        <v>1293323.618682165</v>
+        <v>1293323.630874461</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
@@ -17265,10 +17257,10 @@
         <v>991</v>
       </c>
       <c r="N392" t="n">
-        <v>2403.5229357459</v>
+        <v>2403.523063498</v>
       </c>
       <c r="O392" t="n">
-        <v>2381891.229324187</v>
+        <v>2381891.355926518</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
@@ -17297,7 +17289,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -17306,19 +17298,19 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="N393" t="n">
         <v>24267.77</v>
       </c>
       <c r="O393" t="n">
-        <v>752300.87</v>
+        <v>1213388.5</v>
       </c>
       <c r="P393" t="n">
         <v>33400</v>
       </c>
       <c r="Q393" t="n">
-        <v>1035400</v>
+        <v>1670000</v>
       </c>
     </row>
     <row r="394">
@@ -20090,10 +20082,10 @@
         <v>141</v>
       </c>
       <c r="N457" t="n">
-        <v>4196.8725467746</v>
+        <v>4196.8725524769</v>
       </c>
       <c r="O457" t="n">
-        <v>591759.0290952186</v>
+        <v>591759.0298992429</v>
       </c>
       <c r="P457" t="n">
         <v>5900</v>
@@ -20570,7 +20562,7 @@
         </is>
       </c>
       <c r="J469" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="K469" t="n">
         <v>0</v>
@@ -20579,19 +20571,19 @@
         <v>0</v>
       </c>
       <c r="M469" t="n">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="N469" t="n">
         <v>2286.55</v>
       </c>
       <c r="O469" t="n">
-        <v>70883.05</v>
+        <v>208076.05</v>
       </c>
       <c r="P469" t="n">
         <v>3200</v>
       </c>
       <c r="Q469" t="n">
-        <v>99200</v>
+        <v>291200</v>
       </c>
     </row>
     <row r="470">
@@ -21366,10 +21358,10 @@
         <v>64</v>
       </c>
       <c r="N488" t="n">
-        <v>22485.695378691</v>
+        <v>22485.69534282</v>
       </c>
       <c r="O488" t="n">
-        <v>1439084.504236224</v>
+        <v>1439084.50194048</v>
       </c>
       <c r="P488" t="n">
         <v>36500</v>
@@ -21661,10 +21653,10 @@
         <v>145</v>
       </c>
       <c r="N495" t="n">
-        <v>2680.7396929825</v>
+        <v>2680.7396925972</v>
       </c>
       <c r="O495" t="n">
-        <v>388707.2554824625</v>
+        <v>388707.255426594</v>
       </c>
       <c r="P495" t="n">
         <v>4900</v>
@@ -21702,10 +21694,10 @@
         <v>1306</v>
       </c>
       <c r="N496" t="n">
-        <v>880.32993798065</v>
+        <v>880.329947852</v>
       </c>
       <c r="O496" t="n">
-        <v>1149710.899002729</v>
+        <v>1149710.911894712</v>
       </c>
       <c r="P496" t="n">
         <v>1200</v>
@@ -22330,7 +22322,7 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -22339,19 +22331,19 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>209</v>
+        <v>277</v>
       </c>
       <c r="N511" t="n">
-        <v>6207.9882013781</v>
+        <v>6207.9881978301</v>
       </c>
       <c r="O511" t="n">
-        <v>1297469.534088023</v>
+        <v>1719612.730798938</v>
       </c>
       <c r="P511" t="n">
         <v>9900</v>
       </c>
       <c r="Q511" t="n">
-        <v>2069100</v>
+        <v>2742300</v>
       </c>
     </row>
     <row r="512">
@@ -22560,10 +22552,10 @@
         <v>267</v>
       </c>
       <c r="N516" t="n">
-        <v>4285.1966145833</v>
+        <v>4285.1966318538</v>
       </c>
       <c r="O516" t="n">
-        <v>1144147.496093741</v>
+        <v>1144147.500704965</v>
       </c>
       <c r="P516" t="n">
         <v>6900</v>
@@ -23244,16 +23236,16 @@
         <v>165</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633516301</v>
+        <v>4814.2633494176</v>
       </c>
       <c r="O532" t="n">
-        <v>794353.4530189666</v>
+        <v>794353.452653904</v>
       </c>
       <c r="P532" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1633500</v>
+        <v>1303500</v>
       </c>
     </row>
     <row r="533">
@@ -23273,7 +23265,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -23282,19 +23274,19 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>107</v>
+        <v>272</v>
       </c>
       <c r="N533" t="n">
         <v>3591.13</v>
       </c>
       <c r="O533" t="n">
-        <v>384250.91</v>
+        <v>976787.36</v>
       </c>
       <c r="P533" t="n">
         <v>6900</v>
       </c>
       <c r="Q533" t="n">
-        <v>738300</v>
+        <v>1876800</v>
       </c>
     </row>
     <row r="534">
@@ -23377,10 +23369,10 @@
         <v>48</v>
       </c>
       <c r="N535" t="n">
-        <v>11562.038381503</v>
+        <v>11562.038362573</v>
       </c>
       <c r="O535" t="n">
-        <v>554977.842312144</v>
+        <v>554977.8414035039</v>
       </c>
       <c r="P535" t="n">
         <v>18500</v>
@@ -23423,10 +23415,10 @@
         <v>49</v>
       </c>
       <c r="N536" t="n">
-        <v>13513.643727273</v>
+        <v>13513.644019608</v>
       </c>
       <c r="O536" t="n">
-        <v>662168.542636377</v>
+        <v>662168.556960792</v>
       </c>
       <c r="P536" t="n">
         <v>21900</v>
@@ -24312,7 +24304,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -24321,19 +24313,19 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>177</v>
+        <v>297</v>
       </c>
       <c r="N557" t="n">
         <v>4793.53</v>
       </c>
       <c r="O557" t="n">
-        <v>848454.8099999999</v>
+        <v>1423678.41</v>
       </c>
       <c r="P557" t="n">
         <v>7900</v>
       </c>
       <c r="Q557" t="n">
-        <v>1398300</v>
+        <v>2346300</v>
       </c>
     </row>
     <row r="558">
@@ -25066,10 +25058,10 @@
         <v>18</v>
       </c>
       <c r="N574" t="n">
-        <v>1561.0074054054</v>
+        <v>1561.0125437573</v>
       </c>
       <c r="O574" t="n">
-        <v>28098.1332972972</v>
+        <v>28098.2257876314</v>
       </c>
       <c r="P574" t="n">
         <v>2900</v>
@@ -27762,10 +27754,10 @@
         <v>15</v>
       </c>
       <c r="N635" t="n">
-        <v>9456.2957818182</v>
+        <v>9188.98</v>
       </c>
       <c r="O635" t="n">
-        <v>141844.436727273</v>
+        <v>137834.7</v>
       </c>
       <c r="P635" t="n">
         <v>12900</v>
@@ -28121,7 +28113,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -28130,19 +28122,19 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N643" t="n">
         <v>63521</v>
       </c>
       <c r="O643" t="n">
-        <v>63521</v>
+        <v>889294</v>
       </c>
       <c r="P643" t="n">
         <v>105900</v>
       </c>
       <c r="Q643" t="n">
-        <v>105900</v>
+        <v>1482600</v>
       </c>
     </row>
     <row r="644">
@@ -28271,10 +28263,10 @@
         <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>23521.620277778</v>
+        <v>23521.618709677</v>
       </c>
       <c r="O646" t="n">
-        <v>94086.48111111201</v>
+        <v>94086.474838708</v>
       </c>
       <c r="P646" t="n">
         <v>39000</v>
@@ -30577,10 +30569,10 @@
         <v>5</v>
       </c>
       <c r="N696" t="n">
-        <v>10642.355555556</v>
+        <v>10411</v>
       </c>
       <c r="O696" t="n">
-        <v>53211.77777778</v>
+        <v>52055</v>
       </c>
       <c r="P696" t="n">
         <v>16900</v>
@@ -31909,10 +31901,10 @@
         <v>8</v>
       </c>
       <c r="N725" t="n">
-        <v>4907.8228222222</v>
+        <v>4907.8228863636</v>
       </c>
       <c r="O725" t="n">
-        <v>39262.5825777776</v>
+        <v>39262.5830909088</v>
       </c>
       <c r="P725" t="n">
         <v>8200</v>
@@ -32035,7 +32027,7 @@
         </is>
       </c>
       <c r="J728" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K728" t="n">
         <v>0</v>
@@ -32044,19 +32036,19 @@
         <v>0</v>
       </c>
       <c r="M728" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N728" t="n">
         <v>100129</v>
       </c>
       <c r="O728" t="n">
-        <v>500645</v>
+        <v>1301677</v>
       </c>
       <c r="P728" t="n">
         <v>159900</v>
       </c>
       <c r="Q728" t="n">
-        <v>799500</v>
+        <v>2078700</v>
       </c>
     </row>
     <row r="729">
@@ -32185,10 +32177,10 @@
         <v>17</v>
       </c>
       <c r="N731" t="n">
-        <v>3903.7403351955</v>
+        <v>3903.7404686036</v>
       </c>
       <c r="O731" t="n">
-        <v>66363.5856983235</v>
+        <v>66363.5879662612</v>
       </c>
       <c r="P731" t="n">
         <v>7500</v>
@@ -32732,10 +32724,10 @@
         <v>454</v>
       </c>
       <c r="N743" t="n">
-        <v>5869.1723052295</v>
+        <v>5869.1722639485</v>
       </c>
       <c r="O743" t="n">
-        <v>2664604.226574193</v>
+        <v>2664604.207832619</v>
       </c>
       <c r="P743" t="n">
         <v>9500</v>
@@ -35404,10 +35396,10 @@
         <v>347</v>
       </c>
       <c r="N801" t="n">
-        <v>1516.0386990066</v>
+        <v>1516.0386973545</v>
       </c>
       <c r="O801" t="n">
-        <v>526065.4285552902</v>
+        <v>526065.4279820116</v>
       </c>
       <c r="P801" t="n">
         <v>2300</v>
@@ -35540,10 +35532,10 @@
         <v>1087</v>
       </c>
       <c r="N804" t="n">
-        <v>2458.5122658275</v>
+        <v>2458.5122572276</v>
       </c>
       <c r="O804" t="n">
-        <v>2672402.832954492</v>
+        <v>2672402.823606401</v>
       </c>
       <c r="P804" t="n">
         <v>3500</v>
@@ -35724,10 +35716,10 @@
         <v>911</v>
       </c>
       <c r="N808" t="n">
-        <v>1803.0176523702</v>
+        <v>1803.0176696833</v>
       </c>
       <c r="O808" t="n">
-        <v>1642549.081309252</v>
+        <v>1642549.097081486</v>
       </c>
       <c r="P808" t="n">
         <v>2500</v>
@@ -35862,10 +35854,10 @@
         <v>525</v>
       </c>
       <c r="N811" t="n">
-        <v>2108.8000229358</v>
+        <v>2108.8001384083</v>
       </c>
       <c r="O811" t="n">
-        <v>1107120.012041295</v>
+        <v>1107120.072664357</v>
       </c>
       <c r="P811" t="n">
         <v>2900</v>
@@ -35908,10 +35900,10 @@
         <v>955</v>
       </c>
       <c r="N812" t="n">
-        <v>2056.081010453</v>
+        <v>2056.0810065359</v>
       </c>
       <c r="O812" t="n">
-        <v>1963557.364982615</v>
+        <v>1963557.361241785</v>
       </c>
       <c r="P812" t="n">
         <v>2900</v>
@@ -36415,10 +36407,10 @@
         <v>2</v>
       </c>
       <c r="N823" t="n">
-        <v>2153.2609259259</v>
+        <v>1906.1622222222</v>
       </c>
       <c r="O823" t="n">
-        <v>4306.5218518518</v>
+        <v>3812.3244444444</v>
       </c>
       <c r="P823" t="n">
         <v>2900</v>
@@ -36553,10 +36545,10 @@
         <v>175</v>
       </c>
       <c r="N826" t="n">
-        <v>1259.2751769231</v>
+        <v>1259.2751809084</v>
       </c>
       <c r="O826" t="n">
-        <v>220373.1559615425</v>
+        <v>220373.15665897</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
@@ -36689,10 +36681,10 @@
         <v>13</v>
       </c>
       <c r="N829" t="n">
-        <v>692.15254743047</v>
+        <v>692.15255307366</v>
       </c>
       <c r="O829" t="n">
-        <v>8997.98311659611</v>
+        <v>8997.98318995758</v>
       </c>
       <c r="P829" t="n">
         <v>1200</v>
@@ -37673,10 +37665,10 @@
         <v>272</v>
       </c>
       <c r="N850" t="n">
-        <v>8949.4124778362</v>
+        <v>8945.379999999999</v>
       </c>
       <c r="O850" t="n">
-        <v>2434240.193971446</v>
+        <v>2433143.36</v>
       </c>
       <c r="P850" t="n">
         <v>14900</v>
@@ -40278,10 +40270,10 @@
         <v>2652</v>
       </c>
       <c r="N908" t="n">
-        <v>703.7945904135599</v>
+        <v>703.79458486774</v>
       </c>
       <c r="O908" t="n">
-        <v>1866463.253776761</v>
+        <v>1866463.239069246</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
@@ -41807,7 +41799,7 @@
         </is>
       </c>
       <c r="J942" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K942" t="n">
         <v>0</v>
@@ -41816,19 +41808,19 @@
         <v>0</v>
       </c>
       <c r="M942" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N942" t="n">
         <v>10548.76</v>
       </c>
       <c r="O942" t="n">
-        <v>116036.36</v>
+        <v>242621.48</v>
       </c>
       <c r="P942" t="n">
         <v>35900</v>
       </c>
       <c r="Q942" t="n">
-        <v>394900</v>
+        <v>825700</v>
       </c>
     </row>
     <row r="943">
@@ -42984,10 +42976,10 @@
         <v>1</v>
       </c>
       <c r="N967" t="n">
-        <v>19429.807619048</v>
+        <v>10737.525135135</v>
       </c>
       <c r="O967" t="n">
-        <v>19429.807619048</v>
+        <v>10737.525135135</v>
       </c>
       <c r="P967" t="n">
         <v>18900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -2104,10 +2104,10 @@
         <v>38</v>
       </c>
       <c r="N42" t="n">
-        <v>15238.01</v>
+        <v>15304.843377193</v>
       </c>
       <c r="O42" t="n">
-        <v>579044.38</v>
+        <v>581584.048333334</v>
       </c>
       <c r="P42" t="n">
         <v>40400</v>
@@ -3540,10 +3540,10 @@
         <v>16</v>
       </c>
       <c r="N78" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O78" t="n">
-        <v>341339.04</v>
+        <v>342804.014420608</v>
       </c>
       <c r="P78" t="n">
         <v>30000</v>
@@ -6332,10 +6332,10 @@
         <v>20</v>
       </c>
       <c r="N142" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O142" t="n">
-        <v>540000</v>
+        <v>570000</v>
       </c>
       <c r="P142" t="n">
         <v>20000</v>
@@ -10928,10 +10928,10 @@
         <v>2</v>
       </c>
       <c r="N249" t="n">
-        <v>13593.35</v>
+        <v>13694.165945612</v>
       </c>
       <c r="O249" t="n">
-        <v>27186.7</v>
+        <v>27388.331891224</v>
       </c>
       <c r="P249" t="n">
         <v>25500</v>
@@ -11579,10 +11579,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O264" t="n">
-        <v>219491.6502788805</v>
+        <v>219491.648239059</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -13061,10 +13061,10 @@
         <v>70</v>
       </c>
       <c r="N297" t="n">
-        <v>4890.9300565371</v>
+        <v>4890.9300570207</v>
       </c>
       <c r="O297" t="n">
-        <v>342365.103957597</v>
+        <v>342365.103991449</v>
       </c>
       <c r="P297" t="n">
         <v>8900</v>
@@ -14167,10 +14167,10 @@
         <v>69</v>
       </c>
       <c r="N322" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O322" t="n">
-        <v>1022744.138171727</v>
+        <v>1023376.24208898</v>
       </c>
       <c r="P322" t="n">
         <v>24900</v>
@@ -14474,10 +14474,10 @@
         <v>89</v>
       </c>
       <c r="N329" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O329" t="n">
-        <v>1105599.20782592</v>
+        <v>1105599.208181386</v>
       </c>
       <c r="P329" t="n">
         <v>19900</v>
@@ -14654,10 +14654,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.948873358</v>
+        <v>1243074.953777063</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -14875,10 +14875,10 @@
         <v>185</v>
       </c>
       <c r="N338" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O338" t="n">
-        <v>808667.0000401316</v>
+        <v>808667.0001284505</v>
       </c>
       <c r="P338" t="n">
         <v>8900</v>
@@ -16986,10 +16986,10 @@
         <v>793</v>
       </c>
       <c r="N386" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O386" t="n">
-        <v>1293323.630874461</v>
+        <v>1295052.673161779</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
@@ -17165,10 +17165,10 @@
         <v>2285</v>
       </c>
       <c r="N390" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O390" t="n">
-        <v>3542195.489442288</v>
+        <v>3542195.492475854</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
@@ -17257,10 +17257,10 @@
         <v>991</v>
       </c>
       <c r="N392" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O392" t="n">
-        <v>2381891.355926518</v>
+        <v>2382776.159550529</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
@@ -23236,10 +23236,10 @@
         <v>165</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O532" t="n">
-        <v>794353.452653904</v>
+        <v>794353.4522886104</v>
       </c>
       <c r="P532" t="n">
         <v>7900</v>
@@ -23415,10 +23415,10 @@
         <v>49</v>
       </c>
       <c r="N536" t="n">
-        <v>13513.644019608</v>
+        <v>13513.644059406</v>
       </c>
       <c r="O536" t="n">
-        <v>662168.556960792</v>
+        <v>662168.558910894</v>
       </c>
       <c r="P536" t="n">
         <v>21900</v>
@@ -24674,10 +24674,10 @@
         <v>29</v>
       </c>
       <c r="N565" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O565" t="n">
-        <v>786589.1730444019</v>
+        <v>786589.172711859</v>
       </c>
       <c r="P565" t="n">
         <v>44500</v>
@@ -25834,10 +25834,10 @@
         <v>22</v>
       </c>
       <c r="N592" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O592" t="n">
-        <v>285594.98</v>
+        <v>286746.572661296</v>
       </c>
       <c r="P592" t="n">
         <v>21900</v>
@@ -27754,10 +27754,10 @@
         <v>15</v>
       </c>
       <c r="N635" t="n">
-        <v>9188.98</v>
+        <v>9254.3819928826</v>
       </c>
       <c r="O635" t="n">
-        <v>137834.7</v>
+        <v>138815.729893239</v>
       </c>
       <c r="P635" t="n">
         <v>12900</v>
@@ -28631,10 +28631,10 @@
         <v>29</v>
       </c>
       <c r="N654" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O654" t="n">
-        <v>740486</v>
+        <v>741753.232173408</v>
       </c>
       <c r="P654" t="n">
         <v>40900</v>
@@ -29646,10 +29646,10 @@
         <v>92</v>
       </c>
       <c r="N676" t="n">
-        <v>2260</v>
+        <v>2280.7339449541</v>
       </c>
       <c r="O676" t="n">
-        <v>207920</v>
+        <v>209827.5229357772</v>
       </c>
       <c r="P676" t="n">
         <v>3800</v>
@@ -30569,10 +30569,10 @@
         <v>5</v>
       </c>
       <c r="N696" t="n">
-        <v>10411</v>
+        <v>10448.858181818</v>
       </c>
       <c r="O696" t="n">
-        <v>52055</v>
+        <v>52244.29090908999</v>
       </c>
       <c r="P696" t="n">
         <v>16900</v>
@@ -31579,10 +31579,10 @@
         <v>50</v>
       </c>
       <c r="N718" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O718" t="n">
-        <v>450150</v>
+        <v>450907.82828283</v>
       </c>
       <c r="P718" t="n">
         <v>14900</v>
@@ -33647,10 +33647,10 @@
         <v>106</v>
       </c>
       <c r="N763" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O763" t="n">
-        <v>1907152</v>
+        <v>1909645.009150288</v>
       </c>
       <c r="P763" t="n">
         <v>28900</v>
@@ -34703,10 +34703,10 @@
         <v>82</v>
       </c>
       <c r="N786" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O786" t="n">
-        <v>713400</v>
+        <v>714307.6335877882</v>
       </c>
       <c r="P786" t="n">
         <v>14900</v>
@@ -34933,10 +34933,10 @@
         <v>39</v>
       </c>
       <c r="N791" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O791" t="n">
-        <v>603408</v>
+        <v>605127.11111112</v>
       </c>
       <c r="P791" t="n">
         <v>25900</v>
@@ -35396,10 +35396,10 @@
         <v>347</v>
       </c>
       <c r="N801" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O801" t="n">
-        <v>526065.4279820116</v>
+        <v>526065.4279341602</v>
       </c>
       <c r="P801" t="n">
         <v>2300</v>
@@ -35578,10 +35578,10 @@
         <v>321</v>
       </c>
       <c r="N805" t="n">
-        <v>1907.3922142857</v>
+        <v>1909.6656257449</v>
       </c>
       <c r="O805" t="n">
-        <v>612272.9007857097</v>
+        <v>613002.6658641129</v>
       </c>
       <c r="P805" t="n">
         <v>2500</v>
@@ -35716,10 +35716,10 @@
         <v>911</v>
       </c>
       <c r="N808" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O808" t="n">
-        <v>1642549.097081486</v>
+        <v>1642549.100244478</v>
       </c>
       <c r="P808" t="n">
         <v>2500</v>
@@ -35762,10 +35762,10 @@
         <v>143</v>
       </c>
       <c r="N809" t="n">
-        <v>3306.5942675159</v>
+        <v>3306.5942492013</v>
       </c>
       <c r="O809" t="n">
-        <v>472842.9802547737</v>
+        <v>472842.9776357859</v>
       </c>
       <c r="P809" t="n">
         <v>4900</v>
@@ -36545,10 +36545,10 @@
         <v>175</v>
       </c>
       <c r="N826" t="n">
-        <v>1259.2751809084</v>
+        <v>1259.2751822382</v>
       </c>
       <c r="O826" t="n">
-        <v>220373.15665897</v>
+        <v>220373.156891685</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
@@ -37007,10 +37007,10 @@
         <v>82</v>
       </c>
       <c r="N836" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O836" t="n">
-        <v>1108476</v>
+        <v>1108785.543702892</v>
       </c>
       <c r="P836" t="n">
         <v>21900</v>
@@ -37474,10 +37474,10 @@
         <v>1</v>
       </c>
       <c r="N846" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="O846" t="n">
-        <v>15423.36</v>
+        <v>15547.741935484</v>
       </c>
       <c r="P846" t="n">
         <v>24900</v>
@@ -40270,10 +40270,10 @@
         <v>2652</v>
       </c>
       <c r="N908" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O908" t="n">
-        <v>1866463.239069246</v>
+        <v>1866463.234418487</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
@@ -42976,10 +42976,10 @@
         <v>1</v>
       </c>
       <c r="N967" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="O967" t="n">
-        <v>10737.525135135</v>
+        <v>10737.525</v>
       </c>
       <c r="P967" t="n">
         <v>18900</v>
@@ -43347,10 +43347,10 @@
         <v>2</v>
       </c>
       <c r="N975" t="n">
-        <v>2000.7487209302</v>
+        <v>2000.7532142857</v>
       </c>
       <c r="O975" t="n">
-        <v>4001.4974418604</v>
+        <v>4001.5064285714</v>
       </c>
       <c r="P975" t="n">
         <v>2000</v>
@@ -47617,10 +47617,10 @@
         <v>59</v>
       </c>
       <c r="N1072" t="n">
-        <v>4985.4086330935</v>
+        <v>5058.1883211679</v>
       </c>
       <c r="O1072" t="n">
-        <v>294139.1093525165</v>
+        <v>298433.1109489061</v>
       </c>
       <c r="P1072" t="n">
         <v>7900</v>
@@ -48766,10 +48766,10 @@
         <v>114</v>
       </c>
       <c r="N1097" t="n">
-        <v>7920</v>
+        <v>7953.8461538462</v>
       </c>
       <c r="O1097" t="n">
-        <v>902880</v>
+        <v>906738.4615384667</v>
       </c>
       <c r="P1097" t="n">
         <v>10500</v>
@@ -48815,10 +48815,10 @@
         <v>72</v>
       </c>
       <c r="N1098" t="n">
-        <v>7920</v>
+        <v>7971.0967741935</v>
       </c>
       <c r="O1098" t="n">
-        <v>570240</v>
+        <v>573918.967741932</v>
       </c>
       <c r="P1098" t="n">
         <v>10500</v>
@@ -49045,10 +49045,10 @@
         <v>5</v>
       </c>
       <c r="N1103" t="n">
-        <v>4576</v>
+        <v>4591.2533333333</v>
       </c>
       <c r="O1103" t="n">
-        <v>22880</v>
+        <v>22956.2666666665</v>
       </c>
       <c r="P1103" t="n">
         <v>5900</v>
@@ -49091,10 +49091,10 @@
         <v>258</v>
       </c>
       <c r="N1104" t="n">
-        <v>5280</v>
+        <v>5285.1815505397</v>
       </c>
       <c r="O1104" t="n">
-        <v>1362240</v>
+        <v>1363576.840039243</v>
       </c>
       <c r="P1104" t="n">
         <v>6900</v>

--- a/bodegas/CM-02.xlsx
+++ b/bodegas/CM-02.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -2104,10 +2104,10 @@
         <v>38</v>
       </c>
       <c r="N42" t="n">
-        <v>15304.843377193</v>
+        <v>15238.01</v>
       </c>
       <c r="O42" t="n">
-        <v>581584.048333334</v>
+        <v>579044.38</v>
       </c>
       <c r="P42" t="n">
         <v>40400</v>
@@ -3111,10 +3111,10 @@
         <v>74</v>
       </c>
       <c r="N67" t="n">
-        <v>2474.7033461538</v>
+        <v>2474.7028512397</v>
       </c>
       <c r="O67" t="n">
-        <v>183128.0476153812</v>
+        <v>183128.0109917378</v>
       </c>
       <c r="P67" t="n">
         <v>4500</v>
@@ -3267,10 +3267,10 @@
         <v>167</v>
       </c>
       <c r="N71" t="n">
-        <v>3716.3301980198</v>
+        <v>3716.3301983471</v>
       </c>
       <c r="O71" t="n">
-        <v>620627.1430693066</v>
+        <v>620627.1431239657</v>
       </c>
       <c r="P71" t="n">
         <v>9500</v>
@@ -3501,10 +3501,10 @@
         <v>15</v>
       </c>
       <c r="N77" t="n">
-        <v>27000</v>
+        <v>27051.823416507</v>
       </c>
       <c r="O77" t="n">
-        <v>405000</v>
+        <v>405777.351247605</v>
       </c>
       <c r="P77" t="n">
         <v>30000</v>
@@ -3540,10 +3540,10 @@
         <v>16</v>
       </c>
       <c r="N78" t="n">
-        <v>21425.250901288</v>
+        <v>21333.69</v>
       </c>
       <c r="O78" t="n">
-        <v>342804.014420608</v>
+        <v>341339.04</v>
       </c>
       <c r="P78" t="n">
         <v>30000</v>
@@ -3657,10 +3657,10 @@
         <v>23</v>
       </c>
       <c r="N81" t="n">
-        <v>14857.623287671</v>
+        <v>14857.623302752</v>
       </c>
       <c r="O81" t="n">
-        <v>341725.335616433</v>
+        <v>341725.335963296</v>
       </c>
       <c r="P81" t="n">
         <v>34900</v>
@@ -4728,10 +4728,10 @@
         <v>9</v>
       </c>
       <c r="N105" t="n">
-        <v>16486.4056</v>
+        <v>16486.405306122</v>
       </c>
       <c r="O105" t="n">
-        <v>148377.6504</v>
+        <v>148377.647755098</v>
       </c>
       <c r="P105" t="n">
         <v>30500</v>
@@ -4809,10 +4809,10 @@
         <v>20</v>
       </c>
       <c r="N107" t="n">
-        <v>15711.963708609</v>
+        <v>15711.963537415</v>
       </c>
       <c r="O107" t="n">
-        <v>314239.27417218</v>
+        <v>314239.2707483</v>
       </c>
       <c r="P107" t="n">
         <v>28500</v>
@@ -5888,10 +5888,10 @@
         <v>2</v>
       </c>
       <c r="N132" t="n">
-        <v>344599.178</v>
+        <v>344599.17787879</v>
       </c>
       <c r="O132" t="n">
-        <v>689198.356</v>
+        <v>689198.35575758</v>
       </c>
       <c r="P132" t="n">
         <v>532900</v>
@@ -6332,10 +6332,10 @@
         <v>20</v>
       </c>
       <c r="N142" t="n">
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="O142" t="n">
-        <v>570000</v>
+        <v>540000</v>
       </c>
       <c r="P142" t="n">
         <v>20000</v>
@@ -7589,10 +7589,10 @@
         <v>31</v>
       </c>
       <c r="N171" t="n">
-        <v>27000</v>
+        <v>27118.421052632</v>
       </c>
       <c r="O171" t="n">
-        <v>837000</v>
+        <v>840671.0526315919</v>
       </c>
       <c r="P171" t="n">
         <v>20000</v>
@@ -9313,10 +9313,10 @@
         <v>123</v>
       </c>
       <c r="N211" t="n">
-        <v>4937.3101888412</v>
+        <v>4937.3101890034</v>
       </c>
       <c r="O211" t="n">
-        <v>607289.1532274677</v>
+        <v>607289.1532474182</v>
       </c>
       <c r="P211" t="n">
         <v>7500</v>
@@ -9470,7 +9470,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9479,19 +9479,19 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="N215" t="n">
         <v>6513</v>
       </c>
       <c r="O215" t="n">
-        <v>273546</v>
+        <v>664326</v>
       </c>
       <c r="P215" t="n">
         <v>11500</v>
       </c>
       <c r="Q215" t="n">
-        <v>483000</v>
+        <v>1173000</v>
       </c>
     </row>
     <row r="216">
@@ -10928,10 +10928,10 @@
         <v>2</v>
       </c>
       <c r="N249" t="n">
-        <v>13694.165945612</v>
+        <v>13593.35</v>
       </c>
       <c r="O249" t="n">
-        <v>27388.331891224</v>
+        <v>27186.7</v>
       </c>
       <c r="P249" t="n">
         <v>25500</v>
@@ -11579,10 +11579,10 @@
         <v>85</v>
       </c>
       <c r="N264" t="n">
-        <v>2582.2546851654</v>
+        <v>2582.2546595174</v>
       </c>
       <c r="O264" t="n">
-        <v>219491.648239059</v>
+        <v>219491.646058979</v>
       </c>
       <c r="P264" t="n">
         <v>4500</v>
@@ -11973,10 +11973,10 @@
         <v>560</v>
       </c>
       <c r="N273" t="n">
-        <v>3158.8608437109</v>
+        <v>3158.8608442176</v>
       </c>
       <c r="O273" t="n">
-        <v>1768962.072478104</v>
+        <v>1768962.072761856</v>
       </c>
       <c r="P273" t="n">
         <v>5600</v>
@@ -12795,10 +12795,10 @@
         <v>282</v>
       </c>
       <c r="N291" t="n">
-        <v>3795.7100076628</v>
+        <v>3795.7100076717</v>
       </c>
       <c r="O291" t="n">
-        <v>1070390.22216091</v>
+        <v>1070390.222163419</v>
       </c>
       <c r="P291" t="n">
         <v>6200</v>
@@ -13061,10 +13061,10 @@
         <v>70</v>
       </c>
       <c r="N297" t="n">
-        <v>4890.9300570207</v>
+        <v>4890.9300571837</v>
       </c>
       <c r="O297" t="n">
-        <v>342365.103991449</v>
+        <v>342365.104002859</v>
       </c>
       <c r="P297" t="n">
         <v>8900</v>
@@ -14029,10 +14029,10 @@
         <v>62</v>
       </c>
       <c r="N319" t="n">
-        <v>3240.8500597015</v>
+        <v>3240.8500619195</v>
       </c>
       <c r="O319" t="n">
-        <v>200932.703701493</v>
+        <v>200932.703839009</v>
       </c>
       <c r="P319" t="n">
         <v>5200</v>
@@ -14167,10 +14167,10 @@
         <v>69</v>
       </c>
       <c r="N322" t="n">
-        <v>14831.53974042</v>
+        <v>14822.378811881</v>
       </c>
       <c r="O322" t="n">
-        <v>1023376.24208898</v>
+        <v>1022744.138019789</v>
       </c>
       <c r="P322" t="n">
         <v>24900</v>
@@ -14474,10 +14474,10 @@
         <v>89</v>
       </c>
       <c r="N329" t="n">
-        <v>12422.463013274</v>
+        <v>12422.46301728</v>
       </c>
       <c r="O329" t="n">
-        <v>1105599.208181386</v>
+        <v>1105599.20853792</v>
       </c>
       <c r="P329" t="n">
         <v>19900</v>
@@ -14654,10 +14654,10 @@
         <v>358</v>
       </c>
       <c r="N333" t="n">
-        <v>3472.2764071985</v>
+        <v>3472.2764292368</v>
       </c>
       <c r="O333" t="n">
-        <v>1243074.953777063</v>
+        <v>1243074.961666774</v>
       </c>
       <c r="P333" t="n">
         <v>5900</v>
@@ -14875,10 +14875,10 @@
         <v>185</v>
       </c>
       <c r="N338" t="n">
-        <v>4371.1729736673</v>
+        <v>4371.1729765349</v>
       </c>
       <c r="O338" t="n">
-        <v>808667.0001284505</v>
+        <v>808667.0006589565</v>
       </c>
       <c r="P338" t="n">
         <v>8900</v>
@@ -15479,7 +15479,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>347</v>
+        <v>527</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -15488,19 +15488,19 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>347</v>
+        <v>527</v>
       </c>
       <c r="N352" t="n">
         <v>4648.6</v>
       </c>
       <c r="O352" t="n">
-        <v>1613064.2</v>
+        <v>2449812.2</v>
       </c>
       <c r="P352" t="n">
         <v>8900</v>
       </c>
       <c r="Q352" t="n">
-        <v>3088300</v>
+        <v>4690300</v>
       </c>
     </row>
     <row r="353">
@@ -16413,10 +16413,10 @@
         <v>1</v>
       </c>
       <c r="N373" t="n">
-        <v>21670.98</v>
+        <v>32506.47</v>
       </c>
       <c r="O373" t="n">
-        <v>21670.98</v>
+        <v>32506.47</v>
       </c>
       <c r="P373" t="n">
         <v>32000</v>
@@ -16833,7 +16833,7 @@
         </is>
       </c>
       <c r="J383" t="n">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16842,19 +16842,19 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>779</v>
+        <v>844</v>
       </c>
       <c r="N383" t="n">
         <v>3751</v>
       </c>
       <c r="O383" t="n">
-        <v>2922029</v>
+        <v>3165844</v>
       </c>
       <c r="P383" t="n">
         <v>6400</v>
       </c>
       <c r="Q383" t="n">
-        <v>4985600</v>
+        <v>5401600</v>
       </c>
     </row>
     <row r="384">
@@ -16986,10 +16986,10 @@
         <v>793</v>
       </c>
       <c r="N386" t="n">
-        <v>1633.1055147059</v>
+        <v>1630.9252455662</v>
       </c>
       <c r="O386" t="n">
-        <v>1295052.673161779</v>
+        <v>1293323.719733997</v>
       </c>
       <c r="P386" t="n">
         <v>2500</v>
@@ -17119,10 +17119,10 @@
         <v>427</v>
       </c>
       <c r="N389" t="n">
-        <v>1690.5726046512</v>
+        <v>1690.5719339623</v>
       </c>
       <c r="O389" t="n">
-        <v>721874.5021860624</v>
+        <v>721874.2158019021</v>
       </c>
       <c r="P389" t="n">
         <v>2900</v>
@@ -17165,10 +17165,10 @@
         <v>2285</v>
       </c>
       <c r="N390" t="n">
-        <v>1550.1949638844</v>
+        <v>1550.1949858928</v>
       </c>
       <c r="O390" t="n">
-        <v>3542195.492475854</v>
+        <v>3542195.542765048</v>
       </c>
       <c r="P390" t="n">
         <v>2500</v>
@@ -17257,10 +17257,10 @@
         <v>991</v>
       </c>
       <c r="N392" t="n">
-        <v>2404.4159026746</v>
+        <v>2403.5234112326</v>
       </c>
       <c r="O392" t="n">
-        <v>2382776.159550529</v>
+        <v>2381891.700531507</v>
       </c>
       <c r="P392" t="n">
         <v>3500</v>
@@ -18532,10 +18532,10 @@
         <v>27</v>
       </c>
       <c r="N421" t="n">
-        <v>10034.5</v>
+        <v>10166.532894737</v>
       </c>
       <c r="O421" t="n">
-        <v>270931.5</v>
+        <v>274496.388157899</v>
       </c>
       <c r="P421" t="n">
         <v>12900</v>
@@ -20854,7 +20854,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -20863,19 +20863,19 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="N476" t="n">
         <v>6652</v>
       </c>
       <c r="O476" t="n">
-        <v>305992</v>
+        <v>645244</v>
       </c>
       <c r="P476" t="n">
         <v>5900</v>
       </c>
       <c r="Q476" t="n">
-        <v>271400</v>
+        <v>572300</v>
       </c>
     </row>
     <row r="477">
@@ -21112,10 +21112,10 @@
         <v>396</v>
       </c>
       <c r="N482" t="n">
-        <v>2029.8742613636</v>
+        <v>2029.8742906178</v>
       </c>
       <c r="O482" t="n">
-        <v>803830.2074999856</v>
+        <v>803830.2190846488</v>
       </c>
       <c r="P482" t="n">
         <v>3600</v>
@@ -21559,7 +21559,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -21568,19 +21568,19 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="N493" t="n">
         <v>24538.02</v>
       </c>
       <c r="O493" t="n">
-        <v>1006058.82</v>
+        <v>1521357.24</v>
       </c>
       <c r="P493" t="n">
         <v>52900</v>
       </c>
       <c r="Q493" t="n">
-        <v>2168900</v>
+        <v>3279800</v>
       </c>
     </row>
     <row r="494">
@@ -22334,10 +22334,10 @@
         <v>277</v>
       </c>
       <c r="N511" t="n">
-        <v>6207.9881978301</v>
+        <v>6207.9881950325</v>
       </c>
       <c r="O511" t="n">
-        <v>1719612.730798938</v>
+        <v>1719612.730024002</v>
       </c>
       <c r="P511" t="n">
         <v>9900</v>
@@ -23236,10 +23236,10 @@
         <v>165</v>
       </c>
       <c r="N532" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.263336112</v>
       </c>
       <c r="O532" t="n">
-        <v>794353.4522886104</v>
+        <v>794353.4504584799</v>
       </c>
       <c r="P532" t="n">
         <v>7900</v>
@@ -23369,10 +23369,10 @@
         <v>48</v>
       </c>
       <c r="N535" t="n">
-        <v>11562.038362573</v>
+        <v>11562.038338279</v>
       </c>
       <c r="O535" t="n">
-        <v>554977.8414035039</v>
+        <v>554977.840237392</v>
       </c>
       <c r="P535" t="n">
         <v>18500</v>
@@ -23415,10 +23415,10 @@
         <v>49</v>
       </c>
       <c r="N536" t="n">
-        <v>13513.644059406</v>
+        <v>13513.644408602</v>
       </c>
       <c r="O536" t="n">
-        <v>662168.558910894</v>
+        <v>662168.576021498</v>
       </c>
       <c r="P536" t="n">
         <v>21900</v>
@@ -25058,10 +25058,10 @@
         <v>18</v>
       </c>
       <c r="N574" t="n">
-        <v>1561.0125437573</v>
+        <v>1561.0077085243</v>
       </c>
       <c r="O574" t="n">
-        <v>28098.2257876314</v>
+        <v>28098.1387534374</v>
       </c>
       <c r="P574" t="n">
         <v>2900</v>
@@ -25834,10 +25834,10 @@
         <v>22</v>
       </c>
       <c r="N592" t="n">
-        <v>13033.935120968</v>
+        <v>12981.59</v>
       </c>
       <c r="O592" t="n">
-        <v>286746.572661296</v>
+        <v>285594.98</v>
       </c>
       <c r="P592" t="n">
         <v>21900</v>
@@ -28217,10 +28217,10 @@
         <v>64</v>
       </c>
       <c r="N645" t="n">
-        <v>3646</v>
+        <v>3656.7445972495</v>
       </c>
       <c r="O645" t="n">
-        <v>233344</v>
+        <v>234031.654223968</v>
       </c>
       <c r="P645" t="n">
         <v>6900</v>
@@ -28263,10 +28263,10 @@
         <v>4</v>
       </c>
       <c r="N646" t="n">
-        <v>23521.618709677</v>
+        <v>23521.6175</v>
       </c>
       <c r="O646" t="n">
-        <v>94086.474838708</v>
+        <v>94086.47</v>
       </c>
       <c r="P646" t="n">
         <v>39000</v>
@@ -28309,10 +28309,10 @@
         <v>68</v>
       </c>
       <c r="N647" t="n">
-        <v>3486</v>
+        <v>3488.1801125704</v>
       </c>
       <c r="O647" t="n">
-        <v>237048</v>
+        <v>237196.2476547872</v>
       </c>
       <c r="P647" t="n">
         <v>6900</v>
@@ -28355,10 +28355,10 @@
         <v>1208</v>
       </c>
       <c r="N648" t="n">
-        <v>1778.4728955224</v>
+        <v>1779.3581483325</v>
       </c>
       <c r="O648" t="n">
-        <v>2148395.257791059</v>
+        <v>2149464.64318566</v>
       </c>
       <c r="P648" t="n">
         <v>4900</v>
@@ -28631,10 +28631,10 @@
         <v>29</v>
       </c>
       <c r="N654" t="n">
-        <v>25577.697661152</v>
+        <v>25534</v>
       </c>
       <c r="O654" t="n">
-        <v>741753.232173408</v>
+        <v>740486</v>
       </c>
       <c r="P654" t="n">
         <v>40900</v>
@@ -28680,10 +28680,10 @@
         <v>1</v>
       </c>
       <c r="N655" t="n">
-        <v>26956</v>
+        <v>28541.647058824</v>
       </c>
       <c r="O655" t="n">
-        <v>26956</v>
+        <v>28541.647058824</v>
       </c>
       <c r="P655" t="n">
         <v>44900</v>
@@ -30465,7 +30465,7 @@
         </is>
       </c>
       <c r="J694" t="n">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="K694" t="n">
         <v>0</v>
@@ -30474,19 +30474,19 @@
         <v>0</v>
       </c>
       <c r="M694" t="n">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="N694" t="n">
         <v>8858.16</v>
       </c>
       <c r="O694" t="n">
-        <v>2719455.12</v>
+        <v>3144646.8</v>
       </c>
       <c r="P694" t="n">
         <v>15500</v>
       </c>
       <c r="Q694" t="n">
-        <v>4758500</v>
+        <v>5502500</v>
       </c>
     </row>
     <row r="695">
@@ -30569,10 +30569,10 @@
         <v>5</v>
       </c>
       <c r="N696" t="n">
-        <v>10448.858181818</v>
+        <v>10411</v>
       </c>
       <c r="O696" t="n">
-        <v>52244.29090908999</v>
+        <v>52055</v>
       </c>
       <c r="P696" t="n">
         <v>16900</v>
@@ -31119,10 +31119,10 @@
         <v>649</v>
       </c>
       <c r="N708" t="n">
-        <v>2328.1186316472</v>
+        <v>2328.1186298701</v>
       </c>
       <c r="O708" t="n">
-        <v>1510948.991939033</v>
+        <v>1510948.990785695</v>
       </c>
       <c r="P708" t="n">
         <v>4500</v>
@@ -31211,10 +31211,10 @@
         <v>64</v>
       </c>
       <c r="N710" t="n">
-        <v>21676</v>
+        <v>21700.382452193</v>
       </c>
       <c r="O710" t="n">
-        <v>1387264</v>
+        <v>1388824.476940352</v>
       </c>
       <c r="P710" t="n">
         <v>34900</v>
@@ -31257,10 +31257,10 @@
         <v>1</v>
       </c>
       <c r="N711" t="n">
-        <v>9384</v>
+        <v>9474.8129032258</v>
       </c>
       <c r="O711" t="n">
-        <v>9384</v>
+        <v>9474.8129032258</v>
       </c>
       <c r="P711" t="n">
         <v>15900</v>
@@ -31579,10 +31579,10 @@
         <v>50</v>
       </c>
       <c r="N718" t="n">
-        <v>9018.1565656566</v>
+        <v>9003</v>
       </c>
       <c r="O718" t="n">
-        <v>450907.82828283</v>
+        <v>450150</v>
       </c>
       <c r="P718" t="n">
         <v>14900</v>
@@ -31901,10 +31901,10 @@
         <v>8</v>
       </c>
       <c r="N725" t="n">
-        <v>4907.8228863636</v>
+        <v>4907.8230382775</v>
       </c>
       <c r="O725" t="n">
-        <v>39262.5830909088</v>
+        <v>39262.58430622</v>
       </c>
       <c r="P725" t="n">
         <v>8200</v>
@@ -32073,7 +32073,7 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
@@ -32082,19 +32082,19 @@
         <v>0</v>
       </c>
       <c r="M729" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N729" t="n">
         <v>76839</v>
       </c>
       <c r="O729" t="n">
-        <v>768390</v>
+        <v>1690458</v>
       </c>
       <c r="P729" t="n">
         <v>122900</v>
       </c>
       <c r="Q729" t="n">
-        <v>1229000</v>
+        <v>2703800</v>
       </c>
     </row>
     <row r="730">
@@ -32758,7 +32758,7 @@
         </is>
       </c>
       <c r="J744" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="K744" t="n">
         <v>0</v>
@@ -32767,19 +32767,19 @@
         <v>0</v>
       </c>
       <c r="M744" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="N744" t="n">
         <v>6849.2</v>
       </c>
       <c r="O744" t="n">
-        <v>602729.6</v>
+        <v>931491.2</v>
       </c>
       <c r="P744" t="n">
         <v>11500</v>
       </c>
       <c r="Q744" t="n">
-        <v>1012000</v>
+        <v>1564000</v>
       </c>
     </row>
     <row r="745">
@@ -33218,7 +33218,7 @@
         </is>
       </c>
       <c r="J754" t="n">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="K754" t="n">
         <v>0</v>
@@ -33227,19 +33227,19 @@
         <v>0</v>
       </c>
       <c r="M754" t="n">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="N754" t="n">
         <v>3898</v>
       </c>
       <c r="O754" t="n">
-        <v>947214</v>
+        <v>1414974</v>
       </c>
       <c r="P754" t="n">
         <v>6900</v>
       </c>
       <c r="Q754" t="n">
-        <v>1676700</v>
+        <v>2504700</v>
       </c>
     </row>
     <row r="755">
@@ -34703,10 +34703,10 @@
         <v>82</v>
       </c>
       <c r="N786" t="n">
-        <v>8711.0687022901</v>
+        <v>8700</v>
       </c>
       <c r="O786" t="n">
-        <v>714307.6335877882</v>
+        <v>713400</v>
       </c>
       <c r="P786" t="n">
         <v>14900</v>
@@ -34921,7 +34921,7 @@
         </is>
       </c>
       <c r="J791" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="K791" t="n">
         <v>0</v>
@@ -34930,19 +34930,19 @@
         <v>0</v>
       </c>
       <c r="M791" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="N791" t="n">
-        <v>15516.07977208</v>
+        <v>15472</v>
       </c>
       <c r="O791" t="n">
-        <v>605127.11111112</v>
+        <v>1160400</v>
       </c>
       <c r="P791" t="n">
         <v>25900</v>
       </c>
       <c r="Q791" t="n">
-        <v>1010100</v>
+        <v>1942500</v>
       </c>
     </row>
     <row r="792">
@@ -35163,10 +35163,10 @@
         <v>83</v>
       </c>
       <c r="N796" t="n">
-        <v>15223.06</v>
+        <v>15594.354146341</v>
       </c>
       <c r="O796" t="n">
-        <v>1263513.98</v>
+        <v>1294331.394146303</v>
       </c>
       <c r="P796" t="n">
         <v>17500</v>
@@ -35258,10 +35258,10 @@
         <v>130</v>
       </c>
       <c r="N798" t="n">
-        <v>1803</v>
+        <v>1820.7199017199</v>
       </c>
       <c r="O798" t="n">
-        <v>234390</v>
+        <v>236693.587223587</v>
       </c>
       <c r="P798" t="n">
         <v>3900</v>
@@ -35396,10 +35396,10 @@
         <v>347</v>
       </c>
       <c r="N801" t="n">
-        <v>1516.0386972166</v>
+        <v>1516.0386977679</v>
       </c>
       <c r="O801" t="n">
-        <v>526065.4279341602</v>
+        <v>526065.4281254613</v>
       </c>
       <c r="P801" t="n">
         <v>2300</v>
@@ -35532,10 +35532,10 @@
         <v>1087</v>
       </c>
       <c r="N804" t="n">
-        <v>2458.5122572276</v>
+        <v>2458.5121994025</v>
       </c>
       <c r="O804" t="n">
-        <v>2672402.823606401</v>
+        <v>2672402.760750517</v>
       </c>
       <c r="P804" t="n">
         <v>3500</v>
@@ -35670,10 +35670,10 @@
         <v>558</v>
       </c>
       <c r="N807" t="n">
-        <v>2079.3831463696</v>
+        <v>2079.3831437356</v>
       </c>
       <c r="O807" t="n">
-        <v>1160295.795674237</v>
+        <v>1160295.794204465</v>
       </c>
       <c r="P807" t="n">
         <v>2900</v>
@@ -35716,10 +35716,10 @@
         <v>911</v>
       </c>
       <c r="N808" t="n">
-        <v>1803.0176731553</v>
+        <v>1803.0177185792</v>
       </c>
       <c r="O808" t="n">
-        <v>1642549.100244478</v>
+        <v>1642549.141625651</v>
       </c>
       <c r="P808" t="n">
         <v>2500</v>
@@ -35854,10 +35854,10 @@
         <v>525</v>
       </c>
       <c r="N811" t="n">
-        <v>2108.8001384083</v>
+        <v>2108.8003733956</v>
       </c>
       <c r="O811" t="n">
-        <v>1107120.072664357</v>
+        <v>1107120.19603269</v>
       </c>
       <c r="P811" t="n">
         <v>2900</v>
@@ -35946,10 +35946,10 @@
         <v>168</v>
       </c>
       <c r="N813" t="n">
-        <v>3224.5700392597</v>
+        <v>3224.5700448934</v>
       </c>
       <c r="O813" t="n">
-        <v>541727.7665956296</v>
+        <v>541727.7675420912</v>
       </c>
       <c r="P813" t="n">
         <v>4500</v>
@@ -36349,7 +36349,7 @@
         </is>
       </c>
       <c r="J822" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="K822" t="n">
         <v>0</v>
@@ -36358,19 +36358,19 @@
         <v>0</v>
       </c>
       <c r="M822" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="N822" t="n">
         <v>5347.73</v>
       </c>
       <c r="O822" t="n">
-        <v>155084.17</v>
+        <v>422470.67</v>
       </c>
       <c r="P822" t="n">
         <v>9500</v>
       </c>
       <c r="Q822" t="n">
-        <v>275500</v>
+        <v>750500</v>
       </c>
     </row>
     <row r="823">
@@ -36453,10 +36453,10 @@
         <v>56</v>
       </c>
       <c r="N824" t="n">
-        <v>2060.1582208589</v>
+        <v>2060.1580497925</v>
       </c>
       <c r="O824" t="n">
-        <v>115368.8603680984</v>
+        <v>115368.85078838</v>
       </c>
       <c r="P824" t="n">
         <v>2900</v>
@@ -36545,10 +36545,10 @@
         <v>175</v>
       </c>
       <c r="N826" t="n">
-        <v>1259.2751822382</v>
+        <v>1259.2752022675</v>
       </c>
       <c r="O826" t="n">
-        <v>220373.156891685</v>
+        <v>220373.1603968125</v>
       </c>
       <c r="P826" t="n">
         <v>1900</v>
@@ -36625,7 +36625,7 @@
         </is>
       </c>
       <c r="J828" t="n">
-        <v>583</v>
+        <v>1159</v>
       </c>
       <c r="K828" t="n">
         <v>0</v>
@@ -36634,19 +36634,19 @@
         <v>0</v>
       </c>
       <c r="M828" t="n">
-        <v>583</v>
+        <v>1159</v>
       </c>
       <c r="N828" t="n">
         <v>1801</v>
       </c>
       <c r="O828" t="n">
-        <v>1049983</v>
+        <v>2087359</v>
       </c>
       <c r="P828" t="n">
         <v>2900</v>
       </c>
       <c r="Q828" t="n">
-        <v>1690700</v>
+        <v>3361100</v>
       </c>
     </row>
     <row r="829">
@@ -37007,10 +37007,10 @@
         <v>82</v>
       </c>
       <c r="N836" t="n">
-        <v>13521.774923206</v>
+        <v>13518</v>
       </c>
       <c r="O836" t="n">
-        <v>1108785.543702892</v>
+        <v>1108476</v>
       </c>
       <c r="P836" t="n">
         <v>21900</v>
@@ -37093,7 +37093,7 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
@@ -37102,19 +37102,19 @@
         <v>0</v>
       </c>
       <c r="M838" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="N838" t="n">
         <v>44470</v>
       </c>
       <c r="O838" t="n">
-        <v>1156220</v>
+        <v>2134560</v>
       </c>
       <c r="P838" t="n">
         <v>71900</v>
       </c>
       <c r="Q838" t="n">
-        <v>1869400</v>
+        <v>3451200</v>
       </c>
     </row>
     <row r="839">
@@ -37474,10 +37474,10 @@
         <v>1</v>
       </c>
       <c r="N846" t="n">
-        <v>15547.741935484</v>
+        <v>15423.36</v>
       </c>
       <c r="O846" t="n">
-        <v>15547.741935484</v>
+        <v>15423.36</v>
       </c>
       <c r="P846" t="n">
         <v>24900</v>
@@ -38533,10 +38533,10 @@
         <v>2</v>
       </c>
       <c r="N869" t="n">
-        <v>2270.3215151515</v>
+        <v>2270.3217241379</v>
       </c>
       <c r="O869" t="n">
-        <v>4540.643030303</v>
+        <v>4540.6434482758</v>
       </c>
       <c r="P869" t="n">
         <v>3900</v>
@@ -38577,10 +38577,10 @@
         <v>561</v>
       </c>
       <c r="N870" t="n">
-        <v>481.48790068997</v>
+        <v>481.48790045249</v>
       </c>
       <c r="O870" t="n">
-        <v>270114.7122870731</v>
+        <v>270114.7121538469</v>
       </c>
       <c r="P870" t="n">
         <v>650</v>
@@ -39729,10 +39729,10 @@
         <v>56</v>
       </c>
       <c r="N896" t="n">
-        <v>4032.3967801047</v>
+        <v>4032.3967716535</v>
       </c>
       <c r="O896" t="n">
-        <v>225814.2196858632</v>
+        <v>225814.219212596</v>
       </c>
       <c r="P896" t="n">
         <v>4200</v>
@@ -39822,10 +39822,10 @@
         <v>4348</v>
       </c>
       <c r="N898" t="n">
-        <v>517.29686746988</v>
+        <v>517.29687747036</v>
       </c>
       <c r="O898" t="n">
-        <v>2249206.779759038</v>
+        <v>2249206.823241125</v>
       </c>
       <c r="P898" t="n">
         <v>900</v>
@@ -40270,10 +40270,10 @@
         <v>2652</v>
       </c>
       <c r="N908" t="n">
-        <v>703.7945831140599</v>
+        <v>703.79457726026</v>
       </c>
       <c r="O908" t="n">
-        <v>1866463.234418487</v>
+        <v>1866463.218894209</v>
       </c>
       <c r="P908" t="n">
         <v>900</v>
@@ -40499,10 +40499,10 @@
         <v>3</v>
       </c>
       <c r="N913" t="n">
-        <v>2501.3837931034</v>
+        <v>2501.3837572254</v>
       </c>
       <c r="O913" t="n">
-        <v>7504.1513793102</v>
+        <v>7504.151271676201</v>
       </c>
       <c r="P913" t="n">
         <v>4100</v>
@@ -42976,10 +42976,10 @@
         <v>1</v>
       </c>
       <c r="N967" t="n">
-        <v>10737.525</v>
+        <v>10737.524705882</v>
       </c>
       <c r="O967" t="n">
-        <v>10737.525</v>
+        <v>10737.524705882</v>
       </c>
       <c r="P967" t="n">
         <v>18900</v>
@@ -43347,10 +43347,10 @@
         <v>2</v>
       </c>
       <c r="N975" t="n">
-        <v>2000.7532142857</v>
+        <v>2000.7579268293</v>
       </c>
       <c r="O975" t="n">
-        <v>4001.5064285714</v>
+        <v>4001.5158536586</v>
       </c>
       <c r="P975" t="n">
         <v>2000</v>
@@ -43772,10 +43772,10 @@
         <v>98</v>
       </c>
       <c r="N984" t="n">
-        <v>24338.47</v>
+        <v>24602.063537906</v>
       </c>
       <c r="O984" t="n">
-        <v>2385170.06</v>
+        <v>2411002.226714788</v>
       </c>
       <c r="P984" t="n">
         <v>27900</v>
@@ -47617,10 +47617,10 @@
         <v>59</v>
       </c>
       <c r="N1072" t="n">
-        <v>5058.1883211679</v>
+        <v>4985.4088235294</v>
       </c>
       <c r="O1072" t="n">
-        <v>298433.1109489061</v>
+        <v>294139.1205882346</v>
       </c>
       <c r="P1072" t="n">
         <v>7900</v>
@@ -47809,10 +47809,10 @@
         <v>57</v>
       </c>
       <c r="N1076" t="n">
-        <v>2367.6159259259</v>
+        <v>2367.6158955224</v>
       </c>
       <c r="O1076" t="n">
-        <v>134954.1077777763</v>
+        <v>134954.1060447768</v>
       </c>
       <c r="P1076" t="n">
         <v>2900</v>
@@ -48766,10 +48766,10 @@
         <v>114</v>
       </c>
       <c r="N1097" t="n">
-        <v>7953.8461538462</v>
+        <v>7920</v>
       </c>
       <c r="O1097" t="n">
-        <v>906738.4615384667</v>
+        <v>902880</v>
       </c>
       <c r="P1097" t="n">
         <v>10500</v>
@@ -48815,10 +48815,10 @@
         <v>72</v>
       </c>
       <c r="N1098" t="n">
-        <v>7971.0967741935</v>
+        <v>7920</v>
       </c>
       <c r="O1098" t="n">
-        <v>573918.967741932</v>
+        <v>570240</v>
       </c>
       <c r="P1098" t="n">
         <v>10500</v>
@@ -49045,10 +49045,10 @@
         <v>5</v>
       </c>
       <c r="N1103" t="n">
-        <v>4591.2533333333</v>
+        <v>4576</v>
       </c>
       <c r="O1103" t="n">
-        <v>22956.2666666665</v>
+        <v>22880</v>
       </c>
       <c r="P1103" t="n">
         <v>5900</v>
